--- a/FINAL_LIST_2026.xlsx
+++ b/FINAL_LIST_2026.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1040"/>
+  <dimension ref="A1:R1038"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -51630,6 +51630,21 @@
       </c>
     </row>
     <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>252P</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>LINEAR</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>P/2000 G1</t>
+        </is>
+      </c>
       <c r="D871" t="inlineStr">
         <is>
           <t>Comet</t>
@@ -58265,6 +58280,16 @@
       </c>
     </row>
     <row r="991">
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>Boattini</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>C/2007 W1</t>
+        </is>
+      </c>
       <c r="D991" t="inlineStr">
         <is>
           <t>Comet</t>
@@ -58375,6 +58400,16 @@
       </c>
     </row>
     <row r="994">
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>LINEAR</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>C/2001 A2</t>
+        </is>
+      </c>
       <c r="D994" t="inlineStr">
         <is>
           <t>Comet</t>
@@ -58410,6 +58445,21 @@
       </c>
     </row>
     <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>153P</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>Ikeya-Zhang</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>P/2002 C1</t>
+        </is>
+      </c>
       <c r="D995" t="inlineStr">
         <is>
           <t>Comet</t>
@@ -58547,7 +58597,7 @@
       </c>
       <c r="D998" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Moons</t>
         </is>
       </c>
       <c r="E998" t="inlineStr">
@@ -58637,7 +58687,7 @@
       </c>
       <c r="D1000" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Moons</t>
         </is>
       </c>
       <c r="E1000" t="inlineStr">
@@ -58687,7 +58737,7 @@
       </c>
       <c r="D1001" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Moons</t>
         </is>
       </c>
       <c r="E1001" t="inlineStr">
@@ -58732,7 +58782,7 @@
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Moons</t>
         </is>
       </c>
       <c r="E1002" t="inlineStr">
@@ -58777,7 +58827,7 @@
       </c>
       <c r="D1003" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Moons</t>
         </is>
       </c>
       <c r="E1003" t="inlineStr">
@@ -58815,9 +58865,19 @@
       </c>
     </row>
     <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>Jupiter III</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>Ganymede</t>
+        </is>
+      </c>
       <c r="D1004" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Moons</t>
         </is>
       </c>
       <c r="E1004" t="inlineStr">
@@ -58828,14 +58888,24 @@
       <c r="H1004" t="n">
         <v>1</v>
       </c>
+      <c r="I1004" t="inlineStr">
+        <is>
+          <t>-2.1 (F)</t>
+        </is>
+      </c>
+      <c r="J1004" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O1004" t="inlineStr">
+        <is>
+          <t>[1] Harmon, J. K., Ostro, S. J., Chandler, J. F., &amp; Hudson, R. S. (1994). Radar ranging to Ganymede and Callisto. The Astronomical Journal, 107, 1175. https://doi.org/10.1086/116929 [2] Ostro, S. J., Campbell, D. B., Simpson, R. A., Hudson, R. S., Chandler, J. F., Rosema, K. D., Shapiro, I. I., Standish, E. M., Winkler, R., Yeomans, D. K., Vélez, R., &amp; Goldstein, R. M. (1992). Europa, Ganymede, and Callisto: New radar results from Arecibo and Goldstone. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/92je01992 [3] Harcke, L. J., Zebker, H. A., Tyler, G. L., Simpson, R. A., Ostro, S. J., &amp; Harmon, J. K. (2001). Radar Imaging of Europa, Ganymede, and Callisto with the Upgraded Arecibo 13 cm Radar. American Astronomical Society Meeting Abstracts #198.</t>
+        </is>
+      </c>
       <c r="P1004" t="inlineStr">
         <is>
-          <t>1978, 1979, 1980, 1987, 1988, 1989, 1990, 1991, 2015, 2016</t>
-        </is>
-      </c>
-      <c r="Q1004" t="inlineStr">
-        <is>
-          <t>1999 logged, type unconfirmed; 2000 logged, type unconfirmed</t>
+          <t>1999(2), 2000, 2002, 2016(2)[2]</t>
         </is>
       </c>
       <c r="R1004" t="inlineStr">
@@ -58847,17 +58917,17 @@
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>Jupiter III</t>
+          <t>Saturn VIII</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>Ganymede</t>
+          <t>Iapetus</t>
         </is>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Moons</t>
         </is>
       </c>
       <c r="E1005" t="inlineStr">
@@ -58870,22 +58940,17 @@
       </c>
       <c r="I1005" t="inlineStr">
         <is>
-          <t>-2.1 (F)</t>
-        </is>
-      </c>
-      <c r="J1005" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>1.79 (F)</t>
         </is>
       </c>
       <c r="O1005" t="inlineStr">
         <is>
-          <t>[1] Harmon, J. K., Ostro, S. J., Chandler, J. F., &amp; Hudson, R. S. (1994). Radar ranging to Ganymede and Callisto. The Astronomical Journal, 107, 1175. https://doi.org/10.1086/116929 [2] Ostro, S. J., Campbell, D. B., Simpson, R. A., Hudson, R. S., Chandler, J. F., Rosema, K. D., Shapiro, I. I., Standish, E. M., Winkler, R., Yeomans, D. K., Vélez, R., &amp; Goldstein, R. M. (1992). Europa, Ganymede, and Callisto: New radar results from Arecibo and Goldstone. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/92je01992 [3] Harcke, L. J., Zebker, H. A., Tyler, G. L., Simpson, R. A., Ostro, S. J., &amp; Harmon, J. K. (2001). Radar Imaging of Europa, Ganymede, and Callisto with the Upgraded Arecibo 13 cm Radar. American Astronomical Society Meeting Abstracts #198.</t>
+          <t>[1] Gall, A. L., Raza, S., Lellouch, E., Butler, B., Bonnefoy, L., Leyrat, C., Schmidt, F., Mergny, C., Robin, C., Meyer, F., &amp; Harrar, L. (2024). Iapetus: Investigating the most dramatic hemispheric dichotomy in the Solar system&amp;amp;#160;with radio observations. https://doi.org/10.5194/epsc2024-618 [2] Tinaut-Ruano, F., Leon, J. M. d., Rizos, J. L., Tatsumi, E., Pinilla-Alonso, N., Vilas, F., &amp; Hendrix, A. (2024). The Iapetus&amp;amp;#8217; case:&amp;amp;#160;NUV as tracer of two populations of dark material. https://doi.org/10.5194/epsc2024-1071 [3] Black, G.J., D.B. Campbell, L.M. Carter, and S.J. Ostro, Radar Detection of Iapetus, Science 304, 553, 2004 http://dx.doi.org/10.1126/science.1096470</t>
         </is>
       </c>
       <c r="P1005" t="inlineStr">
         <is>
-          <t>1999(2), 2000, 2002, 2016(2)[2]</t>
+          <t>2000, 2002, 2003</t>
         </is>
       </c>
       <c r="R1005" t="inlineStr">
@@ -58897,17 +58962,17 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>Saturn VIII</t>
+          <t>Jupiter I</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>Iapetus</t>
+          <t>Io</t>
         </is>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Moons</t>
         </is>
       </c>
       <c r="E1006" t="inlineStr">
@@ -58920,17 +58985,27 @@
       </c>
       <c r="I1006" t="inlineStr">
         <is>
-          <t>1.79 (F)</t>
+          <t>-1.67 (F)</t>
+        </is>
+      </c>
+      <c r="J1006" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="O1006" t="inlineStr">
         <is>
-          <t>[1] Gall, A. L., Raza, S., Lellouch, E., Butler, B., Bonnefoy, L., Leyrat, C., Schmidt, F., Mergny, C., Robin, C., Meyer, F., &amp; Harrar, L. (2024). Iapetus: Investigating the most dramatic hemispheric dichotomy in the Solar system&amp;amp;#160;with radio observations. https://doi.org/10.5194/epsc2024-618 [2] Tinaut-Ruano, F., Leon, J. M. d., Rizos, J. L., Tatsumi, E., Pinilla-Alonso, N., Vilas, F., &amp; Hendrix, A. (2024). The Iapetus&amp;amp;#8217; case:&amp;amp;#160;NUV as tracer of two populations of dark material. https://doi.org/10.5194/epsc2024-1071 [3] Black, G.J., D.B. Campbell, L.M. Carter, and S.J. Ostro, Radar Detection of Iapetus, Science 304, 553, 2004 http://dx.doi.org/10.1126/science.1096470</t>
+          <t>[1] Campbell, D. B., Chandler, J. F., Pettengill, G. H., &amp; Shapiro, I. I. (1977). Galilean Satellites of Jupiter: 12.6-Centimeter Radar Observations. Science, 196, 650-653. https://doi.org/10.1126/science.196.4290.650 [2] Warwick, J. (1967). Radiophysics of Jupiter. Space Science Reviews. https://doi.org/10.1007/bf00222408 [3] Ostro, S. J., Campbell, D. B., Chandler, J. F., Shapiro, I. I., &amp; Rosema, K. D. (1990). Io's Radar Properties. Bulletin of the American Astronomical Society.</t>
         </is>
       </c>
       <c r="P1006" t="inlineStr">
         <is>
-          <t>2000, 2002, 2003</t>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q1006" t="inlineStr">
+        <is>
+          <t>1999 CW</t>
         </is>
       </c>
       <c r="R1006" t="inlineStr">
@@ -58940,19 +59015,9 @@
       </c>
     </row>
     <row r="1007">
-      <c r="A1007" t="inlineStr">
-        <is>
-          <t>Jupiter I</t>
-        </is>
-      </c>
-      <c r="B1007" t="inlineStr">
-        <is>
-          <t>Io</t>
-        </is>
-      </c>
       <c r="D1007" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Comet</t>
         </is>
       </c>
       <c r="E1007" t="inlineStr">
@@ -58963,29 +59028,14 @@
       <c r="H1007" t="n">
         <v>1</v>
       </c>
-      <c r="I1007" t="inlineStr">
-        <is>
-          <t>-1.67 (F)</t>
-        </is>
-      </c>
-      <c r="J1007" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O1007" t="inlineStr">
-        <is>
-          <t>[1] Campbell, D. B., Chandler, J. F., Pettengill, G. H., &amp; Shapiro, I. I. (1977). Galilean Satellites of Jupiter: 12.6-Centimeter Radar Observations. Science, 196, 650-653. https://doi.org/10.1126/science.196.4290.650 [2] Warwick, J. (1967). Radiophysics of Jupiter. Space Science Reviews. https://doi.org/10.1007/bf00222408 [3] Ostro, S. J., Campbell, D. B., Chandler, J. F., Shapiro, I. I., &amp; Rosema, K. D. (1990). Io's Radar Properties. Bulletin of the American Astronomical Society.</t>
-        </is>
-      </c>
       <c r="P1007" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="Q1007" t="inlineStr">
         <is>
-          <t>1999 CW</t>
+          <t>2013 CW</t>
         </is>
       </c>
       <c r="R1007" t="inlineStr">
@@ -58995,9 +59045,19 @@
       </c>
     </row>
     <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>Planet 4</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>Mars</t>
+        </is>
+      </c>
       <c r="D1008" t="inlineStr">
         <is>
-          <t>Comet</t>
+          <t>Planets</t>
         </is>
       </c>
       <c r="E1008" t="inlineStr">
@@ -59008,14 +59068,29 @@
       <c r="H1008" t="n">
         <v>1</v>
       </c>
+      <c r="I1008" t="inlineStr">
+        <is>
+          <t>-1.6 (F)</t>
+        </is>
+      </c>
+      <c r="J1008" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O1008" t="inlineStr">
+        <is>
+          <t>[1] Harmon, J. K., Arvidson, R. E., Guinness, E. A., Campbell, B. A., &amp; Slade, M. A. (1999). Mars mapping with delay‐Doppler radar. Journal of Geophysical Research: Planets, 104, 14065-14089. https://doi.org/10.1029/1998je900042 [2] Harmon, J. K., Nolan, M. C., Husmann, D. I., &amp; Campbell, B. A. (2012). Arecibo radar imagery of Mars: The major volcanic provinces. Icarus. https://doi.org/10.1016/j.icarus.2012.06.030 [3] Muhleman, D. O., Grossman, A. W., &amp; Butler, B. (1995). Radar Investigation of Mars, Mercury, and Titan. Annual Review of Earth and Planetary Sciences. https://doi.org/10.1146/annurev.ea.23.050195.002005 [4] Simpson, R. A., Tyler, G. L., &amp; Campbell, D. B. (1978). Arecibo radar observations of Mars surface characteristics in the northern hemisphere. Icarus. https://doi.org/10.1016/0019-1035(78)90101-x [5] Harmon, J. K. (1985). Mars: Dual-polarization radar observations with extended coverage. Icarus. https://doi.org/10.1016/0019-1035(85)90175-7 [6] Harmon, J. K., Slade, M. A., &amp; Hudson, R. S. (1992). Mars radar scattering: Arecibo/Goldstone results at 12.6- and 3.5-cm wavelengths. Icarus. https://doi.org/10.1016/0019-1035(92)90093-m [7] Harmon, J. K., Campbell, D. B., &amp; Ostro, S. J. (1982). Dual-polarization radar observations of Mars: Tharsis and Environs. Icarus. https://doi.org/10.1016/0019-1035(82)90177-4 [8] Harmon, J. K. (1997). A radar study of the Chryse region, Mars. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/96je01953 [9] Wu, S. S. C. (1978). Mars synthetic topographic mapping. Icarus. https://doi.org/10.1016/0019-1035(78)90182-3 [10] Harmon, J. K., &amp; Nolan, M. C. (2016). Arecibo radar imagery of Mars: II. Chryse–Xanthe, polar caps, and other regions. Icarus. https://doi.org/10.1016/j.icarus.2016.08.015 [11] Harmon, J. K., Sulzer, M. P., Perillat, P. J., &amp; Chandler, J. F. (1992). Mars radar mapping: Strong backscatter from the Elysium basin and outflow channel. Icarus, 95, 153-156. https://doi.org/10.1016/0019-1035(92)90197-f [12] Harmon, J. K., &amp; Nolan, M. C. (2007). Arecibo Radar Imaging of Mars During the 2005 Opposition. Seventh International Conference on Mars. [13] Simpson, R. A., Tyler, G. L., &amp; Lipa, B. J. (1977). Mars surface properties observed by earth-based radar at 70-, 12.5-, and 3.8-cm wavelengths. Icarus, 32, 147-167. https://doi.org/10.1016/0019-1035(77)90057-4 [14] Putzig, N. E., Morgan, G. A., Campbell, B. A., Grima, C., Smith, I. B., Phillips, R. J., &amp; Golombek, M. P. (2016). Radar-Derived Properties of the InSight Landing Site in Western Elysium Planitia on Mars. Space Science Reviews. https://doi.org/10.1007/s11214-016-0322-8 [15] Thompson, T. W., &amp; Moore, H. J. (1988). A Model for Depolarized Radar Echoes from Mars. Bulletin of the American Astronomical Society.</t>
+        </is>
+      </c>
       <c r="P1008" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1978, 1980, 1981, 1982, 1983, 1988, 1990, 1991, 2000, 2005(2), 2007, 2008, 2010, 2012</t>
         </is>
       </c>
       <c r="Q1008" t="inlineStr">
         <is>
-          <t>2013 CW</t>
+          <t>2006 DD</t>
         </is>
       </c>
       <c r="R1008" t="inlineStr">
@@ -59027,17 +59102,17 @@
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>Planet 4</t>
+          <t>Planet 1</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
-          <t>Planet</t>
+          <t>Planets</t>
         </is>
       </c>
       <c r="E1009" t="inlineStr">
@@ -59050,7 +59125,7 @@
       </c>
       <c r="I1009" t="inlineStr">
         <is>
-          <t>-1.6 (F)</t>
+          <t>-0.613 (F)</t>
         </is>
       </c>
       <c r="J1009" t="inlineStr">
@@ -59060,17 +59135,17 @@
       </c>
       <c r="O1009" t="inlineStr">
         <is>
-          <t>[1] Harmon, J. K., Arvidson, R. E., Guinness, E. A., Campbell, B. A., &amp; Slade, M. A. (1999). Mars mapping with delay‐Doppler radar. Journal of Geophysical Research: Planets, 104, 14065-14089. https://doi.org/10.1029/1998je900042 [2] Harmon, J. K., Nolan, M. C., Husmann, D. I., &amp; Campbell, B. A. (2012). Arecibo radar imagery of Mars: The major volcanic provinces. Icarus. https://doi.org/10.1016/j.icarus.2012.06.030 [3] Muhleman, D. O., Grossman, A. W., &amp; Butler, B. (1995). Radar Investigation of Mars, Mercury, and Titan. Annual Review of Earth and Planetary Sciences. https://doi.org/10.1146/annurev.ea.23.050195.002005 [4] Simpson, R. A., Tyler, G. L., &amp; Campbell, D. B. (1978). Arecibo radar observations of Mars surface characteristics in the northern hemisphere. Icarus. https://doi.org/10.1016/0019-1035(78)90101-x [5] Harmon, J. K. (1985). Mars: Dual-polarization radar observations with extended coverage. Icarus. https://doi.org/10.1016/0019-1035(85)90175-7 [6] Harmon, J. K., Slade, M. A., &amp; Hudson, R. S. (1992). Mars radar scattering: Arecibo/Goldstone results at 12.6- and 3.5-cm wavelengths. Icarus. https://doi.org/10.1016/0019-1035(92)90093-m [7] Harmon, J. K., Campbell, D. B., &amp; Ostro, S. J. (1982). Dual-polarization radar observations of Mars: Tharsis and Environs. Icarus. https://doi.org/10.1016/0019-1035(82)90177-4 [8] Harmon, J. K. (1997). A radar study of the Chryse region, Mars. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/96je01953 [9] Wu, S. S. C. (1978). Mars synthetic topographic mapping. Icarus. https://doi.org/10.1016/0019-1035(78)90182-3 [10] Harmon, J. K., &amp; Nolan, M. C. (2016). Arecibo radar imagery of Mars: II. Chryse–Xanthe, polar caps, and other regions. Icarus. https://doi.org/10.1016/j.icarus.2016.08.015 [11] Harmon, J. K., Sulzer, M. P., Perillat, P. J., &amp; Chandler, J. F. (1992). Mars radar mapping: Strong backscatter from the Elysium basin and outflow channel. Icarus, 95, 153-156. https://doi.org/10.1016/0019-1035(92)90197-f [12] Harmon, J. K., &amp; Nolan, M. C. (2007). Arecibo Radar Imaging of Mars During the 2005 Opposition. Seventh International Conference on Mars. [13] Simpson, R. A., Tyler, G. L., &amp; Lipa, B. J. (1977). Mars surface properties observed by earth-based radar at 70-, 12.5-, and 3.8-cm wavelengths. Icarus, 32, 147-167. https://doi.org/10.1016/0019-1035(77)90057-4 [14] Putzig, N. E., Morgan, G. A., Campbell, B. A., Grima, C., Smith, I. B., Phillips, R. J., &amp; Golombek, M. P. (2016). Radar-Derived Properties of the InSight Landing Site in Western Elysium Planitia on Mars. Space Science Reviews. https://doi.org/10.1007/s11214-016-0322-8 [15] Thompson, T. W., &amp; Moore, H. J. (1988). A Model for Depolarized Radar Echoes from Mars. Bulletin of the American Astronomical Society.</t>
+          <t>[1] Harmon, J. K. (1997). Mercury radar studies and lunar comparisons. Advances in Space Research, 19, 1487-1496. https://doi.org/10.1016/s0273-1177(97)00347-5 [2] Pettengill, G. H., &amp; Dyce, R. B. (1965). A Radar Determination of the Rotation of the Planet Mercury. Nature, 206, 1240-1240. https://doi.org/10.1038/2061240a0 [3] Harmon, J. K., &amp; Slade, M. A. (1992). Radar Mapping of Mercury: Full-Disk Images and Polar Anomalies. Science. https://doi.org/10.1126/science.258.5082.640 [4] Muhleman, D. O., Grossman, A. W., &amp; Butler, B. (1995). Radar Investigation of Mars, Mercury, and Titan. Annual Review of Earth and Planetary Sciences. https://doi.org/10.1146/annurev.ea.23.050195.002005 [5] Harmon, J. K., Campbell, D. B., Bindschadler, D. L., Head, J. W., &amp; Shapiro, I. I. (1986). Radar altimetry of Mercury: A Preliminary analysis. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/jb091ib01p00385 [6] Dyce, B. R., Pettengill, G. H., &amp; Shapiro, I. I. (1967). Radar determination of the rotations of Venus and Mercury. The Astronomical Journal. https://doi.org/10.1086/110231 [7] Harmon, J. K., Slade, M. A., Butler, B. J., Head, J. W., Rice, M. S., &amp; Campbell, D. B. (2006). Mercury: Radar images of the equatorial and midlatitude zones. Icarus, 187, 374-405. https://doi.org/10.1016/j.icarus.2006.09.026 [8] Pettengill, G. H., Dyce, R. B., &amp; Campbell, D. B. (1967). Radar measurements at 70 CM of Venus and Mercury. The Astronomical Journal, 72, 330. https://doi.org/10.1086/110229 [9] Harmon, J. K., &amp; Campbell, D. B. (2001). Mercury Radar Imaging At Arecibo. EGSGA. http://dx.doi.org/10.1006/icar.2000.6544 [10] Slade, M. A., Harmon, J. K., Harcke, L. J., &amp; Jürgens, R. (2004). 3.5-cm Radar Observations of Polar Regions of Mercury Using Goldstone to Arecibo Configuration. 35th COSPAR Scientific Assembly. [11] Black, G., Campbell, D. B., &amp; Harmon, J. K. (2009). Radar measurements of Mercury’s north pole at 70cm wavelength. Icarus. https://doi.org/10.1016/j.icarus.2009.10.009 [12] Harmon, J. K. (2008). Radar imagery of the southern Caloris region, Mercury. Icarus. https://doi.org/10.1016/j.icarus.2008.03.003 [13] Slade, M. A., Jurgens, R. F., Margot, J., &amp; Standish, E. M. (2001). Repeat-Orbit Interferometric Precision Measurement of Mercury Obliquity. NASA Technical Reports Server (NASA). [14] Harcke, L. J., Zebker, H. A., &amp; Jurgens, R. F. (2001). Radar Imaging of Mercury's North and South Poles at 3.5 cm Wavelength. NASA Technical Reports Server (NASA). [15] Harmon, J. K. (1993). Radar Mapping of Mercury at Arecibo. National Radio Science Meeting. [16] Glantzberg, A. K., Chabot, N. L., Barker, M. K., Mazarico, E., Siegler, M. A., Martinez Camacho, J. M., Hamill, C. D., Rivera-Valentín, E. G., Meyer, H., Bertone, S., and Deutsch, A. N., Investigating the Stability and Distribution of Surface Ice in Mercury's Northernmost Craters, The Planetary Science Journal, 4, p.107, 2023 https://ui.adsabs.harvard.edu/abs/2023PSJ.....4..107G [17] Rivera-Valentín, E. G., Meyer, H. M., Taylor, P. A., Mazarico, E., Bhiravarasu, S. S., Virkki, A. K., Nolan, M. C., Chabot, N. L., and Giorgini, J. D., Arecibo S-band Radar Characterization of Local-scale Heterogeneities within Mercury's North Polar Deposits, The Planetary Science Journal, 3, p.62, 2022 https://ui.adsabs.harvard.edu/abs/2022PSJ.....3...62R [18] Chabot, N.L., E.E. Shread, and J.K. Harmon, Investigating Mercury's South Polar Deposits: Arecibo Radar Observations and High-Resolution Determination of Illumination Conditions, Journal of Geophysical Research: Planets 123, 666-681, 2018 https://doi.org/10.1002/2017JE005500 [19] Neish, C.D., D.T. Blewett, J.K. Harmon, E.I. Coman, J.T.S. Cahill, and C.M. Ernst, A Comparison of Rayed Craters on the Moon and Mercury, Journal of Geophysical Research (Planets) 118, 2247-2261, 2013 http://dx.doi.org/10.1002/jgre.20166 [20] Harmon, J.K., M.A. Slade, and M.S. Rice, Radar Imagery of Mercury`s Putative Polar Ice: 1999-2005 Arecibo Results, Icarus 211, 37-50, 2011 http://dx.doi.org/10.1016/j.icarus.2010.08.007 [21] Harmon, J.K., Radar Imaging of Mercury, Space Science Reviews 132, 307-349, 2007 http://dx.doi.org/10.1007/s11214-007-9234-y [22] Margot, J.L, S.J. Peale, R.F. Jurgens, M.A. Slade, and I.V. Holin, Large Longitude Libration of Mercury Reveals a Molten Core, Science 316, 710-714, 2007 http://dx.doi.org/10.1126/science.1140514 [23] Harmon, J.K., M.A. Slade, R.A. Velez, A. Crespo, M.J. Dryer, and J.M. Johnson, Radar Mapping of Mercury`s Polar Anomalies, Nature 369, 213-215, 1994 http://dx.doi.org/10.1038/369213a0 [24] Shapiro, I.I., G.H. Pettengill, M.E. Ash, R.P. Ingalls, D.B. Campbell, and R.B. Dyce, Mercury`s Perihelion Advance: Determination by Radar, Physical Review Letters 28, 1594-1597, 1972 http://dx.doi.org/10.1103/PhysRevLett.28.1594</t>
         </is>
       </c>
       <c r="P1009" t="inlineStr">
         <is>
-          <t>1978, 1980, 1981, 1982, 1983, 1988, 1990, 1991, 2000, 2005(2), 2007, 2008, 2010, 2012</t>
+          <t>1978, 1979, 1980, 1981, 1982, 1983, 1984, 1985, 1986, 1987, 1988, 1989, 1990, 1991, 1998(2), 1999, 2000, 2001, 2002(3), 2003, 2004(2), 2005(2), 2006, 2012, 2020(8)[8]</t>
         </is>
       </c>
       <c r="Q1009" t="inlineStr">
         <is>
-          <t>2006 DD</t>
+          <t>2004 logged, type unconfirmed; 2012 logged, type unconfirmed</t>
         </is>
       </c>
       <c r="R1009" t="inlineStr">
@@ -59082,17 +59157,17 @@
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>Planet 1</t>
+          <t>Earth I</t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
-          <t>Planet</t>
+          <t>Moons</t>
         </is>
       </c>
       <c r="E1010" t="inlineStr">
@@ -59105,7 +59180,7 @@
       </c>
       <c r="I1010" t="inlineStr">
         <is>
-          <t>-0.613 (F)</t>
+          <t>-0.08 (F)</t>
         </is>
       </c>
       <c r="J1010" t="inlineStr">
@@ -59115,17 +59190,17 @@
       </c>
       <c r="O1010" t="inlineStr">
         <is>
-          <t>[1] Harmon, J. K. (1997). Mercury radar studies and lunar comparisons. Advances in Space Research, 19, 1487-1496. https://doi.org/10.1016/s0273-1177(97)00347-5 [2] Pettengill, G. H., &amp; Dyce, R. B. (1965). A Radar Determination of the Rotation of the Planet Mercury. Nature, 206, 1240-1240. https://doi.org/10.1038/2061240a0 [3] Harmon, J. K., &amp; Slade, M. A. (1992). Radar Mapping of Mercury: Full-Disk Images and Polar Anomalies. Science. https://doi.org/10.1126/science.258.5082.640 [4] Muhleman, D. O., Grossman, A. W., &amp; Butler, B. (1995). Radar Investigation of Mars, Mercury, and Titan. Annual Review of Earth and Planetary Sciences. https://doi.org/10.1146/annurev.ea.23.050195.002005 [5] Harmon, J. K., Campbell, D. B., Bindschadler, D. L., Head, J. W., &amp; Shapiro, I. I. (1986). Radar altimetry of Mercury: A Preliminary analysis. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/jb091ib01p00385 [6] Dyce, B. R., Pettengill, G. H., &amp; Shapiro, I. I. (1967). Radar determination of the rotations of Venus and Mercury. The Astronomical Journal. https://doi.org/10.1086/110231 [7] Harmon, J. K., Slade, M. A., Butler, B. J., Head, J. W., Rice, M. S., &amp; Campbell, D. B. (2006). Mercury: Radar images of the equatorial and midlatitude zones. Icarus, 187, 374-405. https://doi.org/10.1016/j.icarus.2006.09.026 [8] Pettengill, G. H., Dyce, R. B., &amp; Campbell, D. B. (1967). Radar measurements at 70 CM of Venus and Mercury. The Astronomical Journal, 72, 330. https://doi.org/10.1086/110229 [9] Harmon, J. K., &amp; Campbell, D. B. (2001). Mercury Radar Imaging At Arecibo. EGSGA. http://dx.doi.org/10.1006/icar.2000.6544 [10] Slade, M. A., Harmon, J. K., Harcke, L. J., &amp; Jürgens, R. (2004). 3.5-cm Radar Observations of Polar Regions of Mercury Using Goldstone to Arecibo Configuration. 35th COSPAR Scientific Assembly. [11] Black, G., Campbell, D. B., &amp; Harmon, J. K. (2009). Radar measurements of Mercury’s north pole at 70cm wavelength. Icarus. https://doi.org/10.1016/j.icarus.2009.10.009 [12] Harmon, J. K. (2008). Radar imagery of the southern Caloris region, Mercury. Icarus. https://doi.org/10.1016/j.icarus.2008.03.003 [13] Slade, M. A., Jurgens, R. F., Margot, J., &amp; Standish, E. M. (2001). Repeat-Orbit Interferometric Precision Measurement of Mercury Obliquity. NASA Technical Reports Server (NASA). [14] Harcke, L. J., Zebker, H. A., &amp; Jurgens, R. F. (2001). Radar Imaging of Mercury's North and South Poles at 3.5 cm Wavelength. NASA Technical Reports Server (NASA). [15] Harmon, J. K. (1993). Radar Mapping of Mercury at Arecibo. National Radio Science Meeting. [16] Glantzberg, A. K., Chabot, N. L., Barker, M. K., Mazarico, E., Siegler, M. A., Martinez Camacho, J. M., Hamill, C. D., Rivera-Valentín, E. G., Meyer, H., Bertone, S., and Deutsch, A. N., Investigating the Stability and Distribution of Surface Ice in Mercury's Northernmost Craters, The Planetary Science Journal, 4, p.107, 2023 https://ui.adsabs.harvard.edu/abs/2023PSJ.....4..107G [17] Rivera-Valentín, E. G., Meyer, H. M., Taylor, P. A., Mazarico, E., Bhiravarasu, S. S., Virkki, A. K., Nolan, M. C., Chabot, N. L., and Giorgini, J. D., Arecibo S-band Radar Characterization of Local-scale Heterogeneities within Mercury's North Polar Deposits, The Planetary Science Journal, 3, p.62, 2022 https://ui.adsabs.harvard.edu/abs/2022PSJ.....3...62R [18] Chabot, N.L., E.E. Shread, and J.K. Harmon, Investigating Mercury's South Polar Deposits: Arecibo Radar Observations and High-Resolution Determination of Illumination Conditions, Journal of Geophysical Research: Planets 123, 666-681, 2018 https://doi.org/10.1002/2017JE005500 [19] Neish, C.D., D.T. Blewett, J.K. Harmon, E.I. Coman, J.T.S. Cahill, and C.M. Ernst, A Comparison of Rayed Craters on the Moon and Mercury, Journal of Geophysical Research (Planets) 118, 2247-2261, 2013 http://dx.doi.org/10.1002/jgre.20166 [20] Harmon, J.K., M.A. Slade, and M.S. Rice, Radar Imagery of Mercury`s Putative Polar Ice: 1999-2005 Arecibo Results, Icarus 211, 37-50, 2011 http://dx.doi.org/10.1016/j.icarus.2010.08.007 [21] Harmon, J.K., Radar Imaging of Mercury, Space Science Reviews 132, 307-349, 2007 http://dx.doi.org/10.1007/s11214-007-9234-y [22] Margot, J.L, S.J. Peale, R.F. Jurgens, M.A. Slade, and I.V. Holin, Large Longitude Libration of Mercury Reveals a Molten Core, Science 316, 710-714, 2007 http://dx.doi.org/10.1126/science.1140514 [23] Harmon, J.K., M.A. Slade, R.A. Velez, A. Crespo, M.J. Dryer, and J.M. Johnson, Radar Mapping of Mercury`s Polar Anomalies, Nature 369, 213-215, 1994 http://dx.doi.org/10.1038/369213a0 [24] Shapiro, I.I., G.H. Pettengill, M.E. Ash, R.P. Ingalls, D.B. Campbell, and R.B. Dyce, Mercury`s Perihelion Advance: Determination by Radar, Physical Review Letters 28, 1594-1597, 1972 http://dx.doi.org/10.1103/PhysRevLett.28.1594</t>
+          <t>[1] Campbell, B. A., Hawke, B. R., &amp; Thompson, T. W. (1997). Regolith composition and structure in the lunar maria: Results of long‐wavelength radar studies. Journal of Geophysical Research: Planets, 102, 19307-19320. https://doi.org/10.1029/97je00858 [2] Stacy, N. J. S., Campbell, D. B., &amp; Ford, P. G. (1997). Arecibo Radar Mapping of the Lunar Poles: A Search for Ice Deposits. Science. https://doi.org/10.1126/science.276.5318.1527 [3] Shkuratov, Y. G. (2001). Regolith Layer Thickness Mapping of the Moon by Radar and Optical Data. Icarus. https://doi.org/10.1006/icar.2000.6545 [4] Patterson, G. W., Stickle, A. M., Turner, F. S., Jensen, J. R., Bussey, D. B. J., Spudis, P. D., Espiritu, R. C., Schulze, R., Yocky, D. A., Wahl, D. E., Zimmerman, M. I., Cahill, J. T. S., Nolan, M. C., Carter, L. M., &amp; Neish, C. D. (2016). Bistatic radar observations of the Moon using Mini-RF on LRO and the Arecibo Observatory. Icarus. https://doi.org/10.1016/j.icarus.2016.05.017 [5] Fa, W., &amp; Wieczorek, M. A. (2012). Regolith thickness over the lunar nearside: Results from Earth-based 70-cm Arecibo radar observations. Icarus. https://doi.org/10.1016/j.icarus.2012.01.010 [6] Campbell, B. A., Campbell, D. B., Margot, J. L., Ghent, R. R., Nolan, M., Chandler, J., Carter, L. M., &amp; Stacy, N. J. S. (2007). Focused 70-cm Wavelength Radar Mapping of the Moon. IEEE Transactions on Geoscience and Remote Sensing, 45, 4032-4042. https://doi.org/10.1109/tgrs.2007.906582 [7] Thompson, T. W., Pollack, J. B., Campbell, M. J., &amp; O'Leary, B. (1970). Radar Maps of the Moon at 70‐cm Wavelength and Their Interpretation. Radio Science. https://doi.org/10.1029/rs005i002p00253 [8] Campbell, B. A., Carter, L. M., Campbell, D. B., Nolan, M. C., Chandler, J. F., Ghent, R. R., Hawke, B. R., Anderson, R. F., &amp; Wells, K. S. (2010). Earth-based 12.6-cm wavelength radar mapping of the Moon: New views of impact melt distribution and mare physical properties. Icarus. https://doi.org/10.1016/j.icarus.2010.03.011 [9] Campbell, B., &amp; Campbell, D. (2005). Regolith properties in the south polar region of the Moon from 70-cm radar polarimetry. Icarus, 180, 1-7. https://doi.org/10.1016/j.icarus.2005.08.018 [10] Carter, L. M., Campbell, B. A., Hawke, B. R., Campbell, D. B., &amp; Nolan, M. C. (2009). Radar remote sensing of pyroclastic deposits in the southern Mare Serenitatis and Mare Vaporum regions of the Moon. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/2009je003406 [11] Busch, M. W., Ostro, S. J., Benner, L. A. M., Giorgini, J. D., Magri, C., Howell, E. S., Nolan, M. C., Hine, A. A., Campbell, D. B., Shapiro, I. I., &amp; Chandler, J. F. (2006). Arecibo radar observations of Phobos and Deimos. Icarus. https://doi.org/10.1016/j.icarus.2006.11.003 [12] Black, G. (2001). Icy Galilean Satellites: 70 cm Radar Results from Arecibo. Icarus. https://doi.org/10.1006/icar.2001.6615 [13] Thompson, T. W. (1979). A review of earth-based radar mapping of the moon. The Moon and the Planets. https://doi.org/10.1007/bf00898069 [14] Spudis, P. D., Bussey, B., Plescia, J. B., Josset, J., &amp; Beauvivre, S. (2008). Geology of Shackleton Crater and the south pole of the Moon. Geophysical Research Letters. https://doi.org/10.1029/2008gl034468 [15] Black, G. J., Campbell, D. B., &amp; Carter, L. M. (2007). Arecibo radar observations of Rhea, Dione, Tethys, and Enceladus. Icarus, 191, 702-711. https://doi.org/10.1016/j.icarus.2007.06.009 [16] Muhleman, D. O., Grossman, A. W., &amp; Butler, B. (1995). Radar Investigation of Mars, Mercury, and Titan. Annual Review of Earth and Planetary Sciences. https://doi.org/10.1146/annurev.ea.23.050195.002005 [17] Campbell, D. B., &amp; Burns, B. A. (1980). Earth‐based radar imagery of Venus. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/ja085ia13p08271 [18] Harmon, J. K. (1985). Mars: Dual-polarization radar observations with extended coverage. Icarus. https://doi.org/10.1016/0019-1035(85)90175-7 [19] Rivera‐Valentín, E. G., Meyer, H., Taylor, P., Mazarico, E., Bhiravarasu, S. S., Virkki, A., Nolan, M. C., Chabot, N. L., &amp; Giorgini, J. D. (2022). Arecibo S-band Radar Characterization of Local-scale Heterogeneities within Mercury’s North Polar Deposits. The Planetary Science Journal. https://doi.org/10.3847/psj/ac54a0 [20] Thompson, T. W. (1987). High-resolution lunar radar map at 70-cm wavelength. Earth Moon and Planets. https://doi.org/10.1007/bf00054324 [21] Mitchell, D. L., Ostro, S. J., Hudson, R. S., Rosema, K. D., Campbell, D. B., Vélez, R., Chandler, J. F., Shapiro, I. I., Giorgini, J. D., &amp; Yeomans, D. K. (1996). Radar Observations of Asteroids 1 Ceres, 2 Pallas, and 4 Vesta. Icarus. https://doi.org/10.1006/icar.1996.0193</t>
         </is>
       </c>
       <c r="P1010" t="inlineStr">
         <is>
-          <t>1978, 1979, 1980, 1981, 1982, 1983, 1984, 1985, 1986, 1987, 1988, 1989, 1990, 1991, 1998(2), 1999, 2000, 2001, 2002(3), 2003, 2004(2), 2005(2), 2006, 2012, 2020(8)[8]</t>
+          <t>1982, 1986, 1987, 1990, 1992, 2000, 2003(2), 2004, 2005(4), 2006(4), 2007, 2008(4), 2009(4), 2010(2), 2011, 2012, 2013(3), 2014(2), 2015, 2017(6)[2], 2019[1], 2020(7)[7]</t>
         </is>
       </c>
       <c r="Q1010" t="inlineStr">
         <is>
-          <t>2004 logged, type unconfirmed; 2012 logged, type unconfirmed</t>
+          <t>2009 logged, type unconfirmed</t>
         </is>
       </c>
       <c r="R1010" t="inlineStr">
@@ -59135,19 +59210,9 @@
       </c>
     </row>
     <row r="1011">
-      <c r="A1011" t="inlineStr">
-        <is>
-          <t>Earth I</t>
-        </is>
-      </c>
-      <c r="B1011" t="inlineStr">
-        <is>
-          <t>Moon</t>
-        </is>
-      </c>
       <c r="D1011" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Spacecraft</t>
         </is>
       </c>
       <c r="E1011" t="inlineStr">
@@ -59158,29 +59223,19 @@
       <c r="H1011" t="n">
         <v>1</v>
       </c>
-      <c r="I1011" t="inlineStr">
-        <is>
-          <t>-0.08 (F)</t>
-        </is>
-      </c>
-      <c r="J1011" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="O1011" t="inlineStr">
         <is>
-          <t>[1] Campbell, B. A., Hawke, B. R., &amp; Thompson, T. W. (1997). Regolith composition and structure in the lunar maria: Results of long‐wavelength radar studies. Journal of Geophysical Research: Planets, 102, 19307-19320. https://doi.org/10.1029/97je00858 [2] Stacy, N. J. S., Campbell, D. B., &amp; Ford, P. G. (1997). Arecibo Radar Mapping of the Lunar Poles: A Search for Ice Deposits. Science. https://doi.org/10.1126/science.276.5318.1527 [3] Shkuratov, Y. G. (2001). Regolith Layer Thickness Mapping of the Moon by Radar and Optical Data. Icarus. https://doi.org/10.1006/icar.2000.6545 [4] Patterson, G. W., Stickle, A. M., Turner, F. S., Jensen, J. R., Bussey, D. B. J., Spudis, P. D., Espiritu, R. C., Schulze, R., Yocky, D. A., Wahl, D. E., Zimmerman, M. I., Cahill, J. T. S., Nolan, M. C., Carter, L. M., &amp; Neish, C. D. (2016). Bistatic radar observations of the Moon using Mini-RF on LRO and the Arecibo Observatory. Icarus. https://doi.org/10.1016/j.icarus.2016.05.017 [5] Fa, W., &amp; Wieczorek, M. A. (2012). Regolith thickness over the lunar nearside: Results from Earth-based 70-cm Arecibo radar observations. Icarus. https://doi.org/10.1016/j.icarus.2012.01.010 [6] Campbell, B. A., Campbell, D. B., Margot, J. L., Ghent, R. R., Nolan, M., Chandler, J., Carter, L. M., &amp; Stacy, N. J. S. (2007). Focused 70-cm Wavelength Radar Mapping of the Moon. IEEE Transactions on Geoscience and Remote Sensing, 45, 4032-4042. https://doi.org/10.1109/tgrs.2007.906582 [7] Thompson, T. W., Pollack, J. B., Campbell, M. J., &amp; O'Leary, B. (1970). Radar Maps of the Moon at 70‐cm Wavelength and Their Interpretation. Radio Science. https://doi.org/10.1029/rs005i002p00253 [8] Campbell, B. A., Carter, L. M., Campbell, D. B., Nolan, M. C., Chandler, J. F., Ghent, R. R., Hawke, B. R., Anderson, R. F., &amp; Wells, K. S. (2010). Earth-based 12.6-cm wavelength radar mapping of the Moon: New views of impact melt distribution and mare physical properties. Icarus. https://doi.org/10.1016/j.icarus.2010.03.011 [9] Campbell, B., &amp; Campbell, D. (2005). Regolith properties in the south polar region of the Moon from 70-cm radar polarimetry. Icarus, 180, 1-7. https://doi.org/10.1016/j.icarus.2005.08.018 [10] Carter, L. M., Campbell, B. A., Hawke, B. R., Campbell, D. B., &amp; Nolan, M. C. (2009). Radar remote sensing of pyroclastic deposits in the southern Mare Serenitatis and Mare Vaporum regions of the Moon. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/2009je003406 [11] Busch, M. W., Ostro, S. J., Benner, L. A. M., Giorgini, J. D., Magri, C., Howell, E. S., Nolan, M. C., Hine, A. A., Campbell, D. B., Shapiro, I. I., &amp; Chandler, J. F. (2006). Arecibo radar observations of Phobos and Deimos. Icarus. https://doi.org/10.1016/j.icarus.2006.11.003 [12] Black, G. (2001). Icy Galilean Satellites: 70 cm Radar Results from Arecibo. Icarus. https://doi.org/10.1006/icar.2001.6615 [13] Thompson, T. W. (1979). A review of earth-based radar mapping of the moon. The Moon and the Planets. https://doi.org/10.1007/bf00898069 [14] Spudis, P. D., Bussey, B., Plescia, J. B., Josset, J., &amp; Beauvivre, S. (2008). Geology of Shackleton Crater and the south pole of the Moon. Geophysical Research Letters. https://doi.org/10.1029/2008gl034468 [15] Black, G. J., Campbell, D. B., &amp; Carter, L. M. (2007). Arecibo radar observations of Rhea, Dione, Tethys, and Enceladus. Icarus, 191, 702-711. https://doi.org/10.1016/j.icarus.2007.06.009 [16] Muhleman, D. O., Grossman, A. W., &amp; Butler, B. (1995). Radar Investigation of Mars, Mercury, and Titan. Annual Review of Earth and Planetary Sciences. https://doi.org/10.1146/annurev.ea.23.050195.002005 [17] Campbell, D. B., &amp; Burns, B. A. (1980). Earth‐based radar imagery of Venus. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/ja085ia13p08271 [18] Harmon, J. K. (1985). Mars: Dual-polarization radar observations with extended coverage. Icarus. https://doi.org/10.1016/0019-1035(85)90175-7 [19] Rivera‐Valentín, E. G., Meyer, H., Taylor, P., Mazarico, E., Bhiravarasu, S. S., Virkki, A., Nolan, M. C., Chabot, N. L., &amp; Giorgini, J. D. (2022). Arecibo S-band Radar Characterization of Local-scale Heterogeneities within Mercury’s North Polar Deposits. The Planetary Science Journal. https://doi.org/10.3847/psj/ac54a0 [20] Thompson, T. W. (1987). High-resolution lunar radar map at 70-cm wavelength. Earth Moon and Planets. https://doi.org/10.1007/bf00054324 [21] Mitchell, D. L., Ostro, S. J., Hudson, R. S., Rosema, K. D., Campbell, D. B., Vélez, R., Chandler, J. F., Shapiro, I. I., Giorgini, J. D., &amp; Yeomans, D. K. (1996). Radar Observations of Asteroids 1 Ceres, 2 Pallas, and 4 Vesta. Icarus. https://doi.org/10.1006/icar.1996.0193</t>
+          <t>[1] Brozovic, M., et al. (2017). Radar observations of spacecraft in lunar orbit. https://echo.jpl.nasa.gov/asteroids/brozovic.etal.2017.lunar.spacecraft.paper.pdf</t>
         </is>
       </c>
       <c r="P1011" t="inlineStr">
         <is>
-          <t>1982, 1986, 1987, 1990, 1992, 2000, 2003(2), 2004, 2005(4), 2006(4), 2007, 2008(4), 2009(4), 2010(2), 2011, 2012, 2013(3), 2014(2), 2015, 2017(6)[2], 2019[1], 2020(7)[7]</t>
+          <t>2016, 2018</t>
         </is>
       </c>
       <c r="Q1011" t="inlineStr">
         <is>
-          <t>2009 logged, type unconfirmed</t>
+          <t>2016 logged, type unconfirmed</t>
         </is>
       </c>
       <c r="R1011" t="inlineStr">
@@ -59190,9 +59245,24 @@
       </c>
     </row>
     <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>1P</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>Halley</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>P/1758 Y1</t>
+        </is>
+      </c>
       <c r="D1012" t="inlineStr">
         <is>
-          <t>Spacecraft</t>
+          <t>Comet</t>
         </is>
       </c>
       <c r="E1012" t="inlineStr">
@@ -59203,19 +59273,19 @@
       <c r="H1012" t="n">
         <v>1</v>
       </c>
+      <c r="I1012" t="inlineStr">
+        <is>
+          <t>4 (F)</t>
+        </is>
+      </c>
       <c r="O1012" t="inlineStr">
         <is>
-          <t>[1] Brozovic, M., et al. (2017). Radar observations of spacecraft in lunar orbit. https://echo.jpl.nasa.gov/asteroids/brozovic.etal.2017.lunar.spacecraft.paper.pdf</t>
+          <t>[1] Campbell, D. B., Harmon, J. K., &amp; Shapiro, I. I. (1989). Radar observations of Comet Halley. The Astrophysical Journal, 338, 1094. https://doi.org/10.1086/167259 [2] (2013). Chapter One. The First Anticipated Return: Halley’s Comet 1758. When Computers Were Human, 11-25. https://doi.org/10.1515/9781400849369.11 [3] Kerr, R. B., Tepley, C. A., Cageao, R. P., Atreya, S. K., Donahue, T. M., &amp; Cherchneff, I. M. (1987). Observations of comet Halley at Hα and 6300 Å. Geophysical Research Letters, 14, 53-56. https://doi.org/10.1029/gl014i001p00053 [4] Cordes, J. M., Terzian, Y., Falchi, A. M., Tofani, G., &amp; Lewis, B. M. (1990). Radio OH emission from Comet Halley with 3 arcmin resolution. The Astronomical Journal, 100, 1655. https://doi.org/10.1086/115625 [5] Kerr, R. B., Cageao, R. P., Atreya, S. K., Donahue, T. M., &amp; Tepley, C. A. (1985). High spectral resolution Fabry-Perot interferometer measurements of comet Halley at H-alpha and 6300 Å. Advances in Space Research, 5, 283-287. https://doi.org/10.1016/0273-1177(85)90098-5 [6] Atreya, S. K. (1988). Gaseous cometary coronal. NASA STI Repository (National Aeronautics and Space Administration). [7] French, L. M. (2006). Asteroid. Encyclopedia of Earth Science, 27-33. https://doi.org/10.1007/1-4020-4520-4_20</t>
         </is>
       </c>
       <c r="P1012" t="inlineStr">
         <is>
-          <t>2016, 2018</t>
-        </is>
-      </c>
-      <c r="Q1012" t="inlineStr">
-        <is>
-          <t>2016 logged, type unconfirmed</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="R1012" t="inlineStr">
@@ -59227,17 +59297,17 @@
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>1P</t>
+          <t>2P</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>Halley</t>
+          <t>Encke</t>
         </is>
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>P/1758 Y1</t>
+          <t>P/1786 B1</t>
         </is>
       </c>
       <c r="D1013" t="inlineStr">
@@ -59255,17 +59325,22 @@
       </c>
       <c r="I1013" t="inlineStr">
         <is>
-          <t>4 (F)</t>
+          <t>11.5 (F)</t>
         </is>
       </c>
       <c r="O1013" t="inlineStr">
         <is>
-          <t>[1] Campbell, D. B., Harmon, J. K., &amp; Shapiro, I. I. (1989). Radar observations of Comet Halley. The Astrophysical Journal, 338, 1094. https://doi.org/10.1086/167259 [2] (2013). Chapter One. The First Anticipated Return: Halley’s Comet 1758. When Computers Were Human, 11-25. https://doi.org/10.1515/9781400849369.11 [3] Kerr, R. B., Tepley, C. A., Cageao, R. P., Atreya, S. K., Donahue, T. M., &amp; Cherchneff, I. M. (1987). Observations of comet Halley at Hα and 6300 Å. Geophysical Research Letters, 14, 53-56. https://doi.org/10.1029/gl014i001p00053 [4] Cordes, J. M., Terzian, Y., Falchi, A. M., Tofani, G., &amp; Lewis, B. M. (1990). Radio OH emission from Comet Halley with 3 arcmin resolution. The Astronomical Journal, 100, 1655. https://doi.org/10.1086/115625 [5] Kerr, R. B., Cageao, R. P., Atreya, S. K., Donahue, T. M., &amp; Tepley, C. A. (1985). High spectral resolution Fabry-Perot interferometer measurements of comet Halley at H-alpha and 6300 Å. Advances in Space Research, 5, 283-287. https://doi.org/10.1016/0273-1177(85)90098-5 [6] Atreya, S. K. (1988). Gaseous cometary coronal. NASA STI Repository (National Aeronautics and Space Administration). [7] French, L. M. (2006). Asteroid. Encyclopedia of Earth Science, 27-33. https://doi.org/10.1007/1-4020-4520-4_20</t>
+          <t>[1] Marsden, B. G., &amp; Sekanina, Z. (1974). Comets and nongravitational forces. VI. Periodic comet Encke 1786-1971 . The Astronomical Journal, 79, 413. https://doi.org/10.1086/111560 [2] Kamoun, P. G., Campbell, D. B., Ostro, S. J., Pettengill, G. H., &amp; Shapiro, I. I. (1982). Comet Encke: Radar Detection of Nucleus. Science, 216, 293-295. https://doi.org/10.1126/science.216.4543.293 [3] Harmon, J., &amp; Nolan, M. (2005). Radar observations of Comet 2P/Encke during the 2003 apparition. Icarus, 176, 175-183. https://doi.org/10.1016/j.icarus.2005.01.012 [4] Skirmante, K., Bleiders, M., Jekabsons, N., Bezrukovs, V., &amp; Jasmonts, G. (2020). Observations of OH masers of comets in 1.6GHz frequency band using the Irbene RT32 radio telescope. https://doi.org/10.5194/epsc2020-171</t>
         </is>
       </c>
       <c r="P1013" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1980, 2003, 2013(2)</t>
+        </is>
+      </c>
+      <c r="Q1013" t="inlineStr">
+        <is>
+          <t>2003 DD; 2013 CW</t>
         </is>
       </c>
       <c r="R1013" t="inlineStr">
@@ -59277,17 +59352,17 @@
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>2P</t>
+          <t>8P</t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t>Encke</t>
+          <t>Tuttle</t>
         </is>
       </c>
       <c r="C1014" t="inlineStr">
         <is>
-          <t>P/1786 B1</t>
+          <t>P/1790 A2</t>
         </is>
       </c>
       <c r="D1014" t="inlineStr">
@@ -59305,22 +59380,22 @@
       </c>
       <c r="I1014" t="inlineStr">
         <is>
-          <t>11.5 (F)</t>
+          <t>8 (F)</t>
         </is>
       </c>
       <c r="O1014" t="inlineStr">
         <is>
-          <t>[1] Marsden, B. G., &amp; Sekanina, Z. (1974). Comets and nongravitational forces. VI. Periodic comet Encke 1786-1971 . The Astronomical Journal, 79, 413. https://doi.org/10.1086/111560 [2] Kamoun, P. G., Campbell, D. B., Ostro, S. J., Pettengill, G. H., &amp; Shapiro, I. I. (1982). Comet Encke: Radar Detection of Nucleus. Science, 216, 293-295. https://doi.org/10.1126/science.216.4543.293 [3] Harmon, J., &amp; Nolan, M. (2005). Radar observations of Comet 2P/Encke during the 2003 apparition. Icarus, 176, 175-183. https://doi.org/10.1016/j.icarus.2005.01.012 [4] Skirmante, K., Bleiders, M., Jekabsons, N., Bezrukovs, V., &amp; Jasmonts, G. (2020). Observations of OH masers of comets in 1.6GHz frequency band using the Irbene RT32 radio telescope. https://doi.org/10.5194/epsc2020-171</t>
+          <t>[1] Harmon, J. K., Nolan, M. C., Giorgini, J. D., &amp; Howell, E. S. (2010). Radar observations of 8P/Tuttle: A contact-binary comet. Icarus, 207, 499-502. https://doi.org/10.1016/j.icarus.2009.12.026 [2] Harmon, J. K., Nolan, M. C., Howell, E. S., &amp; Giorgini, J. D. (2008). Comet 8P/Tuttle: Arecibo Radar Observations of the First Bilobate Comet. [3] Groussin, O., Lamy, P. L., Kelley, M. S. P., Toth, I., Jorda, L., Fernández, Y. R., &amp; Weaver, H. A. (2019). SpitzerSpace Telescope observations of bilobate comet 8P/Tuttle. Astronomy &amp;amp; Astrophysics, 632, A104. https://doi.org/10.1051/0004-6361/201936458 [4] Harmon, J. K., Nolan, M. C., Howell, E. S., Giorgini, J. D., &amp; Magri, C. (2008). Arecibo Radar Observations of Comet 8P/Tuttle: A Possible Contact Binary. AAS/Division for Planetary Sciences Meeting Abstracts #40.</t>
         </is>
       </c>
       <c r="P1014" t="inlineStr">
         <is>
-          <t>1980, 2003, 2013(2)</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="Q1014" t="inlineStr">
         <is>
-          <t>2003 DD; 2013 CW</t>
+          <t>2008 DD</t>
         </is>
       </c>
       <c r="R1014" t="inlineStr">
@@ -59332,17 +59407,17 @@
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>8P</t>
+          <t>289P</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>Tuttle</t>
+          <t>Blanpain</t>
         </is>
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>P/1790 A2</t>
+          <t>P/1819 W1</t>
         </is>
       </c>
       <c r="D1015" t="inlineStr">
@@ -59360,22 +59435,17 @@
       </c>
       <c r="I1015" t="inlineStr">
         <is>
-          <t>8 (F)</t>
-        </is>
-      </c>
-      <c r="O1015" t="inlineStr">
-        <is>
-          <t>[1] Harmon, J. K., Nolan, M. C., Giorgini, J. D., &amp; Howell, E. S. (2010). Radar observations of 8P/Tuttle: A contact-binary comet. Icarus, 207, 499-502. https://doi.org/10.1016/j.icarus.2009.12.026 [2] Harmon, J. K., Nolan, M. C., Howell, E. S., &amp; Giorgini, J. D. (2008). Comet 8P/Tuttle: Arecibo Radar Observations of the First Bilobate Comet. [3] Groussin, O., Lamy, P. L., Kelley, M. S. P., Toth, I., Jorda, L., Fernández, Y. R., &amp; Weaver, H. A. (2019). SpitzerSpace Telescope observations of bilobate comet 8P/Tuttle. Astronomy &amp;amp; Astrophysics, 632, A104. https://doi.org/10.1051/0004-6361/201936458 [4] Harmon, J. K., Nolan, M. C., Howell, E. S., Giorgini, J. D., &amp; Magri, C. (2008). Arecibo Radar Observations of Comet 8P/Tuttle: A Possible Contact Binary. AAS/Division for Planetary Sciences Meeting Abstracts #40.</t>
+          <t>19 (F)</t>
         </is>
       </c>
       <c r="P1015" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2019(3)[3], 2020(6)[4]</t>
         </is>
       </c>
       <c r="Q1015" t="inlineStr">
         <is>
-          <t>2008 DD</t>
+          <t>2019 CW; 2020 CW</t>
         </is>
       </c>
       <c r="R1015" t="inlineStr">
@@ -59387,17 +59457,17 @@
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>289P</t>
+          <t>41P</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t>Blanpain</t>
+          <t>Tuttle-Giacobini-Kresak</t>
         </is>
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>P/1819 W1</t>
+          <t>P/1858 J1</t>
         </is>
       </c>
       <c r="D1016" t="inlineStr">
@@ -59415,17 +59485,22 @@
       </c>
       <c r="I1016" t="inlineStr">
         <is>
-          <t>19 (F)</t>
+          <t>10 (F)</t>
+        </is>
+      </c>
+      <c r="O1016" t="inlineStr">
+        <is>
+          <t>[1] Howell, E. S., Lejoly, C., Taylor, P., Rivera‐Valentín, E. G., Zambrano-Marin, L. F., Giorgini, J. D., Nolan, M. C., Samarasinha, N. H., Mueller, B. E. A., Aponte-Hernández, B., Bhiravarasu, S. S., Sánchez-Vahamonde, C. R., &amp; Harris, W. M. (2017). Arecibo radar observations of 41P/Tuttle-Giacobini-Kresák constrain the nucleus size and rotation. AAS/Division for Planetary Sciences Meeting Abstracts #49.</t>
         </is>
       </c>
       <c r="P1016" t="inlineStr">
         <is>
-          <t>2019(3)[3], 2020(6)[4]</t>
+          <t>2017(18)[7]</t>
         </is>
       </c>
       <c r="Q1016" t="inlineStr">
         <is>
-          <t>2019 CW; 2020 CW</t>
+          <t>2017 CW+DD</t>
         </is>
       </c>
       <c r="R1016" t="inlineStr">
@@ -59437,17 +59512,17 @@
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>41P</t>
+          <t>26P</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>Tuttle-Giacobini-Kresak</t>
+          <t>Grigg-Skjellerup</t>
         </is>
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>P/1858 J1</t>
+          <t>P/1902 O1</t>
         </is>
       </c>
       <c r="D1017" t="inlineStr">
@@ -59465,22 +59540,17 @@
       </c>
       <c r="I1017" t="inlineStr">
         <is>
-          <t>10 (F)</t>
+          <t>12 (F)</t>
         </is>
       </c>
       <c r="O1017" t="inlineStr">
         <is>
-          <t>[1] Howell, E. S., Lejoly, C., Taylor, P., Rivera‐Valentín, E. G., Zambrano-Marin, L. F., Giorgini, J. D., Nolan, M. C., Samarasinha, N. H., Mueller, B. E. A., Aponte-Hernández, B., Bhiravarasu, S. S., Sánchez-Vahamonde, C. R., &amp; Harris, W. M. (2017). Arecibo radar observations of 41P/Tuttle-Giacobini-Kresák constrain the nucleus size and rotation. AAS/Division for Planetary Sciences Meeting Abstracts #49.</t>
+          <t>[1] Kamoun, P., Campbell, D., Pettengill, G., &amp; Shapiro, I. (1998). Radar observations of three comets and detection of echoes from one: P/Grigg-Skjellerup. Planetary and Space Science, 47, 23-28. https://doi.org/10.1016/s0032-0633(98)00108-1</t>
         </is>
       </c>
       <c r="P1017" t="inlineStr">
         <is>
-          <t>2017(18)[7]</t>
-        </is>
-      </c>
-      <c r="Q1017" t="inlineStr">
-        <is>
-          <t>2017 CW+DD</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="R1017" t="inlineStr">
@@ -59492,17 +59562,17 @@
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>26P</t>
+          <t>46P</t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>Grigg-Skjellerup</t>
+          <t>Wirtanen</t>
         </is>
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>P/1902 O1</t>
+          <t>P/1948 A1</t>
         </is>
       </c>
       <c r="D1018" t="inlineStr">
@@ -59520,17 +59590,17 @@
       </c>
       <c r="I1018" t="inlineStr">
         <is>
-          <t>12 (F)</t>
-        </is>
-      </c>
-      <c r="O1018" t="inlineStr">
-        <is>
-          <t>[1] Kamoun, P., Campbell, D., Pettengill, G., &amp; Shapiro, I. (1998). Radar observations of three comets and detection of echoes from one: P/Grigg-Skjellerup. Planetary and Space Science, 47, 23-28. https://doi.org/10.1016/s0032-0633(98)00108-1</t>
+          <t>14 (F)</t>
         </is>
       </c>
       <c r="P1018" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2018(23)[23]</t>
+        </is>
+      </c>
+      <c r="Q1018" t="inlineStr">
+        <is>
+          <t>2018 CW+DD</t>
         </is>
       </c>
       <c r="R1018" t="inlineStr">
@@ -59542,17 +59612,17 @@
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>46P</t>
+          <t>45P</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>Wirtanen</t>
+          <t>Honda-Mrkos-Pajdusakova</t>
         </is>
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>P/1948 A1</t>
+          <t>P/1948 X1</t>
         </is>
       </c>
       <c r="D1019" t="inlineStr">
@@ -59570,17 +59640,22 @@
       </c>
       <c r="I1019" t="inlineStr">
         <is>
-          <t>14 (F)</t>
+          <t>13.5 (F)</t>
+        </is>
+      </c>
+      <c r="O1019" t="inlineStr">
+        <is>
+          <t>[1] Springmann, A., Harris, W. M., Ryan, E. L., Lejoly, C., Howell, E. S., Mueller, B. E. A., Samarasinha, N. H., Woodney, L. M., &amp; Steckloff, J. K. (2022). Repeating Gas Ejection Events from Comet 45P/Honda–Mrkos–Pajdušáková. The Planetary Science Journal, 3, 15. https://doi.org/10.3847/psj/ac3e66 [2] Springmann, A., Howell, E. S., Harmon, J. K., Lejoly, C., Rivera‐Valentín, E. G., Virkki, A., Zambrano-Marin, L. F., Taylor, P., Harris, W. M., Mueller, B. E. A., Samarasinha, N. H., &amp; Sánchez-Vahamonde, C. R. (2017). Particle Sizes in the Coma of Comet 45P/Honda-Mrkos-Pajdušáková from Arecibo Radar Observations. DPS. [3] Springmann, A., Howell, E. S., Nolan, M. C., Lejoly, C., Taylor, P., Rivera‐Valentín, E. G., Virkki, A., Zambrano-Marin, L. F., Harris, W. M., Harmon, J. K., &amp; Sánchez-Vahamonde, C. R. (2018). Modeling the large-grain (&gt;2 cm) coma of comet 45P/Honda-Mrkos-Pajdušáková from Arecibo Observatory radar observations. AAS/Division for Planetary Sciences Meeting Abstracts #50. [4] Springmann, A., Harris, W. M., Ryan, E. L., Lejoly, C., Howell, E. S., Mueller, B. E. A., Samarasinha, N. H., Woodney, L. M., &amp; Steckloff, J. K. (2021). Repeating gas ejection events from comet 45P/Honda-Mrkos-Pajdu\v{s}\'{a}kov\'{a}. arXiv (Cornell University).</t>
         </is>
       </c>
       <c r="P1019" t="inlineStr">
         <is>
-          <t>2018(23)[23]</t>
+          <t>2017(28)</t>
         </is>
       </c>
       <c r="Q1019" t="inlineStr">
         <is>
-          <t>2018 CW+DD</t>
+          <t>2017 CW+DD</t>
         </is>
       </c>
       <c r="R1019" t="inlineStr">
@@ -59592,17 +59667,17 @@
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>45P</t>
+          <t>103P</t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>Honda-Mrkos-Pajdusakova</t>
+          <t>Hartley 2</t>
         </is>
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>P/1948 X1</t>
+          <t>P/1986 E2</t>
         </is>
       </c>
       <c r="D1020" t="inlineStr">
@@ -59620,22 +59695,22 @@
       </c>
       <c r="I1020" t="inlineStr">
         <is>
-          <t>13.5 (F)</t>
+          <t>8.5 (F)</t>
         </is>
       </c>
       <c r="O1020" t="inlineStr">
         <is>
-          <t>[1] Springmann, A., Harris, W. M., Ryan, E. L., Lejoly, C., Howell, E. S., Mueller, B. E. A., Samarasinha, N. H., Woodney, L. M., &amp; Steckloff, J. K. (2022). Repeating Gas Ejection Events from Comet 45P/Honda–Mrkos–Pajdušáková. The Planetary Science Journal, 3, 15. https://doi.org/10.3847/psj/ac3e66 [2] Springmann, A., Howell, E. S., Harmon, J. K., Lejoly, C., Rivera‐Valentín, E. G., Virkki, A., Zambrano-Marin, L. F., Taylor, P., Harris, W. M., Mueller, B. E. A., Samarasinha, N. H., &amp; Sánchez-Vahamonde, C. R. (2017). Particle Sizes in the Coma of Comet 45P/Honda-Mrkos-Pajdušáková from Arecibo Radar Observations. DPS. [3] Springmann, A., Howell, E. S., Nolan, M. C., Lejoly, C., Taylor, P., Rivera‐Valentín, E. G., Virkki, A., Zambrano-Marin, L. F., Harris, W. M., Harmon, J. K., &amp; Sánchez-Vahamonde, C. R. (2018). Modeling the large-grain (&gt;2 cm) coma of comet 45P/Honda-Mrkos-Pajdušáková from Arecibo Observatory radar observations. AAS/Division for Planetary Sciences Meeting Abstracts #50. [4] Springmann, A., Harris, W. M., Ryan, E. L., Lejoly, C., Howell, E. S., Mueller, B. E. A., Samarasinha, N. H., Woodney, L. M., &amp; Steckloff, J. K. (2021). Repeating gas ejection events from comet 45P/Honda-Mrkos-Pajdu\v{s}\'{a}kov\'{a}. arXiv (Cornell University).</t>
+          <t>[1] Skirmante, K., Bleiders, M., Jekabsons, N., Bezrukovs, V., &amp; Jasmonts, G. (2020). Observations of OH masers of comets in 1.6GHz frequency band using the Irbene RT32 radio telescope. https://doi.org/10.5194/epsc2020-171 [2] Harmon, J. K., Nolan, M. C., Howell, E. S., Giorgini, J. D., &amp; Taylor, P. (2011). Comet 103P/Hartley; radar observations of the nucleus and large-grain coma. Abstracts of Papers Submitted to the Lunar and Planetary Science Conference.</t>
         </is>
       </c>
       <c r="P1020" t="inlineStr">
         <is>
-          <t>2017(28)</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="Q1020" t="inlineStr">
         <is>
-          <t>2017 CW+DD</t>
+          <t>2010 CW+DD</t>
         </is>
       </c>
       <c r="R1020" t="inlineStr">
@@ -59647,17 +59722,17 @@
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>103P</t>
+          <t>209P</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t>Hartley 2</t>
+          <t>LINEAR</t>
         </is>
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>P/1986 E2</t>
+          <t>P/2004 CB</t>
         </is>
       </c>
       <c r="D1021" t="inlineStr">
@@ -59675,22 +59750,22 @@
       </c>
       <c r="I1021" t="inlineStr">
         <is>
-          <t>8.5 (F)</t>
+          <t>17 (F)</t>
         </is>
       </c>
       <c r="O1021" t="inlineStr">
         <is>
-          <t>[1] Skirmante, K., Bleiders, M., Jekabsons, N., Bezrukovs, V., &amp; Jasmonts, G. (2020). Observations of OH masers of comets in 1.6GHz frequency band using the Irbene RT32 radio telescope. https://doi.org/10.5194/epsc2020-171 [2] Harmon, J. K., Nolan, M. C., Howell, E. S., Giorgini, J. D., &amp; Taylor, P. (2011). Comet 103P/Hartley; radar observations of the nucleus and large-grain coma. Abstracts of Papers Submitted to the Lunar and Planetary Science Conference.</t>
+          <t>[1] Nolan, M. C., Harmon, J. K., Howell, E. S., Campbell, D. B., &amp; Margot, J. L. (2006). Detection of large grains in the coma of Comet C/2001 A2 (LINEAR) from Arecibo radar observations. Icarus, 181, 432-441. https://doi.org/10.1016/j.icarus.2005.11.010 [2] Hickson, D. C., Virkki, A. K., Perillat, P., Nolan, M. C., &amp; Bhiravarasu, S. S. (2021). Polarimetric Decomposition of Near-Earth Asteroids Using Arecibo Radar Observations. The Planetary Science Journal, 2, 30. https://doi.org/10.3847/psj/abd846 [3] Senske, D. A., Campbell, D. B., Head, J. W., Fisher, P. C., Hine, A. A., deCharon, A., Frank, S. L., Keddie, S. T., Roberts, K. M., Stofan, E. R., Aubele, J. C., Crumpler, L. S., &amp; Stacy, N. (1991). Geology and tectonics of the Themis Regio-Lavinia Planitia-Alpha Regio-Lada Terra area, Venus: Results from Arecibo image data. Earth, Moon, and Planets, 55, 97-161. https://doi.org/10.1007/bf00058900</t>
         </is>
       </c>
       <c r="P1021" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="Q1021" t="inlineStr">
         <is>
-          <t>2010 CW+DD</t>
+          <t>2014 CW+DD</t>
         </is>
       </c>
       <c r="R1021" t="inlineStr">
@@ -59702,17 +59777,17 @@
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>209P</t>
+          <t>300P</t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>LINEAR</t>
+          <t>Catalina</t>
         </is>
       </c>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>P/2004 CB</t>
+          <t>P/2005 JQ5</t>
         </is>
       </c>
       <c r="D1022" t="inlineStr">
@@ -59730,22 +59805,22 @@
       </c>
       <c r="I1022" t="inlineStr">
         <is>
-          <t>17 (F)</t>
+          <t>16 (F)</t>
         </is>
       </c>
       <c r="O1022" t="inlineStr">
         <is>
-          <t>[1] Nolan, M. C., Harmon, J. K., Howell, E. S., Campbell, D. B., &amp; Margot, J. L. (2006). Detection of large grains in the coma of Comet C/2001 A2 (LINEAR) from Arecibo radar observations. Icarus, 181, 432-441. https://doi.org/10.1016/j.icarus.2005.11.010 [2] Hickson, D. C., Virkki, A. K., Perillat, P., Nolan, M. C., &amp; Bhiravarasu, S. S. (2021). Polarimetric Decomposition of Near-Earth Asteroids Using Arecibo Radar Observations. The Planetary Science Journal, 2, 30. https://doi.org/10.3847/psj/abd846 [3] Senske, D. A., Campbell, D. B., Head, J. W., Fisher, P. C., Hine, A. A., deCharon, A., Frank, S. L., Keddie, S. T., Roberts, K. M., Stofan, E. R., Aubele, J. C., Crumpler, L. S., &amp; Stacy, N. (1991). Geology and tectonics of the Themis Regio-Lavinia Planitia-Alpha Regio-Lada Terra area, Venus: Results from Arecibo image data. Earth, Moon, and Planets, 55, 97-161. https://doi.org/10.1007/bf00058900</t>
+          <t>[1] Harmon, J., Nolan, M., Margot, J., Campbell, D., Benner, L., &amp; Giorgini, J. (2006). Radar observations of Comet P/2005 JQ5 (Catalina). Icarus, 184, 285-288. https://doi.org/10.1016/j.icarus.2006.05.014 [2] Kruzins, E., Benner, L., Boyce, R., Brown, M., Coward, D., Darwell, S., Edwards, P., Elizabeth-Glina, L., Giorgini, J., Horiuchi, S., Lambert, A., Lazio, J., Calves, G. M., Moore, J., Peters, E., et al. (2023). Deep space debris—Detection of potentially hazardous asteroids and objects from the southern hemisphere. Frontiers in Space Technologies, 4. https://doi.org/10.3389/frspt.2023.1162915 [3] Kwiatkowski, T., Kryszczyńska, A., Polińska, M., Buckley, D. A. H., O'Donaghue, D., Charles, P. A., Crause, L. A., Crawford, S. M., Hashimoto, Y., Kniazev, A. Y., Loaring, N. S., Romero‐Colmenero, E., Sefako, R., Still, M., &amp; Väisänen, P. (2008). Photometry of Asteroid 2006 RH120 During Its Short Visit to a Geocentric Orbit. LPICo.</t>
         </is>
       </c>
       <c r="P1022" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="Q1022" t="inlineStr">
         <is>
-          <t>2014 CW+DD</t>
+          <t>2005 DD</t>
         </is>
       </c>
       <c r="R1022" t="inlineStr">
@@ -59757,22 +59832,17 @@
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>300P</t>
+          <t>Mars I</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>Catalina</t>
-        </is>
-      </c>
-      <c r="C1023" t="inlineStr">
-        <is>
-          <t>P/2005 JQ5</t>
+          <t>Phobos</t>
         </is>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
-          <t>Comet</t>
+          <t>Moons</t>
         </is>
       </c>
       <c r="E1023" t="inlineStr">
@@ -59785,22 +59855,22 @@
       </c>
       <c r="I1023" t="inlineStr">
         <is>
-          <t>16 (F)</t>
+          <t>11.8 (F)</t>
         </is>
       </c>
       <c r="O1023" t="inlineStr">
         <is>
-          <t>[1] Harmon, J., Nolan, M., Margot, J., Campbell, D., Benner, L., &amp; Giorgini, J. (2006). Radar observations of Comet P/2005 JQ5 (Catalina). Icarus, 184, 285-288. https://doi.org/10.1016/j.icarus.2006.05.014 [2] Kruzins, E., Benner, L., Boyce, R., Brown, M., Coward, D., Darwell, S., Edwards, P., Elizabeth-Glina, L., Giorgini, J., Horiuchi, S., Lambert, A., Lazio, J., Calves, G. M., Moore, J., Peters, E., et al. (2023). Deep space debris—Detection of potentially hazardous asteroids and objects from the southern hemisphere. Frontiers in Space Technologies, 4. https://doi.org/10.3389/frspt.2023.1162915 [3] Kwiatkowski, T., Kryszczyńska, A., Polińska, M., Buckley, D. A. H., O'Donaghue, D., Charles, P. A., Crause, L. A., Crawford, S. M., Hashimoto, Y., Kniazev, A. Y., Loaring, N. S., Romero‐Colmenero, E., Sefako, R., Still, M., &amp; Väisänen, P. (2008). Photometry of Asteroid 2006 RH120 During Its Short Visit to a Geocentric Orbit. LPICo.</t>
+          <t>[1] Busch, M. W., Ostro, S. J., Benner, L. A. M., Giorgini, J. D., Magri, C., Howell, E. S., Nolan, M. C., Hine, A. A., Campbell, D. B., Shapiro, I. I., &amp; Chandler, J. F. (2006). Arecibo radar observations of Phobos and Deimos. Icarus. https://doi.org/10.1016/j.icarus.2006.11.003</t>
         </is>
       </c>
       <c r="P1023" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1988, 1990, 2005</t>
         </is>
       </c>
       <c r="Q1023" t="inlineStr">
         <is>
-          <t>2005 DD</t>
+          <t>2005 logged, type unconfirmed</t>
         </is>
       </c>
       <c r="R1023" t="inlineStr">
@@ -59812,17 +59882,17 @@
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>Mars I</t>
+          <t>Saturn V</t>
         </is>
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t>Phobos</t>
+          <t>Rhea</t>
         </is>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Moons</t>
         </is>
       </c>
       <c r="E1024" t="inlineStr">
@@ -59835,22 +59905,17 @@
       </c>
       <c r="I1024" t="inlineStr">
         <is>
-          <t>11.8 (F)</t>
+          <t>0.09 (F)</t>
         </is>
       </c>
       <c r="O1024" t="inlineStr">
         <is>
-          <t>[1] Busch, M. W., Ostro, S. J., Benner, L. A. M., Giorgini, J. D., Magri, C., Howell, E. S., Nolan, M. C., Hine, A. A., Campbell, D. B., Shapiro, I. I., &amp; Chandler, J. F. (2006). Arecibo radar observations of Phobos and Deimos. Icarus. https://doi.org/10.1016/j.icarus.2006.11.003</t>
+          <t>[1] Black, G. J., Campbell, D. B., &amp; Carter, L. M. (2007). Arecibo radar observations of Rhea, Dione, Tethys, and Enceladus. Icarus, 191, 702-711. https://doi.org/10.1016/j.icarus.2007.06.009 [2] Black, G. J., &amp; Campbell, D. B. (2006). Arecibo Radar Observations Of Enceladus, Tethys, Dione, And Rhea. AAS/Division for Planetary Sciences Meeting Abstracts #38.</t>
         </is>
       </c>
       <c r="P1024" t="inlineStr">
         <is>
-          <t>1988, 1990, 2005</t>
-        </is>
-      </c>
-      <c r="Q1024" t="inlineStr">
-        <is>
-          <t>2005 logged, type unconfirmed</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="R1024" t="inlineStr">
@@ -59862,17 +59927,17 @@
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>Saturn V</t>
+          <t>Saturn 0</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>Rhea</t>
+          <t>Saturn’s rings</t>
         </is>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Moons</t>
         </is>
       </c>
       <c r="E1025" t="inlineStr">
@@ -59880,22 +59945,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H1025" t="n">
-        <v>1</v>
-      </c>
-      <c r="I1025" t="inlineStr">
-        <is>
-          <t>0.09 (F)</t>
-        </is>
-      </c>
       <c r="O1025" t="inlineStr">
         <is>
-          <t>[1] Black, G. J., Campbell, D. B., &amp; Carter, L. M. (2007). Arecibo radar observations of Rhea, Dione, Tethys, and Enceladus. Icarus, 191, 702-711. https://doi.org/10.1016/j.icarus.2007.06.009 [2] Black, G. J., &amp; Campbell, D. B. (2006). Arecibo Radar Observations Of Enceladus, Tethys, Dione, And Rhea. AAS/Division for Planetary Sciences Meeting Abstracts #38.</t>
+          <t>[1] Nicholson, P. D., French, R. G., Campbell, D. B., Margot, J.-L., Nolan, M. C., Black, G. J., &amp; Salo, H. J. (2005). Radar imaging of Saturn’s rings. Icarus, 177, 32–62. https://doi.org/10.1016/j.icarus.2005.02.019</t>
         </is>
       </c>
       <c r="P1025" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>1978, 1979, 1999, 2000(2), 2001, 2003(2), 2005, 2006(2), 2007, 2008, 2002</t>
         </is>
       </c>
       <c r="R1025" t="inlineStr">
@@ -59905,9 +59962,19 @@
       </c>
     </row>
     <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>73P-B</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>Schwassmann-Wachmann 3-B</t>
+        </is>
+      </c>
       <c r="D1026" t="inlineStr">
         <is>
-          <t>Planet</t>
+          <t>Comet</t>
         </is>
       </c>
       <c r="E1026" t="inlineStr">
@@ -59918,14 +59985,24 @@
       <c r="H1026" t="n">
         <v>1</v>
       </c>
+      <c r="I1026" t="inlineStr">
+        <is>
+          <t>9 (F)</t>
+        </is>
+      </c>
       <c r="O1026" t="inlineStr">
         <is>
-          <t>[1] Ostro, S. J., Pettengill, G. H., Campbell, D. B., &amp; Goldstein, R. M. (1982). Delay-Doppler radar observations of Saturn's rings. Icarus, 49, 367-381. https://doi.org/10.1016/0019-1035(82)90042-2 [2] Ostro, S.J., and the Cassini Radar Team, New Cassini RADAR Results for Saturn's Icy Satellites, Icarus 206, 498-506, 2010 http://dx.doi.org/10.1016/j.icarus.2009.07.041 [3] Nicholson, P.D., R.G. French, D.B. Campbell, J.L. Margot, M.C. Nolan, G.J. Black, and H.J. Salo, Radar Imaging of Saturn`s Rings, Icarus 177, 32-62, 2005 http://dx.doi.org/10.1016/j.icarus.2005.03.023 [4] Ostro, S.J., G.H. Pettengill, and D.B. Campbell, Radar Observations of Saturn`s Rings at Intermediate Tilt Angles, Icarus 41, 381-388, 1980 http://dx.doi.org/10.1016/0019-1035(80)90222-5 [5] Goldstein, R.M., R.R. Green, G.H. Pettengill, and D.B. Campbell, The Rings of Saturn - Two-Frequency Radar Observations, Icarus 30, 104-110, 1977 http://dx.doi.org/10.1016/0019-1035(77)90125-7</t>
+          <t>[1] Virkki, A., Zubko, E., Nolan, M. C., Howell, E. S., Benner, L. A. M., &amp; Harmon, J. K. (2019). Decimeter-scale particle characterization in the coma of 73P/Schwassmann-Wachmann 3 using dual-wavelength radar observations. Icarus, 325, 94-104. https://doi.org/10.1016/j.icarus.2019.02.009 [2] Nolan, M. C., Harmon, J. K., Howell, E. S., Benner, L. A. M., Giorgini, J. D., Ostro, S. J., Campbell, D. B., &amp; Margot, J. (2006). Radar Observations Of Comet 73P/Schwassmann-Wachmann 3. AAS/Division for Planetary Sciences Meeting Abstracts #38. [3] Virkki, A., Evgenij, Z., Nolan, M. C., Howell, E. S., Benner, L., &amp; Harmon, J. K. (2018). Decimeter-Scale Coma Particle Characterization of Comet 73P/Schwassmann-Wachmann 3 Using Dual-Wavelength Radar Observations. AAS/Division for Planetary Sciences Meeting Abstracts #50.</t>
         </is>
       </c>
       <c r="P1026" t="inlineStr">
         <is>
-          <t>1978, 1979, 1999, 2000, 2001, 2002, 2003, 2005, 2006, 2007, 2008</t>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q1026" t="inlineStr">
+        <is>
+          <t>2018 CW+DD</t>
         </is>
       </c>
       <c r="R1026" t="inlineStr">
@@ -59937,17 +60014,17 @@
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>Saturn 0</t>
+          <t>73P-C</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>Saturn’s rings</t>
+          <t>Schwassmann-Wachmann 3-C</t>
         </is>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
-          <t>Rings</t>
+          <t>Comet</t>
         </is>
       </c>
       <c r="E1027" t="inlineStr">
@@ -59955,14 +60032,27 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="H1027" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1027" t="inlineStr">
+        <is>
+          <t>9 (F)</t>
+        </is>
+      </c>
       <c r="O1027" t="inlineStr">
         <is>
-          <t>[1] Nicholson, P. D., French, R. G., Campbell, D. B., Margot, J.-L., Nolan, M. C., Black, G. J., &amp; Salo, H. J. (2005). Radar imaging of Saturn’s rings. Icarus, 177, 32–62. https://doi.org/10.1016/j.icarus.2005.02.019</t>
+          <t>[1] Virkki, A., Zubko, E., Nolan, M. C., Howell, E. S., Benner, L. A. M., &amp; Harmon, J. K. (2019). Decimeter-scale particle characterization in the coma of 73P/Schwassmann-Wachmann 3 using dual-wavelength radar observations. Icarus, 325, 94-104. https://doi.org/10.1016/j.icarus.2019.02.009 [2] Nolan, M. C., Harmon, J. K., Howell, E. S., Benner, L. A. M., Giorgini, J. D., Ostro, S. J., Campbell, D. B., &amp; Margot, J. (2006). Radar Observations Of Comet 73P/Schwassmann-Wachmann 3. AAS/Division for Planetary Sciences Meeting Abstracts #38. [3] Virkki, A., Evgenij, Z., Nolan, M. C., Howell, E. S., Benner, L., &amp; Harmon, J. K. (2018). Decimeter-Scale Coma Particle Characterization of Comet 73P/Schwassmann-Wachmann 3 Using Dual-Wavelength Radar Observations. AAS/Division for Planetary Sciences Meeting Abstracts #50.</t>
         </is>
       </c>
       <c r="P1027" t="inlineStr">
         <is>
-          <t>1978, 1979, 1999, 2000(2), 2001, 2003(2), 2005, 2006(2), 2007, 2008, 2002</t>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q1027" t="inlineStr">
+        <is>
+          <t>2018 DD</t>
         </is>
       </c>
       <c r="R1027" t="inlineStr">
@@ -59972,19 +60062,14 @@
       </c>
     </row>
     <row r="1028">
-      <c r="A1028" t="inlineStr">
-        <is>
-          <t>73P-B</t>
-        </is>
-      </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t>Schwassmann-Wachmann 3-B</t>
+          <t>SOHO</t>
         </is>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
-          <t>Comet</t>
+          <t>Spacecraft</t>
         </is>
       </c>
       <c r="E1028" t="inlineStr">
@@ -59995,24 +60080,14 @@
       <c r="H1028" t="n">
         <v>1</v>
       </c>
-      <c r="I1028" t="inlineStr">
-        <is>
-          <t>9 (F)</t>
-        </is>
-      </c>
       <c r="O1028" t="inlineStr">
         <is>
-          <t>[1] Virkki, A., Zubko, E., Nolan, M. C., Howell, E. S., Benner, L. A. M., &amp; Harmon, J. K. (2019). Decimeter-scale particle characterization in the coma of 73P/Schwassmann-Wachmann 3 using dual-wavelength radar observations. Icarus, 325, 94-104. https://doi.org/10.1016/j.icarus.2019.02.009 [2] Nolan, M. C., Harmon, J. K., Howell, E. S., Benner, L. A. M., Giorgini, J. D., Ostro, S. J., Campbell, D. B., &amp; Margot, J. (2006). Radar Observations Of Comet 73P/Schwassmann-Wachmann 3. AAS/Division for Planetary Sciences Meeting Abstracts #38. [3] Virkki, A., Evgenij, Z., Nolan, M. C., Howell, E. S., Benner, L., &amp; Harmon, J. K. (2018). Decimeter-Scale Coma Particle Characterization of Comet 73P/Schwassmann-Wachmann 3 Using Dual-Wavelength Radar Observations. AAS/Division for Planetary Sciences Meeting Abstracts #50.</t>
+          <t>[1] European Space Agency. (1998). SOHO spacecraft located with ground-based radar [Press release]. https://www.esa.int/Newsroom/Press_Releases/SOHO_spacecraft_located_with_ground-based_radar [2] Vandenbussche, F. C. (1999). SOHO's recovery - An unprecedented success story. ESA Bulletin, 97. https://www.esa.int/esapub/bulletin/bullet97/vandenbu.pdf</t>
         </is>
       </c>
       <c r="P1028" t="inlineStr">
         <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="Q1028" t="inlineStr">
-        <is>
-          <t>2018 CW+DD</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="R1028" t="inlineStr">
@@ -60024,17 +60099,17 @@
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>73P-C</t>
+          <t>Saturn III</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>Schwassmann-Wachmann 3-C</t>
+          <t>Tethys</t>
         </is>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
-          <t>Comet</t>
+          <t>Moons</t>
         </is>
       </c>
       <c r="E1029" t="inlineStr">
@@ -60047,22 +60122,17 @@
       </c>
       <c r="I1029" t="inlineStr">
         <is>
-          <t>9 (F)</t>
+          <t>0.73 (F)</t>
         </is>
       </c>
       <c r="O1029" t="inlineStr">
         <is>
-          <t>[1] Virkki, A., Zubko, E., Nolan, M. C., Howell, E. S., Benner, L. A. M., &amp; Harmon, J. K. (2019). Decimeter-scale particle characterization in the coma of 73P/Schwassmann-Wachmann 3 using dual-wavelength radar observations. Icarus, 325, 94-104. https://doi.org/10.1016/j.icarus.2019.02.009 [2] Nolan, M. C., Harmon, J. K., Howell, E. S., Benner, L. A. M., Giorgini, J. D., Ostro, S. J., Campbell, D. B., &amp; Margot, J. (2006). Radar Observations Of Comet 73P/Schwassmann-Wachmann 3. AAS/Division for Planetary Sciences Meeting Abstracts #38. [3] Virkki, A., Evgenij, Z., Nolan, M. C., Howell, E. S., Benner, L., &amp; Harmon, J. K. (2018). Decimeter-Scale Coma Particle Characterization of Comet 73P/Schwassmann-Wachmann 3 Using Dual-Wavelength Radar Observations. AAS/Division for Planetary Sciences Meeting Abstracts #50.</t>
+          <t>[1] Black, G. J., Campbell, D. B., &amp; Carter, L. M. (2007). Arecibo radar observations of Rhea, Dione, Tethys, and Enceladus. Icarus, 191, 702-711. https://doi.org/10.1016/j.icarus.2007.06.009 [2] Black, G. J., &amp; Campbell, D. B. (2006). Arecibo Radar Observations Of Enceladus, Tethys, Dione, And Rhea. AAS/Division for Planetary Sciences Meeting Abstracts #38.</t>
         </is>
       </c>
       <c r="P1029" t="inlineStr">
         <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="Q1029" t="inlineStr">
-        <is>
-          <t>2018 DD</t>
+          <t>2005(5), 2006(3), 2007(4)</t>
         </is>
       </c>
       <c r="R1029" t="inlineStr">
@@ -60072,14 +60142,19 @@
       </c>
     </row>
     <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>Saturn VI</t>
+        </is>
+      </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>SOHO</t>
+          <t>Titan</t>
         </is>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
-          <t>Spacecraft</t>
+          <t>Moons</t>
         </is>
       </c>
       <c r="E1030" t="inlineStr">
@@ -60090,14 +60165,24 @@
       <c r="H1030" t="n">
         <v>1</v>
       </c>
+      <c r="I1030" t="inlineStr">
+        <is>
+          <t>-1.3 (F)</t>
+        </is>
+      </c>
       <c r="O1030" t="inlineStr">
         <is>
-          <t>[1] European Space Agency. (1998). SOHO spacecraft located with ground-based radar [Press release]. https://www.esa.int/Newsroom/Press_Releases/SOHO_spacecraft_located_with_ground-based_radar [2] Vandenbussche, F. C. (1999). SOHO's recovery - An unprecedented success story. ESA Bulletin, 97. https://www.esa.int/esapub/bulletin/bullet97/vandenbu.pdf</t>
+          <t>[1] Campbell, D. B., Black, G. J., Carter, L. M., &amp; Ostro, S. J. (2003). Radar Evidence for Liquid Surfaces on Titan. Science, 302, 431-434. https://doi.org/10.1126/science.1088969 [2] Muhleman, D. O., Grossman, A. W., &amp; Butler, B. (1995). Radar Investigation of Mars, Mercury, and Titan. Annual Review of Earth and Planetary Sciences. https://doi.org/10.1146/annurev.ea.23.050195.002005 [3] Black, G. J., Campbell, D. B., &amp; Carter, L. M. (2010). Ground-based radar observations of Titan: 2000–2008. Icarus, 212, 300-320. https://doi.org/10.1016/j.icarus.2010.10.025 [4] Hofgartner, J. D., Hayes, A. G., Campbell, D. B., Lunine, J. I., Black, G. J., MacKenzie, S. M., Birch, S. P. D., Elachi, C., Kirk, R. D., Gall, A. L., Lorenz, R. D., &amp; Wall, S. D. (2020). The root of anomalously specular reflections from solid surfaces on Saturn’s moon Titan. Nature Communications, 11. https://doi.org/10.1038/s41467-020-16663-1 [5] Lorenz, R. (2023). Slopes on Titan and application to spacecraft landing safety. Planetary and Space Science, 235, 105745. https://doi.org/10.1016/j.pss.2023.105745 [6] Campbell, D. B., Black, G., Carter, L. M., Hine, A. A., Margot, J., Nolan, M. C., &amp; Ostro, S. J. (2002). The Surface of Titan: Arecibo Radar Observations. DPS. [7] Duxbury, T. C., &amp; Lieske, J. H. (1976). Arecibo Radar Observations of the Galilean Satellites and Titan. Bulletin of the American Astronomical Society. [8] Black, G. J., Campbell, D. B., &amp; Carter, L. M. (2008). Surface Properties of Titan from Arecibo/GBT Radar Observations. AAS/Division for Planetary Sciences Meeting Abstracts #40. [9] Campbell, D. B., Black, G., Carter, L. M., &amp; Nolan, M. C. (2007). Titan: 13 cm Arecibo Radar Observations and Comparisons with Cassini ISS and Radar Imagery. Lunar and Planetary Science Conference. [10] Bell, P. M. (1983). Methane ocean on Titan?. Eos, Transactions American Geophysical Union, 64, 84-84. https://doi.org/10.1029/eo064i009p00084-01 [11] Brighi, G., Poggiali, V., Mastrogiuseppe, M., Zannoni, M., Hayes, A. G., &amp; Tortora, P. (2025). Cassini Bistatic Radar Campaign during the Prime and Equinox Missions: Heterogeneous Reflections from Titan's Solid Surfaces. https://doi.org/10.5194/egusphere-egu25-18169 [12] Sultan-Salem, A.K., and T.G. Leonard, Revisiting Titan's Earth-Based Scattering Data at 13-cm Wavelength, Geophysical Research Letters 34, L12201, 2007 http://dx.doi.org/10.1029/2007GL029928</t>
         </is>
       </c>
       <c r="P1030" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1979, 1997, 1998, 1999, 2000, 2001(2), 2002(2), 2004, 2005, 2006, 2007, 2008</t>
+        </is>
+      </c>
+      <c r="Q1030" t="inlineStr">
+        <is>
+          <t>1997 logged, type unconfirmed; 2007 DD; 2008 logged, type unconfirmed</t>
         </is>
       </c>
       <c r="R1030" t="inlineStr">
@@ -60109,17 +60194,17 @@
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>Saturn III</t>
+          <t>Planet 2</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>Tethys</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Planets</t>
         </is>
       </c>
       <c r="E1031" t="inlineStr">
@@ -60132,17 +60217,27 @@
       </c>
       <c r="I1031" t="inlineStr">
         <is>
-          <t>0.73 (F)</t>
+          <t>-4.38 (F)</t>
+        </is>
+      </c>
+      <c r="J1031" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="O1031" t="inlineStr">
         <is>
-          <t>[1] Black, G. J., Campbell, D. B., &amp; Carter, L. M. (2007). Arecibo radar observations of Rhea, Dione, Tethys, and Enceladus. Icarus, 191, 702-711. https://doi.org/10.1016/j.icarus.2007.06.009 [2] Black, G. J., &amp; Campbell, D. B. (2006). Arecibo Radar Observations Of Enceladus, Tethys, Dione, And Rhea. AAS/Division for Planetary Sciences Meeting Abstracts #38.</t>
+          <t>[1] Senske, D. A., Campbell, D. B., Head, J. W., Fisher, P. C., Hine, A. A., deCharon, A., Frank, S. L., Keddie, S. T., Roberts, K. M., Stofan, E. R., Aubele, J. C., Crumpler, L. S., &amp; Stacy, N. (1991). Geology and tectonics of the Themis Regio-Lavinia Planitia-Alpha Regio-Lada Terra area, Venus: Results from Arecibo image data. Earth, Moon, and Planets, 55, 97-161. https://doi.org/10.1007/bf00058900 [2] Campbell, D. B., Head, J. W., Senske, D. A., Fisher, P. C., Hine, A. A., &amp; Harmon, J. K. (1989). Styles of Volcanism on Venus: New Arecibo High Resolution Radar Data. Science. https://doi.org/10.1126/science.246.4928.373 [3] Carter, L. M., Campbell, D. B., &amp; Campbell, B. A. (2004). Impact crater related surficial deposits on Venus: Multipolarization radar observations with Arecibo. Journal of Geophysical Research: Planets, 109. https://doi.org/10.1029/2003je002227 [4] Campbell, B. A., &amp; Campbell, D. B. (1992). Analysis of volcanic surface morphology on Venus from comparison of Arecibo, Magellan, and terrestrial airborne radar data. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/92je01558 [5] Campbell, D. B., &amp; Burns, B. A. (1980). Earth‐based radar imagery of Venus. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/ja085ia13p08271 [6] Senske, D. A., Head, J. W., Stofan, E. R., &amp; Campbell, D. B. (1991). Geology and structure of Beta Regio, Venus: Results from Arecibo Radar Imaging. Geophysical Research Letters. https://doi.org/10.1029/91gl01001 [7] Dyce, B. R., Pettengill, G. H., &amp; Shapiro, I. I. (1967). Radar determination of the rotations of Venus and Mercury. The Astronomical Journal. https://doi.org/10.1086/110231 [8] Crumpler, L. S., Head, J. W., &amp; Campbell, D. B. (1986). Orogenic belts on Venus. Geology, 14, 1031. https://doi.org/10.1130/0091-7613(1986)14&lt;1031:obov&gt;2.0.co;2 [9] Campbell, B. A., Campbell, D. B., &amp; DeVries, C. H. (1999). Surface processes in the Venus highlands: Results from analysis of Magellan and Arecibo data. Journal of Geophysical Research: Planets, 104, 1897-1916. https://doi.org/10.1029/1998je900022 [10] Campbell, B. A., Arvidson, R. E., &amp; Shepard, M. K. (1993). Radar polarization properties of volcanic and playa surfaces: Applications to terrestrial remote sensing and Venus data interpretation. Journal of Geophysical Research: Planets, 98, 17099-17113. https://doi.org/10.1029/93je01541 [11] Burns, B. A., &amp; Campbell, D. B. (1985). Radar evidence for cratering on Venus. Journal of Geophysical Research: Solid Earth, 90, 3037-3047. https://doi.org/10.1029/jb090ib04p03037 [12] Senske, D. A. (1990). Geology of the Venus equatorial region from Pioneer Venus radar imaging. Earth Moon and Planets. https://doi.org/10.1007/bf00142397 [13] Campbell, D. B., Head, J. W., Harmon, J. K., &amp; Hine, A. A. (1983). Venus: Identification of Banded Terrain in the Mountains of Ishtar Terra. Science. https://doi.org/10.1126/science.221.4611.644 [14] Campbell, B. A., &amp; Campbell, D. B. (2022). Arecibo Radar Maps of Venus from 1988 to 2020. The Planetary Science Journal. https://doi.org/10.3847/psj/ac4f43 [15] Pettengill, G. H., Dyce, R. B., &amp; Campbell, D. B. (1967). Radar measurements at 70 CM of Venus and Mercury. The Astronomical Journal, 72, 330. https://doi.org/10.1086/110229 [16] Carter, L. M., Campbell, D. B., &amp; Campbell, B. A. (2006). Volcanic deposits in shield fields and highland regions on Venus: Surface properties from radar polarimetry. Journal of Geophysical Research: Planets, 111. https://doi.org/10.1029/2005je002519 [17] Stofan, E. R., Head, J. W., Campbell, D. B., Zisk, S. H., Bogomolov, A. F., Rzhiga, O. N., Basilevsky, A. T., &amp; Armand, N. A. (1989). Geology of a rift zone on Venus: Beta Regio and Devana Chasma. Geological Society of America Bulletin. https://doi.org/10.1130/0016-7606(1989)101&lt;0143:goarzo&gt;2.3.co;2 [18] Kratter, K. M., Carter, L. M., &amp; Campbell, D. B. (2007). An expanded view of Lada Terra, Venus: New Arecibo radar observations of Quetzalpetlatl Corona and surrounding flows. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/2006je002722 [19] Campbell, B.A. and Campbell, D.B., Arecibo Radar Maps of Venus from 1988 to 2020, The Planetary Science Journal, 3(3), p.55, 2022 https://iopscience.iop.org/article/10.3847/PSJ/ac4f43/meta [20] Campbell, B.A, D.B. Campbell, L.M. Carter, J.F. Chandler, J.D. Giorgini, J.-L. Margot, G.A. Morgan; M.C. Nolan, P.J. Perillat, and J. L. Whitten, The Mean Rotation Rate of Venus from 29 Years of Earth-Based Radar Observations, Icarus 332, 19-23, 2019 https://doi.org/10.1016/j.icarus.2019.06.019 [21] Campbell, B.A., D.B. Campbell, G.A. Morgan, L.M. Carter, M.C. Nolan, and J.F. Chandler, Evidence for Crater Ejecta on Venus Tessera Terrain from Earth-Based Radar Images, Icarus 250, 123-130, 2015 http://dx.doi.org/10.1016/j.icarus.2014.11.025 [22] Campbell, D.B., D.A. Senske, J.W. Head, P.C. Fisher, and A.A. Hine, Venus Southern Hemisphere - Geologic Character and Age of Terrains in the Themis-Alpha-Lada Region, Science 251, 180-183, 1991 http://dx.doi.org/10.1126/science.251.4990.180 [23] Shapiro, I.I., J.F. Chandler, D.B. Campbell, A.A. Hine, and N.J.S. Stacy, The Spin Vector of Venus, Astronomical Journal 100, 1363-1368, 1990 http://dx.doi.org/10.1086/115602 [24] Campbell, D.B., N.J.S. Stacy, and A.A. Hine, Venus - Crater Distributions at Low Northern Latitudes and in the Southern Hemisphere from New Arecibo Observations, Geophysical Review Letters 17, 1389-1392, 1990 http://dx.doi.org/10.1029/GL017i009p01389 [25] Campbell, B.A., and D.B. Campbell, Western Eisila Regio, Venus - Radar Properties of Volcanic Deposits, Geophysical Research Letters 17, 1353-1356, 1990 http://dx.doi.org/10.1029/GL017i009p01353 [26] Bruegge, R.W.V., J.W. Head, and D.B. Campbell, Orogeny and Large-Scale Strike-Slip Faulting on Venus: Tectonic Evolution of Maxwell Montes, Journal of Geophysical Research 95, 8357-8381, 1990 http://dx.doi.org/10.1029/JB095iB06p08357 [27] Stofan, E.R., J.W. Head, and D.B. Campbell, Geology of the Southern Ishtar Terra/Guinevere and Sedna Planitae Region on Venus, Earth, Moon, and Planets 38, 183-207, 1987 http://dx.doi.org/10.1007/BF00119682 [28] Campbell, D.B., J.W. Head, J.K. Harmon, and A.A. Hine, Venus - Volcanism and Rift Information in Beta Regio, Science 226, 167-170, 1984 http://dx.doi.org/10.1126/science.226.4671.167 [29] Cutts, J.A., T.W. Thompson, and B.H. Lewis, Origin of Bright Ring-Shaped Craters in Radar Images of Venus, Icarus 48, 428-452, 1981 http://dx.doi.org/10.1016/0019-1035(81)90054-3 [30] Campbell, D.B., B.A. Burns, and V. Boriakoff, Venus - Further Evidence of Impact Cratering and Tectonic Activity from Radar Observations, Science 204, 1424-1427, 1979 http://dx.doi.org/10.1126/science.204.4400.1424 [31] Shapiro, I.I., D.B. Campbell, and W.M. de Campli, Nonresonance Rotation of Venus, Astrophysical Journal 230, L123-L126, 1979 http://dx.doi.org/10.1086/182975 [32] Campbell, D.B., R.B. Dyce, and G.H. Pettengill, New Radar Image of Venus, Science 193, 1123-1124, 1976 http://dx.doi.org/10.1126/science.193.4258.1123 [33] Hagfors, R., and D.B. Campbell, Radar Backscattering from Venus at Oblique Incidence at a Wavelength of 70 cm, Astronomical Journal 79, 493-502, 1974 http://dx.doi.org/10.1086/111572 [34] Campbell, D.B., R.B. Dyce, R.P. Ingalls, G.H. Pettengill, and I.I. Shapiro, Venus: Topography Revealed by Radar Data, Science 175, 514-516, 1972 http://dx.doi.org/10.1126/science.175.4021.514 [35] Campbell, D.B., R.F. Jurgens, R.B. Dyce, F.S. Harris, and G.H. Pettengill, Radar Interferometric Observations of Venus at 70-Centimeter Wavelength, Science 170, 1090-1092, 1970 http://dx.doi.org/10.1126/science.170.3962.1090 [36] Jurgens, R.F and R.B. Dyce, Radar Backscattering Properties of Venus at 70 cm, Astronomical Journal 75, 297-314, 1970 http://dx.doi.org/10.1086/110977 [37] Jurgens, R.F., Some Preliminary Results of the 70-cm Radar Studies of Venus, Radio Science 5, 435-442, 1970 http://dx.doi.org/10.1029/RS005i002p00435 [38] Campbell, D.B., and D.O. Muhleman, Measurements of the Electron Content of the Interplanetary Medium Between Earth and Venus, Journal of Geophysical Research 74, 1138, 1969 http://dx.doi.org/10.1029/JA074i005p01138 [39] Jurgens, R.F., Radar Scattering from Venus at Large Angles of Incidence and the Question of Polar Ice Caps, Science 162, 1388-1390, 1968 http://dx.doi.org/10.1126/science.162.3860.1388 [40] Ash, M.E., D.B. Campbell, R.B. Dyce, R.P. Ingalls, R. Jurgens, G.H. Pettengill, I.I. Shapiro, M.A. Slade, and T.W. Thompson, The Case for the Radar Radius of Venus, Science 160, 985-987, 1968 http://dx.doi.org/10.1126/science.160.3831.985</t>
         </is>
       </c>
       <c r="P1031" t="inlineStr">
         <is>
-          <t>2005(5), 2006(3), 2007(4)</t>
+          <t>1978, 1979, 1980, 1981, 1982, 1983, 1984, 1985, 1986, 1987, 1988, 1989, 1999, 2000, 2001(2), 2003, 2004, 2009, 2012, 2015, 2017(6), 2020(8)[8]</t>
+        </is>
+      </c>
+      <c r="Q1031" t="inlineStr">
+        <is>
+          <t>2003 logged, type unconfirmed; 2004 DD; 2012 DD; 2015 logged, type unconfirmed; 2020 CW+DD</t>
         </is>
       </c>
       <c r="R1031" t="inlineStr">
@@ -60152,19 +60247,19 @@
       </c>
     </row>
     <row r="1032">
-      <c r="A1032" t="inlineStr">
-        <is>
-          <t>Saturn VI</t>
-        </is>
-      </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>Titan</t>
+          <t>Space-Debris</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>WT1190F</t>
         </is>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Space debris</t>
         </is>
       </c>
       <c r="E1032" t="inlineStr">
@@ -60175,24 +60270,14 @@
       <c r="H1032" t="n">
         <v>1</v>
       </c>
-      <c r="I1032" t="inlineStr">
-        <is>
-          <t>-1.3 (F)</t>
-        </is>
-      </c>
-      <c r="O1032" t="inlineStr">
-        <is>
-          <t>[1] Campbell, D. B., Black, G. J., Carter, L. M., &amp; Ostro, S. J. (2003). Radar Evidence for Liquid Surfaces on Titan. Science, 302, 431-434. https://doi.org/10.1126/science.1088969 [2] Muhleman, D. O., Grossman, A. W., &amp; Butler, B. (1995). Radar Investigation of Mars, Mercury, and Titan. Annual Review of Earth and Planetary Sciences. https://doi.org/10.1146/annurev.ea.23.050195.002005 [3] Black, G. J., Campbell, D. B., &amp; Carter, L. M. (2010). Ground-based radar observations of Titan: 2000–2008. Icarus, 212, 300-320. https://doi.org/10.1016/j.icarus.2010.10.025 [4] Hofgartner, J. D., Hayes, A. G., Campbell, D. B., Lunine, J. I., Black, G. J., MacKenzie, S. M., Birch, S. P. D., Elachi, C., Kirk, R. D., Gall, A. L., Lorenz, R. D., &amp; Wall, S. D. (2020). The root of anomalously specular reflections from solid surfaces on Saturn’s moon Titan. Nature Communications, 11. https://doi.org/10.1038/s41467-020-16663-1 [5] Lorenz, R. (2023). Slopes on Titan and application to spacecraft landing safety. Planetary and Space Science, 235, 105745. https://doi.org/10.1016/j.pss.2023.105745 [6] Campbell, D. B., Black, G., Carter, L. M., Hine, A. A., Margot, J., Nolan, M. C., &amp; Ostro, S. J. (2002). The Surface of Titan: Arecibo Radar Observations. DPS. [7] Duxbury, T. C., &amp; Lieske, J. H. (1976). Arecibo Radar Observations of the Galilean Satellites and Titan. Bulletin of the American Astronomical Society. [8] Black, G. J., Campbell, D. B., &amp; Carter, L. M. (2008). Surface Properties of Titan from Arecibo/GBT Radar Observations. AAS/Division for Planetary Sciences Meeting Abstracts #40. [9] Campbell, D. B., Black, G., Carter, L. M., &amp; Nolan, M. C. (2007). Titan: 13 cm Arecibo Radar Observations and Comparisons with Cassini ISS and Radar Imagery. Lunar and Planetary Science Conference. [10] Bell, P. M. (1983). Methane ocean on Titan?. Eos, Transactions American Geophysical Union, 64, 84-84. https://doi.org/10.1029/eo064i009p00084-01 [11] Brighi, G., Poggiali, V., Mastrogiuseppe, M., Zannoni, M., Hayes, A. G., &amp; Tortora, P. (2025). Cassini Bistatic Radar Campaign during the Prime and Equinox Missions: Heterogeneous Reflections from Titan's Solid Surfaces. https://doi.org/10.5194/egusphere-egu25-18169 [12] Sultan-Salem, A.K., and T.G. Leonard, Revisiting Titan's Earth-Based Scattering Data at 13-cm Wavelength, Geophysical Research Letters 34, L12201, 2007 http://dx.doi.org/10.1029/2007GL029928</t>
-        </is>
-      </c>
       <c r="P1032" t="inlineStr">
         <is>
-          <t>1979, 1997, 1998, 1999, 2000, 2001(2), 2002(2), 2004, 2005, 2006, 2007, 2008</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="Q1032" t="inlineStr">
         <is>
-          <t>1997 logged, type unconfirmed; 2007 DD; 2008 logged, type unconfirmed</t>
+          <t>2015 CW+DD</t>
         </is>
       </c>
       <c r="R1032" t="inlineStr">
@@ -60204,17 +60289,22 @@
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>Planet 2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Hebe</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>A847 NA</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
-          <t>Planet</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="E1033" t="inlineStr">
@@ -60227,27 +60317,17 @@
       </c>
       <c r="I1033" t="inlineStr">
         <is>
-          <t>-4.38 (F)</t>
-        </is>
-      </c>
-      <c r="J1033" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>5.62 (J)</t>
         </is>
       </c>
       <c r="O1033" t="inlineStr">
         <is>
-          <t>[1] Senske, D. A., Campbell, D. B., Head, J. W., Fisher, P. C., Hine, A. A., deCharon, A., Frank, S. L., Keddie, S. T., Roberts, K. M., Stofan, E. R., Aubele, J. C., Crumpler, L. S., &amp; Stacy, N. (1991). Geology and tectonics of the Themis Regio-Lavinia Planitia-Alpha Regio-Lada Terra area, Venus: Results from Arecibo image data. Earth, Moon, and Planets, 55, 97-161. https://doi.org/10.1007/bf00058900 [2] Campbell, D. B., Head, J. W., Senske, D. A., Fisher, P. C., Hine, A. A., &amp; Harmon, J. K. (1989). Styles of Volcanism on Venus: New Arecibo High Resolution Radar Data. Science. https://doi.org/10.1126/science.246.4928.373 [3] Carter, L. M., Campbell, D. B., &amp; Campbell, B. A. (2004). Impact crater related surficial deposits on Venus: Multipolarization radar observations with Arecibo. Journal of Geophysical Research: Planets, 109. https://doi.org/10.1029/2003je002227 [4] Campbell, B. A., &amp; Campbell, D. B. (1992). Analysis of volcanic surface morphology on Venus from comparison of Arecibo, Magellan, and terrestrial airborne radar data. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/92je01558 [5] Campbell, D. B., &amp; Burns, B. A. (1980). Earth‐based radar imagery of Venus. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/ja085ia13p08271 [6] Senske, D. A., Head, J. W., Stofan, E. R., &amp; Campbell, D. B. (1991). Geology and structure of Beta Regio, Venus: Results from Arecibo Radar Imaging. Geophysical Research Letters. https://doi.org/10.1029/91gl01001 [7] Dyce, B. R., Pettengill, G. H., &amp; Shapiro, I. I. (1967). Radar determination of the rotations of Venus and Mercury. The Astronomical Journal. https://doi.org/10.1086/110231 [8] Crumpler, L. S., Head, J. W., &amp; Campbell, D. B. (1986). Orogenic belts on Venus. Geology, 14, 1031. https://doi.org/10.1130/0091-7613(1986)14&lt;1031:obov&gt;2.0.co;2 [9] Campbell, B. A., Campbell, D. B., &amp; DeVries, C. H. (1999). Surface processes in the Venus highlands: Results from analysis of Magellan and Arecibo data. Journal of Geophysical Research: Planets, 104, 1897-1916. https://doi.org/10.1029/1998je900022 [10] Campbell, B. A., Arvidson, R. E., &amp; Shepard, M. K. (1993). Radar polarization properties of volcanic and playa surfaces: Applications to terrestrial remote sensing and Venus data interpretation. Journal of Geophysical Research: Planets, 98, 17099-17113. https://doi.org/10.1029/93je01541 [11] Burns, B. A., &amp; Campbell, D. B. (1985). Radar evidence for cratering on Venus. Journal of Geophysical Research: Solid Earth, 90, 3037-3047. https://doi.org/10.1029/jb090ib04p03037 [12] Senske, D. A. (1990). Geology of the Venus equatorial region from Pioneer Venus radar imaging. Earth Moon and Planets. https://doi.org/10.1007/bf00142397 [13] Campbell, D. B., Head, J. W., Harmon, J. K., &amp; Hine, A. A. (1983). Venus: Identification of Banded Terrain in the Mountains of Ishtar Terra. Science. https://doi.org/10.1126/science.221.4611.644 [14] Campbell, B. A., &amp; Campbell, D. B. (2022). Arecibo Radar Maps of Venus from 1988 to 2020. The Planetary Science Journal. https://doi.org/10.3847/psj/ac4f43 [15] Pettengill, G. H., Dyce, R. B., &amp; Campbell, D. B. (1967). Radar measurements at 70 CM of Venus and Mercury. The Astronomical Journal, 72, 330. https://doi.org/10.1086/110229 [16] Carter, L. M., Campbell, D. B., &amp; Campbell, B. A. (2006). Volcanic deposits in shield fields and highland regions on Venus: Surface properties from radar polarimetry. Journal of Geophysical Research: Planets, 111. https://doi.org/10.1029/2005je002519 [17] Stofan, E. R., Head, J. W., Campbell, D. B., Zisk, S. H., Bogomolov, A. F., Rzhiga, O. N., Basilevsky, A. T., &amp; Armand, N. A. (1989). Geology of a rift zone on Venus: Beta Regio and Devana Chasma. Geological Society of America Bulletin. https://doi.org/10.1130/0016-7606(1989)101&lt;0143:goarzo&gt;2.3.co;2 [18] Kratter, K. M., Carter, L. M., &amp; Campbell, D. B. (2007). An expanded view of Lada Terra, Venus: New Arecibo radar observations of Quetzalpetlatl Corona and surrounding flows. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/2006je002722 [19] Campbell, B.A. and Campbell, D.B., Arecibo Radar Maps of Venus from 1988 to 2020, The Planetary Science Journal, 3(3), p.55, 2022 https://iopscience.iop.org/article/10.3847/PSJ/ac4f43/meta [20] Campbell, B.A, D.B. Campbell, L.M. Carter, J.F. Chandler, J.D. Giorgini, J.-L. Margot, G.A. Morgan; M.C. Nolan, P.J. Perillat, and J. L. Whitten, The Mean Rotation Rate of Venus from 29 Years of Earth-Based Radar Observations, Icarus 332, 19-23, 2019 https://doi.org/10.1016/j.icarus.2019.06.019 [21] Campbell, B.A., D.B. Campbell, G.A. Morgan, L.M. Carter, M.C. Nolan, and J.F. Chandler, Evidence for Crater Ejecta on Venus Tessera Terrain from Earth-Based Radar Images, Icarus 250, 123-130, 2015 http://dx.doi.org/10.1016/j.icarus.2014.11.025 [22] Campbell, D.B., D.A. Senske, J.W. Head, P.C. Fisher, and A.A. Hine, Venus Southern Hemisphere - Geologic Character and Age of Terrains in the Themis-Alpha-Lada Region, Science 251, 180-183, 1991 http://dx.doi.org/10.1126/science.251.4990.180 [23] Shapiro, I.I., J.F. Chandler, D.B. Campbell, A.A. Hine, and N.J.S. Stacy, The Spin Vector of Venus, Astronomical Journal 100, 1363-1368, 1990 http://dx.doi.org/10.1086/115602 [24] Campbell, D.B., N.J.S. Stacy, and A.A. Hine, Venus - Crater Distributions at Low Northern Latitudes and in the Southern Hemisphere from New Arecibo Observations, Geophysical Review Letters 17, 1389-1392, 1990 http://dx.doi.org/10.1029/GL017i009p01389 [25] Campbell, B.A., and D.B. Campbell, Western Eisila Regio, Venus - Radar Properties of Volcanic Deposits, Geophysical Research Letters 17, 1353-1356, 1990 http://dx.doi.org/10.1029/GL017i009p01353 [26] Bruegge, R.W.V., J.W. Head, and D.B. Campbell, Orogeny and Large-Scale Strike-Slip Faulting on Venus: Tectonic Evolution of Maxwell Montes, Journal of Geophysical Research 95, 8357-8381, 1990 http://dx.doi.org/10.1029/JB095iB06p08357 [27] Stofan, E.R., J.W. Head, and D.B. Campbell, Geology of the Southern Ishtar Terra/Guinevere and Sedna Planitae Region on Venus, Earth, Moon, and Planets 38, 183-207, 1987 http://dx.doi.org/10.1007/BF00119682 [28] Campbell, D.B., J.W. Head, J.K. Harmon, and A.A. Hine, Venus - Volcanism and Rift Information in Beta Regio, Science 226, 167-170, 1984 http://dx.doi.org/10.1126/science.226.4671.167 [29] Cutts, J.A., T.W. Thompson, and B.H. Lewis, Origin of Bright Ring-Shaped Craters in Radar Images of Venus, Icarus 48, 428-452, 1981 http://dx.doi.org/10.1016/0019-1035(81)90054-3 [30] Campbell, D.B., B.A. Burns, and V. Boriakoff, Venus - Further Evidence of Impact Cratering and Tectonic Activity from Radar Observations, Science 204, 1424-1427, 1979 http://dx.doi.org/10.1126/science.204.4400.1424 [31] Shapiro, I.I., D.B. Campbell, and W.M. de Campli, Nonresonance Rotation of Venus, Astrophysical Journal 230, L123-L126, 1979 http://dx.doi.org/10.1086/182975 [32] Campbell, D.B., R.B. Dyce, and G.H. Pettengill, New Radar Image of Venus, Science 193, 1123-1124, 1976 http://dx.doi.org/10.1126/science.193.4258.1123 [33] Hagfors, R., and D.B. Campbell, Radar Backscattering from Venus at Oblique Incidence at a Wavelength of 70 cm, Astronomical Journal 79, 493-502, 1974 http://dx.doi.org/10.1086/111572 [34] Campbell, D.B., R.B. Dyce, R.P. Ingalls, G.H. Pettengill, and I.I. Shapiro, Venus: Topography Revealed by Radar Data, Science 175, 514-516, 1972 http://dx.doi.org/10.1126/science.175.4021.514 [35] Campbell, D.B., R.F. Jurgens, R.B. Dyce, F.S. Harris, and G.H. Pettengill, Radar Interferometric Observations of Venus at 70-Centimeter Wavelength, Science 170, 1090-1092, 1970 http://dx.doi.org/10.1126/science.170.3962.1090 [36] Jurgens, R.F and R.B. Dyce, Radar Backscattering Properties of Venus at 70 cm, Astronomical Journal 75, 297-314, 1970 http://dx.doi.org/10.1086/110977 [37] Jurgens, R.F., Some Preliminary Results of the 70-cm Radar Studies of Venus, Radio Science 5, 435-442, 1970 http://dx.doi.org/10.1029/RS005i002p00435 [38] Campbell, D.B., and D.O. Muhleman, Measurements of the Electron Content of the Interplanetary Medium Between Earth and Venus, Journal of Geophysical Research 74, 1138, 1969 http://dx.doi.org/10.1029/JA074i005p01138 [39] Jurgens, R.F., Radar Scattering from Venus at Large Angles of Incidence and the Question of Polar Ice Caps, Science 162, 1388-1390, 1968 http://dx.doi.org/10.1126/science.162.3860.1388 [40] Ash, M.E., D.B. Campbell, R.B. Dyce, R.P. Ingalls, R. Jurgens, G.H. Pettengill, I.I. Shapiro, M.A. Slade, and T.W. Thompson, The Case for the Radar Radius of Venus, Science 160, 985-987, 1968 http://dx.doi.org/10.1126/science.160.3831.985</t>
+          <t>[1] JPL Asteroid Radar Research: Detection history, object A847 NA (6 Hebe), 1985 Jan, Arecibo monostatic. https://echo.jpl.nasa.gov/History/</t>
         </is>
       </c>
       <c r="P1033" t="inlineStr">
         <is>
-          <t>1978, 1979, 1980, 1981, 1982, 1983, 1984, 1985, 1986, 1987, 1988, 1989, 1999, 2000, 2001(2), 2003, 2004, 2009, 2012, 2015, 2017(6), 2020(8)[8]</t>
-        </is>
-      </c>
-      <c r="Q1033" t="inlineStr">
-        <is>
-          <t>2003 logged, type unconfirmed; 2004 DD; 2012 DD; 2015 logged, type unconfirmed; 2020 CW+DD</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="R1033" t="inlineStr">
@@ -60257,19 +60337,24 @@
       </c>
     </row>
     <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>Space-Debris</t>
+          <t>Pales</t>
         </is>
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>WT1190F</t>
+          <t>A857 SB</t>
         </is>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
-          <t>Space debris</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="E1034" t="inlineStr">
@@ -60280,14 +60365,19 @@
       <c r="H1034" t="n">
         <v>1</v>
       </c>
+      <c r="I1034" t="inlineStr">
+        <is>
+          <t>7.99 (J)</t>
+        </is>
+      </c>
+      <c r="O1034" t="inlineStr">
+        <is>
+          <t>[1] JPL Asteroid Radar Research: Detection history, object A857 SB (49 Pales), 2004 Oct, Arecibo monostatic. https://echo.jpl.nasa.gov/History/</t>
+        </is>
+      </c>
       <c r="P1034" t="inlineStr">
         <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="Q1034" t="inlineStr">
-        <is>
-          <t>2015 CW+DD</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="R1034" t="inlineStr">
@@ -60297,24 +60387,9 @@
       </c>
     </row>
     <row r="1035">
-      <c r="A1035" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B1035" t="inlineStr">
-        <is>
-          <t>Hebe</t>
-        </is>
-      </c>
-      <c r="C1035" t="inlineStr">
-        <is>
-          <t>A847 NA</t>
-        </is>
-      </c>
       <c r="D1035" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>NEA</t>
         </is>
       </c>
       <c r="E1035" t="inlineStr">
@@ -60322,49 +60397,39 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="H1035" t="n">
         <v>1</v>
       </c>
       <c r="I1035" t="inlineStr">
         <is>
-          <t>5.62 (J)</t>
-        </is>
-      </c>
-      <c r="O1035" t="inlineStr">
-        <is>
-          <t>[1] JPL Asteroid Radar Research: Detection history, object A847 NA (6 Hebe), 1985 Jan, Arecibo monostatic. https://echo.jpl.nasa.gov/History/</t>
-        </is>
-      </c>
-      <c r="P1035" t="inlineStr">
-        <is>
-          <t>1985</t>
+          <t>24.18 (J)</t>
+        </is>
+      </c>
+      <c r="N1035" t="inlineStr">
+        <is>
+          <t>0.115 ± 0.134</t>
+        </is>
+      </c>
+      <c r="Q1035" t="inlineStr">
+        <is>
+          <t>2016 CW</t>
         </is>
       </c>
       <c r="R1035" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="1036">
-      <c r="A1036" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="B1036" t="inlineStr">
-        <is>
-          <t>Pales</t>
-        </is>
-      </c>
-      <c r="C1036" t="inlineStr">
-        <is>
-          <t>A857 SB</t>
-        </is>
-      </c>
       <c r="D1036" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>NEA</t>
         </is>
       </c>
       <c r="E1036" t="inlineStr">
@@ -60372,27 +60437,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="H1036" t="n">
         <v>1</v>
       </c>
       <c r="I1036" t="inlineStr">
         <is>
-          <t>7.99 (J)</t>
-        </is>
-      </c>
-      <c r="O1036" t="inlineStr">
-        <is>
-          <t>[1] JPL Asteroid Radar Research: Detection history, object A857 SB (49 Pales), 2004 Oct, Arecibo monostatic. https://echo.jpl.nasa.gov/History/</t>
-        </is>
-      </c>
-      <c r="P1036" t="inlineStr">
-        <is>
-          <t>2004</t>
+          <t>25.18 (J)</t>
+        </is>
+      </c>
+      <c r="N1036" t="inlineStr">
+        <is>
+          <t>0.040 (n=1)</t>
+        </is>
+      </c>
+      <c r="Q1036" t="inlineStr">
+        <is>
+          <t>2019 CW+DD</t>
         </is>
       </c>
       <c r="R1036" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -60417,17 +60487,17 @@
       </c>
       <c r="I1037" t="inlineStr">
         <is>
-          <t>24.18 (J)</t>
+          <t>20.06 (J)</t>
         </is>
       </c>
       <c r="N1037" t="inlineStr">
         <is>
-          <t>0.115 ± 0.134</t>
+          <t>0.610 (n=1)</t>
         </is>
       </c>
       <c r="Q1037" t="inlineStr">
         <is>
-          <t>2016 CW</t>
+          <t>2013 CW</t>
         </is>
       </c>
       <c r="R1037" t="inlineStr">
@@ -60457,100 +60527,20 @@
       </c>
       <c r="I1038" t="inlineStr">
         <is>
-          <t>25.18 (J)</t>
+          <t>26.8 (J)</t>
         </is>
       </c>
       <c r="N1038" t="inlineStr">
         <is>
-          <t>0.040 (n=1)</t>
+          <t>2.150 (n=1)</t>
         </is>
       </c>
       <c r="Q1038" t="inlineStr">
         <is>
-          <t>2019 CW+DD</t>
+          <t>2019 CW</t>
         </is>
       </c>
       <c r="R1038" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="1039">
-      <c r="D1039" t="inlineStr">
-        <is>
-          <t>NEA</t>
-        </is>
-      </c>
-      <c r="E1039" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F1039" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H1039" t="n">
-        <v>1</v>
-      </c>
-      <c r="I1039" t="inlineStr">
-        <is>
-          <t>20.06 (J)</t>
-        </is>
-      </c>
-      <c r="N1039" t="inlineStr">
-        <is>
-          <t>0.610 (n=1)</t>
-        </is>
-      </c>
-      <c r="Q1039" t="inlineStr">
-        <is>
-          <t>2013 CW</t>
-        </is>
-      </c>
-      <c r="R1039" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="1040">
-      <c r="D1040" t="inlineStr">
-        <is>
-          <t>NEA</t>
-        </is>
-      </c>
-      <c r="E1040" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F1040" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H1040" t="n">
-        <v>1</v>
-      </c>
-      <c r="I1040" t="inlineStr">
-        <is>
-          <t>26.8 (J)</t>
-        </is>
-      </c>
-      <c r="N1040" t="inlineStr">
-        <is>
-          <t>2.150 (n=1)</t>
-        </is>
-      </c>
-      <c r="Q1040" t="inlineStr">
-        <is>
-          <t>2019 CW</t>
-        </is>
-      </c>
-      <c r="R1040" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>

--- a/FINAL_LIST_2026.xlsx
+++ b/FINAL_LIST_2026.xlsx
@@ -8580,7 +8580,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>[1] (2014). N. , 337. https://ui.adsabs.harvard.edu/abs/2014acm..conf..337M/abstract</t>
+          <t>[1] Marshall, S. E. (2014). Near-Earth asteroid (137032) 1998 UO1: Shape model and thermal properties. Asteroids, Comets, Meteors 2014, 337. https://ui.adsabs.harvard.edu/abs/2014acm..conf..337M/abstract</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -56850,7 +56850,7 @@
       </c>
       <c r="O965" t="inlineStr">
         <is>
-          <t>[1] Ostro, S. J., Jurgens, R. F., Rosema, K. D., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., Shapiro, I. I., Hine, A. A., &amp; Velez, R. (1991). Asteroid radar astrometry. The Astronomical Journal, 102, 1490. https://doi.org/10.1086/115975 [2] sciencedirect.com (access blocked for automated fetch; see link for full citation) https://www.sciencedirect.com/science/article/abs/pii/001910357690097X [3] echo.jpl.nasa.gov (access blocked for automated fetch; see link for full citation) https://echo.jpl.nasa.gov/asteroids/mitchell+1998_eros_icarus.pdf [4] Magri, C., Consolmagno, G. J., Ostrch, S. J., Benner, L. A. M., &amp; Beeney, B. R. (2001). Radar constraints on asteroid regolith properties using 433 Eros as ground truth. Meteoritics &amp;amp; Planetary Science, 36, 1697-1709. https://doi.org/10.1111/j.1945-5100.2001.tb01857.x [5] Campbell, D.B., G.H. Pettengill, and I.I. Shapiro, 70-cm Radar Observations of 433 Eros, Icarus 28, 17-20, 1976 http://dx.doi.org/10.1016/0019-1035(76)90080-4</t>
+          <t>[1] Ostro, S. J., Jurgens, R. F., Rosema, K. D., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., Shapiro, I. I., Hine, A. A., &amp; Velez, R. (1991). Asteroid radar astrometry. The Astronomical Journal, 102, 1490. https://doi.org/10.1086/115975 [2] Zellner, B. (1976). Physical properties of asteroid 433 Eros. Icarus, 28, 149-153. https://doi.org/10.1016/0019-1035(76)90097-X [3] Mitchell, D. L., Hudson, R. S., Ostro, S. J., &amp; Rosema, K. D. (1998). Shape of Asteroid 433 Eros from Inversion of Goldstone Radar Doppler Spectra. Icarus, 131, 4-14. https://doi.org/10.1006/icar.1997.5815 [4] Magri, C., Consolmagno, G. J., Ostrch, S. J., Benner, L. A. M., &amp; Beeney, B. R. (2001). Radar constraints on asteroid regolith properties using 433 Eros as ground truth. Meteoritics &amp;amp; Planetary Science, 36, 1697-1709. https://doi.org/10.1111/j.1945-5100.2001.tb01857.x [5] Campbell, D.B., G.H. Pettengill, and I.I. Shapiro, 70-cm Radar Observations of 433 Eros, Icarus 28, 17-20, 1976 http://dx.doi.org/10.1016/0019-1035(76)90080-4 [6] Fernandez, Y. R., Hinkle, M. L., Howell, E. S., Magri, C., Nolan, M. C., Marshall, S. E., Vervack, R. J., &amp; Myers, S. A. (2025). Rotationally-Resolved Radar Scattering Properties of Near-Earth Asteroid (433) Eros. EPSC-DPS2025, abstract 364. https://meetingorganizer.copernicus.org/EPSC-DPS2025/EPSC-DPS2025-364.html</t>
         </is>
       </c>
       <c r="P965" t="inlineStr">
@@ -59810,7 +59810,7 @@
       </c>
       <c r="O1022" t="inlineStr">
         <is>
-          <t>[1] Harmon, J., Nolan, M., Margot, J., Campbell, D., Benner, L., &amp; Giorgini, J. (2006). Radar observations of Comet P/2005 JQ5 (Catalina). Icarus, 184, 285-288. https://doi.org/10.1016/j.icarus.2006.05.014 [2] Kruzins, E., Benner, L., Boyce, R., Brown, M., Coward, D., Darwell, S., Edwards, P., Elizabeth-Glina, L., Giorgini, J., Horiuchi, S., Lambert, A., Lazio, J., Calves, G. M., Moore, J., Peters, E., et al. (2023). Deep space debris—Detection of potentially hazardous asteroids and objects from the southern hemisphere. Frontiers in Space Technologies, 4. https://doi.org/10.3389/frspt.2023.1162915 [3] Kwiatkowski, T., Kryszczyńska, A., Polińska, M., Buckley, D. A. H., O'Donaghue, D., Charles, P. A., Crause, L. A., Crawford, S. M., Hashimoto, Y., Kniazev, A. Y., Loaring, N. S., Romero‐Colmenero, E., Sefako, R., Still, M., &amp; Väisänen, P. (2008). Photometry of Asteroid 2006 RH120 During Its Short Visit to a Geocentric Orbit. LPICo.</t>
+          <t>[1] Harmon, J., Nolan, M., Margot, J., Campbell, D., Benner, L., &amp; Giorgini, J. (2006). Radar observations of Comet P/2005 JQ5 (Catalina). Icarus, 184, 285-288. https://doi.org/10.1016/j.icarus.2006.05.014 [2] Kwiatkowski, T., Kryszczyńska, A., Polińska, M., Buckley, D. A. H., O'Donaghue, D., Charles, P. A., Crause, L. A., Crawford, S. M., Hashimoto, Y., Kniazev, A. Y., Loaring, N. S., Romero‐Colmenero, E., Sefako, R., Still, M., &amp; Väisänen, P. (2008). Photometry of Asteroid 2006 RH120 During Its Short Visit to a Geocentric Orbit. LPICo.</t>
         </is>
       </c>
       <c r="P1022" t="inlineStr">

--- a/FINAL_LIST_2026.xlsx
+++ b/FINAL_LIST_2026.xlsx
@@ -1240,7 +1240,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>[1] Busch, M., Giorgini, J., Ostro, S., Benner, L., Jurgens, R., Rose, R., Hicks, M., Pravec, P., Kusnirak, P., &amp; Ireland, M. (2007). Physical modeling of near-Earth Asteroid (29075) 1950 DA. Icarus, 190, 608-621. https://doi.org/10.1016/j.icarus.2007.03.032 [2] Farnocchia, D., &amp; Chesley, S. R. (2014). Assessment of the 2880 impact threat from Asteroid (29075) 1950 DA. Icarus, 229, 321-327. https://doi.org/10.1016/j.icarus.2013.09.022 [3] Hirabayashi, M., &amp; Scheeres, D. J. (2014). STRESS AND FAILURE ANALYSIS OF RAPIDLY ROTATING ASTEROID (29075) 1950 DA. The Astrophysical Journal, 798, L8. https://doi.org/10.1088/2041-8205/798/1/l8 [4] Rozitis, B., MacLennan, E., &amp; Emery, J. P. (2014). Cohesive forces prevent the rotational breakup of rubble-pile asteroid (29075) 1950 DA. Nature, 512, 174-176. https://doi.org/10.1038/nature13632 [5] Gundlach, B., &amp; Blum, J. (2015). Regolith grain size and cohesive strength of near-Earth Asteroid (29075) 1950 DA. Icarus, 257, 126-129. https://doi.org/10.1016/j.icarus.2015.04.032 [6] None https://iopscience.iop.org/article/10.1088/2041-8205/798/1/L8/meta [7] None https://www.sciencedirect.com/science/article/abs/pii/S001910351500175X [8] None https://www.nature.com/articles/nature13632 [9] None https://science.sciencemag.org/content/296/5565/132?casa_token=XoRARJqgmh8AAAAA:23tSGSHIWTbpuczVSuDksj4pf_opCrvPufnPLao619yNSbn4N020IQ-w_03xUsTWtDMAhp1Gosq6-86m [10] None https://www.sciencedirect.com/science/article/abs/pii/S0019103507001467 [11] None https://www.sciencedirect.com/science/article/abs/pii/S0019103513004132 [12] sciencedirect.com (access blocked for automated fetch; see link for full citation) https://www.sciencedirect.com/science/article/abs/pii/S001910351500175X [13] science.sciencemag.org (access blocked for automated fetch; see link for full citation) https://science.sciencemag.org/content/296/5565/132?casa_token=XoRARJqgmh8AAAAA:23tSGSHIWTbpuczVSuDksj4pf_opCrvPufnPLao619yNSbn4N020IQ-w_03xUsTWtDMAhp1Gosq6-86m [14] Giorgini, J.D., and 13 colleagues (including M.C. Nolan), Asteroid 1950 DA`s Encounter with Earth in 2880: Physical Limits of Collision Probability Prediction, Science 296, 132-136, 2002 http://dx.doi.org/10.1126/science.1068191</t>
+          <t>[1] Busch, M., Giorgini, J., Ostro, S., Benner, L., Jurgens, R., Rose, R., Hicks, M., Pravec, P., Kusnirak, P., &amp; Ireland, M. (2007). Physical modeling of near-Earth Asteroid (29075) 1950 DA. Icarus, 190, 608-621. https://doi.org/10.1016/j.icarus.2007.03.032 [2] Farnocchia, D., &amp; Chesley, S. R. (2014). Assessment of the 2880 impact threat from Asteroid (29075) 1950 DA. Icarus, 229, 321-327. https://doi.org/10.1016/j.icarus.2013.09.022 [3] Hirabayashi, M., &amp; Scheeres, D. J. (2014). STRESS AND FAILURE ANALYSIS OF RAPIDLY ROTATING ASTEROID (29075) 1950 DA. The Astrophysical Journal, 798, L8. https://doi.org/10.1088/2041-8205/798/1/l8 [4] Rozitis, B., MacLennan, E., &amp; Emery, J. P. (2014). Cohesive forces prevent the rotational breakup of rubble-pile asteroid (29075) 1950 DA. Nature, 512, 174-176. https://doi.org/10.1038/nature13632 [5] Gundlach, B., &amp; Blum, J. (2015). Regolith grain size and cohesive strength of near-Earth Asteroid (29075) 1950 DA. Icarus, 257, 126-129. https://doi.org/10.1016/j.icarus.2015.04.032 [6] Giorgini, J. D., Ostro, S. J., Benner, L. A. M., Chodas, P. W., Chesley, S. R., Hudson, R. S., Nolan, M. C., Klemola, A. R., Standish, E. M., Jurgens, R. F., Rose, R., Chamberlin, A. B., Yeomans, D. K., &amp; Margot, J. L. (2002). Asteroid 1950 DA's Encounter with Earth in 2880: Physical Limits of Collision Probability Prediction. Science, 296(5565), 132-136. https://doi.org/10.1126/science.1068191</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>[1] Ostro, S. J., Choate, D., Dendrenos, P., Giorgini, J. D., Hills, D. L., Howard, D., Jurgens, R. F., Mitchell, D. L., Rose, R., Rosema, K. D., Slade, M. A., Strobert, D. R., Winkler, R., &amp; Yoemans, D. K. (1994). abstract) Asteroid Radar Astronomy at Goldstone in the 1990s. NASA Technical Reports Server (NASA). [2] Ostro, S. J., Hudson, R. S., Jurgens, R. F., Rosema, K. D., Campbell, D. B., Yeomans, D. K., Chandler, J. F., Giorgini, J. D., Winkler, R., Rose, R., Howard, S. D., Slade, M. A., Perillat, P., &amp; Shapiro, I. I. (1995). Radar Images of Asteroid 4179 Toutatis. Science, 270, 80-83. https://doi.org/10.1126/science.270.5233.80 [3] Quijano-Vodniza, A., &amp; P., M. R. (2017). The Asteroid 2014 JO25. DPS. [4] MacLennan, E., Virkki, A., &amp; Marshall, S. (2025). Radar Shape Modeling of NEA (242643) 2005 NZ6: A Toutatis Twin?. https://doi.org/10.5194/epsc-dps2025-1476 [5] B. et al. (2013). Bulletin of the American Astronomical Society (DPS meeting abstract), Vol. 4510105. [ADS record] https://ui.adsabs.harvard.edu/abs/2013DPS....4510105B/abstract [6] H. et al. (1996). Bulletin of the American Astronomical Society (DPS meeting abstract), Vol. 28, 1040. [ADS record] https://ui.adsabs.harvard.edu/abs/1996DPS....28.1040H/abstract [7] adsabs.harvard.edu (access blocked for automated fetch; see link for full citation) http://adsabs.harvard.edu/full/1993DPS....25.3407O [8] M. et al. (1993). Space Flight, Vol. 35, 207. [ADS record] https://ui.adsabs.harvard.edu/abs/1993SpFl...35..207M/abstract [9] trs.jpl.nasa.gov (access blocked for automated fetch; see link for full citation) https://trs.jpl.nasa.gov/bitstream/handle/2014/19433/98-0808.pdf?sequence=1&amp;isAllowed=y [10] sciencedirect.com (access blocked for automated fetch; see link for full citation) https://www.sciencedirect.com/science/article/pii/S0032063316300538 [11] Hudson, R. S., &amp; Ostro, S. J. (1995). Shape and Non-Principal Axis Spin State of Asteroid 4179 Toutatis. Science, 270, 84-86. https://doi.org/10.1126/science.270.5233.84 [12] Takahashi, Y., M.W. Busch, and D.J. Scheeres, Spin State and Moment of Inertia Characterization of 4179 Toutatis, Astronomical Journal 146, 95, 2013 http://dx.doi.org/10.1088/0004-6256/146/4/95 [13] Hudson, R.S., S.J. Ostro, and D.J. Scheeres, High-Resolution Model of Asteroid 4179 Toutatis, Icarus 161, 346-355, 2003 http://dx.doi.org/10.1016/S0019-1035(02)00042-8</t>
+          <t>[1] Ostro, S. J., Choate, D., Dendrenos, P., Giorgini, J. D., Hills, D. L., Howard, D., Jurgens, R. F., Mitchell, D. L., Rose, R., Rosema, K. D., Slade, M. A., Strobert, D. R., Winkler, R., &amp; Yoemans, D. K. (1994). abstract) Asteroid Radar Astronomy at Goldstone in the 1990s. NASA Technical Reports Server (NASA). [2] Ostro, S. J., Hudson, R. S., Jurgens, R. F., Rosema, K. D., Campbell, D. B., Yeomans, D. K., Chandler, J. F., Giorgini, J. D., Winkler, R., Rose, R., Howard, S. D., Slade, M. A., Perillat, P., &amp; Shapiro, I. I. (1995). Radar Images of Asteroid 4179 Toutatis. Science, 270, 80-83. https://doi.org/10.1126/science.270.5233.80 [3] Quijano-Vodniza, A., &amp; P., M. R. (2017). The Asteroid 2014 JO25. DPS. [4] MacLennan, E., Virkki, A., &amp; Marshall, S. (2025). Radar Shape Modeling of NEA (242643) 2005 NZ6: A Toutatis Twin?. https://doi.org/10.5194/epsc-dps2025-1476 [5] B. et al. (2013). Bulletin of the American Astronomical Society (DPS meeting abstract), Vol. 4510105. [ADS record] https://ui.adsabs.harvard.edu/abs/2013DPS....4510105B/abstract [6] H. et al. (1996). Bulletin of the American Astronomical Society (DPS meeting abstract), Vol. 28, 1040. [ADS record] https://ui.adsabs.harvard.edu/abs/1996DPS....28.1040H/abstract [7] Ostro, S. J., et al. (1993). Radar Imaging of Asteroid 4179 Toutatis. Bulletin of the American Astronomical Society, 25. https://ui.adsabs.harvard.edu/abs/1993DPS....25.3407O/abstract [8] M. et al. (1993). Space Flight, Vol. 35, 207. [ADS record] https://ui.adsabs.harvard.edu/abs/1993SpFl...35..207M/abstract [9] Ostro, S. J., Hudson, R. S., Rosema, K. D., Giorgini, J. D., Jurgens, R. F., Yeomans, D. K., Chodas, P. W., Winkler, R., Rose, R., Choate, D., Cormier, R. A., Kelley, D., Littlefair, R., Benner, L. A. M., Thomas, M. L., &amp; Slade, M. A. (1999). Asteroid 4179 Toutatis: 1996 Radar Observations. Icarus, 137, 122-139. https://doi.org/10.1006/icar.1998.6031 [10] Zhao, Y., Xiao, Z., Liu, W., Sun, J., Huang, B., &amp; Tang, C. (2016). Radar model fusion of asteroid (4179) Toutatis via its optical images observed by Chang'e-2 probe. Planetary and Space Science, 125, 87-95. https://doi.org/10.1016/j.pss.2016.03.008 [11] Hudson, R. S., &amp; Ostro, S. J. (1995). Shape and Non-Principal Axis Spin State of Asteroid 4179 Toutatis. Science, 270, 84-86. https://doi.org/10.1126/science.270.5233.84 [12] Takahashi, Y., M.W. Busch, and D.J. Scheeres, Spin State and Moment of Inertia Characterization of 4179 Toutatis, Astronomical Journal 146, 95, 2013 http://dx.doi.org/10.1088/0004-6256/146/4/95 [13] Hudson, R.S., S.J. Ostro, and D.J. Scheeres, High-Resolution Model of Asteroid 4179 Toutatis, Icarus 161, 346-355, 2003 http://dx.doi.org/10.1016/S0019-1035(02)00042-8</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>[1] Gavrik, Y. A., Gavrik, A. L., &amp; Smyslov, A. A. (2016). Distribution of the surface radio brightness of asteroid Golevka constructed from the radar data. Journal of Communications Technology and Electronics, 61, 1347-1353. https://link.springer.com/article/10.1134/S106422691612007X [2] Greenberg, A. H., Margot, J. L., Verma, A. K., Taylor, P. A., &amp; Hodge, S. E. (2020). Yarkovsky Drift Detections for 247 Near-Earth Asteroids. The Astronomical Journal, 159, 92. https://doi.org/10.3847/1538-3881/ab62a3 [3] None https://ui.adsabs.harvard.edu/abs/2000PDSS...11....7H/abstract [4] None https://ui.adsabs.harvard.edu/abs/2000PDSS...11.....N/abstract [5] None https://trs.jpl.nasa.gov/bitstream/handle/2014/7286/03-1021.pdf?sequence=1 [6] None https://www.researchgate.net/profile/Yasuhiro_Koyama2/publication/4703392_Radar_Observations_of_Near_Earth_Asteroids_6489_Golevka_and_4197_1982_TA/links/02e7e51ad9d5918550000000/Radar-Observations-of-Near-Earth-Asteroids-6489-Golevka-and-4197-1982-TA.pdf [7] None https://www.sciencedirect.com/science/article/pii/S0032063397000421 [8] None https://www.sciencedirect.com/science/article/pii/S0019103500964832 [9] None https://science.sciencemag.org/content/302/5651/1739 [10] H. et al. (2000). Planetary and Space Science, Vol. 11, 7. [ADS record] https://ui.adsabs.harvard.edu/abs/2000PDSS...11....7H/abstract [11] N. et al. (2000). Planetary and Space Science, Vol. 11. [ADS record] https://ui.adsabs.harvard.edu/abs/2000PDSS...11.....N/abstract [12] trs.jpl.nasa.gov (access blocked for automated fetch; see link for full citation) https://trs.jpl.nasa.gov/bitstream/handle/2014/7286/03-1021.pdf?sequence=1 [13] researchgate.net (access blocked for automated fetch; see link for full citation) https://www.researchgate.net/profile/Yasuhiro_Koyama2/publication/4703392_Radar_Observations_of_Near_Earth_Asteroids_6489_Golevka_and_4197_1982_TA/links/02e7e51ad9d5918550000000/Radar-Observations-of-Near-Earth-Asteroids-6489-Golevka-and-4197-1982-TA.pdf [14] sciencedirect.com (access blocked for automated fetch; see link for full citation) https://www.sciencedirect.com/science/article/pii/S0032063397000421 [15] Chesley, S. R., Ostro, S. J., Vokrouhlický, D., Čapek, D., Giorgini, J. D., Nolan, M. C., Margot, J. L., Hine, A. A., Benner, L. A. M., &amp; Chamberlin, A. B. (2003). Direct Detection of the Yarkovsky Effect by Radar Ranging to Asteroid 6489 Golevka. Science, 302, 1739-1742. https://doi.org/10.1126/science.1091452</t>
+          <t>[1] Gavrik, Y. A., Gavrik, A. L., &amp; Smyslov, A. A. (2016). Distribution of the surface radio brightness of asteroid Golevka constructed from the radar data. Journal of Communications Technology and Electronics, 61, 1347-1353. https://link.springer.com/article/10.1134/S106422691612007X [2] Greenberg, A. H., Margot, J. L., Verma, A. K., Taylor, P. A., &amp; Hodge, S. E. (2020). Yarkovsky Drift Detections for 247 Near-Earth Asteroids. The Astronomical Journal, 159, 92. https://doi.org/10.3847/1538-3881/ab62a3 [3] H. et al. (2000). Planetary and Space Science, Vol. 11, 7. [ADS record] https://ui.adsabs.harvard.edu/abs/2000PDSS...11....7H/abstract [4] N. et al. (2000). Planetary and Space Science, Vol. 11. [ADS record] https://ui.adsabs.harvard.edu/abs/2000PDSS...11.....N/abstract [5] Hudson, R. S., Ostro, S. J., Jurgens, R. F., Rosema, K. D., Giorgini, J. D., Winkler, R., Rose, R., Choate, D., Cormier, R. A., Franck, C. R., Frye, R., Howard, D., Kelley, D., Littlefair, R., Slade, M. A., Benner, L. A. M., Thomas, M. L., Mitchell, D. L., Chodas, P. W., Yeomans, D. K., Scheeres, D. J., Palmer, P., Zaitsev, A., Koyama, Y., Nakamura, A., Harris, A. W., &amp; Meshkov, M. N. (2000). Radar Observations and Physical Model of Asteroid 6489 Golevka. Icarus, 148, 37-51. https://doi.org/10.1006/icar.2000.6483 [6] Koyama, Y., Nakajima, J., Sekido, M., Yoshikawa, M., Nakamura, A. M., Hirabayashi, H., Okada, T., Abe, M., Nishibori, T., Fuse, T., Ostro, S. J., Choate, D., Cormier, R. A., Winkler, R., Jurgens, R. F., Giorgini, J. D., Yeomans, D. K., Slade, M. A., &amp; Zaitsev, A. L. (2001). Radar observations of near-Earth asteroids 6489 Golevka and 4197 (1982 TA). Communications Research Laboratory Review, 47, 145. https://ui.adsabs.harvard.edu/abs/2001CRLRv..47..145K/abstract [7] Zaitsev, A. L., Ostro, S. J., Ignatov, S. M., Yeomans, D. K., Petrenko, B. L., Choate, D., Margorin, O. K., Cormier, R. A., Mardyshkin, V. P., Winkler, R., Rghiga, D., Jurgens, R. F., Shubin, K. L., Giorgini, J. D., Krivtsov, A. P., Rosema, K. D., Koluka, Y. F., Slade, M. A., Gavrik, A. L., Andreev, O. N., Ivanov, A. E., Peshin, S. V., Koyama, Y., Yoshikawa, M., &amp; Nakamura, A. (1997). Intercontinental bistatic radar observations of 6489 Golevka (1991 JX). Planetary and Space Science, 45, 771-778. https://doi.org/10.1016/S0032-0633(97)00042-1 [8] Chesley, S. R., Ostro, S. J., Vokrouhlický, D., Čapek, D., Giorgini, J. D., Nolan, M. C., Margot, J. L., Hine, A. A., Benner, L. A. M., &amp; Chamberlin, A. B. (2003). Direct Detection of the Yarkovsky Effect by Radar Ranging to Asteroid 6489 Golevka. Science, 302, 1739-1742. https://doi.org/10.1126/science.1091452</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -39075,7 +39075,7 @@
       </c>
       <c r="O629" t="inlineStr">
         <is>
-          <t>[1] Müller, T. G., Marciniak, A., Butkiewicz-Bąk, M., Duffard, R., Oszkiewicz, D., Käufl, H. U., Szakáts, R., Santana-Ros, T., Kiss, C., &amp; Santos-Sanz, P. (2017). Large Halloween asteroid at lunar distance. Astronomy &amp;amp; Astrophysics, 598, A63. https://doi.org/10.1051/0004-6361/201629584 [2] None https://ui.adsabs.harvard.edu/abs/2016DPS....4832910R/abstract [3] None https://ui.adsabs.harvard.edu/abs/2016AGUFMNH12A..06B/abstract [4] R. et al. (2016). Bulletin of the American Astronomical Society (DPS meeting abstract), Vol. 4832910. [ADS record] https://ui.adsabs.harvard.edu/abs/2016DPS....4832910R/abstract [5] ui.adsabs.harvard.edu (access blocked for automated fetch; see link for full citation) https://ui.adsabs.harvard.edu/abs/2016AGUFMNH12A..06B/abstract</t>
+          <t>[1] Müller, T. G., Marciniak, A., Butkiewicz-Bąk, M., Duffard, R., Oszkiewicz, D., Käufl, H. U., Szakáts, R., Santana-Ros, T., Kiss, C., &amp; Santos-Sanz, P. (2017). Large Halloween asteroid at lunar distance. Astronomy &amp;amp; Astrophysics, 598, A63. https://doi.org/10.1051/0004-6361/201629584 [2] R. et al. (2016). Bulletin of the American Astronomical Society (DPS meeting abstract), Vol. 4832910. [ADS record] https://ui.adsabs.harvard.edu/abs/2016DPS....4832910R/abstract [3] Busch, M. W., et al. (2016). Recent radar observations of potentially hazardous near-Earth asteroids with the Arecibo Observatory and the Deep Space Network. AGU Fall Meeting, abstract NH12A-06. https://ui.adsabs.harvard.edu/abs/2016AGUFMNH12A..06B/abstract</t>
         </is>
       </c>
       <c r="P629" t="inlineStr">

--- a/FINAL_LIST_2026.xlsx
+++ b/FINAL_LIST_2026.xlsx
@@ -1155,7 +1155,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>[1] Shepard, M., Benner, L., Ostro, S., Campbell, D., Shapiro, I., &amp; Chandler, J. (2004). Radar detection of near-Earth Asteroids 1915 Quetzalcoatl, 3199 Nefertiti, 3757 (1982 XB), and 4034 (1986 PA). Icarus, 172, 170-178. https://doi.org/10.1016/j.icarus.2004.06.003 [2] Magri, C., Ostro, S. J., Scheeres, D. J., Nolan, M. C., Giorgini, J. D., Benner, L. A. M., &amp; Margot, J. L. (2007). Radar observations and a physical model of Asteroid 1580 Betulia. Icarus, 186, 152-177. https://doi.org/10.1016/j.icarus.2006.08.004 [3] Ockert-Bell, M. E., Clark, B. E., Shepard, M. K., Rivkin, A. S., Binzel, R. P., Thomas, C. A., DeMeo, F. E., Bus, S. J., &amp; Shah, S. (2008). Observations of X/M asteroids across multiple wavelengths. Icarus, 195, 206-219. https://doi.org/10.1016/j.icarus.2007.11.006 [4] Shepard, M. K., Clark, B. E., Nolan, M. C., Howell, E. S., Magri, C., Giorgini, J. D., Benner, L. A. M., Ostro, S. J., Harris, A. W., Warner, B., Pray, D., Pravec, P., Fauerbach, M., Bennett, T., Klotz, A., et al. (2008). A radar survey of M- and X-class asteroids. Icarus, 195, 184-205. https://doi.org/10.1016/j.icarus.2007.11.032 [5] Shepard, M. K., Kressler, K. M., Clark, B. E., Ockert-Bell, M. E., Nolan, M. C., Howell, E. S., Magri, C., Giorgini, J. D., Benner, L. A. M., &amp; Ostro, S. J. (2008). Radar observations of E-class Asteroids 44 Nysa and 434 Hungaria. Icarus, 195, 220-225. https://doi.org/10.1016/j.icarus.2007.12.018 [6] Shepard, M. K., Clark, B. E., Ockert-Bell, M., Nolan, M. C., Howell, E. S., Magri, C., Giorgini, J. D., Benner, L. A. M., Ostro, S. J., Harris, A. W., Warner, B. D., Stephens, R. D., &amp; Mueller, M. (2010). A radar survey of M- and X-class asteroids II. Summary and synthesis. Icarus, 208, 221-237. https://doi.org/10.1016/j.icarus.2010.01.017 [7] Ockert-Bell, M. E., Clark, B. E., Shepard, M. K., Isaacs, R. A., Cloutis, E. A., Fornasier, S., &amp; Bus, S. J. (2010). The composition of M-type asteroids: Synthesis of spectroscopic and radar observations. Icarus, 210, 674-692. https://doi.org/10.1016/j.icarus.2010.08.002 [8] Shepard, M. K., Harris, A. W., Taylor, P. A., Clark, B. E., Ockert-Bell, M., Nolan, M. C., Howell, E. S., Magri, C., Giorgini, J. D., &amp; Benner, L. A. M. (2011). Radar observations of Asteroids 64 Angelina and 69 Hesperia. Icarus, 215, 547-551. https://doi.org/10.1016/j.icarus.2011.07.027 [9] Neeley, J. R., Clark, B. E., Ockert-Bell, M. E., Shepard, M. K., Conklin, J., Cloutis, E. A., Fornasier, S., &amp; Bus, S. J. (2014). The composition of M-type asteroids II: Synthesis of spectroscopic and radar observations. Icarus, 238, 37-50. https://doi.org/10.1016/j.icarus.2014.05.008 [10] Shepard, M. K., Taylor, P. A., Nolan, M. C., Howell, E. S., Springmann, A., Giorgini, J. D., Warner, B. D., Harris, A. W., Stephens, R., Merline, W. J., Rivkin, A., Benner, L. A. M., Coley, D., Clark, B. E., Ockert-Bell, M., et al. (2015). A radar survey of M- and X-class asteroids. III. Insights into their composition, hydration state, &amp;amp; structure. Icarus, 245, 38-55. https://doi.org/10.1016/j.icarus.2014.09.016 [11] Greenberg, A. H., Margot, J. L., Verma, A. K., Taylor, P. A., Naidu, S. P., Brozovic, M., &amp; Benner, L. A. M. (2017). Asteroid 1566 Icarus’s Size, Shape, Orbit, and Yarkovsky Drift from Radar Observations. The Astronomical Journal, 153, 108. https://doi.org/10.3847/1538-3881/153/3/108 [12] Greenberg, A. H., Margot, J. L., Verma, A. K., Taylor, P. A., &amp; Hodge, S. E. (2020). Yarkovsky Drift Detections for 247 Near-Earth Asteroids. The Astronomical Journal, 159, 92. https://doi.org/10.3847/1538-3881/ab62a3 [13] Skirmante, K., Bleiders, M., Jekabsons, N., Bezrukovs, V., &amp; Jasmonts, G. (2024). Observations of OH masers of comets in 1.6GHz frequency band using the Irbene RT32 radio telescope. https://doi.org/10.5194/epsc2020-171 [14] Medeiros, H., de León, J., Licandro, J., Popescu, M., &amp; Pinilla-Alonso, N. (2024). Physical characterization of near-Earth asteroid (159402) 1999 AP10 in support of the Arecibo Planetary Radar Program within the NEOROCKS project. https://doi.org/10.5194/epsc2021-783 [15] Ferrais, M., Marshall, S., Venditti, F., Devogèle, M., Pravec, P., Scheirich, P., &amp; Jehin, E. (2024). Shape model of the binary NEA (385186) 1994 AW1 from 2015 radar observations and long term lightcurve dataset.&amp;amp;#160;. https://doi.org/10.5194/epsc2024-161 [16] Howell, E., Vervack, R., Fernandez, Y., Myers, S., Hinkle, M., Magri, C., Marshall, S., &amp; Rivera-Valentin, E. (2025). Combining thermal and radar observations of near-Earth asteroids. https://doi.org/10.5194/epsc-dps2025-462 [17] MacLennan, E., Virkki, A., &amp; Marshall, S. (2025). Radar Shape Modeling of NEA (242643) 2005 NZ6: A Toutatis Twin?. https://doi.org/10.5194/epsc-dps2025-1476</t>
+          <t>[1] Shepard, M., Benner, L., Ostro, S., Campbell, D., Shapiro, I., &amp; Chandler, J. (2004). Radar detection of near-Earth Asteroids 1915 Quetzalcoatl, 3199 Nefertiti, 3757 (1982 XB), and 4034 (1986 PA). Icarus, 172, 170-178. https://doi.org/10.1016/j.icarus.2004.06.003 [2] Magri, C., Ostro, S. J., Scheeres, D. J., Nolan, M. C., Giorgini, J. D., Benner, L. A. M., &amp; Margot, J. L. (2007). Radar observations and a physical model of Asteroid 1580 Betulia. Icarus, 186, 152-177. https://doi.org/10.1016/j.icarus.2006.08.004 [3] Ockert-Bell, M. E., Clark, B. E., Shepard, M. K., Rivkin, A. S., Binzel, R. P., Thomas, C. A., DeMeo, F. E., Bus, S. J., &amp; Shah, S. (2008). Observations of X/M asteroids across multiple wavelengths. Icarus, 195, 206-219. https://doi.org/10.1016/j.icarus.2007.11.006 [4] Shepard, M. K., Clark, B. E., Nolan, M. C., Howell, E. S., Magri, C., Giorgini, J. D., Benner, L. A. M., Ostro, S. J., Harris, A. W., Warner, B., Pray, D., Pravec, P., Fauerbach, M., Bennett, T., Klotz, A., et al. (2008). A radar survey of M- and X-class asteroids. Icarus, 195, 184-205. https://doi.org/10.1016/j.icarus.2007.11.032 [5] Shepard, M.K., Kressler, K.M., Clark, B.E., Ockert-Bell, M.E., Nolan, M.C., Howell, E.S., Magri, C., &amp; Giorgini, J.D. (2008). Radar observations of E-class Asteroids 44 Nysa and 434 Hungaria. Icarus, 195, 220-225. https://doi.org/10.1016/j.icarus.2007.12.018 [6] Shepard, M. K., Clark, B. E., Ockert-Bell, M., Nolan, M. C., Howell, E. S., Magri, C., Giorgini, J. D., Benner, L. A. M., Ostro, S. J., Harris, A. W., Warner, B. D., Stephens, R. D., &amp; Mueller, M. (2010). A radar survey of M- and X-class asteroids II. Summary and synthesis. Icarus, 208, 221-237. https://doi.org/10.1016/j.icarus.2010.01.017 [7] Ockert-Bell, M. E., Clark, B. E., Shepard, M. K., Isaacs, R. A., Cloutis, E. A., Fornasier, S., &amp; Bus, S. J. (2010). The composition of M-type asteroids: Synthesis of spectroscopic and radar observations. Icarus, 210, 674-692. https://doi.org/10.1016/j.icarus.2010.08.002 [8] Shepard, M. K., Harris, A. W., Taylor, P. A., Clark, B. E., Ockert-Bell, M., Nolan, M. C., Howell, E. S., Magri, C., Giorgini, J. D., &amp; Benner, L. A. M. (2011). Radar observations of Asteroids 64 Angelina and 69 Hesperia. Icarus, 215, 547-551. https://doi.org/10.1016/j.icarus.2011.07.027 [9] Neeley, J. R., Clark, B. E., Ockert-Bell, M. E., Shepard, M. K., Conklin, J., Cloutis, E. A., Fornasier, S., &amp; Bus, S. J. (2014). The composition of M-type asteroids II: Synthesis of spectroscopic and radar observations. Icarus, 238, 37-50. https://doi.org/10.1016/j.icarus.2014.05.008 [10] Shepard, M. K., Taylor, P. A., Nolan, M. C., Howell, E. S., Springmann, A., Giorgini, J. D., Warner, B. D., Harris, A. W., Stephens, R., Merline, W. J., Rivkin, A., Benner, L. A. M., Coley, D., Clark, B. E., Ockert-Bell, M., et al. (2015). A radar survey of M- and X-class asteroids. III. Insights into their composition, hydration state, &amp;amp; structure. Icarus, 245, 38-55. https://doi.org/10.1016/j.icarus.2014.09.016 [11] Greenberg, A. H., Margot, J. L., Verma, A. K., Taylor, P. A., Naidu, S. P., Brozovic, M., &amp; Benner, L. A. M. (2017). Asteroid 1566 Icarus’s Size, Shape, Orbit, and Yarkovsky Drift from Radar Observations. The Astronomical Journal, 153, 108. https://doi.org/10.3847/1538-3881/153/3/108 [12] Greenberg, A. H., Margot, J. L., Verma, A. K., Taylor, P. A., &amp; Hodge, S. E. (2020). Yarkovsky Drift Detections for 247 Near-Earth Asteroids. The Astronomical Journal, 159, 92. https://doi.org/10.3847/1538-3881/ab62a3 [13] Skirmante, K., Bleiders, M., Jekabsons, N., Bezrukovs, V., &amp; Jasmonts, G. (2024). Observations of OH masers of comets in 1.6GHz frequency band using the Irbene RT32 radio telescope. https://doi.org/10.5194/epsc2020-171 [14] Medeiros, H., de León, J., Licandro, J., Popescu, M., &amp; Pinilla-Alonso, N. (2024). Physical characterization of near-Earth asteroid (159402) 1999 AP10 in support of the Arecibo Planetary Radar Program within the NEOROCKS project. https://doi.org/10.5194/epsc2021-783 [15] Ferrais, M., Marshall, S., Venditti, F., Devogèle, M., Pravec, P., Scheirich, P., &amp; Jehin, E. (2024). Shape model of the binary NEA (385186) 1994 AW1 from 2015 radar observations and long term lightcurve dataset.&amp;amp;#160;. https://doi.org/10.5194/epsc2024-161 [16] Howell, E., Vervack, R., Fernandez, Y., Myers, S., Hinkle, M., Magri, C., Marshall, S., &amp; Rivera-Valentin, E. (2025). Combining thermal and radar observations of near-Earth asteroids. https://doi.org/10.5194/epsc-dps2025-462 [17] MacLennan, E., Virkki, A., &amp; Marshall, S. (2025). Radar Shape Modeling of NEA (242643) 2005 NZ6: A Toutatis Twin?. https://doi.org/10.5194/epsc-dps2025-1476</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>[1] Brozovic, M., Benner, L. A. M., Magri, C., Ostro, S. J., Scheeres, D. J., Giorgini, J. D., Nolan, M. C., Margot, J. L., Jurgens, R. F., &amp; Rose, R. (2010). Radar observations and a physical model of contact binary Asteroid 4486 Mithra. Icarus, 208, 207-220. https://doi.org/10.1016/j.icarus.2010.01.035 [2] None https://echo.jpl.nasa.gov/asteroids/4486_Mithra/brozovic.etal.2010.mithra.pdf [3] None https://ui.adsabs.harvard.edu/abs/2000DPS....32.0807O/abstract [4] Brozovic et al. (2010). Mithra [PDF]. https://echo.jpl.nasa.gov/asteroids/4486_Mithra/brozovic.etal.2010.mithra.pdf [5] O. et al. (2000). Bulletin of the American Astronomical Society (DPS meeting abstract), Vol. 32, 0807. [ADS record] https://ui.adsabs.harvard.edu/abs/2000DPS....32.0807O/abstract</t>
+          <t>[1] Brozovic, M., Benner, L. A. M., Magri, C., Ostro, S. J., Scheeres, D. J., Giorgini, J. D., Nolan, M. C., Margot, J. L., Jurgens, R. F., &amp; Rose, R. (2010). Radar observations and a physical model of contact binary Asteroid 4486 Mithra. Icarus, 208, 207-220. https://doi.org/10.1016/j.icarus.2010.01.035 [2] Brozovic et al. (2010). Mithra [PDF]. https://echo.jpl.nasa.gov/asteroids/4486_Mithra/brozovic.etal.2010.mithra.pdf [3] Ostro, S. J., et al. (2000). Radar Observations of Asteroid 4486 Mithra. AAS/DPS Meeting #32, 08.07. https://ui.adsabs.harvard.edu/abs/2000DPS....32.0807O/abstract</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>[1] Ostro, S. J., Choate, D., Dendrenos, P., Giorgini, J. D., Hills, D. L., Howard, D., Jurgens, R. F., Mitchell, D. L., Rose, R., Rosema, K. D., Slade, M. A., Strobert, D. R., Winkler, R., &amp; Yoemans, D. K. (1994). abstract) Asteroid Radar Astronomy at Goldstone in the 1990s. NASA Technical Reports Server (NASA). [2] Ostro, S. J., Hudson, R. S., Jurgens, R. F., Rosema, K. D., Campbell, D. B., Yeomans, D. K., Chandler, J. F., Giorgini, J. D., Winkler, R., Rose, R., Howard, S. D., Slade, M. A., Perillat, P., &amp; Shapiro, I. I. (1995). Radar Images of Asteroid 4179 Toutatis. Science, 270, 80-83. https://doi.org/10.1126/science.270.5233.80 [3] Quijano-Vodniza, A., &amp; P., M. R. (2017). The Asteroid 2014 JO25. DPS. [4] MacLennan, E., Virkki, A., &amp; Marshall, S. (2025). Radar Shape Modeling of NEA (242643) 2005 NZ6: A Toutatis Twin?. https://doi.org/10.5194/epsc-dps2025-1476 [5] B. et al. (2013). Bulletin of the American Astronomical Society (DPS meeting abstract), Vol. 4510105. [ADS record] https://ui.adsabs.harvard.edu/abs/2013DPS....4510105B/abstract [6] H. et al. (1996). Bulletin of the American Astronomical Society (DPS meeting abstract), Vol. 28, 1040. [ADS record] https://ui.adsabs.harvard.edu/abs/1996DPS....28.1040H/abstract [7] Ostro, S. J., et al. (1993). Radar Imaging of Asteroid 4179 Toutatis. Bulletin of the American Astronomical Society, 25. https://ui.adsabs.harvard.edu/abs/1993DPS....25.3407O/abstract [8] M. et al. (1993). Space Flight, Vol. 35, 207. [ADS record] https://ui.adsabs.harvard.edu/abs/1993SpFl...35..207M/abstract [9] Ostro, S. J., Hudson, R. S., Rosema, K. D., Giorgini, J. D., Jurgens, R. F., Yeomans, D. K., Chodas, P. W., Winkler, R., Rose, R., Choate, D., Cormier, R. A., Kelley, D., Littlefair, R., Benner, L. A. M., Thomas, M. L., &amp; Slade, M. A. (1999). Asteroid 4179 Toutatis: 1996 Radar Observations. Icarus, 137, 122-139. https://doi.org/10.1006/icar.1998.6031 [10] Zhao, Y., Xiao, Z., Liu, W., Sun, J., Huang, B., &amp; Tang, C. (2016). Radar model fusion of asteroid (4179) Toutatis via its optical images observed by Chang'e-2 probe. Planetary and Space Science, 125, 87-95. https://doi.org/10.1016/j.pss.2016.03.008 [11] Hudson, R. S., &amp; Ostro, S. J. (1995). Shape and Non-Principal Axis Spin State of Asteroid 4179 Toutatis. Science, 270, 84-86. https://doi.org/10.1126/science.270.5233.84 [12] Takahashi, Y., M.W. Busch, and D.J. Scheeres, Spin State and Moment of Inertia Characterization of 4179 Toutatis, Astronomical Journal 146, 95, 2013 http://dx.doi.org/10.1088/0004-6256/146/4/95 [13] Hudson, R.S., S.J. Ostro, and D.J. Scheeres, High-Resolution Model of Asteroid 4179 Toutatis, Icarus 161, 346-355, 2003 http://dx.doi.org/10.1016/S0019-1035(02)00042-8</t>
+          <t>[1] Ostro, S. J., Choate, D., Dendrenos, P., Giorgini, J. D., Hills, D. L., Howard, D., Jurgens, R. F., Mitchell, D. L., Rose, R., Rosema, K. D., Slade, M. A., Strobert, D. R., Winkler, R., &amp; Yoemans, D. K. (1994). abstract) Asteroid Radar Astronomy at Goldstone in the 1990s. NASA Technical Reports Server (NASA). [2] Ostro, S. J., Hudson, R. S., Jurgens, R. F., Rosema, K. D., Campbell, D. B., Yeomans, D. K., Chandler, J. F., Giorgini, J. D., Winkler, R., Rose, R., Howard, S. D., Slade, M. A., Perillat, P., &amp; Shapiro, I. I. (1995). Radar Images of Asteroid 4179 Toutatis. Science, 270, 80-83. https://doi.org/10.1126/science.270.5233.80 [3] Quijano-Vodniza, A., &amp; P., M. R. (2017). The Asteroid 2014 JO25. DPS. [4] MacLennan, E., Virkki, A., &amp; Marshall, S. (2025). Radar Shape Modeling of NEA (242643) 2005 NZ6: A Toutatis Twin?. https://doi.org/10.5194/epsc-dps2025-1476 [5] Busch, M. W., et al. (2013). Goldstone/VLA Radar Observations of Near-Earth Asteroid 4179 Toutatis in 2012. AAS/DPS Meeting #45, 105.05. https://ui.adsabs.harvard.edu/abs/2013DPS....4510105B/abstract [6] Hudson, R. S., &amp; Ostro, S. J. (1996). Asteroid 4179 Toutatis: Potential of 1996 Radar Observations for Spin-State Refinement. AAS/DPS Meeting #28, 10.40. https://ui.adsabs.harvard.edu/abs/1996DPS....28.1040H/abstract [7] Ostro, S. J., et al. (1993). Radar Imaging of Asteroid 4179 Toutatis. Bulletin of the American Astronomical Society, 25. https://ui.adsabs.harvard.edu/abs/1993DPS....25.3407O/abstract [8] (1993). Toutatis. Space Flight, 35, 207. https://ui.adsabs.harvard.edu/abs/1993SpFl...35..207M/abstract [9] Ostro, S. J., Hudson, R. S., Rosema, K. D., Giorgini, J. D., Jurgens, R. F., Yeomans, D. K., Chodas, P. W., Winkler, R., Rose, R., Choate, D., Cormier, R. A., Kelley, D., Littlefair, R., Benner, L. A. M., Thomas, M. L., &amp; Slade, M. A. (1999). Asteroid 4179 Toutatis: 1996 Radar Observations. Icarus, 137, 122-139. https://doi.org/10.1006/icar.1998.6031 [10] Zhao, Y., Xiao, Z., Liu, W., Sun, J., Huang, B., &amp; Tang, C. (2016). Radar model fusion of asteroid (4179) Toutatis via its optical images observed by Chang'e-2 probe. Planetary and Space Science, 125, 87-95. https://doi.org/10.1016/j.pss.2016.03.008 [11] Hudson, R. S., &amp; Ostro, S. J. (1995). Shape and Non-Principal Axis Spin State of Asteroid 4179 Toutatis. Science, 270, 84-86. https://doi.org/10.1126/science.270.5233.84 [12] Takahashi, Y., M.W. Busch, and D.J. Scheeres, Spin State and Moment of Inertia Characterization of 4179 Toutatis, Astronomical Journal 146, 95, 2013 http://dx.doi.org/10.1088/0004-6256/146/4/95 [13] Hudson, R.S., S.J. Ostro, and D.J. Scheeres, High-Resolution Model of Asteroid 4179 Toutatis, Icarus 161, 346-355, 2003 http://dx.doi.org/10.1016/S0019-1035(02)00042-8</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>[1] Gavrik, Y. A., Gavrik, A. L., &amp; Smyslov, A. A. (2016). Distribution of the surface radio brightness of asteroid Golevka constructed from the radar data. Journal of Communications Technology and Electronics, 61, 1347-1353. https://link.springer.com/article/10.1134/S106422691612007X [2] Greenberg, A. H., Margot, J. L., Verma, A. K., Taylor, P. A., &amp; Hodge, S. E. (2020). Yarkovsky Drift Detections for 247 Near-Earth Asteroids. The Astronomical Journal, 159, 92. https://doi.org/10.3847/1538-3881/ab62a3 [3] H. et al. (2000). Planetary and Space Science, Vol. 11, 7. [ADS record] https://ui.adsabs.harvard.edu/abs/2000PDSS...11....7H/abstract [4] N. et al. (2000). Planetary and Space Science, Vol. 11. [ADS record] https://ui.adsabs.harvard.edu/abs/2000PDSS...11.....N/abstract [5] Hudson, R. S., Ostro, S. J., Jurgens, R. F., Rosema, K. D., Giorgini, J. D., Winkler, R., Rose, R., Choate, D., Cormier, R. A., Franck, C. R., Frye, R., Howard, D., Kelley, D., Littlefair, R., Slade, M. A., Benner, L. A. M., Thomas, M. L., Mitchell, D. L., Chodas, P. W., Yeomans, D. K., Scheeres, D. J., Palmer, P., Zaitsev, A., Koyama, Y., Nakamura, A., Harris, A. W., &amp; Meshkov, M. N. (2000). Radar Observations and Physical Model of Asteroid 6489 Golevka. Icarus, 148, 37-51. https://doi.org/10.1006/icar.2000.6483 [6] Koyama, Y., Nakajima, J., Sekido, M., Yoshikawa, M., Nakamura, A. M., Hirabayashi, H., Okada, T., Abe, M., Nishibori, T., Fuse, T., Ostro, S. J., Choate, D., Cormier, R. A., Winkler, R., Jurgens, R. F., Giorgini, J. D., Yeomans, D. K., Slade, M. A., &amp; Zaitsev, A. L. (2001). Radar observations of near-Earth asteroids 6489 Golevka and 4197 (1982 TA). Communications Research Laboratory Review, 47, 145. https://ui.adsabs.harvard.edu/abs/2001CRLRv..47..145K/abstract [7] Zaitsev, A. L., Ostro, S. J., Ignatov, S. M., Yeomans, D. K., Petrenko, B. L., Choate, D., Margorin, O. K., Cormier, R. A., Mardyshkin, V. P., Winkler, R., Rghiga, D., Jurgens, R. F., Shubin, K. L., Giorgini, J. D., Krivtsov, A. P., Rosema, K. D., Koluka, Y. F., Slade, M. A., Gavrik, A. L., Andreev, O. N., Ivanov, A. E., Peshin, S. V., Koyama, Y., Yoshikawa, M., &amp; Nakamura, A. (1997). Intercontinental bistatic radar observations of 6489 Golevka (1991 JX). Planetary and Space Science, 45, 771-778. https://doi.org/10.1016/S0032-0633(97)00042-1 [8] Chesley, S. R., Ostro, S. J., Vokrouhlický, D., Čapek, D., Giorgini, J. D., Nolan, M. C., Margot, J. L., Hine, A. A., Benner, L. A. M., &amp; Chamberlin, A. B. (2003). Direct Detection of the Yarkovsky Effect by Radar Ranging to Asteroid 6489 Golevka. Science, 302, 1739-1742. https://doi.org/10.1126/science.1091452</t>
+          <t>[1] Gavrik, Y. A., Gavrik, A. L., &amp; Smyslov, A. A. (2016). Distribution of the surface radio brightness of asteroid Golevka constructed from the radar data. Journal of Communications Technology and Electronics, 61, 1347-1353. https://link.springer.com/article/10.1134/S106422691612007X [2] Greenberg, A. H., Margot, J. L., Verma, A. K., Taylor, P. A., &amp; Hodge, S. E. (2020). Yarkovsky Drift Detections for 247 Near-Earth Asteroids. The Astronomical Journal, 159, 92. https://doi.org/10.3847/1538-3881/ab62a3 [3] Hudson, R. S., et al. (2000). Asteroid radar shape models: 6489 Golevka. Planetary Data System, 11, 7. https://ui.adsabs.harvard.edu/abs/2000PDSS...11....7H/abstract [4] Nolan, M. C., et al. (2000). Asteroid radar shape models. Planetary Data System, 11. https://ui.adsabs.harvard.edu/abs/2000PDSS...11.....N/abstract [5] Hudson, R. S., Ostro, S. J., Jurgens, R. F., Rosema, K. D., Giorgini, J. D., Winkler, R., Rose, R., Choate, D., Cormier, R. A., Franck, C. R., Frye, R., Howard, D., Kelley, D., Littlefair, R., Slade, M. A., Benner, L. A. M., Thomas, M. L., Mitchell, D. L., Chodas, P. W., Yeomans, D. K., Scheeres, D. J., Palmer, P., Zaitsev, A., Koyama, Y., Nakamura, A., Harris, A. W., &amp; Meshkov, M. N. (2000). Radar Observations and Physical Model of Asteroid 6489 Golevka. Icarus, 148, 37-51. https://doi.org/10.1006/icar.2000.6483 [6] Koyama, Y., Nakajima, J., Sekido, M., Yoshikawa, M., Nakamura, A. M., Hirabayashi, H., Okada, T., Abe, M., Nishibori, T., Fuse, T., Ostro, S. J., Choate, D., Cormier, R. A., Winkler, R., Jurgens, R. F., Giorgini, J. D., Yeomans, D. K., Slade, M. A., &amp; Zaitsev, A. L. (2001). Radar observations of near-Earth asteroids 6489 Golevka and 4197 (1982 TA). Communications Research Laboratory Review, 47, 145. https://ui.adsabs.harvard.edu/abs/2001CRLRv..47..145K/abstract [7] Zaitsev, A. L., Ostro, S. J., Ignatov, S. M., Yeomans, D. K., Petrenko, B. L., Choate, D., Margorin, O. K., Cormier, R. A., Mardyshkin, V. P., Winkler, R., Rghiga, D., Jurgens, R. F., Shubin, K. L., Giorgini, J. D., Krivtsov, A. P., Rosema, K. D., Koluka, Y. F., Slade, M. A., Gavrik, A. L., Andreev, O. N., Ivanov, A. E., Peshin, S. V., Koyama, Y., Yoshikawa, M., &amp; Nakamura, A. (1997). Intercontinental bistatic radar observations of 6489 Golevka (1991 JX). Planetary and Space Science, 45, 771-778. https://doi.org/10.1016/S0032-0633(97)00042-1 [8] Chesley, S. R., Ostro, S. J., Vokrouhlický, D., Čapek, D., Giorgini, J. D., Nolan, M. C., Margot, J. L., Hine, A. A., Benner, L. A. M., &amp; Chamberlin, A. B. (2003). Direct Detection of the Yarkovsky Effect by Radar Ranging to Asteroid 6489 Golevka. Science, 302, 1739-1742. https://doi.org/10.1126/science.1091452</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>[1] (2012). (. , 3176, 1. https://ui.adsabs.harvard.edu/abs/2012CBET.3176....1T/abstract</t>
+          <t>[1] (2012). (5143) Heracles. Central Bureau Electronic Telegrams, 3176. https://ui.adsabs.harvard.edu/abs/2012CBET.3176....1T/abstract</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>[1] (2004). R. , 36, 32.29. https://ui.adsabs.harvard.edu/abs/2004DPS....36.3229B/abstract [2] (2012). R. , 44, 302.05. https://ui.adsabs.harvard.edu/abs/2012DPS....4430205B/abstract</t>
+          <t>[1] Benner, L. A. M., Nolan, M. C., Carter, L. M., Ostro, S. J., Giorgini, J. D., Magri, C., &amp; Margot, J. L. (2004). Radar imaging of near-Earth asteroid 11066 Sigurd. AAS/DPS Meeting #36, 32.29. https://ui.adsabs.harvard.edu/abs/2004DPS....36.3229B/abstract [2] Busch, M. W., et al. (2012). Radar Imaging Of 11066 Sigurd, 2000 YF29, And 2004 XL14 And The Obliquity Distribution Of Contact Binary Near-Earth Asteroids. AAS/DPS Meeting #44, 302.05. https://ui.adsabs.harvard.edu/abs/2012DPS....4430205B/abstract</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>[1] (2014). T. , 46, 409.03. https://ui.adsabs.harvard.edu/abs/2014DPS....4640903T/abstract</t>
+          <t>[1] Taylor, P. A., et al. (2014). The Smallest Binary Asteroid? The Discovery of Equal-Mass Binary 1994 CJ1. AAS/DPS Meeting #46, 409.03. https://ui.adsabs.harvard.edu/abs/2014DPS....4640903T/abstract</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>[1] (2005). 1. , 8563, 2. https://ui.adsabs.harvard.edu/abs/2005IAUC.8563....2B/abstract</t>
+          <t>[1] Benner, L. A. M., Nolan, M. C., Ostro, S. J., Giorgini, J. D., Margot, J. L., &amp; Magri, C. (2005). 1994 XD. IAU Circular, 8563. https://ui.adsabs.harvard.edu/abs/2005IAUC.8563....2B/abstract</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>[1] (2012). A. , 1667, 6403. https://ui.adsabs.harvard.edu/abs/2012LPICo1667.6403B/abstract [2] (2012). 1. , EPSC2012-542. https://ui.adsabs.harvard.edu/abs/2012epsc.conf..542C/abstract</t>
+          <t>[1] Benner, L. A. M., et al. (2012). Radar Observations of Near-Earth Asteroid (175706) 1996 FG3. Lunar and Planetary Institute Contributions, 1667, 6403. https://ui.adsabs.harvard.edu/abs/2012LPICo1667.6403B/abstract [2] (2012). 1996 FG3, MarcoPolo-R mission target: Living on the edge. EPSC Abstracts, 7, 542. https://ui.adsabs.harvard.edu/abs/2012epsc.conf..542C/abstract</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>[1] (2020). R. , 348, 113777. https://doi.org/10.1016/j.icarus.2020.113777 [2] (2010). R. , 42, 13.17. https://ui.adsabs.harvard.edu/abs/2010DPS....42.1317B/abstract [3] (2022). A. , 3, 210. https://doi.org/10.3847/PSJ/ac880d [4] (2016). O. , P52B-02. https://ui.adsabs.harvard.edu/abs/2016AGUFM.P52B..02N/abstract [5] (2003). (. , 8244, 2. https://ui.adsabs.harvard.edu/abs/2003IAUC.8244....2P/abstract [6] Pajola, M., Barnouin, O. S., Lucchetti, A., Hirabayashi, M., Ballouz, R.-L., Asphaug, E., Ernst, C. M., Della Corte, V., Farnham, T., Poggiali, G., Sunshine, J. M., Epifani, E. M., Murdoch, N., Ieva, S., Schwartz, S. R., Ivanovski, S., Trigo-Rodriguez, J. M., Rossi, A., Chabot, N. L., Zinzi, A., Rivkin, A., Brucato, J. R., Michel, P., Cremonese, G., Dotto, E., Amoroso, M., Bertini, I., Capannolo, A., Cheng, A., Cotugno, B., Dall'Ora, M., Daly, R. T., Di Tana, V., Deshapriya, J. D. P., Gai, I., Hasselmann, P. H. A., Impresario, G., Lavagna, M., Meneghin, A., Miglioretti, F., Modenini, D., Palumbo, P., Perna, D., Pirrotta, S., Simioni, E., Simonetti, S., Tortora, P., Zannoni, M., and Zanotti, G., Anticipated Geological Assessment of the (65803) Didymos-Dimorphos System, Target of the DART-LICIACube Mission, The Planetary Science Journal, 3, p.210, 2022 https://ui.adsabs.harvard.edu/abs/2022PSJ.....3..210P</t>
+          <t>[1] Naidu, S.P., Benner, L.A.M., Brozovic, M., Nolan, M.C., Ostro, S.J., Margot, J.L., Giorgini, J.D., &amp; Hirabayashi, T. (2020). Radar observations and a physical model of binary near-Earth asteroid 65803 Didymos, target of the DART mission. Icarus, 348, 113777. https://doi.org/10.1016/j.icarus.2020.113777 [2] Benner, L. A. M., et al. (2010). Radar Imaging and a Physical Model of Binary Asteroid 65803 Didymos. AAS/DPS Meeting #42, 13.17. https://ui.adsabs.harvard.edu/abs/2010DPS....42.1317B/abstract [3] Pajola, M., Barnouin, O.S., Lucchetti, A., Hirabayashi, M., Ballouz, R.-L., Asphaug, E., Ernst, C.M., &amp; Della Corte, V. (2022). Anticipated Geological Assessment of the (65803) Didymos-Dimorphos System, Target of the DART-LICIACube Mission. The Planetary Science Journal, 3, 210. https://doi.org/10.3847/PSJ/ac880d [4] Naidu, S. P., et al. (2016). Radar observations of binary near-Earth asteroid 65803 Didymos. AGU Fall Meeting, abstract P52B-02. https://ui.adsabs.harvard.edu/abs/2016AGUFM.P52B..02N/abstract [5] (2003). 65803 Didymos (1996 GT). IAU Circular, 8244. https://ui.adsabs.harvard.edu/abs/2003IAUC.8244....2P/abstract [6] Pajola, M., Barnouin, O. S., Lucchetti, A., Hirabayashi, M., Ballouz, R.-L., Asphaug, E., Ernst, C. M., Della Corte, V., Farnham, T., Poggiali, G., Sunshine, J. M., Epifani, E. M., Murdoch, N., Ieva, S., Schwartz, S. R., Ivanovski, S., Trigo-Rodriguez, J. M., Rossi, A., Chabot, N. L., Zinzi, A., Rivkin, A., Brucato, J. R., Michel, P., Cremonese, G., Dotto, E., Amoroso, M., Bertini, I., Capannolo, A., Cheng, A., Cotugno, B., Dall'Ora, M., Daly, R. T., Di Tana, V., Deshapriya, J. D. P., Gai, I., Hasselmann, P. H. A., Impresario, G., Lavagna, M., Meneghin, A., Miglioretti, F., Modenini, D., Palumbo, P., Perna, D., Pirrotta, S., Simioni, E., Simonetti, S., Tortora, P., Zannoni, M., and Zanotti, G., Anticipated Geological Assessment of the (65803) Didymos-Dimorphos System, Target of the DART-LICIACube Mission, The Planetary Science Journal, 3, p.210, 2022 https://ui.adsabs.harvard.edu/abs/2022PSJ.....3..210P</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -7130,7 +7130,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>[1] (2009). A. , 41, 43.09. https://ui.adsabs.harvard.edu/abs/2009DPS....41.4309B/abstract</t>
+          <t>[1] Benner, L. A. M., et al. (2009). Radar Imaging of Near-Earth Asteroid 1998 CS1. AAS/DPS Meeting #41, 43.09. https://ui.adsabs.harvard.edu/abs/2009DPS....41.4309B/abstract</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>[1] (2003). (. , 8216, 3. https://ui.adsabs.harvard.edu/abs/2003IAUC.8216....3P/abstract</t>
+          <t>[1] (2003). (66063) 1998 RO1. IAU Circular, 8216. https://ui.adsabs.harvard.edu/abs/2003IAUC.8216....3P/abstract</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>[1] (2003). R. , 35, 24.01. https://ui.adsabs.harvard.edu/abs/2003DPS....35.2401B/abstract</t>
+          <t>[1] Benner, L. A. M., et al. (2003). Radar Imaging of Binary Near-Earth Asteroid 1998 ST27. AAS/DPS Meeting #35, 24.01. https://ui.adsabs.harvard.edu/abs/2003DPS....35.2401B/abstract</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>[1] (2013). P. , 5132, 1. https://ui.adsabs.harvard.edu/abs/2013ATel.5132....1H/abstract</t>
+          <t>[1] Hicks, M., et al. (2013). Palomar Spectroscopy of Near-Earth Asteroids 137199 (1999 KX4), 152756 (1999 JV3), 163249 (2002 GT), 163364 (2002 OD20), and 285263 (1998 QE2). The Astronomer's Telegram, 5132. http://www.astronomerstelegram.org/?read=5132</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>[1] (2013). P. , 5132, 1. https://ui.adsabs.harvard.edu/abs/2013ATel.5132....1H/abstract</t>
+          <t>[1] Hicks, M., et al. (2013). Palomar Spectroscopy of Near-Earth Asteroids 137199 (1999 KX4), 152756 (1999 JV3), 163249 (2002 GT), 163364 (2002 OD20), and 285263 (1998 QE2). The Astronomer's Telegram, 5132. http://www.astronomerstelegram.org/?read=5132</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>[1] (2010). B. , 2706, 1. https://ui.adsabs.harvard.edu/abs/2010ATel.2706....1H/abstract</t>
+          <t>[1] Hicks, M., et al. (2010). Broadband Photometry of the Potentially Hazardous Asteroid 1999 MN: Suggestive of YORP and/or Tidal Spin-Up?. The Astronomer's Telegram, 2706. http://www.astronomerstelegram.org/?read=2706</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>[1] (2020). (. , 4787, 1. https://ui.adsabs.harvard.edu/abs/2020CBET.4787....1G/abstract</t>
+          <t>[1] (2020). (264357) 2000 AZ_93. Central Bureau Electronic Telegrams, 4787. https://ui.adsabs.harvard.edu/abs/2020CBET.4787....1G/abstract</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>[1] (2010). R. , 42, 13.18. https://ui.adsabs.harvard.edu/abs/2010DPS....42.1318J/abstract</t>
+          <t>[1] Jimenez, A., et al. (2010). Radar Shape Modeling of Binary Near-Earth Asteroid 2000 CO101. AAS/DPS Meeting #42, 13.18. https://ui.adsabs.harvard.edu/abs/2010DPS....42.1318J/abstract</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>[1] (2012). T. , 44, 111.10. https://ui.adsabs.harvard.edu/abs/2012DPS....4411110V/abstract [2] (2013). R. , 226, 323. https://doi.org/10.1016/j.icarus.2013.05.025 [3] (2012). R. , 44, 302.06. https://ui.adsabs.harvard.edu/abs/2012DPS....4430206N/abstract [4] Marshall, S.E., E.S. Howell, C. Magri, R.J. Vervack, D.B. Campbell, Y.R. Fernandez, M.C. Nolan, J.L. Crowell, M.D. Hicks, K.J. Lawrence, and P.A. Taylor, Thermal Properties and an Improved Shape Model for Near-Earth Asteroid (162421) 2000 ET70, Icarus 292, 22-35, 2017 http://dx.doi.org/10.1016/j.icarus.2017.03.028</t>
+          <t>[1] (2012). The Asteroid 2000 ET70. AAS/DPS Meeting #44, 111.10. https://ui.adsabs.harvard.edu/abs/2012DPS....4411110V/abstract [2] Naidu, S.P., Margot, J.L., Busch, M.W., Taylor, P.A., Nolan, M.C., Brozovic, M., Benner, L.A.M., &amp; Giorgini, J.D. (2013). Radar imaging and physical characterization of near-Earth Asteroid (162421) 2000 ET70. Icarus, 226, 323-335. https://doi.org/10.1016/j.icarus.2013.05.025 [3] Naidu, S. P., &amp; Margot, J. L. (2012). Radar Imaging and Physical Characterization of Near-Earth Asteroid (162421) 2000 ET70. AAS/DPS Meeting #44, 302.06. https://ui.adsabs.harvard.edu/abs/2012DPS....4430206N/abstract [4] Marshall, S.E., E.S. Howell, C. Magri, R.J. Vervack, D.B. Campbell, Y.R. Fernandez, M.C. Nolan, J.L. Crowell, M.D. Hicks, K.J. Lawrence, and P.A. Taylor, Thermal Properties and an Improved Shape Model for Near-Earth Asteroid (162421) 2000 ET70, Icarus 292, 22-35, 2017 http://dx.doi.org/10.1016/j.icarus.2017.03.028</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>[1] (2009). P. , 2323, 1. https://ui.adsabs.harvard.edu/abs/2009ATel.2323....1H/abstract [2] (2009). L. , 2283, 1. https://ui.adsabs.harvard.edu/abs/2009ATel.2283....1H/abstract</t>
+          <t>[1] Hicks, M., et al. (2009). Planetary radar targets 1999 AP10, 2000 TO64, 2000 UJ1, and 2000 XK44: Four S-complex near-Earth asteroids. The Astronomer's Telegram, 2323. http://www.astronomerstelegram.org/?read=2323</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -12230,7 +12230,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>[1] (2001). R. , 2055. https://ui.adsabs.harvard.edu/abs/2001LPI....32.2055N/abstract</t>
+          <t>[1] Nolan, M. C., Margot, J. L., Howell, E. S., &amp; Benner, L. A. M. (2001). Radar Observations of Near-Earth Asteroids 2000 UG11 and 2000 UK11. Lunar and Planetary Science Conference, 32, 2055. https://ui.adsabs.harvard.edu/abs/2001LPI....32.2055N/abstract</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>[1] (2009). P. , 2323, 1. https://ui.adsabs.harvard.edu/abs/2009ATel.2323....1H/abstract [2] (2009). L. , 2283, 1. https://ui.adsabs.harvard.edu/abs/2009ATel.2283....1H/abstract</t>
+          <t>[1] Hicks, M., et al. (2009). Planetary radar targets 1999 AP10, 2000 TO64, 2000 UJ1, and 2000 XK44: Four S-complex near-Earth asteroids. The Astronomer's Telegram, 2323. http://www.astronomerstelegram.org/?read=2323</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -12340,7 +12340,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>[1] (2001). R. , 2055. https://ui.adsabs.harvard.edu/abs/2001LPI....32.2055N/abstract</t>
+          <t>[1] Nolan, M. C., Margot, J. L., Howell, E. S., &amp; Benner, L. A. M. (2001). Radar Observations of Near-Earth Asteroids 2000 UG11 and 2000 UK11. Lunar and Planetary Science Conference, 32, 2055. https://ui.adsabs.harvard.edu/abs/2001LPI....32.2055N/abstract</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -12400,7 +12400,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>[1] (2009). P. , 2323, 1. https://ui.adsabs.harvard.edu/abs/2009ATel.2323....1H/abstract [2] (2010). 2. , 2371, 1. https://ui.adsabs.harvard.edu/abs/2010ATel.2371....1H/abstract</t>
+          <t>[1] Hicks, M., et al. (2009). Planetary radar targets 1999 AP10, 2000 TO64, 2000 UJ1, and 2000 XK44: Four S-complex near-Earth asteroids. The Astronomer's Telegram, 2323. http://www.astronomerstelegram.org/?read=2323</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>[1] (2012). R. , 44, 302.05. https://ui.adsabs.harvard.edu/abs/2012DPS....4430205B/abstract</t>
+          <t>[1] Busch, M. W., et al. (2012). Radar Imaging Of 11066 Sigurd, 2000 YF29, And 2004 XL14 And The Obliquity Distribution Of Contact Binary Near-Earth Asteroids. AAS/DPS Meeting #44, 302.05. https://ui.adsabs.harvard.edu/abs/2012DPS....4430205B/abstract</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>[1] (2010). P. , 2502, 1. https://ui.adsabs.harvard.edu/abs/2010ATel.2502....1H/abstract</t>
+          <t>[1] Hicks, M., et al. (2010). Physical Characterization of the Potentially Hazardous Asteroid and Planetary Radar Target 68216 (2001 CV26): An Excellent Shape/Pole Modeling Candidate. The Astronomer's Telegram, 2502. http://www.astronomerstelegram.org/?read=2502</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>[1] (2021). C. , 95. https://ui.adsabs.harvard.edu/abs/2021plde.confE..95T/abstract</t>
+          <t>[1] Taylor, P. A., et al. (2021). Characterization of Near-Earth Asteroid 153814 (2001 WN5) and Prospects for the 2028 Close Encounter with Earth. 7th IAA Planetary Defense Conference, E-95. https://ui.adsabs.harvard.edu/abs/2021plde.confE..95T/abstract</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
@@ -15230,7 +15230,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>[1] (2013). P. , 45, 208.08. https://ui.adsabs.harvard.edu/abs/2013DPS....4520808T/abstract</t>
+          <t>[1] Taylor, P. A., et al. (2013). Physical Characterization of Binary Near-Earth Asteroid (153958) 2002 AM31. AAS/DPS Meeting #45, 208.08. https://ui.adsabs.harvard.edu/abs/2013DPS....4520808T/abstract</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>[1] (2014). B. , 6090, 1. https://ui.adsabs.harvard.edu/abs/2014ATel.6090....1H/abstract</t>
+          <t>[1] Hicks, M., et al. (2014). Broad-band photometry of NHATS target 387733 (2003 GS). The Astronomer's Telegram, 6090. http://www.astronomerstelegram.org/?read=6090</t>
         </is>
       </c>
       <c r="P270" t="inlineStr">
@@ -18765,7 +18765,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>[1] (2021). (. , 5037, 1. https://ui.adsabs.harvard.edu/abs/2021CBET.5037....1P/abstract</t>
+          <t>[1] (2021). (143649) 2003 QQ_47. Central Bureau Electronic Telegrams, 5037. https://ui.adsabs.harvard.edu/abs/2021CBET.5037....1P/abstract</t>
         </is>
       </c>
       <c r="P285" t="inlineStr">
@@ -19340,7 +19340,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>[1] (2017). (. , 4353, 1. https://ui.adsabs.harvard.edu/abs/2017CBET.4353....1B/abstract</t>
+          <t>[1] (2017). (226514) 2003 UX_34. Central Bureau Electronic Telegrams, 4353. https://ui.adsabs.harvard.edu/abs/2017CBET.4353....1B/abstract</t>
         </is>
       </c>
       <c r="P294" t="inlineStr">
@@ -19875,7 +19875,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>[1] (2004). R. , 36, 28.08. https://ui.adsabs.harvard.edu/abs/2004DPS....36.2808N/abstract [2] (2004). C. , 36, 28.09. https://ui.adsabs.harvard.edu/abs/2004DPS....36.2809A/abstract [3] (2009). B. , 2289, 1. https://ui.adsabs.harvard.edu/abs/2009ATel.2289....1H/abstract</t>
+          <t>[1] Nolan, M. C., et al. (2004). Radar Images of Binary Asteroid 2003 YT1. AAS/DPS Meeting #36, 28.08. https://ui.adsabs.harvard.edu/abs/2004DPS....36.2808N/abstract [2] (2004). Compositional Results of Binary Near-Earth Asteroid 2003 YT1: A Basaltic Achondrite. AAS/DPS Meeting #36, 28.09. https://ui.adsabs.harvard.edu/abs/2004DPS....36.2809A/abstract [3] Hicks, M., et al. (2009). Broad-band Photometry of the Binary Potentially Hazardous Asteroid 2003 YT1. The Astronomer's Telegram, 2289. http://www.astronomerstelegram.org/?read=2289</t>
         </is>
       </c>
       <c r="P302" t="inlineStr">
@@ -20050,7 +20050,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>[1] (2015). R. , 29, 2257549. https://ui.adsabs.harvard.edu/abs/2015IAUGA..2257549B/abstract</t>
+          <t>[1] Benner, L. A. M., et al. (2015). Radar Imaging of Binary Near-Earth Asteroid (357439) 2004 BL86. IAU General Assembly, 22, 57549. https://ui.adsabs.harvard.edu/abs/2015IAUGA..2257549B/abstract</t>
         </is>
       </c>
       <c r="P305" t="inlineStr">
@@ -20200,7 +20200,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>[1] (2006). 2. , 535, 1. https://ui.adsabs.harvard.edu/abs/2006CBET..535....1T/abstract [2] (2006). R. , 38, 50.04. https://ui.adsabs.harvard.edu/abs/2006DPS....38.5004T/abstract</t>
+          <t>[1] (2006). 2004 DC. Central Bureau Electronic Telegrams, 535. https://ui.adsabs.harvard.edu/abs/2006CBET..535....1T/abstract [2] Taylor, P. A., Margot, J. L., Nolan, M. C., Benner, L. A. M., Ostro, S. J., Giorgini, J. D., &amp; Magri, C. (2006). Radar imaging of binary near-Earth Asteroid 2004 DC. Bulletin of the American Astronomical Society, 38, 577. https://ui.adsabs.harvard.edu/abs/2006DPS....38.5004T/abstract</t>
         </is>
       </c>
       <c r="P307" t="inlineStr">
@@ -20420,7 +20420,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>[1] (2012). 2. , 3091, 1. https://ui.adsabs.harvard.edu/abs/2012CBET.3091....1T/abstract</t>
+          <t>[1] (2012). 2004 FG11. Central Bureau Electronic Telegrams, 3091. https://ui.adsabs.harvard.edu/abs/2012CBET.3091....1T/abstract</t>
         </is>
       </c>
       <c r="P310" t="inlineStr">
@@ -21690,7 +21690,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>[1] (2012). R. , 44, 302.05. https://ui.adsabs.harvard.edu/abs/2012DPS....4430205B/abstract</t>
+          <t>[1] Busch, M. W., et al. (2012). Radar Imaging Of 11066 Sigurd, 2000 YF29, And 2004 XL14 And The Obliquity Distribution Of Contact Binary Near-Earth Asteroids. AAS/DPS Meeting #44, 302.05. https://ui.adsabs.harvard.edu/abs/2012DPS....4430205B/abstract</t>
         </is>
       </c>
       <c r="P331" t="inlineStr">
@@ -24080,7 +24080,7 @@
       </c>
       <c r="O371" t="inlineStr">
         <is>
-          <t>[1] (2011). Preparing for asteroid 2005 YU55 at close quarters. Astronomy &amp;amp; Geophysics, 52, 3.06-3.06. https://doi.org/10.1111/j.1468-4004.2011.52304_10.x [2] Vereshchagina, I. A., Sokov, E. N., Gorshanov, D. L., Devyatkin, A. V., L’vov, V. N., Tsekmeister, S. D., Romas, E. S., &amp; Martyusheva, A. A. (2014). Astrometry and photometry of asteroid (308635) 2005 YU55. Solar System Research, 48, 382-390. https://doi.org/10.1134/s0038094614040108</t>
+          <t>[1] (2011). Preparing for asteroid 2005 YU55 at close quarters. Astronomy &amp; Geophysics, 52, 3.06. https://doi.org/10.1111/j.1468-4004.2011.52304_10.x [2] Vereshchagina, I. A., Sokov, E. N., Gorshanov, D. L., Devyatkin, A. V., L’vov, V. N., Tsekmeister, S. D., Romas, E. S., &amp; Martyusheva, A. A. (2014). Astrometry and photometry of asteroid (308635) 2005 YU55. Solar System Research, 48, 382-390. https://doi.org/10.1134/s0038094614040108</t>
         </is>
       </c>
       <c r="P371" t="inlineStr">
@@ -24510,7 +24510,7 @@
       </c>
       <c r="O378" t="inlineStr">
         <is>
-          <t>[1] (2006). 2. , 534, 1. https://ui.adsabs.harvard.edu/abs/2006CBET..534....1B/abstract</t>
+          <t>[1] (2006). 2006 GY2. Central Bureau Electronic Telegrams, 534. https://ui.adsabs.harvard.edu/abs/2006CBET..534....1B/abstract</t>
         </is>
       </c>
       <c r="P378" t="inlineStr">
@@ -25170,7 +25170,7 @@
       </c>
       <c r="O389" t="inlineStr">
         <is>
-          <t>[1] (2025). L. , 52, 100. https://ui.adsabs.harvard.edu/abs/2025MPBu...52..100N/abstract</t>
+          <t>[1] (2025). Lightcurve Analysis and Rotation Period for NEA 2006 WB. Minor Planet Bulletin, 52, 100. https://ui.adsabs.harvard.edu/abs/2025MPBu...52..100N/abstract</t>
         </is>
       </c>
       <c r="P389" t="inlineStr">
@@ -27325,7 +27325,7 @@
       </c>
       <c r="O424" t="inlineStr">
         <is>
-          <t>[1] (2017). S. , 230, 119.01. https://ui.adsabs.harvard.edu/abs/2017AAS...23011901V/abstract</t>
+          <t>[1] Quijano Vodniza, A. (2017). Study of the Asteroid 2009 DL46. AAS Meeting #230, 119.01. https://ui.adsabs.harvard.edu/abs/2017AAS...23011901V/abstract</t>
         </is>
       </c>
       <c r="P424" t="inlineStr">
@@ -28975,7 +28975,7 @@
       </c>
       <c r="O449" t="inlineStr">
         <is>
-          <t>[1] (2016). (. , 4304, 1. https://ui.adsabs.harvard.edu/abs/2016CBET.4304....1G/abstract</t>
+          <t>[1] (2016). (441987) 2010 NY_65. Central Bureau Electronic Telegrams, 4304. https://ui.adsabs.harvard.edu/abs/2016CBET.4304....1G/abstract</t>
         </is>
       </c>
       <c r="P449" t="inlineStr">
@@ -37220,7 +37220,7 @@
       </c>
       <c r="O597" t="inlineStr">
         <is>
-          <t>[1] (2020). 2. , 4786, 1. https://ui.adsabs.harvard.edu/abs/2020CBET.4786....1G/abstract</t>
+          <t>[1] (2020). 2015 EG. Central Bureau Electronic Telegrams, 4786. https://ui.adsabs.harvard.edu/abs/2020CBET.4786....1G/abstract</t>
         </is>
       </c>
       <c r="P597" t="inlineStr">
@@ -37675,7 +37675,7 @@
       </c>
       <c r="O605" t="inlineStr">
         <is>
-          <t>[1] (2015). A. , 47, 402.05. https://ui.adsabs.harvard.edu/abs/2015DPS....4740205B/abstract</t>
+          <t>[1] (2015). Asteroids With Tensile Strength: The Case of 2015 HM10. AAS/DPS Meeting #47, 402.05. https://ui.adsabs.harvard.edu/abs/2015DPS....4740205B/abstract</t>
         </is>
       </c>
       <c r="P605" t="inlineStr">
@@ -39075,7 +39075,7 @@
       </c>
       <c r="O629" t="inlineStr">
         <is>
-          <t>[1] Müller, T. G., Marciniak, A., Butkiewicz-Bąk, M., Duffard, R., Oszkiewicz, D., Käufl, H. U., Szakáts, R., Santana-Ros, T., Kiss, C., &amp; Santos-Sanz, P. (2017). Large Halloween asteroid at lunar distance. Astronomy &amp;amp; Astrophysics, 598, A63. https://doi.org/10.1051/0004-6361/201629584 [2] R. et al. (2016). Bulletin of the American Astronomical Society (DPS meeting abstract), Vol. 4832910. [ADS record] https://ui.adsabs.harvard.edu/abs/2016DPS....4832910R/abstract [3] Busch, M. W., et al. (2016). Recent radar observations of potentially hazardous near-Earth asteroids with the Arecibo Observatory and the Deep Space Network. AGU Fall Meeting, abstract NH12A-06. https://ui.adsabs.harvard.edu/abs/2016AGUFMNH12A..06B/abstract</t>
+          <t>[1] Müller, T. G., Marciniak, A., Butkiewicz-Bąk, M., Duffard, R., Oszkiewicz, D., Käufl, H. U., Szakáts, R., Santana-Ros, T., Kiss, C., &amp; Santos-Sanz, P. (2017). Large Halloween asteroid at lunar distance. Astronomy &amp;amp; Astrophysics, 598, A63. https://doi.org/10.1051/0004-6361/201629584 [2] Rivera-Valentin, E. G., et al. (2016). Radar observations of near-Earth asteroids from Arecibo Observatory. AAS/DPS Meeting #48, 329.10. https://ui.adsabs.harvard.edu/abs/2016DPS....4832910R/abstract [3] Busch, M. W., et al. (2016). Recent radar observations of potentially hazardous near-Earth asteroids with the Arecibo Observatory and the Deep Space Network. AGU Fall Meeting, abstract NH12A-06. https://ui.adsabs.harvard.edu/abs/2016AGUFMNH12A..06B/abstract</t>
         </is>
       </c>
       <c r="P629" t="inlineStr">
@@ -44295,7 +44295,7 @@
       </c>
       <c r="O727" t="inlineStr">
         <is>
-          <t>[1] (2024). R. , 5, 123. https://doi.org/10.3847/PSJ/ad4342</t>
+          <t>[1] Brozovic, M., Benner, L.A.M., Naidu, S.P., Moskovitz, N., Giorgini, J.D., Virkki, A.K., Marshall, S.E., &amp; Dover, L.R. (2024). Radar and Optical Observations and Physical Modeling of Binary Near-Earth Asteroid 2018 EB. The Planetary Science Journal, 5, 123. https://doi.org/10.3847/PSJ/ad4342</t>
         </is>
       </c>
       <c r="P727" t="inlineStr">
@@ -49960,7 +49960,7 @@
       </c>
       <c r="O837" t="inlineStr">
         <is>
-          <t>[1] (2021). 2. , 53, 207.01. https://ui.adsabs.harvard.edu/abs/2021DPS....5320701Z/abstract</t>
+          <t>[1] Zambrano-Marin, L. F., Marshall, S. E., Howell, E. S., de León, J., Pinilla-Alonso, N., Virkki, A. K., Giorgini, J., &amp; Venditti, F. C. F. (2025). 2020 BX12-The Last Binary Asteroid Discovered at Arecibo. The Planetary Science Journal, 6, 91. https://doi.org/10.3847/PSJ/adbe39</t>
         </is>
       </c>
       <c r="P837" t="inlineStr">
@@ -51420,7 +51420,7 @@
       </c>
       <c r="O866" t="inlineStr">
         <is>
-          <t>[1] (2020). A. , 52, 512.07. https://ui.adsabs.harvard.edu/abs/2020DPS....5251207V/abstract</t>
+          <t>[1] Venditti, F., Marshall, S., Virkki, A., Taylor, P., Hickson, D., &amp; Giorgini, J. (2020). Arecibo Observatory radar observation of potentially hazardous asteroid 2020 NK1. AAS/DPS Meeting #52, 512.07. https://ui.adsabs.harvard.edu/abs/2020DPS....5251207V/abstract</t>
         </is>
       </c>
       <c r="P866" t="inlineStr">
@@ -52310,7 +52310,7 @@
       </c>
       <c r="O883" t="inlineStr">
         <is>
-          <t>[1] (1997). T. , 114, 402. https://doi.org/10.1086/118484</t>
+          <t>[1] Hilton, J.L. (1997). The Mass of the Asteroid 15 Eunomia From Observations of 1313 Berna and 1284 Latvia. The Astronomical Journal, 114, 402. https://doi.org/10.1086/118484</t>
         </is>
       </c>
       <c r="P883" t="inlineStr">
@@ -52945,7 +52945,7 @@
       </c>
       <c r="O894" t="inlineStr">
         <is>
-          <t>[1] (2008). R. , 195, 220. https://doi.org/10.1016/j.icarus.2007.12.018 [2] Reddy, V., J.A. Sanchez, W.F. Bottke, A. Thirouin, E.G. Rivera-Valentin, M.S. Kelley, W. Ryan, E.A. Cloutis, S.C. Tegler, E.V. Ryan, P.A. Taylor, J.E. Richardson, N. Moskovitz, and L. Le Corre, Physical Characterization of 2-m Diameter Near-Earth Asteroid 2015 TC25: A Possible Boulder from E-type Asteroid (44) Nysa, Astronomical Journal 152, 162, 2016 http://dx.doi.org/10.3847/0004-6256/152/6/162</t>
+          <t>[1] Shepard, M.K., Kressler, K.M., Clark, B.E., Ockert-Bell, M.E., Nolan, M.C., Howell, E.S., Magri, C., &amp; Giorgini, J.D. (2008). Radar observations of E-class Asteroids 44 Nysa and 434 Hungaria. Icarus, 195, 220-225. https://doi.org/10.1016/j.icarus.2007.12.018 [2] Reddy, V., J.A. Sanchez, W.F. Bottke, A. Thirouin, E.G. Rivera-Valentin, M.S. Kelley, W. Ryan, E.A. Cloutis, S.C. Tegler, E.V. Ryan, P.A. Taylor, J.E. Richardson, N. Moskovitz, and L. Le Corre, Physical Characterization of 2-m Diameter Near-Earth Asteroid 2015 TC25: A Possible Boulder from E-type Asteroid (44) Nysa, Astronomical Journal 152, 162, 2016 http://dx.doi.org/10.3847/0004-6256/152/6/162</t>
         </is>
       </c>
       <c r="P894" t="inlineStr">
@@ -55755,7 +55755,7 @@
       </c>
       <c r="O945" t="inlineStr">
         <is>
-          <t>[1] (1997). P. , 29, 05.08. https://ui.adsabs.harvard.edu/abs/1997DPS....29.0508O/abstract</t>
+          <t>[1] Ostro, S. J., et al. (1997). Radar Observations of 253 Mathilde. AAS/DPS Meeting #29, 05.08. https://ui.adsabs.harvard.edu/abs/1997DPS....29.0508O/abstract</t>
         </is>
       </c>
       <c r="P945" t="inlineStr">
@@ -56905,7 +56905,7 @@
       </c>
       <c r="O966" t="inlineStr">
         <is>
-          <t>[1] Shepard, M. K., Kressler, K. M., Clark, B. E., Ockert-Bell, M. E., Nolan, M. C., Howell, E. S., Magri, C., Giorgini, J. D., Benner, L. A. M., &amp; Ostro, S. J. (2008). Radar observations of E-class Asteroids 44 Nysa and 434 Hungaria. Icarus, 195, 220-225. https://doi.org/10.1016/j.icarus.2007.12.018 [2] Shepard, M. K., Harris, A. W., Taylor, P. A., Clark, B. E., Ockert-Bell, M., Nolan, M. C., Howell, E. S., Magri, C., Giorgini, J. D., &amp; Benner, L. A. M. (2011). Radar observations of Asteroids 64 Angelina and 69 Hesperia. Icarus, 215, 547-551. https://doi.org/10.1016/j.icarus.2011.07.027</t>
+          <t>[1] Shepard, M.K., Kressler, K.M., Clark, B.E., Ockert-Bell, M.E., Nolan, M.C., Howell, E.S., Magri, C., &amp; Giorgini, J.D. (2008). Radar observations of E-class Asteroids 44 Nysa and 434 Hungaria. Icarus, 195, 220-225. https://doi.org/10.1016/j.icarus.2007.12.018 [2] Shepard, M. K., Harris, A. W., Taylor, P. A., Clark, B. E., Ockert-Bell, M., Nolan, M. C., Howell, E. S., Magri, C., Giorgini, J. D., &amp; Benner, L. A. M. (2011). Radar observations of Asteroids 64 Angelina and 69 Hesperia. Icarus, 215, 547-551. https://doi.org/10.1016/j.icarus.2011.07.027</t>
         </is>
       </c>
       <c r="P966" t="inlineStr">
@@ -58385,7 +58385,7 @@
       </c>
       <c r="O993" t="inlineStr">
         <is>
-          <t>[1] (1983). C. , 3832, 1. https://ui.adsabs.harvard.edu/abs/1983IAUC.3832....1W/abstract</t>
+          <t>[1] (1983). Comet Sugano-Saigusa-Fujikawa (1983e). IAU Circular, 3832. https://ui.adsabs.harvard.edu/abs/1983IAUC.3832....1W/abstract</t>
         </is>
       </c>
       <c r="P993" t="inlineStr">

--- a/FINAL_LIST_2026.xlsx
+++ b/FINAL_LIST_2026.xlsx
@@ -790,7 +790,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>[1] Ostro, S. J., Jurgens, R. F., Rosema, K. D., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., Shapiro, I. I., Hine, A. A., &amp; Velez, R. (1991). Asteroid radar astrometry. The Astronomical Journal, 102, 1490. https://doi.org/10.1086/115975 [2] Ostro, S. (2002). Radar Observations of Asteroid 1862 Apollo. Icarus, 156, 580-583. https://doi.org/10.1006/icar.2001.6805 [3] Taylor, P., Howell, E. S., Nolan, M. C., Benner, L. A. M., Brozović, M., Giorgini, J. D., Vervack, R. J., Fernández, Y. R., Magri, C., &amp; Mueller, M. (2010). Characterization of Near-Earth Asteroid 2009 KC3 from Radar and Thermal Infrared Observations. Data Archiving and Networked Services (DANS). [4] Borisov, G., Devogèle, M., Cellino, A., Bagnulo, S., Christou, A., Bendjoya, P., Rivet, J. P., Abe, L., Vernet, D., Donchev, Z., Krugly, Y., Belskaya, I., Bonev, T., Steeghs, D., Galloway, D., et al. (2018). Rotational variation of the linear polarization of the asteroid (3200) Phaethon as evidence for inhomogeneity in its surface properties. Monthly Notices of the Royal Astronomical Society: Letters, 480, L131-L135. https://doi.org/10.1093/mnrasl/sly140 [5] McGlasson, R., Marshall, S., Venditti, F., Benner, L., Brozović, M., Naidu, S. P., Giorgini, J. D., Aponte, B., Harris, A. W., Young, J., Wells, G., Bamberger, D., &amp; Tobak, J. (2019). Shape Model of Potentially Hazardous Asteroid (1981) Midas from Radar and Lightcurve Observations. DigitalCommons-Macalester (Macalester College). [6] Lazzarin, M., La Forgia, F., Siviero, A., Ochner, P., Frattin, E., Pravec, P., &amp; Fatka, P. (2020). Spectroscopic investigation of the large Potentially Hazardous Asteroid (52768) 1998OR2 within NEOROCKS EU project. https://doi.org/10.5194/epsc2020-974 [7] McGlasson, R. A., Marshall, S. E., Venditti, F. C. F., Naidu, S. P., Benner, L. A. M., Brozović, M., Giorgini, J. D., Taylor, P. A., Aponte, B., Virkki, A. K., Harris, A. W., Young, J. W., Husárik, M., Wells, G., Bamberger, D., et al. (2022). Radar and Lightcurve Observations and a Physical Model of Potentially Hazardous Asteroid 1981 Midas. The Planetary Science Journal, 3, 35. https://doi.org/10.3847/psj/ac4963 [8] Kruzins, E., Benner, L., Boyce, R., Brown, M., Coward, D., Darwell, S., Edwards, P., Elizabeth-Glina, L., Giorgini, J., Horiuchi, S., Lambert, A., Lazio, J., Calves, G. M., Moore, J., Peters, E., et al. (2023). Deep space debris—Detection of potentially hazardous asteroids and objects from the southern hemisphere. Frontiers in Space Technologies, 4. https://doi.org/10.3389/frspt.2023.1162915</t>
+          <t>[1] Ostro, S. J., Jurgens, R. F., Rosema, K. D., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., Shapiro, I. I., Hine, A. A., &amp; Velez, R. (1991). Asteroid radar astrometry. The Astronomical Journal, 102, 1490. https://doi.org/10.1086/115975 [2] Ostro, S. (2002). Radar Observations of Asteroid 1862 Apollo. Icarus, 156, 580-583. https://doi.org/10.1006/icar.2001.6805</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>[1] (1937). Planet Hermes (1937 UB). Astronomische Nachrichten, 264, 359-360. https://doi.org/10.1002/asna.19372642103 [2] Rechen‐Institut (1937). Planet 1937 UB. Astronomische Nachrichten, 264, 343-344. https://doi.org/10.1002/asna.19372642008 [3] Gondolatsch, F. (1937). Objekt Reinmuth 1937 UB. Astronomische Nachrichten, 264, 213-214. https://doi.org/10.1002/asna.19372641203 [4] Wachmann, A. A. (1937). Reinmuthsches Objekt 1937 UB. Astronomische Nachrichten, 264, 295-296. https://doi.org/10.1002/asna.19372641704 [5] Gondolatsch, F. (1937). Neue Elemente des Objektes Reinmuth 1937 UB. Astronomische Nachrichten, 264, 229-230. https://doi.org/10.1002/asna.19372641306 [6] Gondolatsch, F. (1937). Neue Elemente des Reinmuthschen Objektes 1937 UB. Astronomische Nachrichten, 264, 183-184. https://doi.org/10.1002/asna.19372641005</t>
+          <t>[1] (1937). Planet Hermes (1937 UB). Astronomische Nachrichten, 264, 359-360. https://doi.org/10.1002/asna.19372642103 [2] Rechen‐Institut (1937). Planet 1937 UB. Astronomische Nachrichten, 264, 343-344. https://doi.org/10.1002/asna.19372642008 [3] Gondolatsch, F. (1937). Objekt Reinmuth 1937 UB. Astronomische Nachrichten, 264, 213-214. https://doi.org/10.1002/asna.19372641203 [4] Wachmann, A. A. (1937). Reinmuthsches Objekt 1937 UB. Astronomische Nachrichten, 264, 295-296. https://doi.org/10.1002/asna.19372641704 [5] Gondolatsch, F. (1937). Neue Elemente des Objektes Reinmuth 1937 UB. Astronomische Nachrichten, 264, 229-230. https://doi.org/10.1002/asna.19372641306 [6] Gondolatsch, F. (1937). Neue Elemente des Reinmuthschen Objektes 1937 UB. Astronomische Nachrichten, 264, 183-184. https://doi.org/10.1002/asna.19372641005 [7] Margot, J. L., Nolan, M. C., Negron, V., Hine, A. A., Campbell, D. B., Howell, E. S., Benner, L. A. M., Ostro, S. J., Giorgini, J. D., &amp; Marsden, B. G. (2003). 1937 UB (Hermes). IAU Circular, 8227. https://ui.adsabs.harvard.edu/abs/2003IAUC.8227....2M/abstract</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>[1] Ostro, S. J., Jurgens, R. F., Rosema, K. D., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., Shapiro, I. I., Hine, A. A., &amp; Velez, R. (1991). Asteroid radar astrometry. The Astronomical Journal, 102, 1490. https://doi.org/10.1086/115975 [2] Rożek, A. (2017). Understanding the influence of non-gravitational forces on the physical evolution of near-earth asteroids and comets. Kent Academic Repository (University of Kent). [3] Dover, L., Lowry, S., Rożek, A., Zegmott, T., Rozitis, B., Green, S., Snodgrass, C., Weissman, P., Krugly, Y., Belskaya, I., &amp; Brozović, M. (2024). Physical modelling of YORP-evolved NEA (23187) 2000 PN9 from optical and radar observations. https://doi.org/10.5194/epsc2020-825</t>
+          <t>[1] Ostro, S. J., Jurgens, R. F., Rosema, K. D., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., Shapiro, I. I., Hine, A. A., &amp; Velez, R. (1991). Asteroid radar astrometry. The Astronomical Journal, 102, 1490. https://doi.org/10.1086/115975 [2] Rożek, A. (2017). Understanding the influence of non-gravitational forces on the physical evolution of near-earth asteroids and comets. Kent Academic Repository (University of Kent). [3] Dover, L., Lowry, S., Rożek, A., Zegmott, T., Rozitis, B., Green, S., Snodgrass, C., Weissman, P., Krugly, Y., Belskaya, I., &amp; Brozović, M. (2024). Physical modelling of YORP-evolved NEA (23187) 2000 PN9 from optical and radar observations. https://doi.org/10.5194/epsc2020-825 [4] Rożek, A., Lowry, S. C., Rozitis, B., Green, S. F., Snodgrass, C., Weissman, P. R., Fitzsimmons, A., Hicks, M., Lawrence, K., Duddy, S. R., Wolters, S. D., Roberts-Borsani, G., Behrend, R., &amp; Manzini, F. (2019). Physical model of near-Earth asteroid (1917) Cuyo from ground-based optical and thermal-IR observations. Astronomy &amp; Astrophysics, 627, A172. https://doi.org/10.1051/0004-6361/201834162</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>[1] McGlasson, R., Marshall, S., Venditti, F., Benner, L., Brozović, M., Naidu, S. P., Giorgini, J. D., Aponte, B., Harris, A. W., Young, J., Wells, G., Bamberger, D., &amp; Tobak, J. (2019). Shape Model of Potentially Hazardous Asteroid (1981) Midas from Radar and Lightcurve Observations. DigitalCommons-Macalester (Macalester College). [2] McGlasson, R. A., Marshall, S. E., Venditti, F. C. F., Naidu, S. P., Benner, L. A. M., Brozović, M., Giorgini, J. D., Taylor, P. A., Aponte, B., Virkki, A. K., Harris, A. W., Young, J. W., Husárik, M., Wells, G., Bamberger, D., et al. (2022). Radar and Lightcurve Observations and a Physical Model of Potentially Hazardous Asteroid 1981 Midas. The Planetary Science Journal, 3, 35. https://doi.org/10.3847/psj/ac4963</t>
+          <t>[1] McGlasson, R., Marshall, S., Venditti, F., Benner, L., Brozović, M., Naidu, S. P., Giorgini, J. D., Aponte, B., Harris, A. W., Young, J., Wells, G., Bamberger, D., &amp; Tobak, J. (2019). Shape Model of Potentially Hazardous Asteroid (1981) Midas from Radar and Lightcurve Observations. American Astronomical Society Meeting Abstracts, 233, 255.03. https://ui.adsabs.harvard.edu/abs/2019AAS...23325503M/abstract [2] McGlasson, R. A., Marshall, S. E., Venditti, F. C. F., Naidu, S. P., Benner, L. A. M., Brozović, M., Giorgini, J. D., Taylor, P. A., Aponte, B., Virkki, A. K., Harris, A. W., Young, J. W., Husárik, M., Wells, G., Bamberger, D., et al. (2022). Radar and Lightcurve Observations and a Physical Model of Potentially Hazardous Asteroid 1981 Midas. The Planetary Science Journal, 3, 35. https://doi.org/10.3847/psj/ac4963</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>[1] Helin, E. F., &amp; Shoemaker, E. M. (1977). Discovery of asteroid 1976 AA. Icarus, 31, 415-419. https://doi.org/10.1016/0019-1035(77)90142-7 [2] Cruikshank, D. P., &amp; Jones, T. J. (1977). The diameter and albedo of asteroid 1976 AA. Icarus, 31, 427-429. https://doi.org/10.1016/0019-1035(77)90145-2 [3] Veeder, G. J., Matson, D. L., &amp; Hansen, O. L. (1977). Photometry of the asteroid 1976 AA at 0.56 and 2.2 μm. Icarus, 31, 424-426. https://doi.org/10.1016/0019-1035(77)90144-0 [4] Benner, L. A. M., Ostro, S. J., Giorgini, J. D., Jurgens, R. F., Mitchell, D. L., Rose, R., Rosema, K. D., Slade, M. A., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., &amp; Shapiro, I. I. (1997). Radar Detection of Near-Earth Asteroids 2062 Aten, 2101 Adonis, 3103 Eger, 4544 Xanthus, and 1992 QN. Icarus, 130, 296-312. https://doi.org/10.1006/icar.1997.5834 [5] Clark, B. E., Shepard, M. K., Bus, S. J., Vilas, F., Rivkin, A. S., Lim, L. F., Lederer, S. M., Jarvis, K. S., Shah, S., &amp; McConnochie, T. (2004). Multi-Wavelength Observations of Asteroid 2100 Ra-Shalom: Visible, Infrared, and Thermal Spectroscopy Results. NASA Technical Reports Server (NASA). [6] Kruzins, E., Benner, L., Boyce, R., Brown, M., Coward, D., Darwell, S., Edwards, P., Elizabeth-Glina, L., Giorgini, J., Horiuchi, S., Lambert, A., Lazio, J., Calves, G. M., Moore, J., Peters, E., et al. (2023). Deep space debris—Detection of potentially hazardous asteroids and objects from the southern hemisphere. Frontiers in Space Technologies, 4. https://doi.org/10.3389/frspt.2023.1162915 [7] Rivera-Valentín, E. G., Aponte-Hernández, B., Taylor, P. A., Nolan, M. C., Howell, E. S., Waller, D., Zambrano-Marín, L. F., Virkki, A. K., Ballouz, R. L., &amp; Stickle, A. M. (2024). Radar Circular Polarization Ratio of Near-Earth Asteroids: Links to Spectral Taxonomy and Surface Processes. The Planetary Science Journal, 5, 232. https://doi.org/10.3847/psj/ad7df1</t>
+          <t>[1] Helin, E. F., &amp; Shoemaker, E. M. (1977). Discovery of asteroid 1976 AA. Icarus, 31, 415-419. https://doi.org/10.1016/0019-1035(77)90142-7 [2] Cruikshank, D. P., &amp; Jones, T. J. (1977). The diameter and albedo of asteroid 1976 AA. Icarus, 31, 427-429. https://doi.org/10.1016/0019-1035(77)90145-2 [3] Veeder, G. J., Matson, D. L., &amp; Hansen, O. L. (1977). Photometry of the asteroid 1976 AA at 0.56 and 2.2 μm. Icarus, 31, 424-426. https://doi.org/10.1016/0019-1035(77)90144-0 [4] Benner, L. A. M., Ostro, S. J., Giorgini, J. D., Jurgens, R. F., Mitchell, D. L., Rose, R., Rosema, K. D., Slade, M. A., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., &amp; Shapiro, I. I. (1997). Radar Detection of Near-Earth Asteroids 2062 Aten, 2101 Adonis, 3103 Eger, 4544 Xanthus, and 1992 QN. Icarus, 130, 296-312. https://doi.org/10.1006/icar.1997.5834 [5] Rivera-Valentín, E. G., Aponte-Hernández, B., Taylor, P. A., Nolan, M. C., Howell, E. S., Waller, D., Zambrano-Marín, L. F., Virkki, A. K., Ballouz, R. L., &amp; Stickle, A. M. (2024). Radar Circular Polarization Ratio of Near-Earth Asteroids: Links to Spectral Taxonomy and Surface Processes. The Planetary Science Journal, 5, 232. https://doi.org/10.3847/psj/ad7df1</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>[1] Brozovic, M., Benner, L. A. M., Magri, C., Ostro, S. J., Scheeres, D. J., Giorgini, J. D., Nolan, M. C., Margot, J. L., Jurgens, R. F., &amp; Rose, R. (2010). Radar observations and a physical model of contact binary Asteroid 4486 Mithra. Icarus, 208, 207-220. https://doi.org/10.1016/j.icarus.2010.01.035 [2] Brozovic et al. (2010). Mithra [PDF]. https://echo.jpl.nasa.gov/asteroids/4486_Mithra/brozovic.etal.2010.mithra.pdf [3] Ostro, S. J., et al. (2000). Radar Observations of Asteroid 4486 Mithra. AAS/DPS Meeting #32, 08.07. https://ui.adsabs.harvard.edu/abs/2000DPS....32.0807O/abstract</t>
+          <t>[1] Brozovic, M., Benner, L. A. M., Magri, C., Ostro, S. J., Scheeres, D. J., Giorgini, J. D., Nolan, M. C., Margot, J. L., Jurgens, R. F., &amp; Rose, R. (2010). Radar observations and a physical model of contact binary Asteroid 4486 Mithra. Icarus, 208, 207-220. https://doi.org/10.1016/j.icarus.2010.01.035 [2] Brozović, M., Benner, L. A. M., Magri, C., Ostro, S. J., Scheeres, D. J., Giorgini, J. D., Nolan, M. C., Margot, J. L., Jurgens, R. F., &amp; Rose, R. (2010). Radar observations and a physical model of contact binary asteroid 4486 Mithra. Icarus, 208, 207-220. https://doi.org/10.1016/j.icarus.2010.01.035 [3] Ostro, S. J., et al. (2000). Radar Observations of Asteroid 4486 Mithra. AAS/DPS Meeting #32, 08.07. https://ui.adsabs.harvard.edu/abs/2000DPS....32.0807O/abstract</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>[1] Radar Observations of Binary Asteroid 5381 Sekhmet. (2003). Bulletin of the American Astronomical Society, 35, 1340. [First author initial "N" per ADS bibcode; full author list not independently verified.] https://ui.adsabs.harvard.edu/abs/2003AAS...20313402N/abstract</t>
+          <t>[1] Nolan, M. C., Howell, E. S., Rivkin, A. S., &amp; Neish, C. D. (2003). Radar Observations of Binary Asteroid 5381 Sekhmet. Bulletin of the American Astronomical Society, 35, 1340. https://ui.adsabs.harvard.edu/abs/2003AAS...20313402N/abstract</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>[1] Greenberg, A. H., Margot, J. L., Verma, A. K., Taylor, P. A., &amp; Hodge, S. E. (2020). Yarkovsky Drift Detections for 247 Near-Earth Asteroids. The Astronomical Journal, 159, 92. https://doi.org/10.3847/1538-3881/ab62a3</t>
+          <t>[1] Greenberg, A. H., Margot, J. L., Verma, A. K., Taylor, P. A., &amp; Hodge, S. E. (2020). Yarkovsky Drift Detections for 247 Near-Earth Asteroids. The Astronomical Journal, 159, 92. https://doi.org/10.3847/1538-3881/ab62a3 [2] Marshall, S. E., et al. (2015). Radar Observations of Near-Earth Asteroid (85989) 1999 JD6. DPS Meeting Abstracts, 47, 204.09. https://ui.adsabs.harvard.edu/abs/2015DPS....4720409M/abstract</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -21030,7 +21030,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>[1] Scheeres, D. J., Benner, L. A. M., Ostro, S. J., Rossi, A., Marzari, F., &amp; Washabaugh, P. (2005). Abrupt alteration of Asteroid 2004 MN4's spin state during its 2029 Earth flyby. Icarus, 178, 281-283. https://doi.org/10.1016/j.icarus.2005.06.002 [2] J., S. D., M., B. L. A., J., O. S., A., R., F., M., &amp; P., W. (2005). Abrupt alteration of asteroid 2004 MN4's spin state during its 2029 earth flyby. ISTI Open Portal. [3] Giorgini, J. D., Benner, L. A. M., Ostro, S. J., Nolan, M. C., &amp; Busch, M. W. (2008). Predicting the Earth encounters of (99942) Apophis. Icarus, 193, 1-19. https://doi.org/10.1016/j.icarus.2007.09.012 [4] Brozović, M., Benner, L. A. M., McMichael, J. G., Giorgini, J. D., Pravec, P., Scheirich, P., Magri, C., Busch, M. W., Jao, J. S., Lee, C. G., Snedeker, L. G., Silva, M. A., Slade, M. A., Semenov, B., Nolan, M. C., et al. (2018). Goldstone and Arecibo radar observations of (99942) Apophis in 2012–2013. Icarus, 300, 115-128. https://doi.org/10.1016/j.icarus.2017.08.032 [5] Ferrín, I., Arcila, A., &amp; Saldarriaga, M. (2018). Secular light curves of NEAs 2201 Oljato, 3200 Phaethon, 99942 Apophis, 162173 Ryugu, 495848 and 6063 Jason. Monthly Notices of the Royal Astronomical Society, 479, 3726-3745. https://doi.org/10.1093/mnras/sty1474 [6] Virkki, A., Venditti, F., Hickson, D., Perillat, P., Marshall, S., Taylor, P., &amp; Hèrique, A. (2020). Bistatic Arecibo Planetary Radar Observations of 99942 Apophis. LPI Contributions. [7] Herique, A., Plettemeier, D., &amp; Kofman, W. (2024). Radar Tomography of Asteroid Deep Interior - JuRa / HERA to Didymos and Ra proposed to APOPHIS. https://doi.org/10.5194/epsc2024-753 [8] Rivera-Valentín, E. G., Aponte-Hernández, B., Taylor, P. A., Nolan, M. C., Howell, E. S., Waller, D., Zambrano-Marín, L. F., Virkki, A. K., Ballouz, R. L., &amp; Stickle, A. M. (2024). Radar Circular Polarization Ratio of Near-Earth Asteroids: Links to Spectral Taxonomy and Surface Processes. The Planetary Science Journal, 5, 232. https://doi.org/10.3847/psj/ad7df1</t>
+          <t>[1] Scheeres, D. J., Benner, L. A. M., Ostro, S. J., Rossi, A., Marzari, F., &amp; Washabaugh, P. (2005). Abrupt alteration of Asteroid 2004 MN4's spin state during its 2029 Earth flyby. Icarus, 178, 281-283. https://doi.org/10.1016/j.icarus.2005.06.002 [2] Scheeres, D. J., Benner, L. A. M., Ostro, S. J., Rossi, A., Marzari, F., &amp; Washabaugh, P. (2005). Abrupt alteration of Asteroid 2004 MN4's spin state during its 2029 Earth flyby. Icarus, 178, 281-283. https://doi.org/10.1016/j.icarus.2005.06.002 [3] Giorgini, J. D., Benner, L. A. M., Ostro, S. J., Nolan, M. C., &amp; Busch, M. W. (2008). Predicting the Earth encounters of (99942) Apophis. Icarus, 193, 1-19. https://doi.org/10.1016/j.icarus.2007.09.012 [4] Brozović, M., Benner, L. A. M., McMichael, J. G., Giorgini, J. D., Pravec, P., Scheirich, P., Magri, C., Busch, M. W., Jao, J. S., Lee, C. G., Snedeker, L. G., Silva, M. A., Slade, M. A., Semenov, B., Nolan, M. C., et al. (2018). Goldstone and Arecibo radar observations of (99942) Apophis in 2012–2013. Icarus, 300, 115-128. https://doi.org/10.1016/j.icarus.2017.08.032 [5] Ferrín, I., Arcila, A., &amp; Saldarriaga, M. (2018). Secular light curves of NEAs 2201 Oljato, 3200 Phaethon, 99942 Apophis, 162173 Ryugu, 495848 and 6063 Jason. Monthly Notices of the Royal Astronomical Society, 479, 3726-3745. https://doi.org/10.1093/mnras/sty1474 [6] Virkki, A., Venditti, F., Hickson, D., Perillat, P., Marshall, S., Taylor, P., &amp; Hèrique, A. (2020). Bistatic Arecibo Planetary Radar Observations of 99942 Apophis. LPI Contributions. [7] Herique, A., Plettemeier, D., &amp; Kofman, W. (2024). Radar Tomography of Asteroid Deep Interior - JuRa / HERA to Didymos and Ra proposed to APOPHIS. https://doi.org/10.5194/epsc2024-753 [8] Rivera-Valentín, E. G., Aponte-Hernández, B., Taylor, P. A., Nolan, M. C., Howell, E. S., Waller, D., Zambrano-Marín, L. F., Virkki, A. K., Ballouz, R. L., &amp; Stickle, A. M. (2024). Radar Circular Polarization Ratio of Near-Earth Asteroids: Links to Spectral Taxonomy and Surface Processes. The Planetary Science Journal, 5, 232. https://doi.org/10.3847/psj/ad7df1</t>
         </is>
       </c>
       <c r="P320" t="inlineStr">

--- a/FINAL_LIST_2026.xlsx
+++ b/FINAL_LIST_2026.xlsx
@@ -655,7 +655,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>[1] Ostro, S. J., Jurgens, R. F., Rosema, K. D., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., Shapiro, I. I., Hine, A. A., &amp; Velez, R. (1991). Asteroid radar astrometry. The Astronomical Journal, 102, 1490. https://doi.org/10.1086/115975 [2] Crowell, J. L., Howell, E. S., Magri, C., Nolan, M. C., Fernández, Y. R., Richardson, J. E., Warner, B. D., Marshall, S. E., Springmann, A., &amp; Vervack, R. J. (2017). Radar and Lightcurve Shape Model of Near-Earth Asteroid (1627) Ivar. Icarus, 291, 254-267. https://doi.org/10.1016/j.icarus.2016.11.008 [3] Jones, J. (2018). Investigating compositional variations of S-complex near-Earth asteroids: (1627) Ivar. Journal of International Crisis and Risk Communication Research. [4] Ostro, S.J., D.B. Campbell, A.A. Hine, I.I. Shapiro, J.F. Chandler, C.L. Werner, and K.D. Rosema, Radar Images of Asteroid 1627 Ivar, Astronomical Journal 99, 2012-2018, 1990 http://dx.doi.org/10.1086/115482</t>
+          <t>[1] Ostro, S. J., Jurgens, R. F., Rosema, K. D., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., Shapiro, I. I., Hine, A. A., &amp; Velez, R. (1991). Asteroid radar astrometry. The Astronomical Journal, 102, 1490. https://doi.org/10.1086/115975 [2] Crowell, J. L., Howell, E. S., Magri, C., Nolan, M. C., Fernández, Y. R., Richardson, J. E., Warner, B. D., Marshall, S. E., Springmann, A., &amp; Vervack, R. J. (2017). Radar and Lightcurve Shape Model of Near-Earth Asteroid (1627) Ivar. Icarus, 291, 254-267. https://doi.org/10.1016/j.icarus.2016.11.008 [3] Ostro, S.J., D.B. Campbell, A.A. Hine, I.I. Shapiro, J.F. Chandler, C.L. Werner, and K.D. Rosema, Radar Images of Asteroid 1627 Ivar, Astronomical Journal 99, 2012-2018, 1990 http://dx.doi.org/10.1086/115482</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>[1] (1937). Planet Hermes (1937 UB). Astronomische Nachrichten, 264, 359-360. https://doi.org/10.1002/asna.19372642103 [2] Rechen‐Institut (1937). Planet 1937 UB. Astronomische Nachrichten, 264, 343-344. https://doi.org/10.1002/asna.19372642008 [3] Gondolatsch, F. (1937). Objekt Reinmuth 1937 UB. Astronomische Nachrichten, 264, 213-214. https://doi.org/10.1002/asna.19372641203 [4] Wachmann, A. A. (1937). Reinmuthsches Objekt 1937 UB. Astronomische Nachrichten, 264, 295-296. https://doi.org/10.1002/asna.19372641704 [5] Gondolatsch, F. (1937). Neue Elemente des Objektes Reinmuth 1937 UB. Astronomische Nachrichten, 264, 229-230. https://doi.org/10.1002/asna.19372641306 [6] Gondolatsch, F. (1937). Neue Elemente des Reinmuthschen Objektes 1937 UB. Astronomische Nachrichten, 264, 183-184. https://doi.org/10.1002/asna.19372641005 [7] Margot, J. L., Nolan, M. C., Negron, V., Hine, A. A., Campbell, D. B., Howell, E. S., Benner, L. A. M., Ostro, S. J., Giorgini, J. D., &amp; Marsden, B. G. (2003). 1937 UB (Hermes). IAU Circular, 8227. https://ui.adsabs.harvard.edu/abs/2003IAUC.8227....2M/abstract</t>
+          <t>[1] Margot, J. L., Nolan, M. C., Negron, V., Hine, A. A., Campbell, D. B., Howell, E. S., Benner, L. A. M., Ostro, S. J., Giorgini, J. D., &amp; Marsden, B. G. (2003). 1937 UB (Hermes). IAU Circular, 8227. https://ui.adsabs.harvard.edu/abs/2003IAUC.8227....2M/abstract</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>[1] Ostro, S. J., Jurgens, R. F., Rosema, K. D., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., Shapiro, I. I., Hine, A. A., &amp; Velez, R. (1991). Asteroid radar astrometry. The Astronomical Journal, 102, 1490. https://doi.org/10.1086/115975 [2] Ferrín, I., Arcila, A., &amp; Saldarriaga, M. (2018). Secular light curves of NEAs 2201 Oljato, 3200 Phaethon, 99942 Apophis, 162173 Ryugu, 495848 and 6063 Jason. Monthly Notices of the Royal Astronomical Society, 479, 3726-3745. https://doi.org/10.1093/mnras/sty1474</t>
+          <t>[1] Ostro, S. J., Jurgens, R. F., Rosema, K. D., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., Shapiro, I. I., Hine, A. A., &amp; Velez, R. (1991). Asteroid radar astrometry. The Astronomical Journal, 102, 1490. https://doi.org/10.1086/115975</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>[1] Ostro, S. J., Campbell, D. B., &amp; Shapiro, I. I. (1983). Radar observations of asteroid 1685 Toro. The Astronomical Journal, 88, 565. https://doi.org/10.1086/113345 [2] Ostro, S. J., Jurgens, R. F., Rosema, K. D., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., Shapiro, I. I., Hine, A. A., &amp; Velez, R. (1991). Asteroid radar astrometry. The Astronomical Journal, 102, 1490. https://doi.org/10.1086/115975 [3] Sannikova, T. N. (2021). Estimation of the Yarkovsky effect on the example of the asteroid 1685 Toro (1948 OA). Астрономия и исследование космического пространства: Всероссийская с международным участием научная конференция студентов и молодых ученых, посвященная памяти Полины Евгеньевны Захаровой, 182-185. https://doi.org/10.15826/b978-5-7996-3229-8.45</t>
+          <t>[1] Ostro, S. J., Campbell, D. B., &amp; Shapiro, I. I. (1983). Radar observations of asteroid 1685 Toro. The Astronomical Journal, 88, 565. https://doi.org/10.1086/113345 [2] Ostro, S. J., Jurgens, R. F., Rosema, K. D., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., Shapiro, I. I., Hine, A. A., &amp; Velez, R. (1991). Asteroid radar astrometry. The Astronomical Journal, 102, 1490. https://doi.org/10.1086/115975</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>[1] Shepard, M., Benner, L., Ostro, S., Campbell, D., Shapiro, I., &amp; Chandler, J. (2004). Radar detection of near-Earth Asteroids 1915 Quetzalcoatl, 3199 Nefertiti, 3757 (1982 XB), and 4034 (1986 PA). Icarus, 172, 170-178. https://doi.org/10.1016/j.icarus.2004.06.003 [2] Magri, C., Ostro, S. J., Scheeres, D. J., Nolan, M. C., Giorgini, J. D., Benner, L. A. M., &amp; Margot, J. L. (2007). Radar observations and a physical model of Asteroid 1580 Betulia. Icarus, 186, 152-177. https://doi.org/10.1016/j.icarus.2006.08.004 [3] Ockert-Bell, M. E., Clark, B. E., Shepard, M. K., Rivkin, A. S., Binzel, R. P., Thomas, C. A., DeMeo, F. E., Bus, S. J., &amp; Shah, S. (2008). Observations of X/M asteroids across multiple wavelengths. Icarus, 195, 206-219. https://doi.org/10.1016/j.icarus.2007.11.006 [4] Shepard, M. K., Clark, B. E., Nolan, M. C., Howell, E. S., Magri, C., Giorgini, J. D., Benner, L. A. M., Ostro, S. J., Harris, A. W., Warner, B., Pray, D., Pravec, P., Fauerbach, M., Bennett, T., Klotz, A., et al. (2008). A radar survey of M- and X-class asteroids. Icarus, 195, 184-205. https://doi.org/10.1016/j.icarus.2007.11.032 [5] Shepard, M.K., Kressler, K.M., Clark, B.E., Ockert-Bell, M.E., Nolan, M.C., Howell, E.S., Magri, C., &amp; Giorgini, J.D. (2008). Radar observations of E-class Asteroids 44 Nysa and 434 Hungaria. Icarus, 195, 220-225. https://doi.org/10.1016/j.icarus.2007.12.018 [6] Shepard, M. K., Clark, B. E., Ockert-Bell, M., Nolan, M. C., Howell, E. S., Magri, C., Giorgini, J. D., Benner, L. A. M., Ostro, S. J., Harris, A. W., Warner, B. D., Stephens, R. D., &amp; Mueller, M. (2010). A radar survey of M- and X-class asteroids II. Summary and synthesis. Icarus, 208, 221-237. https://doi.org/10.1016/j.icarus.2010.01.017 [7] Ockert-Bell, M. E., Clark, B. E., Shepard, M. K., Isaacs, R. A., Cloutis, E. A., Fornasier, S., &amp; Bus, S. J. (2010). The composition of M-type asteroids: Synthesis of spectroscopic and radar observations. Icarus, 210, 674-692. https://doi.org/10.1016/j.icarus.2010.08.002 [8] Shepard, M. K., Harris, A. W., Taylor, P. A., Clark, B. E., Ockert-Bell, M., Nolan, M. C., Howell, E. S., Magri, C., Giorgini, J. D., &amp; Benner, L. A. M. (2011). Radar observations of Asteroids 64 Angelina and 69 Hesperia. Icarus, 215, 547-551. https://doi.org/10.1016/j.icarus.2011.07.027 [9] Neeley, J. R., Clark, B. E., Ockert-Bell, M. E., Shepard, M. K., Conklin, J., Cloutis, E. A., Fornasier, S., &amp; Bus, S. J. (2014). The composition of M-type asteroids II: Synthesis of spectroscopic and radar observations. Icarus, 238, 37-50. https://doi.org/10.1016/j.icarus.2014.05.008 [10] Shepard, M. K., Taylor, P. A., Nolan, M. C., Howell, E. S., Springmann, A., Giorgini, J. D., Warner, B. D., Harris, A. W., Stephens, R., Merline, W. J., Rivkin, A., Benner, L. A. M., Coley, D., Clark, B. E., Ockert-Bell, M., et al. (2015). A radar survey of M- and X-class asteroids. III. Insights into their composition, hydration state, &amp;amp; structure. Icarus, 245, 38-55. https://doi.org/10.1016/j.icarus.2014.09.016 [11] Greenberg, A. H., Margot, J. L., Verma, A. K., Taylor, P. A., Naidu, S. P., Brozovic, M., &amp; Benner, L. A. M. (2017). Asteroid 1566 Icarus’s Size, Shape, Orbit, and Yarkovsky Drift from Radar Observations. The Astronomical Journal, 153, 108. https://doi.org/10.3847/1538-3881/153/3/108 [12] Greenberg, A. H., Margot, J. L., Verma, A. K., Taylor, P. A., &amp; Hodge, S. E. (2020). Yarkovsky Drift Detections for 247 Near-Earth Asteroids. The Astronomical Journal, 159, 92. https://doi.org/10.3847/1538-3881/ab62a3 [13] Skirmante, K., Bleiders, M., Jekabsons, N., Bezrukovs, V., &amp; Jasmonts, G. (2024). Observations of OH masers of comets in 1.6GHz frequency band using the Irbene RT32 radio telescope. https://doi.org/10.5194/epsc2020-171 [14] Medeiros, H., de León, J., Licandro, J., Popescu, M., &amp; Pinilla-Alonso, N. (2024). Physical characterization of near-Earth asteroid (159402) 1999 AP10 in support of the Arecibo Planetary Radar Program within the NEOROCKS project. https://doi.org/10.5194/epsc2021-783 [15] Ferrais, M., Marshall, S., Venditti, F., Devogèle, M., Pravec, P., Scheirich, P., &amp; Jehin, E. (2024). Shape model of the binary NEA (385186) 1994 AW1 from 2015 radar observations and long term lightcurve dataset.&amp;amp;#160;. https://doi.org/10.5194/epsc2024-161 [16] Howell, E., Vervack, R., Fernandez, Y., Myers, S., Hinkle, M., Magri, C., Marshall, S., &amp; Rivera-Valentin, E. (2025). Combining thermal and radar observations of near-Earth asteroids. https://doi.org/10.5194/epsc-dps2025-462 [17] MacLennan, E., Virkki, A., &amp; Marshall, S. (2025). Radar Shape Modeling of NEA (242643) 2005 NZ6: A Toutatis Twin?. https://doi.org/10.5194/epsc-dps2025-1476</t>
+          <t>[1] Shepard, M., Benner, L., Ostro, S., Campbell, D., Shapiro, I., &amp; Chandler, J. (2004). Radar detection of near-Earth Asteroids 1915 Quetzalcoatl, 3199 Nefertiti, 3757 (1982 XB), and 4034 (1986 PA). Icarus, 172, 170-178. https://doi.org/10.1016/j.icarus.2004.06.003 [2] Magri, C., Ostro, S. J., Scheeres, D. J., Nolan, M. C., Giorgini, J. D., Benner, L. A. M., &amp; Margot, J. L. (2007). Radar observations and a physical model of Asteroid 1580 Betulia. Icarus, 186, 152-177. https://doi.org/10.1016/j.icarus.2006.08.004 [3] Shepard, M. K., Clark, B. E., Nolan, M. C., Howell, E. S., Magri, C., Giorgini, J. D., Benner, L. A. M., Ostro, S. J., Harris, A. W., Warner, B., Pray, D., Pravec, P., Fauerbach, M., Bennett, T., Klotz, A., et al. (2008). A radar survey of M- and X-class asteroids. Icarus, 195, 184-205. https://doi.org/10.1016/j.icarus.2007.11.032 [4] Shepard, M.K., Kressler, K.M., Clark, B.E., Ockert-Bell, M.E., Nolan, M.C., Howell, E.S., Magri, C., &amp; Giorgini, J.D. (2008). Radar observations of E-class Asteroids 44 Nysa and 434 Hungaria. Icarus, 195, 220-225. https://doi.org/10.1016/j.icarus.2007.12.018 [5] Shepard, M. K., Clark, B. E., Ockert-Bell, M., Nolan, M. C., Howell, E. S., Magri, C., Giorgini, J. D., Benner, L. A. M., Ostro, S. J., Harris, A. W., Warner, B. D., Stephens, R. D., &amp; Mueller, M. (2010). A radar survey of M- and X-class asteroids II. Summary and synthesis. Icarus, 208, 221-237. https://doi.org/10.1016/j.icarus.2010.01.017 [6] Ockert-Bell, M. E., Clark, B. E., Shepard, M. K., Isaacs, R. A., Cloutis, E. A., Fornasier, S., &amp; Bus, S. J. (2010). The composition of M-type asteroids: Synthesis of spectroscopic and radar observations. Icarus, 210, 674-692. https://doi.org/10.1016/j.icarus.2010.08.002 [7] Shepard, M. K., Harris, A. W., Taylor, P. A., Clark, B. E., Ockert-Bell, M., Nolan, M. C., Howell, E. S., Magri, C., Giorgini, J. D., &amp; Benner, L. A. M. (2011). Radar observations of Asteroids 64 Angelina and 69 Hesperia. Icarus, 215, 547-551. https://doi.org/10.1016/j.icarus.2011.07.027 [8] Neeley, J. R., Clark, B. E., Ockert-Bell, M. E., Shepard, M. K., Conklin, J., Cloutis, E. A., Fornasier, S., &amp; Bus, S. J. (2014). The composition of M-type asteroids II: Synthesis of spectroscopic and radar observations. Icarus, 238, 37-50. https://doi.org/10.1016/j.icarus.2014.05.008 [9] Shepard, M. K., Taylor, P. A., Nolan, M. C., Howell, E. S., Springmann, A., Giorgini, J. D., Warner, B. D., Harris, A. W., Stephens, R., Merline, W. J., Rivkin, A., Benner, L. A. M., Coley, D., Clark, B. E., Ockert-Bell, M., et al. (2015). A radar survey of M- and X-class asteroids. III. Insights into their composition, hydration state, &amp;amp; structure. Icarus, 245, 38-55. https://doi.org/10.1016/j.icarus.2014.09.016 [10] Greenberg, A. H., Margot, J. L., Verma, A. K., Taylor, P. A., Naidu, S. P., Brozovic, M., &amp; Benner, L. A. M. (2017). Asteroid 1566 Icarus’s Size, Shape, Orbit, and Yarkovsky Drift from Radar Observations. The Astronomical Journal, 153, 108. https://doi.org/10.3847/1538-3881/153/3/108 [11] Greenberg, A. H., Margot, J. L., Verma, A. K., Taylor, P. A., &amp; Hodge, S. E. (2020). Yarkovsky Drift Detections for 247 Near-Earth Asteroids. The Astronomical Journal, 159, 92. https://doi.org/10.3847/1538-3881/ab62a3 [12] Medeiros, H., de León, J., Licandro, J., Popescu, M., &amp; Pinilla-Alonso, N. (2024). Physical characterization of near-Earth asteroid (159402) 1999 AP10 in support of the Arecibo Planetary Radar Program within the NEOROCKS project. https://doi.org/10.5194/epsc2021-783 [13] Ferrais, M., Marshall, S., Venditti, F., Devogèle, M., Pravec, P., Scheirich, P., &amp; Jehin, E. (2024). Shape model of the binary NEA (385186) 1994 AW1 from 2015 radar observations and long term lightcurve dataset.&amp;amp;#160;. https://doi.org/10.5194/epsc2024-161 [14] Howell, E., Vervack, R., Fernandez, Y., Myers, S., Hinkle, M., Magri, C., Marshall, S., &amp; Rivera-Valentin, E. (2025). Combining thermal and radar observations of near-Earth asteroids. https://doi.org/10.5194/epsc-dps2025-462 [15] MacLennan, E., Virkki, A., &amp; Marshall, S. (2025). Radar Shape Modeling of NEA (242643) 2005 NZ6: A Toutatis Twin?. https://doi.org/10.5194/epsc-dps2025-1476</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>[1] Busch, M., Giorgini, J., Ostro, S., Benner, L., Jurgens, R., Rose, R., Hicks, M., Pravec, P., Kusnirak, P., &amp; Ireland, M. (2007). Physical modeling of near-Earth Asteroid (29075) 1950 DA. Icarus, 190, 608-621. https://doi.org/10.1016/j.icarus.2007.03.032 [2] Farnocchia, D., &amp; Chesley, S. R. (2014). Assessment of the 2880 impact threat from Asteroid (29075) 1950 DA. Icarus, 229, 321-327. https://doi.org/10.1016/j.icarus.2013.09.022 [3] Hirabayashi, M., &amp; Scheeres, D. J. (2014). STRESS AND FAILURE ANALYSIS OF RAPIDLY ROTATING ASTEROID (29075) 1950 DA. The Astrophysical Journal, 798, L8. https://doi.org/10.1088/2041-8205/798/1/l8 [4] Rozitis, B., MacLennan, E., &amp; Emery, J. P. (2014). Cohesive forces prevent the rotational breakup of rubble-pile asteroid (29075) 1950 DA. Nature, 512, 174-176. https://doi.org/10.1038/nature13632 [5] Gundlach, B., &amp; Blum, J. (2015). Regolith grain size and cohesive strength of near-Earth Asteroid (29075) 1950 DA. Icarus, 257, 126-129. https://doi.org/10.1016/j.icarus.2015.04.032 [6] Giorgini, J. D., Ostro, S. J., Benner, L. A. M., Chodas, P. W., Chesley, S. R., Hudson, R. S., Nolan, M. C., Klemola, A. R., Standish, E. M., Jurgens, R. F., Rose, R., Chamberlin, A. B., Yeomans, D. K., &amp; Margot, J. L. (2002). Asteroid 1950 DA's Encounter with Earth in 2880: Physical Limits of Collision Probability Prediction. Science, 296(5565), 132-136. https://doi.org/10.1126/science.1068191</t>
+          <t>[1] Busch, M., Giorgini, J., Ostro, S., Benner, L., Jurgens, R., Rose, R., Hicks, M., Pravec, P., Kusnirak, P., &amp; Ireland, M. (2007). Physical modeling of near-Earth Asteroid (29075) 1950 DA. Icarus, 190, 608-621. https://doi.org/10.1016/j.icarus.2007.03.032 [2] Giorgini, J. D., Ostro, S. J., Benner, L. A. M., Chodas, P. W., Chesley, S. R., Hudson, R. S., Nolan, M. C., Klemola, A. R., Standish, E. M., Jurgens, R. F., Rose, R., Chamberlin, A. B., Yeomans, D. K., &amp; Margot, J. L. (2002). Asteroid 1950 DA's Encounter with Earth in 2880: Physical Limits of Collision Probability Prediction. Science, 296(5565), 132-136. https://doi.org/10.1126/science.1068191</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>[1] Ostro, S. J., Jurgens, R. F., Rosema, K. D., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., Shapiro, I. I., Hine, A. A., &amp; Velez, R. (1991). Asteroid radar astrometry. The Astronomical Journal, 102, 1490. https://doi.org/10.1086/115975 [2] Rożek, A. (2017). Understanding the influence of non-gravitational forces on the physical evolution of near-earth asteroids and comets. Kent Academic Repository (University of Kent). [3] Dover, L., Lowry, S., Rożek, A., Zegmott, T., Rozitis, B., Green, S., Snodgrass, C., Weissman, P., Krugly, Y., Belskaya, I., &amp; Brozović, M. (2024). Physical modelling of YORP-evolved NEA (23187) 2000 PN9 from optical and radar observations. https://doi.org/10.5194/epsc2020-825 [4] Rożek, A., Lowry, S. C., Rozitis, B., Green, S. F., Snodgrass, C., Weissman, P. R., Fitzsimmons, A., Hicks, M., Lawrence, K., Duddy, S. R., Wolters, S. D., Roberts-Borsani, G., Behrend, R., &amp; Manzini, F. (2019). Physical model of near-Earth asteroid (1917) Cuyo from ground-based optical and thermal-IR observations. Astronomy &amp; Astrophysics, 627, A172. https://doi.org/10.1051/0004-6361/201834162</t>
+          <t>[1] Ostro, S. J., Jurgens, R. F., Rosema, K. D., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., Shapiro, I. I., Hine, A. A., &amp; Velez, R. (1991). Asteroid radar astrometry. The Astronomical Journal, 102, 1490. https://doi.org/10.1086/115975 [2] Dover, L., Lowry, S., Rożek, A., Zegmott, T., Rozitis, B., Green, S., Snodgrass, C., Weissman, P., Krugly, Y., Belskaya, I., &amp; Brozović, M. (2024). Physical modelling of YORP-evolved NEA (23187) 2000 PN9 from optical and radar observations. https://doi.org/10.5194/epsc2020-825</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1658,11 +1658,6 @@
           <t>14.86</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>[1] Gehrels, T., Roemer, E., &amp; Marsden, B. G. (1971). Minor Planets and Related Objects. VIL Asteroid 1971 FA. The Astronomical Journal, 76, 607. https://doi.org/10.1086/111169</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>1985, 2015</t>
@@ -2148,11 +2143,6 @@
           <t>0.188 ± 0.070</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>[1] Rożek, A., Lowry, S. C., Rozitis, B., Dover, L. R., Taylor, P. A., Virkki, A., Green, S. F., Snodgrass, C., Fitzsimmons, A., Campbell-White, J., Sajadian, S., Bozza, V., Burgdorf, M. J., Dominik, M., Figuera Jaimes, R., et al. (2022). Physical properties of near-Earth asteroid (2102) Tantalus from multiwavelength observations. Monthly Notices of the Royal Astronomical Society, 515, 4551-4564. https://doi.org/10.1093/mnras/stac1835</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>1998, 2017(12)</t>
@@ -2225,7 +2215,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>[1] Helin, E. F., &amp; Shoemaker, E. M. (1977). Discovery of asteroid 1976 AA. Icarus, 31, 415-419. https://doi.org/10.1016/0019-1035(77)90142-7 [2] Cruikshank, D. P., &amp; Jones, T. J. (1977). The diameter and albedo of asteroid 1976 AA. Icarus, 31, 427-429. https://doi.org/10.1016/0019-1035(77)90145-2 [3] Veeder, G. J., Matson, D. L., &amp; Hansen, O. L. (1977). Photometry of the asteroid 1976 AA at 0.56 and 2.2 μm. Icarus, 31, 424-426. https://doi.org/10.1016/0019-1035(77)90144-0 [4] Benner, L. A. M., Ostro, S. J., Giorgini, J. D., Jurgens, R. F., Mitchell, D. L., Rose, R., Rosema, K. D., Slade, M. A., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., &amp; Shapiro, I. I. (1997). Radar Detection of Near-Earth Asteroids 2062 Aten, 2101 Adonis, 3103 Eger, 4544 Xanthus, and 1992 QN. Icarus, 130, 296-312. https://doi.org/10.1006/icar.1997.5834 [5] Rivera-Valentín, E. G., Aponte-Hernández, B., Taylor, P. A., Nolan, M. C., Howell, E. S., Waller, D., Zambrano-Marín, L. F., Virkki, A. K., Ballouz, R. L., &amp; Stickle, A. M. (2024). Radar Circular Polarization Ratio of Near-Earth Asteroids: Links to Spectral Taxonomy and Surface Processes. The Planetary Science Journal, 5, 232. https://doi.org/10.3847/psj/ad7df1</t>
+          <t>[1] Benner, L. A. M., Ostro, S. J., Giorgini, J. D., Jurgens, R. F., Mitchell, D. L., Rose, R., Rosema, K. D., Slade, M. A., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., &amp; Shapiro, I. I. (1997). Radar Detection of Near-Earth Asteroids 2062 Aten, 2101 Adonis, 3103 Eger, 4544 Xanthus, and 1992 QN. Icarus, 130, 296-312. https://doi.org/10.1006/icar.1997.5834 [2] Rivera-Valentín, E. G., Aponte-Hernández, B., Taylor, P. A., Nolan, M. C., Howell, E. S., Waller, D., Zambrano-Marín, L. F., Virkki, A. K., Ballouz, R. L., &amp; Stickle, A. M. (2024). Radar Circular Polarization Ratio of Near-Earth Asteroids: Links to Spectral Taxonomy and Surface Processes. The Planetary Science Journal, 5, 232. https://doi.org/10.3847/psj/ad7df1</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2308,11 +2298,6 @@
           <t>0.185 ± 0.035</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>[1] Senske, D. A., Campbell, D. B., Head, J. W., Fisher, P. C., Hine, A. A., deCharon, A., Frank, S. L., Keddie, S. T., Roberts, K. M., Stofan, E. R., Aubele, J. C., Crumpler, L. S., &amp; Stacy, N. (1991). Geology and tectonics of the Themis Regio-Lavinia Planitia-Alpha Regio-Lada Terra area, Venus: Results from Arecibo image data. Earth, Moon, and Planets, 55, 97-161. https://doi.org/10.1007/bf00058900</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>1983, 2014</t>
@@ -2470,7 +2455,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>[1] Ostro, S. J., Harris, A. W., Campbell, D. B., Shapiro, I. I., &amp; Young, J. W. (1984). Radar and photoelectric observations of asteroid 2100 Ra-Shalom. Icarus, 60, 391-403. https://doi.org/10.1016/0019-1035(84)90198-2 [2] Ostro, S. J., Jurgens, R. F., Rosema, K. D., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., Shapiro, I. I., Hine, A. A., &amp; Velez, R. (1991). Asteroid radar astrometry. The Astronomical Journal, 102, 1490. https://doi.org/10.1086/115975 [3] Kiselev, N. N., Rosenbush, V. K., &amp; Jockers, K. (1999). Polarimetry of Asteroid 2100 Ra-Shalom at Large Phase Angle. Icarus, 140, 464-466. https://doi.org/10.1006/icar.1999.6139 [4] Shepard, M. (2000). Radar Observations of Asteroid 2100 Ra-Shalom. Icarus, 147, 520-529. https://doi.org/10.1006/icar.2000.6470 [5] Shepard, M. K., Clark-Joseph, B. E., Benner, L. A. M., Giorgini, J. D., Kušnirák, P., Margot, J., Nolan, M. C., Ostro, S. J., Pravec, P., &amp; Šarounová, L. (2004). Multi-Wavelength Observations of 2100 Ra-Shalom: Radar and Lightcurves. . [6] Clark, B. E., Shepard, M. K., Bus, S. J., Vilas, F., Rivkin, A. S., Lim, L. F., Lederer, S. M., Jarvis, K. S., Shah, S., &amp; McConnochie, T. (2004). Multi-Wavelength Observations of Asteroid 2100 Ra-Shalom: Visible, Infrared, and Thermal Spectroscopy Results. NASA Technical Reports Server (NASA). [7] Shepard, M.K., B.E. Clark, M.C. Nolan, and 14 colleagues, Multi-Wavelength Observations of Asteroid 2100 Ra-Shalom, Icarus 193, 20-38, 2008 http://dx.doi.org/10.1016/j.icarus.2007.09.006</t>
+          <t>[1] Ostro, S. J., Harris, A. W., Campbell, D. B., Shapiro, I. I., &amp; Young, J. W. (1984). Radar and photoelectric observations of asteroid 2100 Ra-Shalom. Icarus, 60, 391-403. https://doi.org/10.1016/0019-1035(84)90198-2 [2] Ostro, S. J., Jurgens, R. F., Rosema, K. D., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., Shapiro, I. I., Hine, A. A., &amp; Velez, R. (1991). Asteroid radar astrometry. The Astronomical Journal, 102, 1490. https://doi.org/10.1086/115975 [3] Shepard, M. (2000). Radar Observations of Asteroid 2100 Ra-Shalom. Icarus, 147, 520-529. https://doi.org/10.1006/icar.2000.6470 [4] Shepard, M. K., Clark-Joseph, B. E., Benner, L. A. M., Giorgini, J. D., Kušnirák, P., Margot, J., Nolan, M. C., Ostro, S. J., Pravec, P., &amp; Šarounová, L. (2004). Multi-Wavelength Observations of 2100 Ra-Shalom: Radar and Lightcurves. . [5] Shepard, M.K., B.E. Clark, M.C. Nolan, and 14 colleagues, Multi-Wavelength Observations of Asteroid 2100 Ra-Shalom, Icarus 193, 20-38, 2008 http://dx.doi.org/10.1016/j.icarus.2007.09.006</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2550,7 +2535,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>[1] Ostro, S. J., Jurgens, R. F., Rosema, K. D., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., Shapiro, I. I., Hine, A. A., &amp; Velez, R. (1991). Asteroid radar astrometry. The Astronomical Journal, 102, 1490. https://doi.org/10.1086/115975 [2] Benner, L. (2002). Radar Observations of Asteroid 3908 Nyx. Icarus, 158, 379-388. https://doi.org/10.1006/icar.2002.6869 [3] Farnocchia, D., S.R. Chesley, D.J. Tholen, and M. Micheli, High Precision Predictions for Near-Earth Asteroids: The Strange Case of (3908) Nyx, Celestial Mechanics and Dynamical Astronomy 119, 301-312, 2014 http://dx.doi.org/10.1007/s10569-014-9536-9</t>
+          <t>[1] Ostro, S. J., Jurgens, R. F., Rosema, K. D., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., Shapiro, I. I., Hine, A. A., &amp; Velez, R. (1991). Asteroid radar astrometry. The Astronomical Journal, 102, 1490. https://doi.org/10.1086/115975 [2] Benner, L. (2002). Radar Observations of Asteroid 3908 Nyx. Icarus, 158, 379-388. https://doi.org/10.1006/icar.2002.6869</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -2700,7 +2685,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>[1] Ostro, S. J., Jurgens, R. F., Rosema, K. D., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., Shapiro, I. I., Hine, A. A., &amp; Velez, R. (1991). Asteroid radar astrometry. The Astronomical Journal, 102, 1490. https://doi.org/10.1086/115975 [2] Gaffey, M. J., Reed, K. L., &amp; Kelley, M. S. (1992). Relationship of E-type Apollo asteroid 3103 (1982 BB) to the enstatite achondrite meteorites and the Hungaria asteroids. Icarus, 100, 95-109. https://doi.org/10.1016/0019-1035(92)90021-x [3] Benner, L. A. M., Ostro, S. J., Giorgini, J. D., Jurgens, R. F., Mitchell, D. L., Rose, R., Rosema, K. D., Slade, M. A., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., &amp; Shapiro, I. I. (1997). Radar Detection of Near-Earth Asteroids 2062 Aten, 2101 Adonis, 3103 Eger, 4544 Xanthus, and 1992 QN. Icarus, 130, 296-312. https://doi.org/10.1006/icar.1997.5834</t>
+          <t>[1] Ostro, S. J., Jurgens, R. F., Rosema, K. D., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., Shapiro, I. I., Hine, A. A., &amp; Velez, R. (1991). Asteroid radar astrometry. The Astronomical Journal, 102, 1490. https://doi.org/10.1086/115975 [2] Benner, L. A. M., Ostro, S. J., Giorgini, J. D., Jurgens, R. F., Mitchell, D. L., Rose, R., Rosema, K. D., Slade, M. A., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., &amp; Shapiro, I. I. (1997). Radar Detection of Near-Earth Asteroids 2062 Aten, 2101 Adonis, 3103 Eger, 4544 Xanthus, and 1992 QN. Icarus, 130, 296-312. https://doi.org/10.1006/icar.1997.5834</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -2760,7 +2745,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>[1] Helin, E. F., Hulkower, N. D., &amp; Bender, D. F. (1984). The discovery of 1982 DB, the most accessible asteroid known. Icarus, 57, 42-47. https://doi.org/10.1016/0019-1035(84)90005-8 [2] Brozovic, M., Ostro, S. J., Benner, L. A. M., Giorgini, J. D., Jurgens, R. F., Rose, R., Nolan, M. C., Hine, A. A., Magri, C., Scheeres, D. J., &amp; Margot, J. L. (2009). Radar observations and a physical model of Asteroid 4660 Nereus, a prime space mission target. Icarus, 201, 153-166. https://doi.org/10.1016/j.icarus.2008.12.029 [3] Greenberg, A. H., Margot, J. L., Verma, A. K., Taylor, P. A., &amp; Hodge, S. E. (2020). Yarkovsky Drift Detections for 247 Near-Earth Asteroids. The Astronomical Journal, 159, 92. https://doi.org/10.3847/1538-3881/ab62a3</t>
+          <t>[1] Brozovic, M., Ostro, S. J., Benner, L. A. M., Giorgini, J. D., Jurgens, R. F., Rose, R., Nolan, M. C., Hine, A. A., Magri, C., Scheeres, D. J., &amp; Margot, J. L. (2009). Radar observations and a physical model of Asteroid 4660 Nereus, a prime space mission target. Icarus, 201, 153-166. https://doi.org/10.1016/j.icarus.2008.12.029 [2] Greenberg, A. H., Margot, J. L., Verma, A. K., Taylor, P. A., &amp; Hodge, S. E. (2020). Yarkovsky Drift Detections for 247 Near-Earth Asteroids. The Astronomical Journal, 159, 92. https://doi.org/10.3847/1538-3881/ab62a3</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -2965,7 +2950,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>[1] Hanuš, J., Vokrouhlický, D., Delbo’, M., Farnocchia, D., Polishook, D., Pravec, P., Hornoch, K., Kučáková, H., Kušnirák, P., Stephens, R., &amp; Warner, B. (2018). (3200) Phaethon: Bulk density from Yarkovsky drift detection. Astronomy &amp;amp; Astrophysics, 620, L8. https://doi.org/10.1051/0004-6361/201834228 [2] Borisov, G., Devogèle, M., Cellino, A., Bagnulo, S., Christou, A., Bendjoya, P., Rivet, J. P., Abe, L., Vernet, D., Donchev, Z., Krugly, Y., Belskaya, I., Bonev, T., Steeghs, D., Galloway, D., et al. (2018). Rotational variation of the linear polarization of the asteroid (3200) Phaethon as evidence for inhomogeneity in its surface properties. Monthly Notices of the Royal Astronomical Society: Letters, 480, L131-L135. https://doi.org/10.1093/mnrasl/sly140 [3] Ferrín, I., Arcila, A., &amp; Saldarriaga, M. (2018). Secular light curves of NEAs 2201 Oljato, 3200 Phaethon, 99942 Apophis, 162173 Ryugu, 495848 and 6063 Jason. Monthly Notices of the Royal Astronomical Society, 479, 3726-3745. https://doi.org/10.1093/mnras/sty1474 [4] Taylor, P. A., Rivera-Valentín, E. G., Benner, L. A. M., Marshall, S. E., Virkki, A. K., Venditti, F. C. F., Zambrano-Marin, L. F., Bhiravarasu, S. S., Aponte-Hernandez, B., Rodriguez Sanchez-Vahamonde, C., &amp; Giorgini, J. D. (2019). Arecibo radar observations of near-Earth asteroid (3200) Phaethon during the 2017 apparition. Planetary and Space Science, 167, 1-8. https://doi.org/10.1016/j.pss.2019.01.009 [5] Tabeshian, M., Wiegert, P., Ye, Q., Hui, M. T., Gao, X., &amp; Tan, H. (2019). Asteroid (3200) Phaethon: Colors, Phase Curve, Limits on Cometary Activity, and Fragmentation. The Astronomical Journal, 158, 30. https://doi.org/10.3847/1538-3881/ab245d [6] Marshall, S., Devogèle, M., Taylor, P., Magri, C., Beniyama, J., Sekiguchi, T., Kuroda, D., Urakawa, S., Yoshida, F., Arai, T., Warner, B. D., Pravec, P., Kučáková, H., Hornoch, K., &amp; Kušnirák, P. (2022). The changing rotation period of 3200 Phaethon. HAL (Le Centre pour la Communication Scientifique Directe). [7] Devogele, M., Venditti, F., Marshall, S., Zambrano Marin, L., Mcgilvrey, A., Virkki, A., Bendjoya, P., Rivet, J. P., Abe, L., Vernet, D., Jehin, E., &amp; Ferrais, M. (2022). Radar shape modeling and physical characterization of the PHA 1998 OR2. https://doi.org/10.5194/epsc2022-600</t>
+          <t>[1] Taylor, P. A., Rivera-Valentín, E. G., Benner, L. A. M., Marshall, S. E., Virkki, A. K., Venditti, F. C. F., Zambrano-Marin, L. F., Bhiravarasu, S. S., Aponte-Hernandez, B., Rodriguez Sanchez-Vahamonde, C., &amp; Giorgini, J. D. (2019). Arecibo radar observations of near-Earth asteroid (3200) Phaethon during the 2017 apparition. Planetary and Space Science, 167, 1-8. https://doi.org/10.1016/j.pss.2019.01.009</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3048,11 +3033,6 @@
           <t>0.297 ± 0.035</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>[1] Bell, J. F., Brown, R. H., &amp; Hawke, B. R. (1988). Composition and size of Apollo asteroid 1984 KB. Icarus, 73, 482-486. https://doi.org/10.1016/0019-1035(88)90057-7 [2] Ferrín, I., Arcila, A., &amp; Saldarriaga, M. (2018). Secular light curves of NEAs 2201 Oljato, 3200 Phaethon, 99942 Apophis, 162173 Ryugu, 495848 and 6063 Jason. Monthly Notices of the Royal Astronomical Society, 479, 3726-3745. https://doi.org/10.1093/mnras/sty1474 [3] Lazzarin, M., La Forgia, F., Siviero, A., Ochner, P., Frattin, E., Pravec, P., &amp; Fatka, P. (2020). Spectroscopic investigation of the large Potentially Hazardous Asteroid (52768) 1998OR2 within NEOROCKS EU project. https://doi.org/10.5194/epsc2020-974</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>2013, 2017(8)[8]</t>
@@ -3620,7 +3600,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>[1] Ostro, S. J., Choate, D., Dendrenos, P., Giorgini, J. D., Hills, D. L., Howard, D., Jurgens, R. F., Mitchell, D. L., Rose, R., Rosema, K. D., Slade, M. A., Strobert, D. R., Winkler, R., &amp; Yoemans, D. K. (1994). abstract) Asteroid Radar Astronomy at Goldstone in the 1990s. NASA Technical Reports Server (NASA). [2] Ostro, S. J., Hudson, R. S., Jurgens, R. F., Rosema, K. D., Campbell, D. B., Yeomans, D. K., Chandler, J. F., Giorgini, J. D., Winkler, R., Rose, R., Howard, S. D., Slade, M. A., Perillat, P., &amp; Shapiro, I. I. (1995). Radar Images of Asteroid 4179 Toutatis. Science, 270, 80-83. https://doi.org/10.1126/science.270.5233.80 [3] Quijano-Vodniza, A., &amp; P., M. R. (2017). The Asteroid 2014 JO25. DPS. [4] MacLennan, E., Virkki, A., &amp; Marshall, S. (2025). Radar Shape Modeling of NEA (242643) 2005 NZ6: A Toutatis Twin?. https://doi.org/10.5194/epsc-dps2025-1476 [5] Busch, M. W., et al. (2013). Goldstone/VLA Radar Observations of Near-Earth Asteroid 4179 Toutatis in 2012. AAS/DPS Meeting #45, 105.05. https://ui.adsabs.harvard.edu/abs/2013DPS....4510105B/abstract [6] Hudson, R. S., &amp; Ostro, S. J. (1996). Asteroid 4179 Toutatis: Potential of 1996 Radar Observations for Spin-State Refinement. AAS/DPS Meeting #28, 10.40. https://ui.adsabs.harvard.edu/abs/1996DPS....28.1040H/abstract [7] Ostro, S. J., et al. (1993). Radar Imaging of Asteroid 4179 Toutatis. Bulletin of the American Astronomical Society, 25. https://ui.adsabs.harvard.edu/abs/1993DPS....25.3407O/abstract [8] (1993). Toutatis. Space Flight, 35, 207. https://ui.adsabs.harvard.edu/abs/1993SpFl...35..207M/abstract [9] Ostro, S. J., Hudson, R. S., Rosema, K. D., Giorgini, J. D., Jurgens, R. F., Yeomans, D. K., Chodas, P. W., Winkler, R., Rose, R., Choate, D., Cormier, R. A., Kelley, D., Littlefair, R., Benner, L. A. M., Thomas, M. L., &amp; Slade, M. A. (1999). Asteroid 4179 Toutatis: 1996 Radar Observations. Icarus, 137, 122-139. https://doi.org/10.1006/icar.1998.6031 [10] Zhao, Y., Xiao, Z., Liu, W., Sun, J., Huang, B., &amp; Tang, C. (2016). Radar model fusion of asteroid (4179) Toutatis via its optical images observed by Chang'e-2 probe. Planetary and Space Science, 125, 87-95. https://doi.org/10.1016/j.pss.2016.03.008 [11] Hudson, R. S., &amp; Ostro, S. J. (1995). Shape and Non-Principal Axis Spin State of Asteroid 4179 Toutatis. Science, 270, 84-86. https://doi.org/10.1126/science.270.5233.84 [12] Takahashi, Y., M.W. Busch, and D.J. Scheeres, Spin State and Moment of Inertia Characterization of 4179 Toutatis, Astronomical Journal 146, 95, 2013 http://dx.doi.org/10.1088/0004-6256/146/4/95 [13] Hudson, R.S., S.J. Ostro, and D.J. Scheeres, High-Resolution Model of Asteroid 4179 Toutatis, Icarus 161, 346-355, 2003 http://dx.doi.org/10.1016/S0019-1035(02)00042-8</t>
+          <t>[1] Ostro, S. J., Choate, D., Dendrenos, P., Giorgini, J. D., Hills, D. L., Howard, D., Jurgens, R. F., Mitchell, D. L., Rose, R., Rosema, K. D., Slade, M. A., Strobert, D. R., Winkler, R., &amp; Yoemans, D. K. (1994). abstract) Asteroid Radar Astronomy at Goldstone in the 1990s. NASA Technical Reports Server (NASA). [2] Ostro, S. J., Hudson, R. S., Jurgens, R. F., Rosema, K. D., Campbell, D. B., Yeomans, D. K., Chandler, J. F., Giorgini, J. D., Winkler, R., Rose, R., Howard, S. D., Slade, M. A., Perillat, P., &amp; Shapiro, I. I. (1995). Radar Images of Asteroid 4179 Toutatis. Science, 270, 80-83. https://doi.org/10.1126/science.270.5233.80 [3] MacLennan, E., Virkki, A., &amp; Marshall, S. (2025). Radar Shape Modeling of NEA (242643) 2005 NZ6: A Toutatis Twin?. https://doi.org/10.5194/epsc-dps2025-1476 [4] Busch, M. W., et al. (2013). Goldstone/VLA Radar Observations of Near-Earth Asteroid 4179 Toutatis in 2012. AAS/DPS Meeting #45, 105.05. https://ui.adsabs.harvard.edu/abs/2013DPS....4510105B/abstract [5] Hudson, R. S., &amp; Ostro, S. J. (1996). Asteroid 4179 Toutatis: Potential of 1996 Radar Observations for Spin-State Refinement. AAS/DPS Meeting #28, 10.40. https://ui.adsabs.harvard.edu/abs/1996DPS....28.1040H/abstract [6] Ostro, S. J., et al. (1993). Radar Imaging of Asteroid 4179 Toutatis. Bulletin of the American Astronomical Society, 25. https://ui.adsabs.harvard.edu/abs/1993DPS....25.3407O/abstract [7] Ostro, S. J., Hudson, R. S., Rosema, K. D., Giorgini, J. D., Jurgens, R. F., Yeomans, D. K., Chodas, P. W., Winkler, R., Rose, R., Choate, D., Cormier, R. A., Kelley, D., Littlefair, R., Benner, L. A. M., Thomas, M. L., &amp; Slade, M. A. (1999). Asteroid 4179 Toutatis: 1996 Radar Observations. Icarus, 137, 122-139. https://doi.org/10.1006/icar.1998.6031 [8] Zhao, Y., Xiao, Z., Liu, W., Sun, J., Huang, B., &amp; Tang, C. (2016). Radar model fusion of asteroid (4179) Toutatis via its optical images observed by Chang'e-2 probe. Planetary and Space Science, 125, 87-95. https://doi.org/10.1016/j.pss.2016.03.008 [9] Hudson, R. S., &amp; Ostro, S. J. (1995). Shape and Non-Principal Axis Spin State of Asteroid 4179 Toutatis. Science, 270, 84-86. https://doi.org/10.1126/science.270.5233.84 [10] Takahashi, Y., M.W. Busch, and D.J. Scheeres, Spin State and Moment of Inertia Characterization of 4179 Toutatis, Astronomical Journal 146, 95, 2013 http://dx.doi.org/10.1088/0004-6256/146/4/95 [11] Hudson, R.S., S.J. Ostro, and D.J. Scheeres, High-Resolution Model of Asteroid 4179 Toutatis, Icarus 161, 346-355, 2003 http://dx.doi.org/10.1016/S0019-1035(02)00042-8</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4763,11 +4743,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>[1] Pravec, P., Wolf, M., &amp; Šarounová, L. (1998). Occultation/Eclipse Events in Binary Asteroid 1991 VH. Icarus, 133, 79-88. https://doi.org/10.1006/icar.1998.5890</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>2008, 2020[1]</t>
@@ -4928,11 +4903,6 @@
           <t>0.248 ± 0.046</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>[1] (2012). (5143) Heracles. Central Bureau Electronic Telegrams, 3176. https://ui.adsabs.harvard.edu/abs/2012CBET.3176....1T/abstract</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>2011, 2016(16)[16]</t>
@@ -5113,11 +5083,6 @@
           <t>0.380 ± 0.052</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>[1] Reddy, V., Gaffey, M. J., Abell, P. A., &amp; Hardersen, P. S. (2012). Constraining albedo, diameter and composition of near-Earth asteroids via near-infrared spectroscopy. Icarus, 219, 382-392. https://doi.org/10.1016/j.icarus.2012.03.005</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>2018(6)[6]</t>
@@ -5173,11 +5138,6 @@
           <t>17.89</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>[1] Volquardsen, E. L., Rivkin, A. S., &amp; Bus, S. J. (2007). Composition of hydrated near-Earth object (100085) 1992 UY4. Icarus, 187, 464-468. https://doi.org/10.1016/j.icarus.2006.10.034 [2] Duong, N. D. (n.d.). Shape modeling and boulder napping of asteroid 1992 UY4. https://doi.org/10.18297/honors/136</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>2005</t>
@@ -5713,11 +5673,6 @@
           <t>0.330 ± 0.170</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>[1] Taylor, P. A., et al. (2014). The Smallest Binary Asteroid? The Discovery of Equal-Mass Binary 1994 CJ1. AAS/DPS Meeting #46, 409.03. https://ui.adsabs.harvard.edu/abs/2014DPS....4640903T/abstract</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>2014</t>
@@ -6320,7 +6275,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>[1] Benner, L. A. M., et al. (2012). Radar Observations of Near-Earth Asteroid (175706) 1996 FG3. Lunar and Planetary Institute Contributions, 1667, 6403. https://ui.adsabs.harvard.edu/abs/2012LPICo1667.6403B/abstract [2] (2012). 1996 FG3, MarcoPolo-R mission target: Living on the edge. EPSC Abstracts, 7, 542. https://ui.adsabs.harvard.edu/abs/2012epsc.conf..542C/abstract</t>
+          <t>[1] Benner, L. A. M., et al. (2012). Radar Observations of Near-Earth Asteroid (175706) 1996 FG3. Lunar and Planetary Institute Contributions, 1667, 6403. https://ui.adsabs.harvard.edu/abs/2012LPICo1667.6403B/abstract</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -6445,7 +6400,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>[1] Naidu, S.P., Benner, L.A.M., Brozovic, M., Nolan, M.C., Ostro, S.J., Margot, J.L., Giorgini, J.D., &amp; Hirabayashi, T. (2020). Radar observations and a physical model of binary near-Earth asteroid 65803 Didymos, target of the DART mission. Icarus, 348, 113777. https://doi.org/10.1016/j.icarus.2020.113777 [2] Benner, L. A. M., et al. (2010). Radar Imaging and a Physical Model of Binary Asteroid 65803 Didymos. AAS/DPS Meeting #42, 13.17. https://ui.adsabs.harvard.edu/abs/2010DPS....42.1317B/abstract [3] Pajola, M., Barnouin, O.S., Lucchetti, A., Hirabayashi, M., Ballouz, R.-L., Asphaug, E., Ernst, C.M., &amp; Della Corte, V. (2022). Anticipated Geological Assessment of the (65803) Didymos-Dimorphos System, Target of the DART-LICIACube Mission. The Planetary Science Journal, 3, 210. https://doi.org/10.3847/PSJ/ac880d [4] Naidu, S. P., et al. (2016). Radar observations of binary near-Earth asteroid 65803 Didymos. AGU Fall Meeting, abstract P52B-02. https://ui.adsabs.harvard.edu/abs/2016AGUFM.P52B..02N/abstract [5] (2003). 65803 Didymos (1996 GT). IAU Circular, 8244. https://ui.adsabs.harvard.edu/abs/2003IAUC.8244....2P/abstract [6] Pajola, M., Barnouin, O. S., Lucchetti, A., Hirabayashi, M., Ballouz, R.-L., Asphaug, E., Ernst, C. M., Della Corte, V., Farnham, T., Poggiali, G., Sunshine, J. M., Epifani, E. M., Murdoch, N., Ieva, S., Schwartz, S. R., Ivanovski, S., Trigo-Rodriguez, J. M., Rossi, A., Chabot, N. L., Zinzi, A., Rivkin, A., Brucato, J. R., Michel, P., Cremonese, G., Dotto, E., Amoroso, M., Bertini, I., Capannolo, A., Cheng, A., Cotugno, B., Dall'Ora, M., Daly, R. T., Di Tana, V., Deshapriya, J. D. P., Gai, I., Hasselmann, P. H. A., Impresario, G., Lavagna, M., Meneghin, A., Miglioretti, F., Modenini, D., Palumbo, P., Perna, D., Pirrotta, S., Simioni, E., Simonetti, S., Tortora, P., Zannoni, M., and Zanotti, G., Anticipated Geological Assessment of the (65803) Didymos-Dimorphos System, Target of the DART-LICIACube Mission, The Planetary Science Journal, 3, p.210, 2022 https://ui.adsabs.harvard.edu/abs/2022PSJ.....3..210P</t>
+          <t>[1] Naidu, S.P., Benner, L.A.M., Brozovic, M., Nolan, M.C., Ostro, S.J., Margot, J.L., Giorgini, J.D., &amp; Hirabayashi, T. (2020). Radar observations and a physical model of binary near-Earth asteroid 65803 Didymos, target of the DART mission. Icarus, 348, 113777. https://doi.org/10.1016/j.icarus.2020.113777 [2] Benner, L. A. M., et al. (2010). Radar Imaging and a Physical Model of Binary Asteroid 65803 Didymos. AAS/DPS Meeting #42, 13.17. https://ui.adsabs.harvard.edu/abs/2010DPS....42.1317B/abstract [3] Naidu, S. P., et al. (2016). Radar observations of binary near-Earth asteroid 65803 Didymos. AGU Fall Meeting, abstract P52B-02. https://ui.adsabs.harvard.edu/abs/2016AGUFM.P52B..02N/abstract</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -6988,11 +6943,6 @@
           <t>0.210 (n=1)</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>[1] Milani, A., &amp; Valsecchi, G. B. (1999). Target Plane Confidence Boundaries: Mathematics of the 1997 XF11 Scare. Impact of Modern Dynamics in Astronomy, 369-370. https://doi.org/10.1007/978-94-011-4527-5_40</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>2016(2)[2]</t>
@@ -7810,7 +7760,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>[1] Battle, A., Reddy, V., Sanchez, J. A., Sharkey, B., Pearson, N., &amp; Bowen, B. (2022). Physical Characterization of Near-Earth Asteroid (52768) 1998 OR2: Evidence of Shock Darkening/Impact Melt. The Planetary Science Journal, 3, 226. https://doi.org/10.3847/psj/ac7223 [2] Devogele, M., Venditti, F., Marshall, S., Zambrano Marin, L., Mcgilvrey, A., Virkki, A., Bendjoya, P., Rivet, J. P., Abe, L., Vernet, D., Jehin, E., &amp; Ferrais, M. (2022). Radar shape modeling and physical characterization of the PHA 1998 OR2. https://doi.org/10.5194/epsc2022-600 [3] Husárik, M., &amp; Ivanova, O. (2022). Photometric results of two PHAs: (52768) 1998 OR2 and (99942) Apophis. https://doi.org/10.5194/epsc2022-671 [4] Емельяненко, В. В., &amp; Карташова, А. П. (2023). Comparison of the orbital evolution of near-Earth asteroids 52768 (1998 OR2) and 159402 (1999 AP10). Научные труды Института астрономии РАН, 8, 306-308. https://doi.org/10.51194/inasan.2023.8.6.010 [5] Devogèle, M., McGilvray, A., MacLennan, E., Monchinski, C., Marshall, S. E., Hickson, D., Virkki, A., Giorgini, J. D., Abe, L., Augustin, D., Aznar-Macías, A., Baudouin, P., Behrend, R., Bendjoya, P., Benkhaldoun, Z., Bosch, J., Cellino, A., Chatelain, J., Deldem, M., Ferrais, M., Goncalves, R., Houdin, G., Husárik, M., Jehin, E., Kareta, T., Kim, M.-J., Licandro, J., Lister, T., Medeiros, H., Pravec, P., Rivet, J.-P., Rousseau, G., Roh, D.-G., Skiff, B., Taylor, P. A., Venditti, F., Vernet, D., Vienney, J.-M., Yim, H.-S., and Zambrano-Marin, L., Surface Heterogeneity, Physical, and Shape Model of Near-Earth Asteroid (52768) 1998 OR2, The Planetary Science Journal, 5, p.44, 2024 https://ui.adsabs.harvard.edu/abs/2024PSJ.....5...44D</t>
+          <t>[1] Devogele, M., Venditti, F., Marshall, S., Zambrano Marin, L., Mcgilvrey, A., Virkki, A., Bendjoya, P., Rivet, J. P., Abe, L., Vernet, D., Jehin, E., &amp; Ferrais, M. (2022). Radar shape modeling and physical characterization of the PHA 1998 OR2. https://doi.org/10.5194/epsc2022-600 [2] Devogèle, M., McGilvray, A., MacLennan, E., Monchinski, C., Marshall, S. E., Hickson, D., Virkki, A., Giorgini, J. D., Abe, L., Augustin, D., Aznar-Macías, A., Baudouin, P., Behrend, R., Bendjoya, P., Benkhaldoun, Z., Bosch, J., Cellino, A., Chatelain, J., Deldem, M., Ferrais, M., Goncalves, R., Houdin, G., Husárik, M., Jehin, E., Kareta, T., Kim, M.-J., Licandro, J., Lister, T., Medeiros, H., Pravec, P., Rivet, J.-P., Rousseau, G., Roh, D.-G., Skiff, B., Taylor, P. A., Venditti, F., Vernet, D., Vienney, J.-M., Yim, H.-S., and Zambrano-Marin, L., Surface Heterogeneity, Physical, and Shape Model of Near-Earth Asteroid (52768) 1998 OR2, The Planetary Science Journal, 5, p.44, 2024 https://ui.adsabs.harvard.edu/abs/2024PSJ.....5...44D</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -7885,7 +7835,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>[1] Fieber-Beyer, S. K., Kareta, T., Reddy, V., &amp; Gaffey, M. J. (2020). Near-earth asteroid: (285263) 1998 QE2. Icarus, 347, 113807. https://doi.org/10.1016/j.icarus.2020.113807 [2] Myers, S. A., Howell, E. S., Magri, C., Vervack, R. J., Fernández, Y. R., Marshall, S. E., &amp; Taylor, P. A. (2023). Constraining the Limitations of NEATM-like Models: A Case Study with Near-Earth Asteroid (285263) 1998 QE2. The Planetary Science Journal, 4, 5. https://doi.org/10.3847/psj/aca89d [3] Venditti, F., &amp; Mota, M. L. (2024). The Dynamical Environment of Potentially Hazardous Binary Asteroid (285263) 1998 QE2. IAF Symposium on Planetary Defense and Near-Earth Objects, 30-36. https://doi.org/10.52202/078387-0005 [4] Deleon, A., Marshall, S., Becker, T., &amp; Venditti, F. (2025). Physical and Mutual Orbit Characteristics of Binary PHA 1998 QE2. https://doi.org/10.5194/epsc-dps2025-880 [5] Myers, S. A., Howell, E. S., Magri, C., Vervack, R. J., Fernández, Y. R., Marshall, S. E., and Taylor, P. A., Constraining the Limitations of NEATM-like Models: A Case Study with Near-Earth Asteroid (285263) 1998 QE2, The Planetary Science Journal, 4, p.5, 2023 https://ui.adsabs.harvard.edu/abs/2023PSJ.....4....5M</t>
+          <t>[1] Myers, S. A., Howell, E. S., Magri, C., Vervack, R. J., Fernández, Y. R., Marshall, S. E., &amp; Taylor, P. A. (2023). Constraining the Limitations of NEATM-like Models: A Case Study with Near-Earth Asteroid (285263) 1998 QE2. The Planetary Science Journal, 4, 5. https://doi.org/10.3847/psj/aca89d [2] Deleon, A., Marshall, S., Becker, T., &amp; Venditti, F. (2025). Physical and Mutual Orbit Characteristics of Binary PHA 1998 QE2. https://doi.org/10.5194/epsc-dps2025-880 [3] Myers, S. A., Howell, E. S., Magri, C., Vervack, R. J., Fernández, Y. R., Marshall, S. E., and Taylor, P. A., Constraining the Limitations of NEATM-like Models: A Case Study with Near-Earth Asteroid (285263) 1998 QE2, The Planetary Science Journal, 4, p.5, 2023 https://ui.adsabs.harvard.edu/abs/2023PSJ.....4....5M</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -8018,11 +7968,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>[1] (2003). (66063) 1998 RO1. IAU Circular, 8216. https://ui.adsabs.harvard.edu/abs/2003IAUC.8216....3P/abstract</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>2003, 2004</t>
@@ -8143,11 +8088,6 @@
           <t>0.05 km</t>
         </is>
       </c>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>[1] Bamberger, D., &amp; Wells, G. (2018). Detection of the Yarkovsky Effect on 1998 SD9 from Optical Observations. Research Notes of the AAS, 2, 164. https://doi.org/10.3847/2515-5172/aadf80</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>2018(7)[7]</t>
@@ -8428,11 +8368,6 @@
           <t>2.3017 h</t>
         </is>
       </c>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>[1] Galád, A. (2006). Lightcurves and Synodic Periods for Asteroids 1998 ST49, (13154) and (27529). Earth, Moon, and Planets, 100, 77-82. https://doi.org/10.1007/s11038-006-9099-1</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>2012</t>
@@ -9368,11 +9303,6 @@
           <t>19.57</t>
         </is>
       </c>
-      <c r="O132" t="inlineStr">
-        <is>
-          <t>[1] Pravec, P. (2000). Slowly Rotating Asteroid 1999 GU3. Icarus, 148, 589-593. https://doi.org/10.1006/icar.2000.6535</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>2002</t>
@@ -9578,11 +9508,6 @@
           <t>0.300 (n=1)</t>
         </is>
       </c>
-      <c r="O135" t="inlineStr">
-        <is>
-          <t>[1] Hicks, M., et al. (2013). Palomar Spectroscopy of Near-Earth Asteroids 137199 (1999 KX4), 152756 (1999 JV3), 163249 (2002 GT), 163364 (2002 OD20), and 285263 (1998 QE2). The Astronomer's Telegram, 5132. http://www.astronomerstelegram.org/?read=5132</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>2013</t>
@@ -9750,7 +9675,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>[1] Fahnestock, E. G., &amp; Scheeres, D. J. (2008). Simulation and analysis of the dynamics of binary near-Earth Asteroid (66391) 1999 KW4. Icarus, 194, 410-435. https://doi.org/10.1016/j.icarus.2007.11.007 [2] McMahon, J., &amp; Scheeres, D. (2010). Detailed prediction for the BYORP effect on binary near-Earth Asteroid (66391) 1999 KW4 and implications for the binary population. Icarus, 209, 494-509. https://doi.org/10.1016/j.icarus.2010.05.016 [3] Scheeres, D. J. (2012). Binary Asteroids: 1999 KW4. Orbital Motion in Strongly Perturbed Environments, 215-229. https://doi.org/10.1007/978-3-642-03256-1_9 [4] Shi, Y., Wang, Y., &amp; Xu, S. (2018). Equilibrium points and associated periodic orbits in the gravity of binary asteroid systems: (66391) 1999 KW4 as an example. Celestial Mechanics and Dynamical Astronomy, 130. https://doi.org/10.1007/s10569-018-9827-7 [5] Oliveira, T. C., &amp; Prado, A. F. B. A. (2020). Search for Stable Orbits around the Binary Asteroid Systems 1999 KW4 and Didymos. Revista Mexicana de Astronomía y Astrofísica, 56, 113-128. https://doi.org/10.22201/ia.01851101p.2020.56.01.12 [6] Reddy, V., Kelley, M. S., Dotson, J., Landis, R. R., McGraw, L. E., Micheli, M., Moskovitz, N. A., Sanchez, J. A., Taylor, P. A., Wheeler, L., Bauer, J. M., Brucker, M. J., Devogèle, M., Emery, J. P., Hainaut, O., et al. (2022). Near-earth asteroid (66391) Moshup (1999 KW4) observing campaign: Results from a global planetary defense characterization exercise. Icarus, 374, 114790. https://doi.org/10.1016/j.icarus.2021.114790 [7] Reddy, V., Kelley, M.S., Dotson, J., Landis, R.R., McGraw, L.E., Micheli, M., Moskovitz, N.A., Sanchez, J.A., Taylor, P.A., Wheeler, L., Bauer, J.M., Brucker, M.J., Devogele, M., Emery, J.P., Hainaut, O., Hickson, D.C., Koschny, D., Larsen, J.A., Marshall, S.E., Millan, R., Skiff, B.A., Venditti, F.C.F, Virkki, A.K., Yang, B. and Zambrano-Marin, L.F., Near-earth asteroid (66391) Moshup (1999 KW4) observing campaign: Results from a global planetary defense characterization exercise, Icarus, p.114790, 2021 https://www.sciencedirect.com/science/article/abs/pii/S0019103521004401 [8] Ostro, S.J., and 15 colleagues (including M.C. Nolan), Radar Imaging of Binary Near-Earth Asteroid (66391) 1999 KW4, Science 314, 1276-1280, 2006 http://dx.doi.org/10.1126/science.1133622 [9] Scheeres, D.J., and 15 colleagues (including M.C. Nolan), Dynamical Configuration of Binary Near-Earth Asteroid (66391) 1999 KW4, Science 314, 1280-1283, 2006 http://dx.doi.org/10.1126/science.1133599</t>
+          <t>[1] Scheeres, D. J. (2012). Binary Asteroids: 1999 KW4. Orbital Motion in Strongly Perturbed Environments, 215-229. https://doi.org/10.1007/978-3-642-03256-1_9 [2] Ostro, S.J., and 15 colleagues (including M.C. Nolan), Radar Imaging of Binary Near-Earth Asteroid (66391) 1999 KW4, Science 314, 1276-1280, 2006 http://dx.doi.org/10.1126/science.1133622 [3] Scheeres, D.J., and 15 colleagues (including M.C. Nolan), Dynamical Configuration of Binary Near-Earth Asteroid (66391) 1999 KW4, Science 314, 1280-1283, 2006 http://dx.doi.org/10.1126/science.1133599</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -9813,11 +9738,6 @@
           <t>0.550 (n=1)</t>
         </is>
       </c>
-      <c r="O138" t="inlineStr">
-        <is>
-          <t>[1] Hicks, M., et al. (2013). Palomar Spectroscopy of Near-Earth Asteroids 137199 (1999 KX4), 152756 (1999 JV3), 163249 (2002 GT), 163364 (2002 OD20), and 285263 (1998 QE2). The Astronomer's Telegram, 5132. http://www.astronomerstelegram.org/?read=5132</t>
-        </is>
-      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>2013</t>
@@ -9923,11 +9843,6 @@
           <t>21.19 (F) / 21.01 (J)</t>
         </is>
       </c>
-      <c r="O140" t="inlineStr">
-        <is>
-          <t>[1] Hicks, M., et al. (2010). Broadband Photometry of the Potentially Hazardous Asteroid 1999 MN: Suggestive of YORP and/or Tidal Spin-Up?. The Astronomer's Telegram, 2706. http://www.astronomerstelegram.org/?read=2706</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>2004, 2005</t>
@@ -10553,11 +10468,6 @@
           <t>0.030 (n=1)</t>
         </is>
       </c>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>[1] (2020). (264357) 2000 AZ_93. Central Bureau Electronic Telegrams, 4787. https://ui.adsabs.harvard.edu/abs/2020CBET.4787....1G/abstract</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>2019(5)[5]</t>
@@ -10633,11 +10543,6 @@
           <t>0.190 ± 0.017</t>
         </is>
       </c>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>[1] Letner, O. N., &amp; Galushina, T. Y. (2020). Motion features of the asteroid 137924 2000 BD19. Planetary and Space Science, 181, 104818. https://doi.org/10.1016/j.pss.2019.104818</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>2006, 2007, 2020(15)[15]</t>
@@ -11173,11 +11078,6 @@
           <t>20.47</t>
         </is>
       </c>
-      <c r="O159" t="inlineStr">
-        <is>
-          <t>[1] Jewitt, D. (2020). 138175 (2000 EE104) and the Source of Interplanetary Field Enhancements. The Planetary Science Journal, 1, 33. https://doi.org/10.3847/psj/aba68f [2] Jewitt, D. (2024). 38175 (2000 EE104) and the Source of Interplanetary Field Enhancements. https://doi.org/10.5194/epsc2020-965</t>
-        </is>
-      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>2000, 2001</t>
@@ -11355,7 +11255,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>[1] (2012). The Asteroid 2000 ET70. AAS/DPS Meeting #44, 111.10. https://ui.adsabs.harvard.edu/abs/2012DPS....4411110V/abstract [2] Naidu, S.P., Margot, J.L., Busch, M.W., Taylor, P.A., Nolan, M.C., Brozovic, M., Benner, L.A.M., &amp; Giorgini, J.D. (2013). Radar imaging and physical characterization of near-Earth Asteroid (162421) 2000 ET70. Icarus, 226, 323-335. https://doi.org/10.1016/j.icarus.2013.05.025 [3] Naidu, S. P., &amp; Margot, J. L. (2012). Radar Imaging and Physical Characterization of Near-Earth Asteroid (162421) 2000 ET70. AAS/DPS Meeting #44, 302.06. https://ui.adsabs.harvard.edu/abs/2012DPS....4430206N/abstract [4] Marshall, S.E., E.S. Howell, C. Magri, R.J. Vervack, D.B. Campbell, Y.R. Fernandez, M.C. Nolan, J.L. Crowell, M.D. Hicks, K.J. Lawrence, and P.A. Taylor, Thermal Properties and an Improved Shape Model for Near-Earth Asteroid (162421) 2000 ET70, Icarus 292, 22-35, 2017 http://dx.doi.org/10.1016/j.icarus.2017.03.028</t>
+          <t>[1] Naidu, S.P., Margot, J.L., Busch, M.W., Taylor, P.A., Nolan, M.C., Brozovic, M., Benner, L.A.M., &amp; Giorgini, J.D. (2013). Radar imaging and physical characterization of near-Earth Asteroid (162421) 2000 ET70. Icarus, 226, 323-335. https://doi.org/10.1016/j.icarus.2013.05.025 [2] Naidu, S. P., &amp; Margot, J. L. (2012). Radar Imaging and Physical Characterization of Near-Earth Asteroid (162421) 2000 ET70. AAS/DPS Meeting #44, 302.06. https://ui.adsabs.harvard.edu/abs/2012DPS....4430206N/abstract [3] Marshall, S.E., E.S. Howell, C. Magri, R.J. Vervack, D.B. Campbell, Y.R. Fernandez, M.C. Nolan, J.L. Crowell, M.D. Hicks, K.J. Lawrence, and P.A. Taylor, Thermal Properties and an Improved Shape Model for Near-Earth Asteroid (162421) 2000 ET70, Icarus 292, 22-35, 2017 http://dx.doi.org/10.1016/j.icarus.2017.03.028</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -11915,7 +11815,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>[1] Belskaya, I. N., Fornasier, S., &amp; Krugly, Y. N. (2009). Polarimetry and BVRI photometry of the potentially hazardous near-Earth Asteroid (23187) 2000 PN9. Icarus, 201, 167-171. https://doi.org/10.1016/j.icarus.2008.12.026 [2] Dover, L., Lowry, S. C., Rożek, A., Rozitis, B., Jackson, S. L., Zegmott, T., Krugly, Y. N., Belskaya, I. N., Fitzsimmons, A., Green, S. F., Snodgrass, C., Weissman, P. R., Brozović, M., Benner, L. A. M., Busch, M. W., et al. (2023). Physical modelling of near-Earth asteroid (23187) 2000 PN9 with ground-based optical and radar observations. Monthly Notices of the Royal Astronomical Society, 525, 4581-4595. https://doi.org/10.1093/mnras/stad2528 [3] Dover, L., Lowry, S., Rożek, A., Zegmott, T., Rozitis, B., Green, S., Snodgrass, C., Weissman, P., Krugly, Y., Belskaya, I., &amp; Brozović, M. (2024). Physical modelling of YORP-evolved NEA (23187) 2000 PN9 from optical and radar observations. https://doi.org/10.5194/epsc2020-825</t>
+          <t>[1] Dover, L., Lowry, S. C., Rożek, A., Rozitis, B., Jackson, S. L., Zegmott, T., Krugly, Y. N., Belskaya, I. N., Fitzsimmons, A., Green, S. F., Snodgrass, C., Weissman, P. R., Brozović, M., Benner, L. A. M., Busch, M. W., et al. (2023). Physical modelling of near-Earth asteroid (23187) 2000 PN9 with ground-based optical and radar observations. Monthly Notices of the Royal Astronomical Society, 525, 4581-4595. https://doi.org/10.1093/mnras/stad2528 [2] Dover, L., Lowry, S., Rożek, A., Zegmott, T., Rozitis, B., Green, S., Snodgrass, C., Weissman, P., Krugly, Y., Belskaya, I., &amp; Brozović, M. (2024). Physical modelling of YORP-evolved NEA (23187) 2000 PN9 from optical and radar observations. https://doi.org/10.5194/epsc2020-825</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -12678,11 +12578,6 @@
           <t>1.020 (n=1)</t>
         </is>
       </c>
-      <c r="O184" t="inlineStr">
-        <is>
-          <t>[1] Wlodarczyk, I. (2019). The potentially hazardous NEA 2001 BB16. Open Astronomy, 28, 180-190. https://doi.org/10.1515/astro-2019-0016</t>
-        </is>
-      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>2016(2)[2]</t>
@@ -12843,11 +12738,6 @@
           <t>3.302 h</t>
         </is>
       </c>
-      <c r="O187" t="inlineStr">
-        <is>
-          <t>[1] Devyatkin, A. V., Gorshanov, D. L., Lvov, V. N., Tsekmeister, S. D., Petrova, S. N., Martyusheva, A. A., &amp; Naumov, K. N. (2025). Astrometric and Photometric Studies of a Potentially Hazardous Asteroid (138971) 2001 CB21. Solar System Research, 59. https://doi.org/10.1134/s0038094624600914</t>
-        </is>
-      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>2006</t>
@@ -14060,7 +13950,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>[1] Sanchez, D. M., &amp; Prado, A. F. B. A. (2019). Searching for Less-Disturbed Orbital Regions Around the Near-Earth Asteroid 2001 SN263. Journal of Spacecraft and Rockets, 56, 1775-1785. https://doi.org/10.2514/1.a34402 [2] Winter, O. C., Valvano, G., Moura, T. S., Borderes-Motta, G., Amarante, A., &amp; Sfair, R. (2020). Asteroid triple-system 2001 SN263: surface characteristics and dynamical environment. Monthly Notices of the Royal Astronomical Society, 492, 4437-4455. https://doi.org/10.1093/mnras/staa097 [3] Goulart, G. d. C. A., Statella, T., &amp; Sfair, R. (2024). Definition of multispectral camera system parameters to model the asteroid 2001 SN263. New Astronomy, 113, 102287. https://doi.org/10.1016/j.newast.2024.102287 [4] Becker, T.M., E.S. Howell, M.C. Nolan, C. Magri, P. Pravec, P.A. Taylor, and 13 colleagues, Physical Modeling of Triple Near-Earth Asteroid (153591) 2001 SN263 from Radar and Optical Light Curve Observations, Icarus 248, 499-515, 2015 http://dx.doi.org/10.1016/j.icarus.2014.10.048 [5] Fang, J., J.L. Margot, M. Brozovic, M.C. Nolan, L.A.M. Benner, and P.A. Taylor, Orbits of Near-Earth Asteroid Triples 2001 SN263 and 1994 CC: Properties, Origin, and Evolution, Astronomical Journal 141, 154-168, 2011 http://iopscience.iop.org/1538-3881/141/5/154/</t>
+          <t>[1] Becker, T.M., E.S. Howell, M.C. Nolan, C. Magri, P. Pravec, P.A. Taylor, and 13 colleagues, Physical Modeling of Triple Near-Earth Asteroid (153591) 2001 SN263 from Radar and Optical Light Curve Observations, Icarus 248, 499-515, 2015 http://dx.doi.org/10.1016/j.icarus.2014.10.048 [2] Fang, J., J.L. Margot, M. Brozovic, M.C. Nolan, L.A.M. Benner, and P.A. Taylor, Orbits of Near-Earth Asteroid Triples 2001 SN263 and 1994 CC: Properties, Origin, and Evolution, Astronomical Journal 141, 154-168, 2011 http://iopscience.iop.org/1538-3881/141/5/154/</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
@@ -15040,7 +14930,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>[1] Ostro, S. J., Giorgini, J. D., Benner, L. A. M., Hine, A. A., Nolan, M. C., Margot, J. L., Chodas, P. W., &amp; Veillet, C. (2003). Radar detection of Asteroid 2002 AA29. Icarus, 166, 271-275. https://doi.org/10.1016/j.icarus.2003.09.001 [2] Wajer, P. (2009). 2002 AA29: Earth's recurrent quasi-satellite?. Icarus, 200, 147-153. https://doi.org/10.1016/j.icarus.2008.10.018</t>
+          <t>[1] Ostro, S. J., Giorgini, J. D., Benner, L. A. M., Hine, A. A., Nolan, M. C., Margot, J. L., Chodas, P. W., &amp; Veillet, C. (2003). Radar detection of Asteroid 2002 AA29. Icarus, 166, 271-275. https://doi.org/10.1016/j.icarus.2003.09.001</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -16503,11 +16393,6 @@
           <t>19</t>
         </is>
       </c>
-      <c r="O248" t="inlineStr">
-        <is>
-          <t>[1] Müller, T. G., Sterzik, M. F., Schütz, O., Pravec, P., &amp; Siebenmorgen, R. (2004). Thermal infrared observations of near-Earth asteroid 2002 NY40. Astronomy &amp;amp; Astrophysics, 424, 1075-1080. https://doi.org/10.1051/0004-6361:20041061 [2] Roberts, L. C., Hall, D. T., Lambert, J. V., Africano, J. L., Knox, K. T., Barros, J. K., Hamada, K. M., Liang, D., Sydney, P. F., &amp; Kervin, P. W. (2007). Characterization of the near-Earth Asteroid 2002 NY40. Icarus, 192, 469-474. https://doi.org/10.1016/j.icarus.2007.08.007</t>
-        </is>
-      </c>
       <c r="P248" t="inlineStr">
         <is>
           <t>2002</t>
@@ -17853,11 +17738,6 @@
           <t>0.110 (n=1)</t>
         </is>
       </c>
-      <c r="O270" t="inlineStr">
-        <is>
-          <t>[1] Hicks, M., et al. (2014). Broad-band photometry of NHATS target 387733 (2003 GS). The Astronomer's Telegram, 6090. http://www.astronomerstelegram.org/?read=6090</t>
-        </is>
-      </c>
       <c r="P270" t="inlineStr">
         <is>
           <t>2014</t>
@@ -18763,11 +18643,6 @@
           <t>0.180 (n=1)</t>
         </is>
       </c>
-      <c r="O285" t="inlineStr">
-        <is>
-          <t>[1] (2021). (143649) 2003 QQ_47. Central Bureau Electronic Telegrams, 5037. https://ui.adsabs.harvard.edu/abs/2021CBET.5037....1P/abstract</t>
-        </is>
-      </c>
       <c r="P285" t="inlineStr">
         <is>
           <t>Not Found</t>
@@ -19338,11 +19213,6 @@
           <t>0.228 ± 0.018</t>
         </is>
       </c>
-      <c r="O294" t="inlineStr">
-        <is>
-          <t>[1] (2017). (226514) 2003 UX_34. Central Bureau Electronic Telegrams, 4353. https://ui.adsabs.harvard.edu/abs/2017CBET.4353....1B/abstract</t>
-        </is>
-      </c>
       <c r="P294" t="inlineStr">
         <is>
           <t>2017(11)</t>
@@ -19603,11 +19473,6 @@
           <t>0.410 ± 0.230</t>
         </is>
       </c>
-      <c r="O298" t="inlineStr">
-        <is>
-          <t>[1] Reddy, V., Gaffey, M. J., Abell, P. A., &amp; Hardersen, P. S. (2012). Constraining albedo, diameter and composition of near-Earth asteroids via near-infrared spectroscopy. Icarus, 219, 382-392. https://doi.org/10.1016/j.icarus.2012.03.005</t>
-        </is>
-      </c>
       <c r="P298" t="inlineStr">
         <is>
           <t>2008, 2019(12)[12]</t>
@@ -19875,7 +19740,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>[1] Nolan, M. C., et al. (2004). Radar Images of Binary Asteroid 2003 YT1. AAS/DPS Meeting #36, 28.08. https://ui.adsabs.harvard.edu/abs/2004DPS....36.2808N/abstract [2] (2004). Compositional Results of Binary Near-Earth Asteroid 2003 YT1: A Basaltic Achondrite. AAS/DPS Meeting #36, 28.09. https://ui.adsabs.harvard.edu/abs/2004DPS....36.2809A/abstract [3] Hicks, M., et al. (2009). Broad-band Photometry of the Binary Potentially Hazardous Asteroid 2003 YT1. The Astronomer's Telegram, 2289. http://www.astronomerstelegram.org/?read=2289</t>
+          <t>[1] Nolan, M. C., et al. (2004). Radar Images of Binary Asteroid 2003 YT1. AAS/DPS Meeting #36, 28.08. https://ui.adsabs.harvard.edu/abs/2004DPS....36.2808N/abstract</t>
         </is>
       </c>
       <c r="P302" t="inlineStr">
@@ -20200,7 +20065,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>[1] (2006). 2004 DC. Central Bureau Electronic Telegrams, 535. https://ui.adsabs.harvard.edu/abs/2006CBET..535....1T/abstract [2] Taylor, P. A., Margot, J. L., Nolan, M. C., Benner, L. A. M., Ostro, S. J., Giorgini, J. D., &amp; Magri, C. (2006). Radar imaging of binary near-Earth Asteroid 2004 DC. Bulletin of the American Astronomical Society, 38, 577. https://ui.adsabs.harvard.edu/abs/2006DPS....38.5004T/abstract</t>
+          <t>[1] Taylor, P. A., Margot, J. L., Nolan, M. C., Benner, L. A. M., Ostro, S. J., Giorgini, J. D., &amp; Magri, C. (2006). Radar imaging of binary near-Earth Asteroid 2004 DC. Bulletin of the American Astronomical Society, 38, 577. https://ui.adsabs.harvard.edu/abs/2006DPS....38.5004T/abstract</t>
         </is>
       </c>
       <c r="P307" t="inlineStr">
@@ -20418,11 +20283,6 @@
           <t>0.310 ± 0.092</t>
         </is>
       </c>
-      <c r="O310" t="inlineStr">
-        <is>
-          <t>[1] (2012). 2004 FG11. Central Bureau Electronic Telegrams, 3091. https://ui.adsabs.harvard.edu/abs/2012CBET.3091....1T/abstract</t>
-        </is>
-      </c>
       <c r="P310" t="inlineStr">
         <is>
           <t>2012, 2014</t>
@@ -21030,7 +20890,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>[1] Scheeres, D. J., Benner, L. A. M., Ostro, S. J., Rossi, A., Marzari, F., &amp; Washabaugh, P. (2005). Abrupt alteration of Asteroid 2004 MN4's spin state during its 2029 Earth flyby. Icarus, 178, 281-283. https://doi.org/10.1016/j.icarus.2005.06.002 [2] Scheeres, D. J., Benner, L. A. M., Ostro, S. J., Rossi, A., Marzari, F., &amp; Washabaugh, P. (2005). Abrupt alteration of Asteroid 2004 MN4's spin state during its 2029 Earth flyby. Icarus, 178, 281-283. https://doi.org/10.1016/j.icarus.2005.06.002 [3] Giorgini, J. D., Benner, L. A. M., Ostro, S. J., Nolan, M. C., &amp; Busch, M. W. (2008). Predicting the Earth encounters of (99942) Apophis. Icarus, 193, 1-19. https://doi.org/10.1016/j.icarus.2007.09.012 [4] Brozović, M., Benner, L. A. M., McMichael, J. G., Giorgini, J. D., Pravec, P., Scheirich, P., Magri, C., Busch, M. W., Jao, J. S., Lee, C. G., Snedeker, L. G., Silva, M. A., Slade, M. A., Semenov, B., Nolan, M. C., et al. (2018). Goldstone and Arecibo radar observations of (99942) Apophis in 2012–2013. Icarus, 300, 115-128. https://doi.org/10.1016/j.icarus.2017.08.032 [5] Ferrín, I., Arcila, A., &amp; Saldarriaga, M. (2018). Secular light curves of NEAs 2201 Oljato, 3200 Phaethon, 99942 Apophis, 162173 Ryugu, 495848 and 6063 Jason. Monthly Notices of the Royal Astronomical Society, 479, 3726-3745. https://doi.org/10.1093/mnras/sty1474 [6] Virkki, A., Venditti, F., Hickson, D., Perillat, P., Marshall, S., Taylor, P., &amp; Hèrique, A. (2020). Bistatic Arecibo Planetary Radar Observations of 99942 Apophis. LPI Contributions. [7] Herique, A., Plettemeier, D., &amp; Kofman, W. (2024). Radar Tomography of Asteroid Deep Interior - JuRa / HERA to Didymos and Ra proposed to APOPHIS. https://doi.org/10.5194/epsc2024-753 [8] Rivera-Valentín, E. G., Aponte-Hernández, B., Taylor, P. A., Nolan, M. C., Howell, E. S., Waller, D., Zambrano-Marín, L. F., Virkki, A. K., Ballouz, R. L., &amp; Stickle, A. M. (2024). Radar Circular Polarization Ratio of Near-Earth Asteroids: Links to Spectral Taxonomy and Surface Processes. The Planetary Science Journal, 5, 232. https://doi.org/10.3847/psj/ad7df1</t>
+          <t>[1] Scheeres, D. J., Benner, L. A. M., Ostro, S. J., Rossi, A., Marzari, F., &amp; Washabaugh, P. (2005). Abrupt alteration of Asteroid 2004 MN4's spin state during its 2029 Earth flyby. Icarus, 178, 281-283. https://doi.org/10.1016/j.icarus.2005.06.002 [2] Scheeres, D. J., Benner, L. A. M., Ostro, S. J., Rossi, A., Marzari, F., &amp; Washabaugh, P. (2005). Abrupt alteration of Asteroid 2004 MN4's spin state during its 2029 Earth flyby. Icarus, 178, 281-283. https://doi.org/10.1016/j.icarus.2005.06.002 [3] Giorgini, J. D., Benner, L. A. M., Ostro, S. J., Nolan, M. C., &amp; Busch, M. W. (2008). Predicting the Earth encounters of (99942) Apophis. Icarus, 193, 1-19. https://doi.org/10.1016/j.icarus.2007.09.012 [4] Brozović, M., Benner, L. A. M., McMichael, J. G., Giorgini, J. D., Pravec, P., Scheirich, P., Magri, C., Busch, M. W., Jao, J. S., Lee, C. G., Snedeker, L. G., Silva, M. A., Slade, M. A., Semenov, B., Nolan, M. C., et al. (2018). Goldstone and Arecibo radar observations of (99942) Apophis in 2012–2013. Icarus, 300, 115-128. https://doi.org/10.1016/j.icarus.2017.08.032 [5] Virkki, A., Venditti, F., Hickson, D., Perillat, P., Marshall, S., Taylor, P., &amp; Hèrique, A. (2020). Bistatic Arecibo Planetary Radar Observations of 99942 Apophis. LPI Contributions. [6] Herique, A., Plettemeier, D., &amp; Kofman, W. (2024). Radar Tomography of Asteroid Deep Interior - JuRa / HERA to Didymos and Ra proposed to APOPHIS. https://doi.org/10.5194/epsc2024-753 [7] Rivera-Valentín, E. G., Aponte-Hernández, B., Taylor, P. A., Nolan, M. C., Howell, E. S., Waller, D., Zambrano-Marín, L. F., Virkki, A. K., Ballouz, R. L., &amp; Stickle, A. M. (2024). Radar Circular Polarization Ratio of Near-Earth Asteroids: Links to Spectral Taxonomy and Surface Processes. The Planetary Science Journal, 5, 232. https://doi.org/10.3847/psj/ad7df1</t>
         </is>
       </c>
       <c r="P320" t="inlineStr">
@@ -21758,11 +21618,6 @@
           <t>0.080 (n=1)</t>
         </is>
       </c>
-      <c r="O332" t="inlineStr">
-        <is>
-          <t>[1] Busch, M., Kulkarni, S., Conrad, A., &amp; Cameron, P. (2007). Keck adaptive optics imaging of near-Earth Asteroid 2004 XP14. Icarus, 189, 589-590. https://doi.org/10.1016/j.icarus.2007.03.020 [2] Reddy, V., Gaffey, M. J., Abell, P. A., &amp; Hardersen, P. S. (2012). Constraining albedo, diameter and composition of near-Earth asteroids via near-infrared spectroscopy. Icarus, 219, 382-392. https://doi.org/10.1016/j.icarus.2012.03.005</t>
-        </is>
-      </c>
       <c r="P332" t="inlineStr">
         <is>
           <t>2020(3)[3]</t>
@@ -23058,11 +22913,6 @@
           <t>1.000 (n=1)</t>
         </is>
       </c>
-      <c r="O354" t="inlineStr">
-        <is>
-          <t>[1] Reddy, V., Gaffey, M. J., Abell, P. A., &amp; Hardersen, P. S. (2012). Constraining albedo, diameter and composition of near-Earth asteroids via near-infrared spectroscopy. Icarus, 219, 382-392. https://doi.org/10.1016/j.icarus.2012.03.005</t>
-        </is>
-      </c>
       <c r="P354" t="inlineStr">
         <is>
           <t>2008</t>
@@ -23473,11 +23323,6 @@
           <t>0.262 ± 0.046</t>
         </is>
       </c>
-      <c r="O361" t="inlineStr">
-        <is>
-          <t>[1] Kondratyev, B. P. (2024). Equilibrium figures of two liquid masses with synchronous rotation. Dynamics of a double asteroid (190166) 2005 UP156. Astronomičeskij žurnal, 101, 651-659. https://doi.org/10.31857/s0004629924070074</t>
-        </is>
-      </c>
       <c r="P361" t="inlineStr">
         <is>
           <t>2017(26)[26]</t>
@@ -23713,11 +23558,6 @@
           <t>0.580 (n=1)</t>
         </is>
       </c>
-      <c r="O365" t="inlineStr">
-        <is>
-          <t>[1] Reddy, V., Gaffey, M. J., Abell, P. A., &amp; Hardersen, P. S. (2012). Constraining albedo, diameter and composition of near-Earth asteroids via near-infrared spectroscopy. Icarus, 219, 382-392. https://doi.org/10.1016/j.icarus.2012.03.005</t>
-        </is>
-      </c>
       <c r="P365" t="inlineStr">
         <is>
           <t>2008</t>
@@ -24078,11 +23918,6 @@
           <t>0.360 ± 0.089</t>
         </is>
       </c>
-      <c r="O371" t="inlineStr">
-        <is>
-          <t>[1] (2011). Preparing for asteroid 2005 YU55 at close quarters. Astronomy &amp; Geophysics, 52, 3.06. https://doi.org/10.1111/j.1468-4004.2011.52304_10.x [2] Vereshchagina, I. A., Sokov, E. N., Gorshanov, D. L., Devyatkin, A. V., L’vov, V. N., Tsekmeister, S. D., Romas, E. S., &amp; Martyusheva, A. A. (2014). Astrometry and photometry of asteroid (308635) 2005 YU55. Solar System Research, 48, 382-390. https://doi.org/10.1134/s0038094614040108</t>
-        </is>
-      </c>
       <c r="P371" t="inlineStr">
         <is>
           <t>2010, 2011</t>
@@ -24508,11 +24343,6 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="O378" t="inlineStr">
-        <is>
-          <t>[1] (2006). 2006 GY2. Central Bureau Electronic Telegrams, 534. https://ui.adsabs.harvard.edu/abs/2006CBET..534....1B/abstract</t>
-        </is>
-      </c>
       <c r="P378" t="inlineStr">
         <is>
           <t>2006</t>
@@ -25168,11 +24998,6 @@
           <t>22.8 (F) / 23.18 (J)</t>
         </is>
       </c>
-      <c r="O389" t="inlineStr">
-        <is>
-          <t>[1] (2025). Lightcurve Analysis and Rotation Period for NEA 2006 WB. Minor Planet Bulletin, 52, 100. https://ui.adsabs.harvard.edu/abs/2025MPBu...52..100N/abstract</t>
-        </is>
-      </c>
       <c r="P389" t="inlineStr">
         <is>
           <t>2006</t>
@@ -25848,11 +25673,6 @@
           <t>0.372 ± 0.020</t>
         </is>
       </c>
-      <c r="O400" t="inlineStr">
-        <is>
-          <t>[1] Fieber-Beyer, S. K., Gaffey, M. J., Bottke, W. F., &amp; Hardersen, P. S. (2015). Potentially hazardous Asteroid 2007 LE: Compositional link to the black chondrite Rose City and Asteroid (6) Hebe. Icarus, 250, 430-437. https://doi.org/10.1016/j.icarus.2014.12.021</t>
-        </is>
-      </c>
       <c r="P400" t="inlineStr">
         <is>
           <t>2012, 2017(5)[5]</t>
@@ -26530,7 +26350,7 @@
       </c>
       <c r="O411" t="inlineStr">
         <is>
-          <t>[1] Busch, M. W., Kulkarni, S. R., Brisken, W., Ostro, S. J., Benner, L. A. M., Giorgini, J. D., &amp; Nolan, M. C. (2010). Determining asteroid spin states using radar speckles. Icarus, 209, 535-541. https://doi.org/10.1016/j.icarus.2010.05.002 [2] Busch, M. W., Ostro, S. J., Benner, L. A. M., Brozovic, M., Giorgini, J. D., Jao, J. S., Scheeres, D. J., Magri, C., Nolan, M. C., Howell, E. S., Taylor, P. A., Margot, J. L., &amp; Brisken, W. (2011). Radar observations and the shape of near-Earth asteroid 2008 EV5. Icarus, 212, 649-660. https://doi.org/10.1016/j.icarus.2011.01.013 [3] Reddy, V., Corre, L. L., Hicks, M., Lawrence, K., Buratti, B. J., Abell, P. A., Gaffey, M. J., &amp; Hardersen, P. S. (2012). Composition of near-Earth Asteroid 2008 EV5: Potential target for robotic and human exploration. Icarus, 221, 678-681. https://doi.org/10.1016/j.icarus.2012.08.035 [4] Busch, M. W., Ostro, S. J., Benner, L. A. M., Brozovic, M., Giorgini, J. D., Jao, J., Scheeres, D. J., Magri, C., Nolan, M. C., Howell, E. S., Taylor, P. A., Margot, J. L., &amp; Brisken, W. (2019). Corrigendum to “Radar observations and the shape of near-Earth asteroid 2008 EV5” [ICARUS 212 (2011) 649–660]. Icarus, 333, 548. https://doi.org/10.1016/j.icarus.2019.06.005 [5] Engels, M., Hudson, S., &amp; Magri, C. (2020). Performance of CUDA-SHAPE on complex synthetic shapes and real data of asteroid (341843) 2008 EV5. Astronomy and Computing, 32, 100401. https://doi.org/10.1016/j.ascom.2020.100401</t>
+          <t>[1] Busch, M. W., Kulkarni, S. R., Brisken, W., Ostro, S. J., Benner, L. A. M., Giorgini, J. D., &amp; Nolan, M. C. (2010). Determining asteroid spin states using radar speckles. Icarus, 209, 535-541. https://doi.org/10.1016/j.icarus.2010.05.002 [2] Busch, M. W., Ostro, S. J., Benner, L. A. M., Brozovic, M., Giorgini, J. D., Jao, J. S., Scheeres, D. J., Magri, C., Nolan, M. C., Howell, E. S., Taylor, P. A., Margot, J. L., &amp; Brisken, W. (2011). Radar observations and the shape of near-Earth asteroid 2008 EV5. Icarus, 212, 649-660. https://doi.org/10.1016/j.icarus.2011.01.013 [3] Busch, M. W., Ostro, S. J., Benner, L. A. M., Brozovic, M., Giorgini, J. D., Jao, J., Scheeres, D. J., Magri, C., Nolan, M. C., Howell, E. S., Taylor, P. A., Margot, J. L., &amp; Brisken, W. (2019). Corrigendum to “Radar observations and the shape of near-Earth asteroid 2008 EV5” [ICARUS 212 (2011) 649–660]. Icarus, 333, 548. https://doi.org/10.1016/j.icarus.2019.06.005 [4] Engels, M., Hudson, S., &amp; Magri, C. (2020). Performance of CUDA-SHAPE on complex synthetic shapes and real data of asteroid (341843) 2008 EV5. Astronomy and Computing, 32, 100401. https://doi.org/10.1016/j.ascom.2020.100401</t>
         </is>
       </c>
       <c r="P411" t="inlineStr">
@@ -27323,11 +27143,6 @@
           <t>21.99</t>
         </is>
       </c>
-      <c r="O424" t="inlineStr">
-        <is>
-          <t>[1] Quijano Vodniza, A. (2017). Study of the Asteroid 2009 DL46. AAS Meeting #230, 119.01. https://ui.adsabs.harvard.edu/abs/2017AAS...23011901V/abstract</t>
-        </is>
-      </c>
       <c r="P424" t="inlineStr">
         <is>
           <t>2016(7)[7]</t>
@@ -27535,7 +27350,7 @@
       </c>
       <c r="O427" t="inlineStr">
         <is>
-          <t>[1] Spoto, F., Milani, A., Farnocchia, D., Chesley, S. R., Micheli, M., Valsecchi, G. B., Perna, D., &amp; Hainaut, O. (2014). Nongravitational perturbations and virtual impactors: the case of asteroid (410777) 2009 FD. Astronomy &amp;amp; Astrophysics, 572, A100. https://doi.org/10.1051/0004-6361/201424743 [2] Del Vigna, A., Roa, J., Farnocchia, D., Micheli, M., Tholen, D., Guerra, F., Spoto, F., &amp; Valsecchi, G. B. (2019). Yarkovsky effect detection and updated impact hazard assessment for near-Earth asteroid (410777) 2009 FD. Astronomy &amp;amp; Astrophysics, 627, L11. https://doi.org/10.1051/0004-6361/201936075</t>
+          <t>[1] Del Vigna, A., Roa, J., Farnocchia, D., Micheli, M., Tholen, D., Guerra, F., Spoto, F., &amp; Valsecchi, G. B. (2019). Yarkovsky effect detection and updated impact hazard assessment for near-Earth asteroid (410777) 2009 FD. Astronomy &amp;amp; Astrophysics, 627, L11. https://doi.org/10.1051/0004-6361/201936075</t>
         </is>
       </c>
       <c r="P427" t="inlineStr">
@@ -27963,11 +27778,6 @@
           <t>0.050 (n=1)</t>
         </is>
       </c>
-      <c r="O434" t="inlineStr">
-        <is>
-          <t>[1] Karashevich, S. V., Devyatkin, A. V., Vereshchagina, I. A., L’vov, V. N., &amp; Tsekmeister, S. D. (2012). Astrometric and photometric studies of the 2009 WZ104 asteroid as it approached the earth. Solar System Research, 46, 130-135. https://doi.org/10.1134/s0038094612010030</t>
-        </is>
-      </c>
       <c r="P434" t="inlineStr">
         <is>
           <t>2013</t>
@@ -28028,11 +27838,6 @@
           <t>0.280 ± 0.080</t>
         </is>
       </c>
-      <c r="O435" t="inlineStr">
-        <is>
-          <t>[1] Кохирова, Г. И., Буриев, А. М., Сафаров, С. Н., &amp; Сатторзода, А. А. (2022). Dynamics and physical peculiarities of a potentially hazardous asteroid 2009 XO from observations in the Gissar Astronomical Observatory. Научные труды Института астрономии РАН, 106-114. https://doi.org/10.51194/inasan.2022.7.2.001</t>
-        </is>
-      </c>
       <c r="P435" t="inlineStr">
         <is>
           <t>2020(14)[14]</t>
@@ -28973,11 +28778,6 @@
           <t>0.346 ± 0.102</t>
         </is>
       </c>
-      <c r="O449" t="inlineStr">
-        <is>
-          <t>[1] (2016). (441987) 2010 NY_65. Central Bureau Electronic Telegrams, 4304. https://ui.adsabs.harvard.edu/abs/2016CBET.4304....1G/abstract</t>
-        </is>
-      </c>
       <c r="P449" t="inlineStr">
         <is>
           <t>2014, 2015, 2017(9)[9], 2016(6)[6], 2018(10)[10], 2019(10)[10], 2020(17)[16]</t>
@@ -35183,11 +34983,6 @@
           <t>0.286 ± 0.011</t>
         </is>
       </c>
-      <c r="O561" t="inlineStr">
-        <is>
-          <t>[1] Quijano-Vodniza, A., &amp; P., M. R. (2017). The Asteroid 2014 JO25. DPS. [2] Petrova, S. N., Devyatkin, A. V., Gorshanov, D. L., &amp; L'vov, V. N. (2018). Astrometric and photometric baseline observations of the asteroid 2014 JO25. Journal of Physics: Conference Series, 1038, 012021. https://doi.org/10.1088/1742-6596/1038/1/012021 [3] Petropoulou, V., Lazzarin, M., Bertini, I., Ochner, P., La Forgia, F., Siviero, A., Ferri, F., &amp; Naletto, G. (2018). Spectroscopic observations of the bilobate potentially hazardous asteroid 2014 JO25 from the Asiago 1.22-m telescope. Planetary and Space Science, 158, 63-68. https://doi.org/10.1016/j.pss.2018.05.003 [4] Venkataramani, K., Ganesh, S., Rai, A., Husárik, M., Baliyan, K. S., &amp; Joshi, U. C. (2019). Time and Phase Resolved Optical Spectra of Potentially Hazardous Asteroid 2014 JO25. The Astronomical Journal, 157, 199. https://doi.org/10.3847/1538-3881/ab0f26 [5] Rumyantsev, V. V., Kiselev, N. N., &amp; Ivanova, A. V. (2019). CCD Polarimetry of Near-Earth Asteroid 2014 JO25 and Comet 41P/Tuttle–Giacobini–Kresák at the Prime Focus of the 2.6-m Shajn Telescope of the Crimean Astrophysical Observatory. Solar System Research, 53, 91-97. https://doi.org/10.1134/s0038094619020060</t>
-        </is>
-      </c>
       <c r="P561" t="inlineStr">
         <is>
           <t>2017(14)</t>
@@ -37218,11 +37013,6 @@
           <t>0.390 ± 0.184</t>
         </is>
       </c>
-      <c r="O597" t="inlineStr">
-        <is>
-          <t>[1] (2020). 2015 EG. Central Bureau Electronic Telegrams, 4786. https://ui.adsabs.harvard.edu/abs/2020CBET.4786....1G/abstract</t>
-        </is>
-      </c>
       <c r="P597" t="inlineStr">
         <is>
           <t>2019(6)[6]</t>
@@ -37673,11 +37463,6 @@
           <t>0.210 (n=1)</t>
         </is>
       </c>
-      <c r="O605" t="inlineStr">
-        <is>
-          <t>[1] (2015). Asteroids With Tensile Strength: The Case of 2015 HM10. AAS/DPS Meeting #47, 402.05. https://ui.adsabs.harvard.edu/abs/2015DPS....4740205B/abstract</t>
-        </is>
-      </c>
       <c r="P605" t="inlineStr">
         <is>
           <t>2015</t>
@@ -39075,7 +38860,7 @@
       </c>
       <c r="O629" t="inlineStr">
         <is>
-          <t>[1] Müller, T. G., Marciniak, A., Butkiewicz-Bąk, M., Duffard, R., Oszkiewicz, D., Käufl, H. U., Szakáts, R., Santana-Ros, T., Kiss, C., &amp; Santos-Sanz, P. (2017). Large Halloween asteroid at lunar distance. Astronomy &amp;amp; Astrophysics, 598, A63. https://doi.org/10.1051/0004-6361/201629584 [2] Rivera-Valentin, E. G., et al. (2016). Radar observations of near-Earth asteroids from Arecibo Observatory. AAS/DPS Meeting #48, 329.10. https://ui.adsabs.harvard.edu/abs/2016DPS....4832910R/abstract [3] Busch, M. W., et al. (2016). Recent radar observations of potentially hazardous near-Earth asteroids with the Arecibo Observatory and the Deep Space Network. AGU Fall Meeting, abstract NH12A-06. https://ui.adsabs.harvard.edu/abs/2016AGUFMNH12A..06B/abstract</t>
+          <t>[1] Rivera-Valentin, E. G., et al. (2016). Radar observations of near-Earth asteroids from Arecibo Observatory. AAS/DPS Meeting #48, 329.10. https://ui.adsabs.harvard.edu/abs/2016DPS....4832910R/abstract [2] Busch, M. W., et al. (2016). Recent radar observations of potentially hazardous near-Earth asteroids with the Arecibo Observatory and the Deep Space Network. AGU Fall Meeting, abstract NH12A-06. https://ui.adsabs.harvard.edu/abs/2016AGUFMNH12A..06B/abstract</t>
         </is>
       </c>
       <c r="P629" t="inlineStr">
@@ -42973,11 +42758,6 @@
           <t>0.090 (n=1)</t>
         </is>
       </c>
-      <c r="O702" t="inlineStr">
-        <is>
-          <t>[1] de la Fuente Marcos, C., &amp; de la Fuente Marcos, R. (2017). Asteroid 2017 FZ2 et al.: signs of recent mass-shedding from YORP?. Monthly Notices of the Royal Astronomical Society, 473, 3434-3453. https://doi.org/10.1093/mnras/stx2540</t>
-        </is>
-      </c>
       <c r="P702" t="inlineStr">
         <is>
           <t>2017(2)</t>
@@ -43833,11 +43613,6 @@
           <t>0.313 ± 0.017</t>
         </is>
       </c>
-      <c r="O718" t="inlineStr">
-        <is>
-          <t>[1] Monteiro, F., Rondón, E., Lazzaro, D., Oey, J., Evangelista-Santana, M., Arcoverde, P., De Cicco, M., Silva-Cabrera, J. S., &amp; Rodrigues, T. (2024). Physical characterization of equal-mass binary near-Earth asteroid 2017 YE5: a possible dormant Jupiter-family comet. https://doi.org/10.5194/epsc2021-400</t>
-        </is>
-      </c>
       <c r="P718" t="inlineStr">
         <is>
           <t>2018(11)[11]</t>
@@ -52308,11 +52083,6 @@
           <t>5.41</t>
         </is>
       </c>
-      <c r="O883" t="inlineStr">
-        <is>
-          <t>[1] Hilton, J.L. (1997). The Mass of the Asteroid 15 Eunomia From Observations of 1313 Berna and 1284 Latvia. The Astronomical Journal, 114, 402. https://doi.org/10.1086/118484</t>
-        </is>
-      </c>
       <c r="P883" t="inlineStr">
         <is>
           <t>1985, 2002</t>
@@ -52945,7 +52715,7 @@
       </c>
       <c r="O894" t="inlineStr">
         <is>
-          <t>[1] Shepard, M.K., Kressler, K.M., Clark, B.E., Ockert-Bell, M.E., Nolan, M.C., Howell, E.S., Magri, C., &amp; Giorgini, J.D. (2008). Radar observations of E-class Asteroids 44 Nysa and 434 Hungaria. Icarus, 195, 220-225. https://doi.org/10.1016/j.icarus.2007.12.018 [2] Reddy, V., J.A. Sanchez, W.F. Bottke, A. Thirouin, E.G. Rivera-Valentin, M.S. Kelley, W. Ryan, E.A. Cloutis, S.C. Tegler, E.V. Ryan, P.A. Taylor, J.E. Richardson, N. Moskovitz, and L. Le Corre, Physical Characterization of 2-m Diameter Near-Earth Asteroid 2015 TC25: A Possible Boulder from E-type Asteroid (44) Nysa, Astronomical Journal 152, 162, 2016 http://dx.doi.org/10.3847/0004-6256/152/6/162</t>
+          <t>[1] Shepard, M.K., Kressler, K.M., Clark, B.E., Ockert-Bell, M.E., Nolan, M.C., Howell, E.S., Magri, C., &amp; Giorgini, J.D. (2008). Radar observations of E-class Asteroids 44 Nysa and 434 Hungaria. Icarus, 195, 220-225. https://doi.org/10.1016/j.icarus.2007.12.018</t>
         </is>
       </c>
       <c r="P894" t="inlineStr">
@@ -56363,11 +56133,6 @@
           <t>9.45</t>
         </is>
       </c>
-      <c r="O956" t="inlineStr">
-        <is>
-          <t>[1] Kruhlyi, Y., Hestroffer, D., &amp; Liu, Z. (2026). Gaia Binary Asteroids: Lightcurve Photometry and Modelling. https://doi.org/10.5194/epsc2026-1126</t>
-        </is>
-      </c>
       <c r="P956" t="inlineStr">
         <is>
           <t>2012</t>
@@ -56850,7 +56615,7 @@
       </c>
       <c r="O965" t="inlineStr">
         <is>
-          <t>[1] Ostro, S. J., Jurgens, R. F., Rosema, K. D., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., Shapiro, I. I., Hine, A. A., &amp; Velez, R. (1991). Asteroid radar astrometry. The Astronomical Journal, 102, 1490. https://doi.org/10.1086/115975 [2] Zellner, B. (1976). Physical properties of asteroid 433 Eros. Icarus, 28, 149-153. https://doi.org/10.1016/0019-1035(76)90097-X [3] Mitchell, D. L., Hudson, R. S., Ostro, S. J., &amp; Rosema, K. D. (1998). Shape of Asteroid 433 Eros from Inversion of Goldstone Radar Doppler Spectra. Icarus, 131, 4-14. https://doi.org/10.1006/icar.1997.5815 [4] Magri, C., Consolmagno, G. J., Ostrch, S. J., Benner, L. A. M., &amp; Beeney, B. R. (2001). Radar constraints on asteroid regolith properties using 433 Eros as ground truth. Meteoritics &amp;amp; Planetary Science, 36, 1697-1709. https://doi.org/10.1111/j.1945-5100.2001.tb01857.x [5] Campbell, D.B., G.H. Pettengill, and I.I. Shapiro, 70-cm Radar Observations of 433 Eros, Icarus 28, 17-20, 1976 http://dx.doi.org/10.1016/0019-1035(76)90080-4 [6] Fernandez, Y. R., Hinkle, M. L., Howell, E. S., Magri, C., Nolan, M. C., Marshall, S. E., Vervack, R. J., &amp; Myers, S. A. (2025). Rotationally-Resolved Radar Scattering Properties of Near-Earth Asteroid (433) Eros. EPSC-DPS2025, abstract 364. https://meetingorganizer.copernicus.org/EPSC-DPS2025/EPSC-DPS2025-364.html</t>
+          <t>[1] Ostro, S. J., Jurgens, R. F., Rosema, K. D., Winkler, R., Yeomans, D. K., Campbell, D. B., Chandler, J. F., Shapiro, I. I., Hine, A. A., &amp; Velez, R. (1991). Asteroid radar astrometry. The Astronomical Journal, 102, 1490. https://doi.org/10.1086/115975 [2] Mitchell, D. L., Hudson, R. S., Ostro, S. J., &amp; Rosema, K. D. (1998). Shape of Asteroid 433 Eros from Inversion of Goldstone Radar Doppler Spectra. Icarus, 131, 4-14. https://doi.org/10.1006/icar.1997.5815 [3] Magri, C., Consolmagno, G. J., Ostrch, S. J., Benner, L. A. M., &amp; Beeney, B. R. (2001). Radar constraints on asteroid regolith properties using 433 Eros as ground truth. Meteoritics &amp;amp; Planetary Science, 36, 1697-1709. https://doi.org/10.1111/j.1945-5100.2001.tb01857.x [4] Campbell, D.B., G.H. Pettengill, and I.I. Shapiro, 70-cm Radar Observations of 433 Eros, Icarus 28, 17-20, 1976 http://dx.doi.org/10.1016/0019-1035(76)90080-4 [5] Fernandez, Y. R., Hinkle, M. L., Howell, E. S., Magri, C., Nolan, M. C., Marshall, S. E., Vervack, R. J., &amp; Myers, S. A. (2025). Rotationally-Resolved Radar Scattering Properties of Near-Earth Asteroid (433) Eros. EPSC-DPS2025, abstract 364. https://meetingorganizer.copernicus.org/EPSC-DPS2025/EPSC-DPS2025-364.html</t>
         </is>
       </c>
       <c r="P965" t="inlineStr">
@@ -57883,11 +57648,6 @@
           <t>0.039</t>
         </is>
       </c>
-      <c r="O984" t="inlineStr">
-        <is>
-          <t>[1] Kruhlyi, Y., Hestroffer, D., &amp; Liu, Z. (2026). Gaia Binary Asteroids: Lightcurve Photometry and Modelling. https://doi.org/10.5194/epsc2026-1126</t>
-        </is>
-      </c>
       <c r="P984" t="inlineStr">
         <is>
           <t>2005, 2013</t>
@@ -58345,7 +58105,7 @@
       </c>
       <c r="O992" t="inlineStr">
         <is>
-          <t>[1] Harmon, J. K., Campbell, D. B., Hine, A. A., Shapiro, I. I., &amp; Marsden, B. G. (1989). Radar observations of Comet IRAS-Araki-Alcock 1983d. The Astrophysical Journal, 338, 1071-1093. https://ui.adsabs.harvard.edu/abs/1989ApJ...338.1071H [2] Groussin, O., Lamy, P. L., &amp; Jorda, L. (2010). The nucleus of comet C/1983 H1 IRAS-Araki-Alcock. Planetary and Space Science, 58, 904-912. https://doi.org/10.1016/j.pss.2010.02.009</t>
+          <t>[1] Harmon, J. K., Campbell, D. B., Hine, A. A., Shapiro, I. I., &amp; Marsden, B. G. (1989). Radar observations of Comet IRAS-Araki-Alcock 1983d. The Astrophysical Journal, 338, 1071-1093. https://ui.adsabs.harvard.edu/abs/1989ApJ...338.1071H</t>
         </is>
       </c>
       <c r="P992" t="inlineStr">
@@ -58383,11 +58143,6 @@
       <c r="H993" t="n">
         <v>1</v>
       </c>
-      <c r="O993" t="inlineStr">
-        <is>
-          <t>[1] (1983). Comet Sugano-Saigusa-Fujikawa (1983e). IAU Circular, 3832. https://ui.adsabs.harvard.edu/abs/1983IAUC.3832....1W/abstract</t>
-        </is>
-      </c>
       <c r="P993" t="inlineStr">
         <is>
           <t>1983</t>
@@ -58425,7 +58180,7 @@
       </c>
       <c r="O994" t="inlineStr">
         <is>
-          <t>[1] Rosenbush, V., Kiselev, N., &amp; Velichko, S. (2002). Polarimetric and Photometric Observations of Split Comet C/2001 A2 (LINEAR). Cometary Science after Hale-Bopp, 423-433. https://doi.org/10.1007/978-94-017-1088-6_43 [2] Luk’yanyk, I. V., &amp; Churyumov, K. I. (2002). Observations of Comet C/2001 A2 (LINEAR) with the Multipupil Fiber Spectrograph. Cometary Science after Hale-Bopp, 177-183. https://doi.org/10.1007/978-94-017-1088-6_19 [3] Kawakita, H., Watanabe, J. I., Fuse, T., Furusho, R., &amp; Abe, S. (2002). Spin Temperature of Ammonia Determined from NH2 in Comet C/2001 A2 (LINEAR). Cometary Science after Hale-Bopp, 371-379. https://doi.org/10.1007/978-94-017-1088-6_37 [4] Nolan, M. C., Harmon, J. K., Howell, E. S., Campbell, D. B., &amp; Margot, J. L. (2006). Detection of large grains in the coma of Comet C/2001 A2 (LINEAR) from Arecibo radar observations. Icarus, 181, 432-441. https://doi.org/10.1016/j.icarus.2005.11.010</t>
+          <t>[1] Nolan, M. C., Harmon, J. K., Howell, E. S., Campbell, D. B., &amp; Margot, J. L. (2006). Detection of large grains in the coma of Comet C/2001 A2 (LINEAR) from Arecibo radar observations. Icarus, 181, 432-441. https://doi.org/10.1016/j.icarus.2005.11.010</t>
         </is>
       </c>
       <c r="P994" t="inlineStr">
@@ -58473,11 +58228,6 @@
       <c r="H995" t="n">
         <v>1</v>
       </c>
-      <c r="O995" t="inlineStr">
-        <is>
-          <t>[1] Kawakita, H., &amp; Watanabe, J. i. (2002). Unidentified Bands in Comet Ikeya-Zhang (C/2002 C1): The Correlation between Unidentified Bands and H[TINF]2[/TINF]O[TSUP]+[/TSUP]. The Astrophysical Journal, 574, L183-L185. https://doi.org/10.1086/342533 [2] Cochran, A. L. (2002). A Search for [FORMULA][F][RM]N[/RM][SUP]+[/SUP][INF]2[/INF][/F][/FORMULA] in Spectra of Comet C/2002 C1 (Ikeya-Zhang). The Astrophysical Journal, 576, L165-L168. https://doi.org/10.1086/343763</t>
-        </is>
-      </c>
       <c r="P995" t="inlineStr">
         <is>
           <t>2002</t>
@@ -58518,11 +58268,6 @@
       <c r="H996" t="n">
         <v>1</v>
       </c>
-      <c r="O996" t="inlineStr">
-        <is>
-          <t>[1] Velichko, S., Kiselev, N., &amp; Velichko, F. (2005). Polarimetry and Photometry of Comet C/2004 Q2 (Machholz). Earth, Moon, and Planets, 97, 379-386. https://doi.org/10.1007/s11038-006-9074-x [2] Maslov, I. A., Nadzhip, A. E., &amp; Shenavrin, V. I. (2008). Near-infrared observations of Comet C/2004 Q2 (Machholz). Astronomy Letters, 34, 353-356. https://doi.org/10.1134/s1063773708050083 [3] Reyniers, M., Degroote, P., Bodewits, D., Cuypers, J., &amp; Waelkens, C. (2008). The rotation and coma profiles of comet C/2004 Q2 (Machholz). Astronomy &amp;amp; Astrophysics, 494, 379-389. https://doi.org/10.1051/0004-6361:20079225 [4] Kobayashi, H., &amp; Kawakita, H. (2009). FORMATION CONDITIONS OF ICY MATERIALS IN COMET C/2004 Q2 (MACHHOLZ). I. MIXING RATIOS OF ORGANIC VOLATILES. The Astrophysical Journal, 703, 121-130. https://doi.org/10.1088/0004-637x/703/1/121 [5] Mikailov, K. M., Churyumov, K. I., Guliev, R. A., &amp; Ismailova, S. K. (2013). Catalogue of emission lines in the spectrum of the comet C/2004 Q2 (Machholz) on 15 January, 2004. Astronomical School’s Report, 9, 119-124. https://doi.org/10.18372/2411-6602.09.2119 [6] De Val-Borro, M., Jarchow, C., Hartogh, P., Villanueva, G. L., &amp; Küppers, M. (n.d.). CONSTRAINING VOLATILE ABUNDANCES IN COMET C/2004 Q2 (MACHHOLZ). Advances in Geosciences - A 6-Volume Set, 149-160. https://doi.org/10.1142/9789814355377_0011</t>
-        </is>
-      </c>
       <c r="P996" t="inlineStr">
         <is>
           <t>2005</t>
@@ -58563,11 +58308,6 @@
       <c r="H997" t="n">
         <v>1</v>
       </c>
-      <c r="O997" t="inlineStr">
-        <is>
-          <t>[1] Ivanova, O., Zubko, E., Videen, G., Mommert, M., Hora, J. L., Krišandová, Z. S., Svoreň, J., Novichonok, A., Borysenko, S., &amp; Shubina, O. (2017). Colour variations of Comet C/2013 UQ4 (Catalina). Monthly Notices of the Royal Astronomical Society, 469, 2695-2703. https://doi.org/10.1093/mnras/stx1004</t>
-        </is>
-      </c>
       <c r="P997" t="inlineStr">
         <is>
           <t>2005</t>
@@ -58620,7 +58360,7 @@
       </c>
       <c r="O998" t="inlineStr">
         <is>
-          <t>[1] Harmon, J. K., Ostro, S. J., Chandler, J. F., &amp; Hudson, R. S. (1994). Radar ranging to Ganymede and Callisto. The Astronomical Journal, 107, 1175. https://doi.org/10.1086/116929 [2] Ostro, S. J., Campbell, D. B., Simpson, R. A., Hudson, R. S., Chandler, J. F., Rosema, K. D., Shapiro, I. I., Standish, E. M., Winkler, R., Yeomans, D. K., Vélez, R., &amp; Goldstein, R. M. (1992). Europa, Ganymede, and Callisto: New radar results from Arecibo and Goldstone. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/92je01992 [3] Harcke, L. J., Zebker, H. A., Tyler, G. L., Simpson, R. A., Ostro, S. J., &amp; Harmon, J. K. (2001). Radar Imaging of Europa, Ganymede, and Callisto with the Upgraded Arecibo 13 cm Radar. American Astronomical Society Meeting Abstracts #198. [4] Schenk, P., &amp; McKinnon, W. B. (2006). Callisto. Kluwer Academic Publishers eBooks. https://doi.org/10.1007/1-4020-4520-4_48</t>
+          <t>[1] Harmon, J. K., Ostro, S. J., Chandler, J. F., &amp; Hudson, R. S. (1994). Radar ranging to Ganymede and Callisto. The Astronomical Journal, 107, 1175. https://doi.org/10.1086/116929 [2] Ostro, S. J., Campbell, D. B., Simpson, R. A., Hudson, R. S., Chandler, J. F., Rosema, K. D., Shapiro, I. I., Standish, E. M., Winkler, R., Yeomans, D. K., Vélez, R., &amp; Goldstein, R. M. (1992). Europa, Ganymede, and Callisto: New radar results from Arecibo and Goldstone. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/92je01992 [3] Harcke, L. J., Zebker, H. A., Tyler, G. L., Simpson, R. A., Ostro, S. J., &amp; Harmon, J. K. (2001). Radar Imaging of Europa, Ganymede, and Callisto with the Upgraded Arecibo 13 cm Radar. American Astronomical Society Meeting Abstracts #198.</t>
         </is>
       </c>
       <c r="P998" t="inlineStr">
@@ -58850,7 +58590,7 @@
       </c>
       <c r="O1003" t="inlineStr">
         <is>
-          <t>[1] Ostro, S. J., Campbell, D. B., Simpson, R. A., Hudson, R. S., Chandler, J. F., Rosema, K. D., Shapiro, I. I., Standish, E. M., Winkler, R., Yeomans, D. K., Velez, R., &amp; Goldstein, R. M. (1992). Europa, Ganymede, and Callisto: New radar results from Arecibo and Goldstone. Journal of Geophysical Research: Planets, 97, 18227-18244. https://doi.org/10.1029/92je01992 [2] Hand, K. P., Berisford, D., Daimaru, T., Foster, J., Hofmann, A. E., &amp; Furst, B. (2019). Penitente formation is unlikely on Europa. Nature Geoscience. https://doi.org/10.1038/s41561-019-0496-2 [3] Hobley, D. E. J., Moore, J. M., Howard, A. D., &amp; Umurhan, O. M. (2019). Reply to: Penitente formation is unlikely on Europa. Nature Geoscience, 13, 20-21. https://doi.org/10.1038/s41561-019-0497-1 [4] Harcke, L. J., Zebker, H. A., Tyler, G. L., Simpson, R. A., Ostro, S. J., &amp; Harmon, J. K. (2001). Radar Imaging of Europa, Ganymede, and Callisto with the Upgraded Arecibo 13 cm Radar. American Astronomical Society Meeting Abstracts #198. [5] McKinnon, W. (2006). Europa. Kluwer Academic Publishers eBooks. https://doi.org/10.1007/1-4020-4520-4_137</t>
+          <t>[1] Ostro, S. J., Campbell, D. B., Simpson, R. A., Hudson, R. S., Chandler, J. F., Rosema, K. D., Shapiro, I. I., Standish, E. M., Winkler, R., Yeomans, D. K., Velez, R., &amp; Goldstein, R. M. (1992). Europa, Ganymede, and Callisto: New radar results from Arecibo and Goldstone. Journal of Geophysical Research: Planets, 97, 18227-18244. https://doi.org/10.1029/92je01992 [2] Harcke, L. J., Zebker, H. A., Tyler, G. L., Simpson, R. A., Ostro, S. J., &amp; Harmon, J. K. (2001). Radar Imaging of Europa, Ganymede, and Callisto with the Upgraded Arecibo 13 cm Radar. American Astronomical Society Meeting Abstracts #198.</t>
         </is>
       </c>
       <c r="P1003" t="inlineStr">
@@ -58945,7 +58685,7 @@
       </c>
       <c r="O1005" t="inlineStr">
         <is>
-          <t>[1] Gall, A. L., Raza, S., Lellouch, E., Butler, B., Bonnefoy, L., Leyrat, C., Schmidt, F., Mergny, C., Robin, C., Meyer, F., &amp; Harrar, L. (2024). Iapetus: Investigating the most dramatic hemispheric dichotomy in the Solar system&amp;amp;#160;with radio observations. https://doi.org/10.5194/epsc2024-618 [2] Tinaut-Ruano, F., Leon, J. M. d., Rizos, J. L., Tatsumi, E., Pinilla-Alonso, N., Vilas, F., &amp; Hendrix, A. (2024). The Iapetus&amp;amp;#8217; case:&amp;amp;#160;NUV as tracer of two populations of dark material. https://doi.org/10.5194/epsc2024-1071 [3] Black, G.J., D.B. Campbell, L.M. Carter, and S.J. Ostro, Radar Detection of Iapetus, Science 304, 553, 2004 http://dx.doi.org/10.1126/science.1096470</t>
+          <t>[1] Black, G.J., D.B. Campbell, L.M. Carter, and S.J. Ostro, Radar Detection of Iapetus, Science 304, 553, 2004 http://dx.doi.org/10.1126/science.1096470</t>
         </is>
       </c>
       <c r="P1005" t="inlineStr">
@@ -58995,7 +58735,7 @@
       </c>
       <c r="O1006" t="inlineStr">
         <is>
-          <t>[1] Campbell, D. B., Chandler, J. F., Pettengill, G. H., &amp; Shapiro, I. I. (1977). Galilean Satellites of Jupiter: 12.6-Centimeter Radar Observations. Science, 196, 650-653. https://doi.org/10.1126/science.196.4290.650 [2] Warwick, J. (1967). Radiophysics of Jupiter. Space Science Reviews. https://doi.org/10.1007/bf00222408 [3] Ostro, S. J., Campbell, D. B., Chandler, J. F., Shapiro, I. I., &amp; Rosema, K. D. (1990). Io's Radar Properties. Bulletin of the American Astronomical Society.</t>
+          <t>[1] Campbell, D. B., Chandler, J. F., Pettengill, G. H., &amp; Shapiro, I. I. (1977). Galilean Satellites of Jupiter: 12.6-Centimeter Radar Observations. Science, 196, 650-653. https://doi.org/10.1126/science.196.4290.650 [2] Ostro, S. J., Campbell, D. B., Chandler, J. F., Shapiro, I. I., &amp; Rosema, K. D. (1990). Io's Radar Properties. Bulletin of the American Astronomical Society.</t>
         </is>
       </c>
       <c r="P1006" t="inlineStr">
@@ -59080,7 +58820,7 @@
       </c>
       <c r="O1008" t="inlineStr">
         <is>
-          <t>[1] Harmon, J. K., Arvidson, R. E., Guinness, E. A., Campbell, B. A., &amp; Slade, M. A. (1999). Mars mapping with delay‐Doppler radar. Journal of Geophysical Research: Planets, 104, 14065-14089. https://doi.org/10.1029/1998je900042 [2] Harmon, J. K., Nolan, M. C., Husmann, D. I., &amp; Campbell, B. A. (2012). Arecibo radar imagery of Mars: The major volcanic provinces. Icarus. https://doi.org/10.1016/j.icarus.2012.06.030 [3] Muhleman, D. O., Grossman, A. W., &amp; Butler, B. (1995). Radar Investigation of Mars, Mercury, and Titan. Annual Review of Earth and Planetary Sciences. https://doi.org/10.1146/annurev.ea.23.050195.002005 [4] Simpson, R. A., Tyler, G. L., &amp; Campbell, D. B. (1978). Arecibo radar observations of Mars surface characteristics in the northern hemisphere. Icarus. https://doi.org/10.1016/0019-1035(78)90101-x [5] Harmon, J. K. (1985). Mars: Dual-polarization radar observations with extended coverage. Icarus. https://doi.org/10.1016/0019-1035(85)90175-7 [6] Harmon, J. K., Slade, M. A., &amp; Hudson, R. S. (1992). Mars radar scattering: Arecibo/Goldstone results at 12.6- and 3.5-cm wavelengths. Icarus. https://doi.org/10.1016/0019-1035(92)90093-m [7] Harmon, J. K., Campbell, D. B., &amp; Ostro, S. J. (1982). Dual-polarization radar observations of Mars: Tharsis and Environs. Icarus. https://doi.org/10.1016/0019-1035(82)90177-4 [8] Harmon, J. K. (1997). A radar study of the Chryse region, Mars. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/96je01953 [9] Wu, S. S. C. (1978). Mars synthetic topographic mapping. Icarus. https://doi.org/10.1016/0019-1035(78)90182-3 [10] Harmon, J. K., &amp; Nolan, M. C. (2016). Arecibo radar imagery of Mars: II. Chryse–Xanthe, polar caps, and other regions. Icarus. https://doi.org/10.1016/j.icarus.2016.08.015 [11] Harmon, J. K., Sulzer, M. P., Perillat, P. J., &amp; Chandler, J. F. (1992). Mars radar mapping: Strong backscatter from the Elysium basin and outflow channel. Icarus, 95, 153-156. https://doi.org/10.1016/0019-1035(92)90197-f [12] Harmon, J. K., &amp; Nolan, M. C. (2007). Arecibo Radar Imaging of Mars During the 2005 Opposition. Seventh International Conference on Mars. [13] Simpson, R. A., Tyler, G. L., &amp; Lipa, B. J. (1977). Mars surface properties observed by earth-based radar at 70-, 12.5-, and 3.8-cm wavelengths. Icarus, 32, 147-167. https://doi.org/10.1016/0019-1035(77)90057-4 [14] Putzig, N. E., Morgan, G. A., Campbell, B. A., Grima, C., Smith, I. B., Phillips, R. J., &amp; Golombek, M. P. (2016). Radar-Derived Properties of the InSight Landing Site in Western Elysium Planitia on Mars. Space Science Reviews. https://doi.org/10.1007/s11214-016-0322-8 [15] Thompson, T. W., &amp; Moore, H. J. (1988). A Model for Depolarized Radar Echoes from Mars. Bulletin of the American Astronomical Society.</t>
+          <t>[1] Harmon, J. K., Arvidson, R. E., Guinness, E. A., Campbell, B. A., &amp; Slade, M. A. (1999). Mars mapping with delay‐Doppler radar. Journal of Geophysical Research: Planets, 104, 14065-14089. https://doi.org/10.1029/1998je900042 [2] Harmon, J. K., Nolan, M. C., Husmann, D. I., &amp; Campbell, B. A. (2012). Arecibo radar imagery of Mars: The major volcanic provinces. Icarus. https://doi.org/10.1016/j.icarus.2012.06.030 [3] Muhleman, D. O., Grossman, A. W., &amp; Butler, B. (1995). Radar Investigation of Mars, Mercury, and Titan. Annual Review of Earth and Planetary Sciences. https://doi.org/10.1146/annurev.ea.23.050195.002005 [4] Simpson, R. A., Tyler, G. L., &amp; Campbell, D. B. (1978). Arecibo radar observations of Mars surface characteristics in the northern hemisphere. Icarus. https://doi.org/10.1016/0019-1035(78)90101-x [5] Harmon, J. K. (1985). Mars: Dual-polarization radar observations with extended coverage. Icarus. https://doi.org/10.1016/0019-1035(85)90175-7 [6] Harmon, J. K., Slade, M. A., &amp; Hudson, R. S. (1992). Mars radar scattering: Arecibo/Goldstone results at 12.6- and 3.5-cm wavelengths. Icarus. https://doi.org/10.1016/0019-1035(92)90093-m [7] Harmon, J. K., Campbell, D. B., &amp; Ostro, S. J. (1982). Dual-polarization radar observations of Mars: Tharsis and Environs. Icarus. https://doi.org/10.1016/0019-1035(82)90177-4 [8] Harmon, J. K. (1997). A radar study of the Chryse region, Mars. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/96je01953 [9] Harmon, J. K., &amp; Nolan, M. C. (2016). Arecibo radar imagery of Mars: II. Chryse–Xanthe, polar caps, and other regions. Icarus. https://doi.org/10.1016/j.icarus.2016.08.015 [10] Harmon, J. K., Sulzer, M. P., Perillat, P. J., &amp; Chandler, J. F. (1992). Mars radar mapping: Strong backscatter from the Elysium basin and outflow channel. Icarus, 95, 153-156. https://doi.org/10.1016/0019-1035(92)90197-f [11] Harmon, J. K., &amp; Nolan, M. C. (2007). Arecibo Radar Imaging of Mars During the 2005 Opposition. Seventh International Conference on Mars. [12] Simpson, R. A., Tyler, G. L., &amp; Lipa, B. J. (1977). Mars surface properties observed by earth-based radar at 70-, 12.5-, and 3.8-cm wavelengths. Icarus, 32, 147-167. https://doi.org/10.1016/0019-1035(77)90057-4 [13] Putzig, N. E., Morgan, G. A., Campbell, B. A., Grima, C., Smith, I. B., Phillips, R. J., &amp; Golombek, M. P. (2016). Radar-Derived Properties of the InSight Landing Site in Western Elysium Planitia on Mars. Space Science Reviews. https://doi.org/10.1007/s11214-016-0322-8 [14] Thompson, T. W., &amp; Moore, H. J. (1988). A Model for Depolarized Radar Echoes from Mars. Bulletin of the American Astronomical Society.</t>
         </is>
       </c>
       <c r="P1008" t="inlineStr">
@@ -59190,7 +58930,7 @@
       </c>
       <c r="O1010" t="inlineStr">
         <is>
-          <t>[1] Campbell, B. A., Hawke, B. R., &amp; Thompson, T. W. (1997). Regolith composition and structure in the lunar maria: Results of long‐wavelength radar studies. Journal of Geophysical Research: Planets, 102, 19307-19320. https://doi.org/10.1029/97je00858 [2] Stacy, N. J. S., Campbell, D. B., &amp; Ford, P. G. (1997). Arecibo Radar Mapping of the Lunar Poles: A Search for Ice Deposits. Science. https://doi.org/10.1126/science.276.5318.1527 [3] Shkuratov, Y. G. (2001). Regolith Layer Thickness Mapping of the Moon by Radar and Optical Data. Icarus. https://doi.org/10.1006/icar.2000.6545 [4] Patterson, G. W., Stickle, A. M., Turner, F. S., Jensen, J. R., Bussey, D. B. J., Spudis, P. D., Espiritu, R. C., Schulze, R., Yocky, D. A., Wahl, D. E., Zimmerman, M. I., Cahill, J. T. S., Nolan, M. C., Carter, L. M., &amp; Neish, C. D. (2016). Bistatic radar observations of the Moon using Mini-RF on LRO and the Arecibo Observatory. Icarus. https://doi.org/10.1016/j.icarus.2016.05.017 [5] Fa, W., &amp; Wieczorek, M. A. (2012). Regolith thickness over the lunar nearside: Results from Earth-based 70-cm Arecibo radar observations. Icarus. https://doi.org/10.1016/j.icarus.2012.01.010 [6] Campbell, B. A., Campbell, D. B., Margot, J. L., Ghent, R. R., Nolan, M., Chandler, J., Carter, L. M., &amp; Stacy, N. J. S. (2007). Focused 70-cm Wavelength Radar Mapping of the Moon. IEEE Transactions on Geoscience and Remote Sensing, 45, 4032-4042. https://doi.org/10.1109/tgrs.2007.906582 [7] Thompson, T. W., Pollack, J. B., Campbell, M. J., &amp; O'Leary, B. (1970). Radar Maps of the Moon at 70‐cm Wavelength and Their Interpretation. Radio Science. https://doi.org/10.1029/rs005i002p00253 [8] Campbell, B. A., Carter, L. M., Campbell, D. B., Nolan, M. C., Chandler, J. F., Ghent, R. R., Hawke, B. R., Anderson, R. F., &amp; Wells, K. S. (2010). Earth-based 12.6-cm wavelength radar mapping of the Moon: New views of impact melt distribution and mare physical properties. Icarus. https://doi.org/10.1016/j.icarus.2010.03.011 [9] Campbell, B., &amp; Campbell, D. (2005). Regolith properties in the south polar region of the Moon from 70-cm radar polarimetry. Icarus, 180, 1-7. https://doi.org/10.1016/j.icarus.2005.08.018 [10] Carter, L. M., Campbell, B. A., Hawke, B. R., Campbell, D. B., &amp; Nolan, M. C. (2009). Radar remote sensing of pyroclastic deposits in the southern Mare Serenitatis and Mare Vaporum regions of the Moon. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/2009je003406 [11] Busch, M. W., Ostro, S. J., Benner, L. A. M., Giorgini, J. D., Magri, C., Howell, E. S., Nolan, M. C., Hine, A. A., Campbell, D. B., Shapiro, I. I., &amp; Chandler, J. F. (2006). Arecibo radar observations of Phobos and Deimos. Icarus. https://doi.org/10.1016/j.icarus.2006.11.003 [12] Black, G. (2001). Icy Galilean Satellites: 70 cm Radar Results from Arecibo. Icarus. https://doi.org/10.1006/icar.2001.6615 [13] Thompson, T. W. (1979). A review of earth-based radar mapping of the moon. The Moon and the Planets. https://doi.org/10.1007/bf00898069 [14] Spudis, P. D., Bussey, B., Plescia, J. B., Josset, J., &amp; Beauvivre, S. (2008). Geology of Shackleton Crater and the south pole of the Moon. Geophysical Research Letters. https://doi.org/10.1029/2008gl034468 [15] Black, G. J., Campbell, D. B., &amp; Carter, L. M. (2007). Arecibo radar observations of Rhea, Dione, Tethys, and Enceladus. Icarus, 191, 702-711. https://doi.org/10.1016/j.icarus.2007.06.009 [16] Muhleman, D. O., Grossman, A. W., &amp; Butler, B. (1995). Radar Investigation of Mars, Mercury, and Titan. Annual Review of Earth and Planetary Sciences. https://doi.org/10.1146/annurev.ea.23.050195.002005 [17] Campbell, D. B., &amp; Burns, B. A. (1980). Earth‐based radar imagery of Venus. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/ja085ia13p08271 [18] Harmon, J. K. (1985). Mars: Dual-polarization radar observations with extended coverage. Icarus. https://doi.org/10.1016/0019-1035(85)90175-7 [19] Rivera‐Valentín, E. G., Meyer, H., Taylor, P., Mazarico, E., Bhiravarasu, S. S., Virkki, A., Nolan, M. C., Chabot, N. L., &amp; Giorgini, J. D. (2022). Arecibo S-band Radar Characterization of Local-scale Heterogeneities within Mercury’s North Polar Deposits. The Planetary Science Journal. https://doi.org/10.3847/psj/ac54a0 [20] Thompson, T. W. (1987). High-resolution lunar radar map at 70-cm wavelength. Earth Moon and Planets. https://doi.org/10.1007/bf00054324 [21] Mitchell, D. L., Ostro, S. J., Hudson, R. S., Rosema, K. D., Campbell, D. B., Vélez, R., Chandler, J. F., Shapiro, I. I., Giorgini, J. D., &amp; Yeomans, D. K. (1996). Radar Observations of Asteroids 1 Ceres, 2 Pallas, and 4 Vesta. Icarus. https://doi.org/10.1006/icar.1996.0193</t>
+          <t>[1] Campbell, B. A., Hawke, B. R., &amp; Thompson, T. W. (1997). Regolith composition and structure in the lunar maria: Results of long‐wavelength radar studies. Journal of Geophysical Research: Planets, 102, 19307-19320. https://doi.org/10.1029/97je00858 [2] Stacy, N. J. S., Campbell, D. B., &amp; Ford, P. G. (1997). Arecibo Radar Mapping of the Lunar Poles: A Search for Ice Deposits. Science. https://doi.org/10.1126/science.276.5318.1527 [3] Shkuratov, Y. G. (2001). Regolith Layer Thickness Mapping of the Moon by Radar and Optical Data. Icarus. https://doi.org/10.1006/icar.2000.6545 [4] Patterson, G. W., Stickle, A. M., Turner, F. S., Jensen, J. R., Bussey, D. B. J., Spudis, P. D., Espiritu, R. C., Schulze, R., Yocky, D. A., Wahl, D. E., Zimmerman, M. I., Cahill, J. T. S., Nolan, M. C., Carter, L. M., &amp; Neish, C. D. (2016). Bistatic radar observations of the Moon using Mini-RF on LRO and the Arecibo Observatory. Icarus. https://doi.org/10.1016/j.icarus.2016.05.017 [5] Fa, W., &amp; Wieczorek, M. A. (2012). Regolith thickness over the lunar nearside: Results from Earth-based 70-cm Arecibo radar observations. Icarus. https://doi.org/10.1016/j.icarus.2012.01.010 [6] Campbell, B. A., Campbell, D. B., Margot, J. L., Ghent, R. R., Nolan, M., Chandler, J., Carter, L. M., &amp; Stacy, N. J. S. (2007). Focused 70-cm Wavelength Radar Mapping of the Moon. IEEE Transactions on Geoscience and Remote Sensing, 45, 4032-4042. https://doi.org/10.1109/tgrs.2007.906582 [7] Thompson, T. W., Pollack, J. B., Campbell, M. J., &amp; O'Leary, B. (1970). Radar Maps of the Moon at 70‐cm Wavelength and Their Interpretation. Radio Science. https://doi.org/10.1029/rs005i002p00253 [8] Campbell, B. A., Carter, L. M., Campbell, D. B., Nolan, M. C., Chandler, J. F., Ghent, R. R., Hawke, B. R., Anderson, R. F., &amp; Wells, K. S. (2010). Earth-based 12.6-cm wavelength radar mapping of the Moon: New views of impact melt distribution and mare physical properties. Icarus. https://doi.org/10.1016/j.icarus.2010.03.011 [9] Campbell, B., &amp; Campbell, D. (2005). Regolith properties in the south polar region of the Moon from 70-cm radar polarimetry. Icarus, 180, 1-7. https://doi.org/10.1016/j.icarus.2005.08.018 [10] Carter, L. M., Campbell, B. A., Hawke, B. R., Campbell, D. B., &amp; Nolan, M. C. (2009). Radar remote sensing of pyroclastic deposits in the southern Mare Serenitatis and Mare Vaporum regions of the Moon. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/2009je003406 [11] Busch, M. W., Ostro, S. J., Benner, L. A. M., Giorgini, J. D., Magri, C., Howell, E. S., Nolan, M. C., Hine, A. A., Campbell, D. B., Shapiro, I. I., &amp; Chandler, J. F. (2006). Arecibo radar observations of Phobos and Deimos. Icarus. https://doi.org/10.1016/j.icarus.2006.11.003 [12] Black, G. (2001). Icy Galilean Satellites: 70 cm Radar Results from Arecibo. Icarus. https://doi.org/10.1006/icar.2001.6615 [13] Thompson, T. W. (1979). A review of earth-based radar mapping of the moon. The Moon and the Planets. https://doi.org/10.1007/bf00898069 [14] Black, G. J., Campbell, D. B., &amp; Carter, L. M. (2007). Arecibo radar observations of Rhea, Dione, Tethys, and Enceladus. Icarus, 191, 702-711. https://doi.org/10.1016/j.icarus.2007.06.009 [15] Muhleman, D. O., Grossman, A. W., &amp; Butler, B. (1995). Radar Investigation of Mars, Mercury, and Titan. Annual Review of Earth and Planetary Sciences. https://doi.org/10.1146/annurev.ea.23.050195.002005 [16] Campbell, D. B., &amp; Burns, B. A. (1980). Earth‐based radar imagery of Venus. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/ja085ia13p08271 [17] Harmon, J. K. (1985). Mars: Dual-polarization radar observations with extended coverage. Icarus. https://doi.org/10.1016/0019-1035(85)90175-7 [18] Rivera‐Valentín, E. G., Meyer, H., Taylor, P., Mazarico, E., Bhiravarasu, S. S., Virkki, A., Nolan, M. C., Chabot, N. L., &amp; Giorgini, J. D. (2022). Arecibo S-band Radar Characterization of Local-scale Heterogeneities within Mercury’s North Polar Deposits. The Planetary Science Journal. https://doi.org/10.3847/psj/ac54a0 [19] Thompson, T. W. (1987). High-resolution lunar radar map at 70-cm wavelength. Earth Moon and Planets. https://doi.org/10.1007/bf00054324 [20] Mitchell, D. L., Ostro, S. J., Hudson, R. S., Rosema, K. D., Campbell, D. B., Vélez, R., Chandler, J. F., Shapiro, I. I., Giorgini, J. D., &amp; Yeomans, D. K. (1996). Radar Observations of Asteroids 1 Ceres, 2 Pallas, and 4 Vesta. Icarus. https://doi.org/10.1006/icar.1996.0193</t>
         </is>
       </c>
       <c r="P1010" t="inlineStr">
@@ -59280,7 +59020,7 @@
       </c>
       <c r="O1012" t="inlineStr">
         <is>
-          <t>[1] Campbell, D. B., Harmon, J. K., &amp; Shapiro, I. I. (1989). Radar observations of Comet Halley. The Astrophysical Journal, 338, 1094. https://doi.org/10.1086/167259 [2] (2013). Chapter One. The First Anticipated Return: Halley’s Comet 1758. When Computers Were Human, 11-25. https://doi.org/10.1515/9781400849369.11 [3] Kerr, R. B., Tepley, C. A., Cageao, R. P., Atreya, S. K., Donahue, T. M., &amp; Cherchneff, I. M. (1987). Observations of comet Halley at Hα and 6300 Å. Geophysical Research Letters, 14, 53-56. https://doi.org/10.1029/gl014i001p00053 [4] Cordes, J. M., Terzian, Y., Falchi, A. M., Tofani, G., &amp; Lewis, B. M. (1990). Radio OH emission from Comet Halley with 3 arcmin resolution. The Astronomical Journal, 100, 1655. https://doi.org/10.1086/115625 [5] Kerr, R. B., Cageao, R. P., Atreya, S. K., Donahue, T. M., &amp; Tepley, C. A. (1985). High spectral resolution Fabry-Perot interferometer measurements of comet Halley at H-alpha and 6300 Å. Advances in Space Research, 5, 283-287. https://doi.org/10.1016/0273-1177(85)90098-5 [6] Atreya, S. K. (1988). Gaseous cometary coronal. NASA STI Repository (National Aeronautics and Space Administration). [7] French, L. M. (2006). Asteroid. Encyclopedia of Earth Science, 27-33. https://doi.org/10.1007/1-4020-4520-4_20</t>
+          <t>[1] Campbell, D. B., Harmon, J. K., &amp; Shapiro, I. I. (1989). Radar observations of Comet Halley. The Astrophysical Journal, 338, 1094. https://doi.org/10.1086/167259</t>
         </is>
       </c>
       <c r="P1012" t="inlineStr">
@@ -59330,7 +59070,7 @@
       </c>
       <c r="O1013" t="inlineStr">
         <is>
-          <t>[1] Marsden, B. G., &amp; Sekanina, Z. (1974). Comets and nongravitational forces. VI. Periodic comet Encke 1786-1971 . The Astronomical Journal, 79, 413. https://doi.org/10.1086/111560 [2] Kamoun, P. G., Campbell, D. B., Ostro, S. J., Pettengill, G. H., &amp; Shapiro, I. I. (1982). Comet Encke: Radar Detection of Nucleus. Science, 216, 293-295. https://doi.org/10.1126/science.216.4543.293 [3] Harmon, J., &amp; Nolan, M. (2005). Radar observations of Comet 2P/Encke during the 2003 apparition. Icarus, 176, 175-183. https://doi.org/10.1016/j.icarus.2005.01.012 [4] Skirmante, K., Bleiders, M., Jekabsons, N., Bezrukovs, V., &amp; Jasmonts, G. (2020). Observations of OH masers of comets in 1.6GHz frequency band using the Irbene RT32 radio telescope. https://doi.org/10.5194/epsc2020-171</t>
+          <t>[1] Kamoun, P. G., Campbell, D. B., Ostro, S. J., Pettengill, G. H., &amp; Shapiro, I. I. (1982). Comet Encke: Radar Detection of Nucleus. Science, 216, 293-295. https://doi.org/10.1126/science.216.4543.293 [2] Harmon, J., &amp; Nolan, M. (2005). Radar observations of Comet 2P/Encke during the 2003 apparition. Icarus, 176, 175-183. https://doi.org/10.1016/j.icarus.2005.01.012</t>
         </is>
       </c>
       <c r="P1013" t="inlineStr">
@@ -59385,7 +59125,7 @@
       </c>
       <c r="O1014" t="inlineStr">
         <is>
-          <t>[1] Harmon, J. K., Nolan, M. C., Giorgini, J. D., &amp; Howell, E. S. (2010). Radar observations of 8P/Tuttle: A contact-binary comet. Icarus, 207, 499-502. https://doi.org/10.1016/j.icarus.2009.12.026 [2] Harmon, J. K., Nolan, M. C., Howell, E. S., &amp; Giorgini, J. D. (2008). Comet 8P/Tuttle: Arecibo Radar Observations of the First Bilobate Comet. [3] Groussin, O., Lamy, P. L., Kelley, M. S. P., Toth, I., Jorda, L., Fernández, Y. R., &amp; Weaver, H. A. (2019). SpitzerSpace Telescope observations of bilobate comet 8P/Tuttle. Astronomy &amp;amp; Astrophysics, 632, A104. https://doi.org/10.1051/0004-6361/201936458 [4] Harmon, J. K., Nolan, M. C., Howell, E. S., Giorgini, J. D., &amp; Magri, C. (2008). Arecibo Radar Observations of Comet 8P/Tuttle: A Possible Contact Binary. AAS/Division for Planetary Sciences Meeting Abstracts #40.</t>
+          <t>[1] Harmon, J. K., Nolan, M. C., Giorgini, J. D., &amp; Howell, E. S. (2010). Radar observations of 8P/Tuttle: A contact-binary comet. Icarus, 207, 499-502. https://doi.org/10.1016/j.icarus.2009.12.026 [2] Harmon, J. K., Nolan, M. C., Howell, E. S., &amp; Giorgini, J. D. (2008). Comet 8P/Tuttle: Arecibo Radar Observations of the First Bilobate Comet. [3] Harmon, J. K., Nolan, M. C., Howell, E. S., Giorgini, J. D., &amp; Magri, C. (2008). Arecibo Radar Observations of Comet 8P/Tuttle: A Possible Contact Binary. AAS/Division for Planetary Sciences Meeting Abstracts #40.</t>
         </is>
       </c>
       <c r="P1014" t="inlineStr">
@@ -59645,7 +59385,7 @@
       </c>
       <c r="O1019" t="inlineStr">
         <is>
-          <t>[1] Springmann, A., Harris, W. M., Ryan, E. L., Lejoly, C., Howell, E. S., Mueller, B. E. A., Samarasinha, N. H., Woodney, L. M., &amp; Steckloff, J. K. (2022). Repeating Gas Ejection Events from Comet 45P/Honda–Mrkos–Pajdušáková. The Planetary Science Journal, 3, 15. https://doi.org/10.3847/psj/ac3e66 [2] Springmann, A., Howell, E. S., Harmon, J. K., Lejoly, C., Rivera‐Valentín, E. G., Virkki, A., Zambrano-Marin, L. F., Taylor, P., Harris, W. M., Mueller, B. E. A., Samarasinha, N. H., &amp; Sánchez-Vahamonde, C. R. (2017). Particle Sizes in the Coma of Comet 45P/Honda-Mrkos-Pajdušáková from Arecibo Radar Observations. DPS. [3] Springmann, A., Howell, E. S., Nolan, M. C., Lejoly, C., Taylor, P., Rivera‐Valentín, E. G., Virkki, A., Zambrano-Marin, L. F., Harris, W. M., Harmon, J. K., &amp; Sánchez-Vahamonde, C. R. (2018). Modeling the large-grain (&gt;2 cm) coma of comet 45P/Honda-Mrkos-Pajdušáková from Arecibo Observatory radar observations. AAS/Division for Planetary Sciences Meeting Abstracts #50. [4] Springmann, A., Harris, W. M., Ryan, E. L., Lejoly, C., Howell, E. S., Mueller, B. E. A., Samarasinha, N. H., Woodney, L. M., &amp; Steckloff, J. K. (2021). Repeating gas ejection events from comet 45P/Honda-Mrkos-Pajdu\v{s}\'{a}kov\'{a}. arXiv (Cornell University).</t>
+          <t>[1] Springmann, A., Howell, E. S., Harmon, J. K., Lejoly, C., Rivera‐Valentín, E. G., Virkki, A., Zambrano-Marin, L. F., Taylor, P., Harris, W. M., Mueller, B. E. A., Samarasinha, N. H., &amp; Sánchez-Vahamonde, C. R. (2017). Particle Sizes in the Coma of Comet 45P/Honda-Mrkos-Pajdušáková from Arecibo Radar Observations. DPS. [2] Springmann, A., Howell, E. S., Nolan, M. C., Lejoly, C., Taylor, P., Rivera‐Valentín, E. G., Virkki, A., Zambrano-Marin, L. F., Harris, W. M., Harmon, J. K., &amp; Sánchez-Vahamonde, C. R. (2018). Modeling the large-grain (&gt;2 cm) coma of comet 45P/Honda-Mrkos-Pajdušáková from Arecibo Observatory radar observations. AAS/Division for Planetary Sciences Meeting Abstracts #50.</t>
         </is>
       </c>
       <c r="P1019" t="inlineStr">
@@ -59700,7 +59440,7 @@
       </c>
       <c r="O1020" t="inlineStr">
         <is>
-          <t>[1] Skirmante, K., Bleiders, M., Jekabsons, N., Bezrukovs, V., &amp; Jasmonts, G. (2020). Observations of OH masers of comets in 1.6GHz frequency band using the Irbene RT32 radio telescope. https://doi.org/10.5194/epsc2020-171 [2] Harmon, J. K., Nolan, M. C., Howell, E. S., Giorgini, J. D., &amp; Taylor, P. (2011). Comet 103P/Hartley; radar observations of the nucleus and large-grain coma. Abstracts of Papers Submitted to the Lunar and Planetary Science Conference.</t>
+          <t>[1] Harmon, J. K., Nolan, M. C., Howell, E. S., Giorgini, J. D., &amp; Taylor, P. (2011). Comet 103P/Hartley; radar observations of the nucleus and large-grain coma. Abstracts of Papers Submitted to the Lunar and Planetary Science Conference.</t>
         </is>
       </c>
       <c r="P1020" t="inlineStr">
@@ -59755,7 +59495,7 @@
       </c>
       <c r="O1021" t="inlineStr">
         <is>
-          <t>[1] Nolan, M. C., Harmon, J. K., Howell, E. S., Campbell, D. B., &amp; Margot, J. L. (2006). Detection of large grains in the coma of Comet C/2001 A2 (LINEAR) from Arecibo radar observations. Icarus, 181, 432-441. https://doi.org/10.1016/j.icarus.2005.11.010 [2] Hickson, D. C., Virkki, A. K., Perillat, P., Nolan, M. C., &amp; Bhiravarasu, S. S. (2021). Polarimetric Decomposition of Near-Earth Asteroids Using Arecibo Radar Observations. The Planetary Science Journal, 2, 30. https://doi.org/10.3847/psj/abd846 [3] Senske, D. A., Campbell, D. B., Head, J. W., Fisher, P. C., Hine, A. A., deCharon, A., Frank, S. L., Keddie, S. T., Roberts, K. M., Stofan, E. R., Aubele, J. C., Crumpler, L. S., &amp; Stacy, N. (1991). Geology and tectonics of the Themis Regio-Lavinia Planitia-Alpha Regio-Lada Terra area, Venus: Results from Arecibo image data. Earth, Moon, and Planets, 55, 97-161. https://doi.org/10.1007/bf00058900</t>
+          <t>[1] Nolan, M. C., Harmon, J. K., Howell, E. S., Campbell, D. B., &amp; Margot, J. L. (2006). Detection of large grains in the coma of Comet C/2001 A2 (LINEAR) from Arecibo radar observations. Icarus, 181, 432-441. https://doi.org/10.1016/j.icarus.2005.11.010 [2] Hickson, D. C., Virkki, A. K., Perillat, P., Nolan, M. C., &amp; Bhiravarasu, S. S. (2021). Polarimetric Decomposition of Near-Earth Asteroids Using Arecibo Radar Observations. The Planetary Science Journal, 2, 30. https://doi.org/10.3847/psj/abd846</t>
         </is>
       </c>
       <c r="P1021" t="inlineStr">
@@ -59810,7 +59550,7 @@
       </c>
       <c r="O1022" t="inlineStr">
         <is>
-          <t>[1] Harmon, J., Nolan, M., Margot, J., Campbell, D., Benner, L., &amp; Giorgini, J. (2006). Radar observations of Comet P/2005 JQ5 (Catalina). Icarus, 184, 285-288. https://doi.org/10.1016/j.icarus.2006.05.014 [2] Kwiatkowski, T., Kryszczyńska, A., Polińska, M., Buckley, D. A. H., O'Donaghue, D., Charles, P. A., Crause, L. A., Crawford, S. M., Hashimoto, Y., Kniazev, A. Y., Loaring, N. S., Romero‐Colmenero, E., Sefako, R., Still, M., &amp; Väisänen, P. (2008). Photometry of Asteroid 2006 RH120 During Its Short Visit to a Geocentric Orbit. LPICo.</t>
+          <t>[1] Harmon, J., Nolan, M., Margot, J., Campbell, D., Benner, L., &amp; Giorgini, J. (2006). Radar observations of Comet P/2005 JQ5 (Catalina). Icarus, 184, 285-288. https://doi.org/10.1016/j.icarus.2006.05.014</t>
         </is>
       </c>
       <c r="P1022" t="inlineStr">
@@ -60172,7 +59912,7 @@
       </c>
       <c r="O1030" t="inlineStr">
         <is>
-          <t>[1] Campbell, D. B., Black, G. J., Carter, L. M., &amp; Ostro, S. J. (2003). Radar Evidence for Liquid Surfaces on Titan. Science, 302, 431-434. https://doi.org/10.1126/science.1088969 [2] Muhleman, D. O., Grossman, A. W., &amp; Butler, B. (1995). Radar Investigation of Mars, Mercury, and Titan. Annual Review of Earth and Planetary Sciences. https://doi.org/10.1146/annurev.ea.23.050195.002005 [3] Black, G. J., Campbell, D. B., &amp; Carter, L. M. (2010). Ground-based radar observations of Titan: 2000–2008. Icarus, 212, 300-320. https://doi.org/10.1016/j.icarus.2010.10.025 [4] Hofgartner, J. D., Hayes, A. G., Campbell, D. B., Lunine, J. I., Black, G. J., MacKenzie, S. M., Birch, S. P. D., Elachi, C., Kirk, R. D., Gall, A. L., Lorenz, R. D., &amp; Wall, S. D. (2020). The root of anomalously specular reflections from solid surfaces on Saturn’s moon Titan. Nature Communications, 11. https://doi.org/10.1038/s41467-020-16663-1 [5] Lorenz, R. (2023). Slopes on Titan and application to spacecraft landing safety. Planetary and Space Science, 235, 105745. https://doi.org/10.1016/j.pss.2023.105745 [6] Campbell, D. B., Black, G., Carter, L. M., Hine, A. A., Margot, J., Nolan, M. C., &amp; Ostro, S. J. (2002). The Surface of Titan: Arecibo Radar Observations. DPS. [7] Duxbury, T. C., &amp; Lieske, J. H. (1976). Arecibo Radar Observations of the Galilean Satellites and Titan. Bulletin of the American Astronomical Society. [8] Black, G. J., Campbell, D. B., &amp; Carter, L. M. (2008). Surface Properties of Titan from Arecibo/GBT Radar Observations. AAS/Division for Planetary Sciences Meeting Abstracts #40. [9] Campbell, D. B., Black, G., Carter, L. M., &amp; Nolan, M. C. (2007). Titan: 13 cm Arecibo Radar Observations and Comparisons with Cassini ISS and Radar Imagery. Lunar and Planetary Science Conference. [10] Bell, P. M. (1983). Methane ocean on Titan?. Eos, Transactions American Geophysical Union, 64, 84-84. https://doi.org/10.1029/eo064i009p00084-01 [11] Brighi, G., Poggiali, V., Mastrogiuseppe, M., Zannoni, M., Hayes, A. G., &amp; Tortora, P. (2025). Cassini Bistatic Radar Campaign during the Prime and Equinox Missions: Heterogeneous Reflections from Titan's Solid Surfaces. https://doi.org/10.5194/egusphere-egu25-18169 [12] Sultan-Salem, A.K., and T.G. Leonard, Revisiting Titan's Earth-Based Scattering Data at 13-cm Wavelength, Geophysical Research Letters 34, L12201, 2007 http://dx.doi.org/10.1029/2007GL029928</t>
+          <t>[1] Campbell, D. B., Black, G. J., Carter, L. M., &amp; Ostro, S. J. (2003). Radar Evidence for Liquid Surfaces on Titan. Science, 302, 431-434. https://doi.org/10.1126/science.1088969 [2] Muhleman, D. O., Grossman, A. W., &amp; Butler, B. (1995). Radar Investigation of Mars, Mercury, and Titan. Annual Review of Earth and Planetary Sciences. https://doi.org/10.1146/annurev.ea.23.050195.002005 [3] Black, G. J., Campbell, D. B., &amp; Carter, L. M. (2010). Ground-based radar observations of Titan: 2000–2008. Icarus, 212, 300-320. https://doi.org/10.1016/j.icarus.2010.10.025 [4] Hofgartner, J. D., Hayes, A. G., Campbell, D. B., Lunine, J. I., Black, G. J., MacKenzie, S. M., Birch, S. P. D., Elachi, C., Kirk, R. D., Gall, A. L., Lorenz, R. D., &amp; Wall, S. D. (2020). The root of anomalously specular reflections from solid surfaces on Saturn’s moon Titan. Nature Communications, 11. https://doi.org/10.1038/s41467-020-16663-1 [5] Campbell, D. B., Black, G., Carter, L. M., Hine, A. A., Margot, J., Nolan, M. C., &amp; Ostro, S. J. (2002). The Surface of Titan: Arecibo Radar Observations. DPS. [6] Duxbury, T. C., &amp; Lieske, J. H. (1976). Arecibo Radar Observations of the Galilean Satellites and Titan. Bulletin of the American Astronomical Society. [7] Black, G. J., Campbell, D. B., &amp; Carter, L. M. (2008). Surface Properties of Titan from Arecibo/GBT Radar Observations. AAS/Division for Planetary Sciences Meeting Abstracts #40. [8] Campbell, D. B., Black, G., Carter, L. M., &amp; Nolan, M. C. (2007). Titan: 13 cm Arecibo Radar Observations and Comparisons with Cassini ISS and Radar Imagery. Lunar and Planetary Science Conference. [9] Brighi, G., Poggiali, V., Mastrogiuseppe, M., Zannoni, M., Hayes, A. G., &amp; Tortora, P. (2025). Cassini Bistatic Radar Campaign during the Prime and Equinox Missions: Heterogeneous Reflections from Titan's Solid Surfaces. https://doi.org/10.5194/egusphere-egu25-18169 [10] Sultan-Salem, A.K., and T.G. Leonard, Revisiting Titan's Earth-Based Scattering Data at 13-cm Wavelength, Geophysical Research Letters 34, L12201, 2007 http://dx.doi.org/10.1029/2007GL029928</t>
         </is>
       </c>
       <c r="P1030" t="inlineStr">
@@ -60227,7 +59967,7 @@
       </c>
       <c r="O1031" t="inlineStr">
         <is>
-          <t>[1] Senske, D. A., Campbell, D. B., Head, J. W., Fisher, P. C., Hine, A. A., deCharon, A., Frank, S. L., Keddie, S. T., Roberts, K. M., Stofan, E. R., Aubele, J. C., Crumpler, L. S., &amp; Stacy, N. (1991). Geology and tectonics of the Themis Regio-Lavinia Planitia-Alpha Regio-Lada Terra area, Venus: Results from Arecibo image data. Earth, Moon, and Planets, 55, 97-161. https://doi.org/10.1007/bf00058900 [2] Campbell, D. B., Head, J. W., Senske, D. A., Fisher, P. C., Hine, A. A., &amp; Harmon, J. K. (1989). Styles of Volcanism on Venus: New Arecibo High Resolution Radar Data. Science. https://doi.org/10.1126/science.246.4928.373 [3] Carter, L. M., Campbell, D. B., &amp; Campbell, B. A. (2004). Impact crater related surficial deposits on Venus: Multipolarization radar observations with Arecibo. Journal of Geophysical Research: Planets, 109. https://doi.org/10.1029/2003je002227 [4] Campbell, B. A., &amp; Campbell, D. B. (1992). Analysis of volcanic surface morphology on Venus from comparison of Arecibo, Magellan, and terrestrial airborne radar data. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/92je01558 [5] Campbell, D. B., &amp; Burns, B. A. (1980). Earth‐based radar imagery of Venus. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/ja085ia13p08271 [6] Senske, D. A., Head, J. W., Stofan, E. R., &amp; Campbell, D. B. (1991). Geology and structure of Beta Regio, Venus: Results from Arecibo Radar Imaging. Geophysical Research Letters. https://doi.org/10.1029/91gl01001 [7] Dyce, B. R., Pettengill, G. H., &amp; Shapiro, I. I. (1967). Radar determination of the rotations of Venus and Mercury. The Astronomical Journal. https://doi.org/10.1086/110231 [8] Crumpler, L. S., Head, J. W., &amp; Campbell, D. B. (1986). Orogenic belts on Venus. Geology, 14, 1031. https://doi.org/10.1130/0091-7613(1986)14&lt;1031:obov&gt;2.0.co;2 [9] Campbell, B. A., Campbell, D. B., &amp; DeVries, C. H. (1999). Surface processes in the Venus highlands: Results from analysis of Magellan and Arecibo data. Journal of Geophysical Research: Planets, 104, 1897-1916. https://doi.org/10.1029/1998je900022 [10] Campbell, B. A., Arvidson, R. E., &amp; Shepard, M. K. (1993). Radar polarization properties of volcanic and playa surfaces: Applications to terrestrial remote sensing and Venus data interpretation. Journal of Geophysical Research: Planets, 98, 17099-17113. https://doi.org/10.1029/93je01541 [11] Burns, B. A., &amp; Campbell, D. B. (1985). Radar evidence for cratering on Venus. Journal of Geophysical Research: Solid Earth, 90, 3037-3047. https://doi.org/10.1029/jb090ib04p03037 [12] Senske, D. A. (1990). Geology of the Venus equatorial region from Pioneer Venus radar imaging. Earth Moon and Planets. https://doi.org/10.1007/bf00142397 [13] Campbell, D. B., Head, J. W., Harmon, J. K., &amp; Hine, A. A. (1983). Venus: Identification of Banded Terrain in the Mountains of Ishtar Terra. Science. https://doi.org/10.1126/science.221.4611.644 [14] Campbell, B. A., &amp; Campbell, D. B. (2022). Arecibo Radar Maps of Venus from 1988 to 2020. The Planetary Science Journal. https://doi.org/10.3847/psj/ac4f43 [15] Pettengill, G. H., Dyce, R. B., &amp; Campbell, D. B. (1967). Radar measurements at 70 CM of Venus and Mercury. The Astronomical Journal, 72, 330. https://doi.org/10.1086/110229 [16] Carter, L. M., Campbell, D. B., &amp; Campbell, B. A. (2006). Volcanic deposits in shield fields and highland regions on Venus: Surface properties from radar polarimetry. Journal of Geophysical Research: Planets, 111. https://doi.org/10.1029/2005je002519 [17] Stofan, E. R., Head, J. W., Campbell, D. B., Zisk, S. H., Bogomolov, A. F., Rzhiga, O. N., Basilevsky, A. T., &amp; Armand, N. A. (1989). Geology of a rift zone on Venus: Beta Regio and Devana Chasma. Geological Society of America Bulletin. https://doi.org/10.1130/0016-7606(1989)101&lt;0143:goarzo&gt;2.3.co;2 [18] Kratter, K. M., Carter, L. M., &amp; Campbell, D. B. (2007). An expanded view of Lada Terra, Venus: New Arecibo radar observations of Quetzalpetlatl Corona and surrounding flows. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/2006je002722 [19] Campbell, B.A. and Campbell, D.B., Arecibo Radar Maps of Venus from 1988 to 2020, The Planetary Science Journal, 3(3), p.55, 2022 https://iopscience.iop.org/article/10.3847/PSJ/ac4f43/meta [20] Campbell, B.A, D.B. Campbell, L.M. Carter, J.F. Chandler, J.D. Giorgini, J.-L. Margot, G.A. Morgan; M.C. Nolan, P.J. Perillat, and J. L. Whitten, The Mean Rotation Rate of Venus from 29 Years of Earth-Based Radar Observations, Icarus 332, 19-23, 2019 https://doi.org/10.1016/j.icarus.2019.06.019 [21] Campbell, B.A., D.B. Campbell, G.A. Morgan, L.M. Carter, M.C. Nolan, and J.F. Chandler, Evidence for Crater Ejecta on Venus Tessera Terrain from Earth-Based Radar Images, Icarus 250, 123-130, 2015 http://dx.doi.org/10.1016/j.icarus.2014.11.025 [22] Campbell, D.B., D.A. Senske, J.W. Head, P.C. Fisher, and A.A. Hine, Venus Southern Hemisphere - Geologic Character and Age of Terrains in the Themis-Alpha-Lada Region, Science 251, 180-183, 1991 http://dx.doi.org/10.1126/science.251.4990.180 [23] Shapiro, I.I., J.F. Chandler, D.B. Campbell, A.A. Hine, and N.J.S. Stacy, The Spin Vector of Venus, Astronomical Journal 100, 1363-1368, 1990 http://dx.doi.org/10.1086/115602 [24] Campbell, D.B., N.J.S. Stacy, and A.A. Hine, Venus - Crater Distributions at Low Northern Latitudes and in the Southern Hemisphere from New Arecibo Observations, Geophysical Review Letters 17, 1389-1392, 1990 http://dx.doi.org/10.1029/GL017i009p01389 [25] Campbell, B.A., and D.B. Campbell, Western Eisila Regio, Venus - Radar Properties of Volcanic Deposits, Geophysical Research Letters 17, 1353-1356, 1990 http://dx.doi.org/10.1029/GL017i009p01353 [26] Bruegge, R.W.V., J.W. Head, and D.B. Campbell, Orogeny and Large-Scale Strike-Slip Faulting on Venus: Tectonic Evolution of Maxwell Montes, Journal of Geophysical Research 95, 8357-8381, 1990 http://dx.doi.org/10.1029/JB095iB06p08357 [27] Stofan, E.R., J.W. Head, and D.B. Campbell, Geology of the Southern Ishtar Terra/Guinevere and Sedna Planitae Region on Venus, Earth, Moon, and Planets 38, 183-207, 1987 http://dx.doi.org/10.1007/BF00119682 [28] Campbell, D.B., J.W. Head, J.K. Harmon, and A.A. Hine, Venus - Volcanism and Rift Information in Beta Regio, Science 226, 167-170, 1984 http://dx.doi.org/10.1126/science.226.4671.167 [29] Cutts, J.A., T.W. Thompson, and B.H. Lewis, Origin of Bright Ring-Shaped Craters in Radar Images of Venus, Icarus 48, 428-452, 1981 http://dx.doi.org/10.1016/0019-1035(81)90054-3 [30] Campbell, D.B., B.A. Burns, and V. Boriakoff, Venus - Further Evidence of Impact Cratering and Tectonic Activity from Radar Observations, Science 204, 1424-1427, 1979 http://dx.doi.org/10.1126/science.204.4400.1424 [31] Shapiro, I.I., D.B. Campbell, and W.M. de Campli, Nonresonance Rotation of Venus, Astrophysical Journal 230, L123-L126, 1979 http://dx.doi.org/10.1086/182975 [32] Campbell, D.B., R.B. Dyce, and G.H. Pettengill, New Radar Image of Venus, Science 193, 1123-1124, 1976 http://dx.doi.org/10.1126/science.193.4258.1123 [33] Hagfors, R., and D.B. Campbell, Radar Backscattering from Venus at Oblique Incidence at a Wavelength of 70 cm, Astronomical Journal 79, 493-502, 1974 http://dx.doi.org/10.1086/111572 [34] Campbell, D.B., R.B. Dyce, R.P. Ingalls, G.H. Pettengill, and I.I. Shapiro, Venus: Topography Revealed by Radar Data, Science 175, 514-516, 1972 http://dx.doi.org/10.1126/science.175.4021.514 [35] Campbell, D.B., R.F. Jurgens, R.B. Dyce, F.S. Harris, and G.H. Pettengill, Radar Interferometric Observations of Venus at 70-Centimeter Wavelength, Science 170, 1090-1092, 1970 http://dx.doi.org/10.1126/science.170.3962.1090 [36] Jurgens, R.F and R.B. Dyce, Radar Backscattering Properties of Venus at 70 cm, Astronomical Journal 75, 297-314, 1970 http://dx.doi.org/10.1086/110977 [37] Jurgens, R.F., Some Preliminary Results of the 70-cm Radar Studies of Venus, Radio Science 5, 435-442, 1970 http://dx.doi.org/10.1029/RS005i002p00435 [38] Campbell, D.B., and D.O. Muhleman, Measurements of the Electron Content of the Interplanetary Medium Between Earth and Venus, Journal of Geophysical Research 74, 1138, 1969 http://dx.doi.org/10.1029/JA074i005p01138 [39] Jurgens, R.F., Radar Scattering from Venus at Large Angles of Incidence and the Question of Polar Ice Caps, Science 162, 1388-1390, 1968 http://dx.doi.org/10.1126/science.162.3860.1388 [40] Ash, M.E., D.B. Campbell, R.B. Dyce, R.P. Ingalls, R. Jurgens, G.H. Pettengill, I.I. Shapiro, M.A. Slade, and T.W. Thompson, The Case for the Radar Radius of Venus, Science 160, 985-987, 1968 http://dx.doi.org/10.1126/science.160.3831.985</t>
+          <t>[1] Campbell, D. B., Head, J. W., Senske, D. A., Fisher, P. C., Hine, A. A., &amp; Harmon, J. K. (1989). Styles of Volcanism on Venus: New Arecibo High Resolution Radar Data. Science. https://doi.org/10.1126/science.246.4928.373 [2] Carter, L. M., Campbell, D. B., &amp; Campbell, B. A. (2004). Impact crater related surficial deposits on Venus: Multipolarization radar observations with Arecibo. Journal of Geophysical Research: Planets, 109. https://doi.org/10.1029/2003je002227 [3] Campbell, B. A., &amp; Campbell, D. B. (1992). Analysis of volcanic surface morphology on Venus from comparison of Arecibo, Magellan, and terrestrial airborne radar data. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/92je01558 [4] Campbell, D. B., &amp; Burns, B. A. (1980). Earth‐based radar imagery of Venus. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/ja085ia13p08271 [5] Senske, D. A., Head, J. W., Stofan, E. R., &amp; Campbell, D. B. (1991). Geology and structure of Beta Regio, Venus: Results from Arecibo Radar Imaging. Geophysical Research Letters. https://doi.org/10.1029/91gl01001 [6] Dyce, B. R., Pettengill, G. H., &amp; Shapiro, I. I. (1967). Radar determination of the rotations of Venus and Mercury. The Astronomical Journal. https://doi.org/10.1086/110231 [7] Crumpler, L. S., Head, J. W., &amp; Campbell, D. B. (1986). Orogenic belts on Venus. Geology, 14, 1031. https://doi.org/10.1130/0091-7613(1986)14&lt;1031:obov&gt;2.0.co;2 [8] Campbell, B. A., Campbell, D. B., &amp; DeVries, C. H. (1999). Surface processes in the Venus highlands: Results from analysis of Magellan and Arecibo data. Journal of Geophysical Research: Planets, 104, 1897-1916. https://doi.org/10.1029/1998je900022 [9] Campbell, B. A., Arvidson, R. E., &amp; Shepard, M. K. (1993). Radar polarization properties of volcanic and playa surfaces: Applications to terrestrial remote sensing and Venus data interpretation. Journal of Geophysical Research: Planets, 98, 17099-17113. https://doi.org/10.1029/93je01541 [10] Burns, B. A., &amp; Campbell, D. B. (1985). Radar evidence for cratering on Venus. Journal of Geophysical Research: Solid Earth, 90, 3037-3047. https://doi.org/10.1029/jb090ib04p03037 [11] Senske, D. A. (1990). Geology of the Venus equatorial region from Pioneer Venus radar imaging. Earth Moon and Planets. https://doi.org/10.1007/bf00142397 [12] Campbell, D. B., Head, J. W., Harmon, J. K., &amp; Hine, A. A. (1983). Venus: Identification of Banded Terrain in the Mountains of Ishtar Terra. Science. https://doi.org/10.1126/science.221.4611.644 [13] Campbell, B. A., &amp; Campbell, D. B. (2022). Arecibo Radar Maps of Venus from 1988 to 2020. The Planetary Science Journal. https://doi.org/10.3847/psj/ac4f43 [14] Pettengill, G. H., Dyce, R. B., &amp; Campbell, D. B. (1967). Radar measurements at 70 CM of Venus and Mercury. The Astronomical Journal, 72, 330. https://doi.org/10.1086/110229 [15] Carter, L. M., Campbell, D. B., &amp; Campbell, B. A. (2006). Volcanic deposits in shield fields and highland regions on Venus: Surface properties from radar polarimetry. Journal of Geophysical Research: Planets, 111. https://doi.org/10.1029/2005je002519 [16] Stofan, E. R., Head, J. W., Campbell, D. B., Zisk, S. H., Bogomolov, A. F., Rzhiga, O. N., Basilevsky, A. T., &amp; Armand, N. A. (1989). Geology of a rift zone on Venus: Beta Regio and Devana Chasma. Geological Society of America Bulletin. https://doi.org/10.1130/0016-7606(1989)101&lt;0143:goarzo&gt;2.3.co;2 [17] Kratter, K. M., Carter, L. M., &amp; Campbell, D. B. (2007). An expanded view of Lada Terra, Venus: New Arecibo radar observations of Quetzalpetlatl Corona and surrounding flows. Journal of Geophysical Research Atmospheres. https://doi.org/10.1029/2006je002722 [18] Campbell, B.A. and Campbell, D.B., Arecibo Radar Maps of Venus from 1988 to 2020, The Planetary Science Journal, 3(3), p.55, 2022 https://iopscience.iop.org/article/10.3847/PSJ/ac4f43/meta [19] Campbell, B.A, D.B. Campbell, L.M. Carter, J.F. Chandler, J.D. Giorgini, J.-L. Margot, G.A. Morgan; M.C. Nolan, P.J. Perillat, and J. L. Whitten, The Mean Rotation Rate of Venus from 29 Years of Earth-Based Radar Observations, Icarus 332, 19-23, 2019 https://doi.org/10.1016/j.icarus.2019.06.019 [20] Campbell, B.A., D.B. Campbell, G.A. Morgan, L.M. Carter, M.C. Nolan, and J.F. Chandler, Evidence for Crater Ejecta on Venus Tessera Terrain from Earth-Based Radar Images, Icarus 250, 123-130, 2015 http://dx.doi.org/10.1016/j.icarus.2014.11.025 [21] Campbell, D.B., D.A. Senske, J.W. Head, P.C. Fisher, and A.A. Hine, Venus Southern Hemisphere - Geologic Character and Age of Terrains in the Themis-Alpha-Lada Region, Science 251, 180-183, 1991 http://dx.doi.org/10.1126/science.251.4990.180 [22] Shapiro, I.I., J.F. Chandler, D.B. Campbell, A.A. Hine, and N.J.S. Stacy, The Spin Vector of Venus, Astronomical Journal 100, 1363-1368, 1990 http://dx.doi.org/10.1086/115602 [23] Campbell, D.B., N.J.S. Stacy, and A.A. Hine, Venus - Crater Distributions at Low Northern Latitudes and in the Southern Hemisphere from New Arecibo Observations, Geophysical Review Letters 17, 1389-1392, 1990 http://dx.doi.org/10.1029/GL017i009p01389 [24] Campbell, B.A., and D.B. Campbell, Western Eisila Regio, Venus - Radar Properties of Volcanic Deposits, Geophysical Research Letters 17, 1353-1356, 1990 http://dx.doi.org/10.1029/GL017i009p01353 [25] Bruegge, R.W.V., J.W. Head, and D.B. Campbell, Orogeny and Large-Scale Strike-Slip Faulting on Venus: Tectonic Evolution of Maxwell Montes, Journal of Geophysical Research 95, 8357-8381, 1990 http://dx.doi.org/10.1029/JB095iB06p08357 [26] Stofan, E.R., J.W. Head, and D.B. Campbell, Geology of the Southern Ishtar Terra/Guinevere and Sedna Planitae Region on Venus, Earth, Moon, and Planets 38, 183-207, 1987 http://dx.doi.org/10.1007/BF00119682 [27] Campbell, D.B., J.W. Head, J.K. Harmon, and A.A. Hine, Venus - Volcanism and Rift Information in Beta Regio, Science 226, 167-170, 1984 http://dx.doi.org/10.1126/science.226.4671.167 [28] Cutts, J.A., T.W. Thompson, and B.H. Lewis, Origin of Bright Ring-Shaped Craters in Radar Images of Venus, Icarus 48, 428-452, 1981 http://dx.doi.org/10.1016/0019-1035(81)90054-3 [29] Campbell, D.B., B.A. Burns, and V. Boriakoff, Venus - Further Evidence of Impact Cratering and Tectonic Activity from Radar Observations, Science 204, 1424-1427, 1979 http://dx.doi.org/10.1126/science.204.4400.1424 [30] Shapiro, I.I., D.B. Campbell, and W.M. de Campli, Nonresonance Rotation of Venus, Astrophysical Journal 230, L123-L126, 1979 http://dx.doi.org/10.1086/182975 [31] Campbell, D.B., R.B. Dyce, and G.H. Pettengill, New Radar Image of Venus, Science 193, 1123-1124, 1976 http://dx.doi.org/10.1126/science.193.4258.1123 [32] Hagfors, R., and D.B. Campbell, Radar Backscattering from Venus at Oblique Incidence at a Wavelength of 70 cm, Astronomical Journal 79, 493-502, 1974 http://dx.doi.org/10.1086/111572 [33] Campbell, D.B., R.B. Dyce, R.P. Ingalls, G.H. Pettengill, and I.I. Shapiro, Venus: Topography Revealed by Radar Data, Science 175, 514-516, 1972 http://dx.doi.org/10.1126/science.175.4021.514 [34] Campbell, D.B., R.F. Jurgens, R.B. Dyce, F.S. Harris, and G.H. Pettengill, Radar Interferometric Observations of Venus at 70-Centimeter Wavelength, Science 170, 1090-1092, 1970 http://dx.doi.org/10.1126/science.170.3962.1090 [35] Jurgens, R.F and R.B. Dyce, Radar Backscattering Properties of Venus at 70 cm, Astronomical Journal 75, 297-314, 1970 http://dx.doi.org/10.1086/110977 [36] Jurgens, R.F., Some Preliminary Results of the 70-cm Radar Studies of Venus, Radio Science 5, 435-442, 1970 http://dx.doi.org/10.1029/RS005i002p00435 [37] Campbell, D.B., and D.O. Muhleman, Measurements of the Electron Content of the Interplanetary Medium Between Earth and Venus, Journal of Geophysical Research 74, 1138, 1969 http://dx.doi.org/10.1029/JA074i005p01138 [38] Jurgens, R.F., Radar Scattering from Venus at Large Angles of Incidence and the Question of Polar Ice Caps, Science 162, 1388-1390, 1968 http://dx.doi.org/10.1126/science.162.3860.1388 [39] Ash, M.E., D.B. Campbell, R.B. Dyce, R.P. Ingalls, R. Jurgens, G.H. Pettengill, I.I. Shapiro, M.A. Slade, and T.W. Thompson, The Case for the Radar Radius of Venus, Science 160, 985-987, 1968 http://dx.doi.org/10.1126/science.160.3831.985</t>
         </is>
       </c>
       <c r="P1031" t="inlineStr">

--- a/FINAL_LIST_2026.xlsx
+++ b/FINAL_LIST_2026.xlsx
@@ -58755,6 +58755,11 @@
       </c>
     </row>
     <row r="1007">
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>ISON</t>
+        </is>
+      </c>
       <c r="D1007" t="inlineStr">
         <is>
           <t>Comet</t>
@@ -58950,6 +58955,11 @@
       </c>
     </row>
     <row r="1011">
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>Ouna</t>
+        </is>
+      </c>
       <c r="D1011" t="inlineStr">
         <is>
           <t>Spacecraft</t>
@@ -60127,6 +60137,11 @@
       </c>
     </row>
     <row r="1035">
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>2016 CF194</t>
+        </is>
+      </c>
       <c r="D1035" t="inlineStr">
         <is>
           <t>NEA</t>
@@ -60167,6 +60182,11 @@
       </c>
     </row>
     <row r="1036">
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>2019 WO2</t>
+        </is>
+      </c>
       <c r="D1036" t="inlineStr">
         <is>
           <t>NEA</t>
@@ -60207,6 +60227,14 @@
       </c>
     </row>
     <row r="1037">
+      <c r="A1037" t="n">
+        <v>359592</v>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>2010 VA1</t>
+        </is>
+      </c>
       <c r="D1037" t="inlineStr">
         <is>
           <t>NEA</t>
@@ -60247,6 +60275,11 @@
       </c>
     </row>
     <row r="1038">
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>2019 DJ1</t>
+        </is>
+      </c>
       <c r="D1038" t="inlineStr">
         <is>
           <t>NEA</t>
